--- a/design/tables/Spot.xlsx
+++ b/design/tables/Spot.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Spot" sheetId="1" r:id="R5490275b5b19439f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Spot" sheetId="1" r:id="R771866257c264fc2"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -7852,6 +7852,380 @@
         <x:v>535</x:v>
       </x:c>
     </x:row>
+    <x:row r="446">
+      <x:c r="A446" t="n">
+        <x:v>2023</x:v>
+      </x:c>
+      <x:c r="B446" t="n">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="C446" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D446" t="n">
+        <x:v>145</x:v>
+      </x:c>
+      <x:c r="E446" t="n">
+        <x:v>185</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="447">
+      <x:c r="A447" t="n">
+        <x:v>2024</x:v>
+      </x:c>
+      <x:c r="B447" t="n">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="C447" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D447" t="n">
+        <x:v>195</x:v>
+      </x:c>
+      <x:c r="E447" t="n">
+        <x:v>185</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="448">
+      <x:c r="A448" t="n">
+        <x:v>2025</x:v>
+      </x:c>
+      <x:c r="B448" t="n">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="C448" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D448" t="n">
+        <x:v>245</x:v>
+      </x:c>
+      <x:c r="E448" t="n">
+        <x:v>185</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="449">
+      <x:c r="A449" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="B449" t="n">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="C449" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D449" t="n">
+        <x:v>295</x:v>
+      </x:c>
+      <x:c r="E449" t="n">
+        <x:v>185</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="450">
+      <x:c r="A450" t="n">
+        <x:v>2027</x:v>
+      </x:c>
+      <x:c r="B450" t="n">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="C450" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D450" t="n">
+        <x:v>145</x:v>
+      </x:c>
+      <x:c r="E450" t="n">
+        <x:v>235</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="451">
+      <x:c r="A451" t="n">
+        <x:v>2028</x:v>
+      </x:c>
+      <x:c r="B451" t="n">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="C451" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D451" t="n">
+        <x:v>195</x:v>
+      </x:c>
+      <x:c r="E451" t="n">
+        <x:v>235</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="452">
+      <x:c r="A452" t="n">
+        <x:v>2029</x:v>
+      </x:c>
+      <x:c r="B452" t="n">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="C452" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="D452" t="n">
+        <x:v>245</x:v>
+      </x:c>
+      <x:c r="E452" t="n">
+        <x:v>235</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="453">
+      <x:c r="A453" t="n">
+        <x:v>2030</x:v>
+      </x:c>
+      <x:c r="B453" t="n">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="C453" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="D453" t="n">
+        <x:v>295</x:v>
+      </x:c>
+      <x:c r="E453" t="n">
+        <x:v>235</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="454">
+      <x:c r="A454" t="n">
+        <x:v>2031</x:v>
+      </x:c>
+      <x:c r="B454" t="n">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="C454" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="D454" t="n">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="E454" t="n">
+        <x:v>335</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="455">
+      <x:c r="A455" t="n">
+        <x:v>2032</x:v>
+      </x:c>
+      <x:c r="B455" t="n">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="C455" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="D455" t="n">
+        <x:v>145</x:v>
+      </x:c>
+      <x:c r="E455" t="n">
+        <x:v>335</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="456">
+      <x:c r="A456" t="n">
+        <x:v>2033</x:v>
+      </x:c>
+      <x:c r="B456" t="n">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="C456" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="D456" t="n">
+        <x:v>195</x:v>
+      </x:c>
+      <x:c r="E456" t="n">
+        <x:v>335</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="457">
+      <x:c r="A457" t="n">
+        <x:v>2034</x:v>
+      </x:c>
+      <x:c r="B457" t="n">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="C457" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="D457" t="n">
+        <x:v>245</x:v>
+      </x:c>
+      <x:c r="E457" t="n">
+        <x:v>335</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="458">
+      <x:c r="A458" t="n">
+        <x:v>2035</x:v>
+      </x:c>
+      <x:c r="B458" t="n">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="C458" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="D458" t="n">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="E458" t="n">
+        <x:v>385</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="459">
+      <x:c r="A459" t="n">
+        <x:v>2036</x:v>
+      </x:c>
+      <x:c r="B459" t="n">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="C459" t="n">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="D459" t="n">
+        <x:v>145</x:v>
+      </x:c>
+      <x:c r="E459" t="n">
+        <x:v>385</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="460">
+      <x:c r="A460" t="n">
+        <x:v>2037</x:v>
+      </x:c>
+      <x:c r="B460" t="n">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="C460" t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="D460" t="n">
+        <x:v>195</x:v>
+      </x:c>
+      <x:c r="E460" t="n">
+        <x:v>385</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="461">
+      <x:c r="A461" t="n">
+        <x:v>2038</x:v>
+      </x:c>
+      <x:c r="B461" t="n">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="C461" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="D461" t="n">
+        <x:v>245</x:v>
+      </x:c>
+      <x:c r="E461" t="n">
+        <x:v>385</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="462">
+      <x:c r="A462" t="n">
+        <x:v>2039</x:v>
+      </x:c>
+      <x:c r="B462" t="n">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="C462" t="n">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="D462" t="n">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="E462" t="n">
+        <x:v>485</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="463">
+      <x:c r="A463" t="n">
+        <x:v>2040</x:v>
+      </x:c>
+      <x:c r="B463" t="n">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="C463" t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="D463" t="n">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="E463" t="n">
+        <x:v>485</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="464">
+      <x:c r="A464" t="n">
+        <x:v>2041</x:v>
+      </x:c>
+      <x:c r="B464" t="n">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="C464" t="n">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="D464" t="n">
+        <x:v>145</x:v>
+      </x:c>
+      <x:c r="E464" t="n">
+        <x:v>485</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="465">
+      <x:c r="A465" t="n">
+        <x:v>2042</x:v>
+      </x:c>
+      <x:c r="B465" t="n">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="C465" t="n">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="D465" t="n">
+        <x:v>195</x:v>
+      </x:c>
+      <x:c r="E465" t="n">
+        <x:v>485</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="466">
+      <x:c r="A466" t="n">
+        <x:v>2043</x:v>
+      </x:c>
+      <x:c r="B466" t="n">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="C466" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="D466" t="n">
+        <x:v>245</x:v>
+      </x:c>
+      <x:c r="E466" t="n">
+        <x:v>485</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="467">
+      <x:c r="A467" t="n">
+        <x:v>2044</x:v>
+      </x:c>
+      <x:c r="B467" t="n">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="C467" t="n">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="D467" t="n">
+        <x:v>245</x:v>
+      </x:c>
+      <x:c r="E467" t="n">
+        <x:v>535</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>

--- a/design/tables/Spot.xlsx
+++ b/design/tables/Spot.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Spot" sheetId="1" r:id="R771866257c264fc2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Spot" sheetId="1" r:id="Ra003c308482340f4"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -7033,7 +7033,7 @@
         <x:v>95</x:v>
       </x:c>
       <x:c r="E397" s="7" t="n">
-        <x:v>385</x:v>
+        <x:v>410</x:v>
       </x:c>
     </x:row>
     <x:row r="398" ht="15" hidden="0" customHeight="1">
@@ -7050,7 +7050,7 @@
         <x:v>145</x:v>
       </x:c>
       <x:c r="E398" s="7" t="n">
-        <x:v>385</x:v>
+        <x:v>410</x:v>
       </x:c>
     </x:row>
     <x:row r="399" ht="15" hidden="0" customHeight="1">
@@ -7067,7 +7067,7 @@
         <x:v>195</x:v>
       </x:c>
       <x:c r="E399" s="7" t="n">
-        <x:v>385</x:v>
+        <x:v>410</x:v>
       </x:c>
     </x:row>
     <x:row r="400" ht="15" hidden="0" customHeight="1">

--- a/design/tables/Spot.xlsx
+++ b/design/tables/Spot.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Spot" sheetId="1" r:id="Ra003c308482340f4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Spot" sheetId="1" r:id="R8ac7c0800b2e4cee"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -386,7 +386,7 @@
         <x:v>145</x:v>
       </x:c>
       <x:c r="E6" s="7" t="n">
-        <x:v>235</x:v>
+        <x:v>250</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="15" hidden="0" customHeight="1">
@@ -403,7 +403,7 @@
         <x:v>195</x:v>
       </x:c>
       <x:c r="E7" s="7" t="n">
-        <x:v>235</x:v>
+        <x:v>250</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="15" hidden="0" customHeight="1">
@@ -420,7 +420,7 @@
         <x:v>245</x:v>
       </x:c>
       <x:c r="E8" s="7" t="n">
-        <x:v>235</x:v>
+        <x:v>250</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="15" hidden="0" customHeight="1">
@@ -437,7 +437,7 @@
         <x:v>295</x:v>
       </x:c>
       <x:c r="E9" s="7" t="n">
-        <x:v>235</x:v>
+        <x:v>250</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="15" hidden="0" customHeight="1">
@@ -454,7 +454,7 @@
         <x:v>95</x:v>
       </x:c>
       <x:c r="E10" s="7" t="n">
-        <x:v>335</x:v>
+        <x:v>350</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="15" hidden="0" customHeight="1">
@@ -471,7 +471,7 @@
         <x:v>145</x:v>
       </x:c>
       <x:c r="E11" s="7" t="n">
-        <x:v>335</x:v>
+        <x:v>360</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="15" hidden="0" customHeight="1">
@@ -488,7 +488,7 @@
         <x:v>195</x:v>
       </x:c>
       <x:c r="E12" s="7" t="n">
-        <x:v>335</x:v>
+        <x:v>360</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="15" hidden="0" customHeight="1">
@@ -505,7 +505,7 @@
         <x:v>245</x:v>
       </x:c>
       <x:c r="E13" s="7" t="n">
-        <x:v>335</x:v>
+        <x:v>360</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="15" hidden="0" customHeight="1">
@@ -519,7 +519,7 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="D14" s="7" t="n">
-        <x:v>95</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="E14" s="7" t="n">
         <x:v>385</x:v>
@@ -539,7 +539,7 @@
         <x:v>145</x:v>
       </x:c>
       <x:c r="E15" s="7" t="n">
-        <x:v>385</x:v>
+        <x:v>470</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="15" hidden="0" customHeight="1">
@@ -556,7 +556,7 @@
         <x:v>195</x:v>
       </x:c>
       <x:c r="E16" s="7" t="n">
-        <x:v>385</x:v>
+        <x:v>470</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="15" hidden="0" customHeight="1">
@@ -573,7 +573,7 @@
         <x:v>245</x:v>
       </x:c>
       <x:c r="E17" s="7" t="n">
-        <x:v>385</x:v>
+        <x:v>470</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="15" hidden="0" customHeight="1">
@@ -692,7 +692,7 @@
         <x:v>145</x:v>
       </x:c>
       <x:c r="E24" s="7" t="n">
-        <x:v>485</x:v>
+        <x:v>570</x:v>
       </x:c>
     </x:row>
     <x:row r="25" ht="15" hidden="0" customHeight="1">
@@ -706,10 +706,10 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="D25" s="7" t="n">
-        <x:v>195</x:v>
+        <x:v>295</x:v>
       </x:c>
       <x:c r="E25" s="7" t="n">
-        <x:v>485</x:v>
+        <x:v>470</x:v>
       </x:c>
     </x:row>
     <x:row r="26" ht="15" hidden="0" customHeight="1">
@@ -726,7 +726,7 @@
         <x:v>245</x:v>
       </x:c>
       <x:c r="E26" s="7" t="n">
-        <x:v>485</x:v>
+        <x:v>570</x:v>
       </x:c>
     </x:row>
     <x:row r="27" ht="15" hidden="0" customHeight="1">
@@ -743,7 +743,7 @@
         <x:v>295</x:v>
       </x:c>
       <x:c r="E27" s="7" t="n">
-        <x:v>485</x:v>
+        <x:v>570</x:v>
       </x:c>
     </x:row>
     <x:row r="28" ht="15" hidden="0" customHeight="1">
@@ -760,7 +760,7 @@
         <x:v>145</x:v>
       </x:c>
       <x:c r="E28" s="7" t="n">
-        <x:v>185</x:v>
+        <x:v>215</x:v>
       </x:c>
     </x:row>
     <x:row r="29" ht="15" hidden="0" customHeight="1">
@@ -777,7 +777,7 @@
         <x:v>195</x:v>
       </x:c>
       <x:c r="E29" s="7" t="n">
-        <x:v>185</x:v>
+        <x:v>215</x:v>
       </x:c>
     </x:row>
     <x:row r="30" ht="15" hidden="0" customHeight="1">
@@ -794,7 +794,7 @@
         <x:v>245</x:v>
       </x:c>
       <x:c r="E30" s="7" t="n">
-        <x:v>185</x:v>
+        <x:v>215</x:v>
       </x:c>
     </x:row>
     <x:row r="31" ht="15" hidden="0" customHeight="1">
@@ -811,7 +811,7 @@
         <x:v>295</x:v>
       </x:c>
       <x:c r="E31" s="7" t="n">
-        <x:v>185</x:v>
+        <x:v>215</x:v>
       </x:c>
     </x:row>
     <x:row r="32" ht="15" hidden="0" customHeight="1">
@@ -828,7 +828,7 @@
         <x:v>95</x:v>
       </x:c>
       <x:c r="E32" s="7" t="n">
-        <x:v>285</x:v>
+        <x:v>325</x:v>
       </x:c>
     </x:row>
     <x:row r="33" ht="15" hidden="0" customHeight="1">
@@ -845,7 +845,7 @@
         <x:v>145</x:v>
       </x:c>
       <x:c r="E33" s="7" t="n">
-        <x:v>285</x:v>
+        <x:v>325</x:v>
       </x:c>
     </x:row>
     <x:row r="34" ht="15" hidden="0" customHeight="1">
@@ -862,7 +862,7 @@
         <x:v>195</x:v>
       </x:c>
       <x:c r="E34" s="7" t="n">
-        <x:v>285</x:v>
+        <x:v>325</x:v>
       </x:c>
     </x:row>
     <x:row r="35" ht="15" hidden="0" customHeight="1">
@@ -879,7 +879,7 @@
         <x:v>245</x:v>
       </x:c>
       <x:c r="E35" s="7" t="n">
-        <x:v>285</x:v>
+        <x:v>325</x:v>
       </x:c>
     </x:row>
     <x:row r="36" ht="15" hidden="0" customHeight="1">
@@ -896,7 +896,7 @@
         <x:v>295</x:v>
       </x:c>
       <x:c r="E36" s="7" t="n">
-        <x:v>285</x:v>
+        <x:v>315</x:v>
       </x:c>
     </x:row>
     <x:row r="37" ht="15" hidden="0" customHeight="1">
@@ -913,7 +913,7 @@
         <x:v>345</x:v>
       </x:c>
       <x:c r="E37" s="7" t="n">
-        <x:v>285</x:v>
+        <x:v>315</x:v>
       </x:c>
     </x:row>
     <x:row r="38" ht="15" hidden="0" customHeight="1">
@@ -930,7 +930,7 @@
         <x:v>95</x:v>
       </x:c>
       <x:c r="E38" s="7" t="n">
-        <x:v>335</x:v>
+        <x:v>435</x:v>
       </x:c>
     </x:row>
     <x:row r="39" ht="15" hidden="0" customHeight="1">
@@ -947,7 +947,7 @@
         <x:v>145</x:v>
       </x:c>
       <x:c r="E39" s="7" t="n">
-        <x:v>335</x:v>
+        <x:v>435</x:v>
       </x:c>
     </x:row>
     <x:row r="40" ht="15" hidden="0" customHeight="1">
@@ -964,7 +964,7 @@
         <x:v>195</x:v>
       </x:c>
       <x:c r="E40" s="7" t="n">
-        <x:v>335</x:v>
+        <x:v>435</x:v>
       </x:c>
     </x:row>
     <x:row r="41" ht="15" hidden="0" customHeight="1">
@@ -981,7 +981,7 @@
         <x:v>245</x:v>
       </x:c>
       <x:c r="E41" s="7" t="n">
-        <x:v>335</x:v>
+        <x:v>435</x:v>
       </x:c>
     </x:row>
     <x:row r="42" ht="15" hidden="0" customHeight="1">
@@ -995,10 +995,10 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="D42" s="7" t="n">
-        <x:v>295</x:v>
+        <x:v>345</x:v>
       </x:c>
       <x:c r="E42" s="7" t="n">
-        <x:v>335</x:v>
+        <x:v>365</x:v>
       </x:c>
     </x:row>
     <x:row r="43" ht="15" hidden="0" customHeight="1">
@@ -1029,10 +1029,10 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="D44" s="7" t="n">
-        <x:v>95</x:v>
+        <x:v>225</x:v>
       </x:c>
       <x:c r="E44" s="7" t="n">
-        <x:v>435</x:v>
+        <x:v>485</x:v>
       </x:c>
     </x:row>
     <x:row r="45" ht="15" hidden="0" customHeight="1">
@@ -1046,10 +1046,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="D45" s="7" t="n">
-        <x:v>145</x:v>
+        <x:v>235</x:v>
       </x:c>
       <x:c r="E45" s="7" t="n">
-        <x:v>435</x:v>
+        <x:v>535</x:v>
       </x:c>
     </x:row>
     <x:row r="46" ht="15" hidden="0" customHeight="1">
@@ -1063,10 +1063,10 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="D46" s="7" t="n">
-        <x:v>195</x:v>
+        <x:v>345</x:v>
       </x:c>
       <x:c r="E46" s="7" t="n">
-        <x:v>435</x:v>
+        <x:v>425</x:v>
       </x:c>
     </x:row>
     <x:row r="47" ht="15" hidden="0" customHeight="1">
@@ -1080,10 +1080,10 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="D47" s="7" t="n">
-        <x:v>245</x:v>
+        <x:v>285</x:v>
       </x:c>
       <x:c r="E47" s="7" t="n">
-        <x:v>435</x:v>
+        <x:v>555</x:v>
       </x:c>
     </x:row>
     <x:row r="48" ht="15" hidden="0" customHeight="1">
@@ -1097,10 +1097,10 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="D48" s="7" t="n">
-        <x:v>245</x:v>
+        <x:v>335</x:v>
       </x:c>
       <x:c r="E48" s="7" t="n">
-        <x:v>485</x:v>
+        <x:v>575</x:v>
       </x:c>
     </x:row>
     <x:row r="49" ht="15" hidden="0" customHeight="1">
@@ -1114,10 +1114,10 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="D49" s="7" t="n">
-        <x:v>245</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="E49" s="7" t="n">
-        <x:v>535</x:v>
+        <x:v>215</x:v>
       </x:c>
     </x:row>
     <x:row r="50" ht="15" hidden="0" customHeight="1">
@@ -1386,7 +1386,7 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="D65" s="7" t="n">
-        <x:v>345</x:v>
+        <x:v>245</x:v>
       </x:c>
       <x:c r="E65" s="7" t="n">
         <x:v>185</x:v>
@@ -1403,7 +1403,7 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="D66" s="7" t="n">
-        <x:v>345</x:v>
+        <x:v>245</x:v>
       </x:c>
       <x:c r="E66" s="7" t="n">
         <x:v>235</x:v>
@@ -1420,7 +1420,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="D67" s="7" t="n">
-        <x:v>345</x:v>
+        <x:v>245</x:v>
       </x:c>
       <x:c r="E67" s="7" t="n">
         <x:v>285</x:v>
@@ -1437,7 +1437,7 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="D68" s="7" t="n">
-        <x:v>345</x:v>
+        <x:v>245</x:v>
       </x:c>
       <x:c r="E68" s="7" t="n">
         <x:v>335</x:v>
@@ -1454,7 +1454,7 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="D69" s="7" t="n">
-        <x:v>345</x:v>
+        <x:v>245</x:v>
       </x:c>
       <x:c r="E69" s="7" t="n">
         <x:v>385</x:v>
@@ -1471,7 +1471,7 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="D70" s="7" t="n">
-        <x:v>345</x:v>
+        <x:v>245</x:v>
       </x:c>
       <x:c r="E70" s="7" t="n">
         <x:v>435</x:v>
@@ -1488,7 +1488,7 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="D71" s="7" t="n">
-        <x:v>345</x:v>
+        <x:v>245</x:v>
       </x:c>
       <x:c r="E71" s="7" t="n">
         <x:v>485</x:v>
@@ -1508,7 +1508,7 @@
         <x:v>145</x:v>
       </x:c>
       <x:c r="E72" s="7" t="n">
-        <x:v>185</x:v>
+        <x:v>240</x:v>
       </x:c>
     </x:row>
     <x:row r="73" ht="15" hidden="0" customHeight="1">
@@ -1525,7 +1525,7 @@
         <x:v>195</x:v>
       </x:c>
       <x:c r="E73" s="7" t="n">
-        <x:v>185</x:v>
+        <x:v>240</x:v>
       </x:c>
     </x:row>
     <x:row r="74" ht="15" hidden="0" customHeight="1">
@@ -1542,7 +1542,7 @@
         <x:v>245</x:v>
       </x:c>
       <x:c r="E74" s="7" t="n">
-        <x:v>185</x:v>
+        <x:v>240</x:v>
       </x:c>
     </x:row>
     <x:row r="75" ht="15" hidden="0" customHeight="1">
@@ -1559,7 +1559,7 @@
         <x:v>295</x:v>
       </x:c>
       <x:c r="E75" s="7" t="n">
-        <x:v>185</x:v>
+        <x:v>240</x:v>
       </x:c>
     </x:row>
     <x:row r="76" ht="15" hidden="0" customHeight="1">
@@ -1576,7 +1576,7 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="E76" s="7" t="n">
-        <x:v>235</x:v>
+        <x:v>250</x:v>
       </x:c>
     </x:row>
     <x:row r="77" ht="15" hidden="0" customHeight="1">
@@ -1593,7 +1593,7 @@
         <x:v>95</x:v>
       </x:c>
       <x:c r="E77" s="7" t="n">
-        <x:v>235</x:v>
+        <x:v>240</x:v>
       </x:c>
     </x:row>
     <x:row r="78" ht="15" hidden="0" customHeight="1">
@@ -1610,7 +1610,7 @@
         <x:v>145</x:v>
       </x:c>
       <x:c r="E78" s="7" t="n">
-        <x:v>235</x:v>
+        <x:v>350</x:v>
       </x:c>
     </x:row>
     <x:row r="79" ht="15" hidden="0" customHeight="1">
@@ -1627,7 +1627,7 @@
         <x:v>195</x:v>
       </x:c>
       <x:c r="E79" s="7" t="n">
-        <x:v>235</x:v>
+        <x:v>350</x:v>
       </x:c>
     </x:row>
     <x:row r="80" ht="15" hidden="0" customHeight="1">
@@ -1644,7 +1644,7 @@
         <x:v>245</x:v>
       </x:c>
       <x:c r="E80" s="7" t="n">
-        <x:v>235</x:v>
+        <x:v>350</x:v>
       </x:c>
     </x:row>
     <x:row r="81" ht="15" hidden="0" customHeight="1">
@@ -1661,7 +1661,7 @@
         <x:v>295</x:v>
       </x:c>
       <x:c r="E81" s="7" t="n">
-        <x:v>235</x:v>
+        <x:v>350</x:v>
       </x:c>
     </x:row>
     <x:row r="82" ht="15" hidden="0" customHeight="1">
@@ -1678,7 +1678,7 @@
         <x:v>95</x:v>
       </x:c>
       <x:c r="E82" s="7" t="n">
-        <x:v>335</x:v>
+        <x:v>350</x:v>
       </x:c>
     </x:row>
     <x:row r="83" ht="15" hidden="0" customHeight="1">
@@ -1695,7 +1695,7 @@
         <x:v>145</x:v>
       </x:c>
       <x:c r="E83" s="7" t="n">
-        <x:v>335</x:v>
+        <x:v>450</x:v>
       </x:c>
     </x:row>
     <x:row r="84" ht="15" hidden="0" customHeight="1">
@@ -1712,7 +1712,7 @@
         <x:v>195</x:v>
       </x:c>
       <x:c r="E84" s="7" t="n">
-        <x:v>335</x:v>
+        <x:v>450</x:v>
       </x:c>
     </x:row>
     <x:row r="85" ht="15" hidden="0" customHeight="1">
@@ -1726,10 +1726,10 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="D85" s="7" t="n">
-        <x:v>245</x:v>
+        <x:v>345</x:v>
       </x:c>
       <x:c r="E85" s="7" t="n">
-        <x:v>335</x:v>
+        <x:v>350</x:v>
       </x:c>
     </x:row>
     <x:row r="86" ht="15" hidden="0" customHeight="1">
@@ -1743,10 +1743,10 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="D86" s="7" t="n">
-        <x:v>295</x:v>
+        <x:v>345</x:v>
       </x:c>
       <x:c r="E86" s="7" t="n">
-        <x:v>335</x:v>
+        <x:v>400</x:v>
       </x:c>
     </x:row>
     <x:row r="87" ht="15" hidden="0" customHeight="1">
@@ -1760,10 +1760,10 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="D87" s="7" t="n">
-        <x:v>45</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="E87" s="7" t="n">
-        <x:v>435</x:v>
+        <x:v>445</x:v>
       </x:c>
     </x:row>
     <x:row r="88" ht="15" hidden="0" customHeight="1">
@@ -1780,7 +1780,7 @@
         <x:v>95</x:v>
       </x:c>
       <x:c r="E88" s="7" t="n">
-        <x:v>435</x:v>
+        <x:v>450</x:v>
       </x:c>
     </x:row>
     <x:row r="89" ht="15" hidden="0" customHeight="1">
@@ -1794,10 +1794,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="D89" s="7" t="n">
-        <x:v>145</x:v>
+        <x:v>225</x:v>
       </x:c>
       <x:c r="E89" s="7" t="n">
-        <x:v>435</x:v>
+        <x:v>495</x:v>
       </x:c>
     </x:row>
     <x:row r="90" ht="15" hidden="0" customHeight="1">
@@ -1811,10 +1811,10 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="D90" s="7" t="n">
-        <x:v>195</x:v>
+        <x:v>225</x:v>
       </x:c>
       <x:c r="E90" s="7" t="n">
-        <x:v>435</x:v>
+        <x:v>545</x:v>
       </x:c>
     </x:row>
     <x:row r="91" ht="15" hidden="0" customHeight="1">
@@ -1828,10 +1828,10 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="D91" s="7" t="n">
-        <x:v>245</x:v>
+        <x:v>345</x:v>
       </x:c>
       <x:c r="E91" s="7" t="n">
-        <x:v>435</x:v>
+        <x:v>450</x:v>
       </x:c>
     </x:row>
     <x:row r="92" ht="15" hidden="0" customHeight="1">
@@ -1845,10 +1845,10 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="D92" s="7" t="n">
-        <x:v>245</x:v>
+        <x:v>275</x:v>
       </x:c>
       <x:c r="E92" s="7" t="n">
-        <x:v>485</x:v>
+        <x:v>565</x:v>
       </x:c>
     </x:row>
     <x:row r="93" ht="15" hidden="0" customHeight="1">
@@ -1862,10 +1862,10 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="D93" s="7" t="n">
-        <x:v>245</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="E93" s="7" t="n">
-        <x:v>535</x:v>
+        <x:v>130</x:v>
       </x:c>
     </x:row>
     <x:row r="94" ht="15" hidden="0" customHeight="1">
@@ -2256,7 +2256,7 @@
         <x:v>95</x:v>
       </x:c>
       <x:c r="E116" s="7" t="n">
-        <x:v>235</x:v>
+        <x:v>250</x:v>
       </x:c>
     </x:row>
     <x:row r="117" ht="15" hidden="0" customHeight="1">
@@ -2273,7 +2273,7 @@
         <x:v>145</x:v>
       </x:c>
       <x:c r="E117" s="7" t="n">
-        <x:v>235</x:v>
+        <x:v>250</x:v>
       </x:c>
     </x:row>
     <x:row r="118" ht="15" hidden="0" customHeight="1">
@@ -2290,7 +2290,7 @@
         <x:v>195</x:v>
       </x:c>
       <x:c r="E118" s="7" t="n">
-        <x:v>235</x:v>
+        <x:v>250</x:v>
       </x:c>
     </x:row>
     <x:row r="119" ht="15" hidden="0" customHeight="1">
@@ -2307,7 +2307,7 @@
         <x:v>245</x:v>
       </x:c>
       <x:c r="E119" s="7" t="n">
-        <x:v>235</x:v>
+        <x:v>250</x:v>
       </x:c>
     </x:row>
     <x:row r="120" ht="15" hidden="0" customHeight="1">
@@ -2324,7 +2324,7 @@
         <x:v>295</x:v>
       </x:c>
       <x:c r="E120" s="7" t="n">
-        <x:v>235</x:v>
+        <x:v>250</x:v>
       </x:c>
     </x:row>
     <x:row r="121" ht="15" hidden="0" customHeight="1">
@@ -2341,7 +2341,7 @@
         <x:v>345</x:v>
       </x:c>
       <x:c r="E121" s="7" t="n">
-        <x:v>235</x:v>
+        <x:v>250</x:v>
       </x:c>
     </x:row>
     <x:row r="122" ht="15" hidden="0" customHeight="1">
@@ -2358,7 +2358,7 @@
         <x:v>95</x:v>
       </x:c>
       <x:c r="E122" s="7" t="n">
-        <x:v>335</x:v>
+        <x:v>360</x:v>
       </x:c>
     </x:row>
     <x:row r="123" ht="15" hidden="0" customHeight="1">
@@ -2375,7 +2375,7 @@
         <x:v>145</x:v>
       </x:c>
       <x:c r="E123" s="7" t="n">
-        <x:v>335</x:v>
+        <x:v>360</x:v>
       </x:c>
     </x:row>
     <x:row r="124" ht="15" hidden="0" customHeight="1">
@@ -2392,7 +2392,7 @@
         <x:v>195</x:v>
       </x:c>
       <x:c r="E124" s="7" t="n">
-        <x:v>335</x:v>
+        <x:v>360</x:v>
       </x:c>
     </x:row>
     <x:row r="125" ht="15" hidden="0" customHeight="1">
@@ -2409,7 +2409,7 @@
         <x:v>245</x:v>
       </x:c>
       <x:c r="E125" s="7" t="n">
-        <x:v>335</x:v>
+        <x:v>360</x:v>
       </x:c>
     </x:row>
     <x:row r="126" ht="15" hidden="0" customHeight="1">
@@ -2426,7 +2426,7 @@
         <x:v>295</x:v>
       </x:c>
       <x:c r="E126" s="7" t="n">
-        <x:v>335</x:v>
+        <x:v>360</x:v>
       </x:c>
     </x:row>
     <x:row r="127" ht="15" hidden="0" customHeight="1">
@@ -2440,10 +2440,10 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="D127" s="7" t="n">
-        <x:v>95</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="E127" s="7" t="n">
-        <x:v>385</x:v>
+        <x:v>370</x:v>
       </x:c>
     </x:row>
     <x:row r="128" ht="15" hidden="0" customHeight="1">
@@ -2460,7 +2460,7 @@
         <x:v>145</x:v>
       </x:c>
       <x:c r="E128" s="7" t="n">
-        <x:v>385</x:v>
+        <x:v>470</x:v>
       </x:c>
     </x:row>
     <x:row r="129" ht="15" hidden="0" customHeight="1">
@@ -2477,7 +2477,7 @@
         <x:v>195</x:v>
       </x:c>
       <x:c r="E129" s="7" t="n">
-        <x:v>385</x:v>
+        <x:v>470</x:v>
       </x:c>
     </x:row>
     <x:row r="130" ht="15" hidden="0" customHeight="1">
@@ -2494,7 +2494,7 @@
         <x:v>245</x:v>
       </x:c>
       <x:c r="E130" s="7" t="n">
-        <x:v>385</x:v>
+        <x:v>470</x:v>
       </x:c>
     </x:row>
     <x:row r="131" ht="15" hidden="0" customHeight="1">
@@ -2511,7 +2511,7 @@
         <x:v>295</x:v>
       </x:c>
       <x:c r="E131" s="7" t="n">
-        <x:v>385</x:v>
+        <x:v>470</x:v>
       </x:c>
     </x:row>
     <x:row r="132" ht="15" hidden="0" customHeight="1">
@@ -2528,7 +2528,7 @@
         <x:v>95</x:v>
       </x:c>
       <x:c r="E132" s="7" t="n">
-        <x:v>485</x:v>
+        <x:v>470</x:v>
       </x:c>
     </x:row>
     <x:row r="133" ht="15" hidden="0" customHeight="1">
@@ -2545,7 +2545,7 @@
         <x:v>145</x:v>
       </x:c>
       <x:c r="E133" s="7" t="n">
-        <x:v>485</x:v>
+        <x:v>570</x:v>
       </x:c>
     </x:row>
     <x:row r="134" ht="15" hidden="0" customHeight="1">
@@ -2562,7 +2562,7 @@
         <x:v>195</x:v>
       </x:c>
       <x:c r="E134" s="7" t="n">
-        <x:v>485</x:v>
+        <x:v>570</x:v>
       </x:c>
     </x:row>
     <x:row r="135" ht="15" hidden="0" customHeight="1">
@@ -2579,7 +2579,7 @@
         <x:v>245</x:v>
       </x:c>
       <x:c r="E135" s="7" t="n">
-        <x:v>485</x:v>
+        <x:v>570</x:v>
       </x:c>
     </x:row>
     <x:row r="136" ht="15" hidden="0" customHeight="1">
@@ -2596,7 +2596,7 @@
         <x:v>295</x:v>
       </x:c>
       <x:c r="E136" s="7" t="n">
-        <x:v>485</x:v>
+        <x:v>570</x:v>
       </x:c>
     </x:row>
     <x:row r="137" ht="15" hidden="0" customHeight="1">
@@ -2610,10 +2610,10 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="D137" s="7" t="n">
-        <x:v>345</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="E137" s="7" t="n">
-        <x:v>485</x:v>
+        <x:v>570</x:v>
       </x:c>
     </x:row>
     <x:row r="138" ht="15" hidden="0" customHeight="1">
@@ -2630,7 +2630,7 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="E138" s="7" t="n">
-        <x:v>185</x:v>
+        <x:v>200</x:v>
       </x:c>
     </x:row>
     <x:row r="139" ht="15" hidden="0" customHeight="1">
@@ -2647,7 +2647,7 @@
         <x:v>95</x:v>
       </x:c>
       <x:c r="E139" s="7" t="n">
-        <x:v>185</x:v>
+        <x:v>200</x:v>
       </x:c>
     </x:row>
     <x:row r="140" ht="15" hidden="0" customHeight="1">
@@ -2664,7 +2664,7 @@
         <x:v>145</x:v>
       </x:c>
       <x:c r="E140" s="7" t="n">
-        <x:v>185</x:v>
+        <x:v>200</x:v>
       </x:c>
     </x:row>
     <x:row r="141" ht="15" hidden="0" customHeight="1">
@@ -2681,7 +2681,7 @@
         <x:v>195</x:v>
       </x:c>
       <x:c r="E141" s="7" t="n">
-        <x:v>185</x:v>
+        <x:v>200</x:v>
       </x:c>
     </x:row>
     <x:row r="142" ht="15" hidden="0" customHeight="1">
@@ -2698,7 +2698,7 @@
         <x:v>245</x:v>
       </x:c>
       <x:c r="E142" s="7" t="n">
-        <x:v>185</x:v>
+        <x:v>200</x:v>
       </x:c>
     </x:row>
     <x:row r="143" ht="15" hidden="0" customHeight="1">
@@ -2715,7 +2715,7 @@
         <x:v>95</x:v>
       </x:c>
       <x:c r="E143" s="7" t="n">
-        <x:v>285</x:v>
+        <x:v>310</x:v>
       </x:c>
     </x:row>
     <x:row r="144" ht="15" hidden="0" customHeight="1">
@@ -2732,7 +2732,7 @@
         <x:v>145</x:v>
       </x:c>
       <x:c r="E144" s="7" t="n">
-        <x:v>285</x:v>
+        <x:v>310</x:v>
       </x:c>
     </x:row>
     <x:row r="145" ht="15" hidden="0" customHeight="1">
@@ -2749,7 +2749,7 @@
         <x:v>195</x:v>
       </x:c>
       <x:c r="E145" s="7" t="n">
-        <x:v>285</x:v>
+        <x:v>310</x:v>
       </x:c>
     </x:row>
     <x:row r="146" ht="15" hidden="0" customHeight="1">
@@ -2766,7 +2766,7 @@
         <x:v>245</x:v>
       </x:c>
       <x:c r="E146" s="7" t="n">
-        <x:v>285</x:v>
+        <x:v>310</x:v>
       </x:c>
     </x:row>
     <x:row r="147" ht="15" hidden="0" customHeight="1">
@@ -2783,7 +2783,7 @@
         <x:v>95</x:v>
       </x:c>
       <x:c r="E147" s="7" t="n">
-        <x:v>335</x:v>
+        <x:v>420</x:v>
       </x:c>
     </x:row>
     <x:row r="148" ht="15" hidden="0" customHeight="1">
@@ -2800,7 +2800,7 @@
         <x:v>145</x:v>
       </x:c>
       <x:c r="E148" s="7" t="n">
-        <x:v>335</x:v>
+        <x:v>420</x:v>
       </x:c>
     </x:row>
     <x:row r="149" ht="15" hidden="0" customHeight="1">
@@ -2817,7 +2817,7 @@
         <x:v>195</x:v>
       </x:c>
       <x:c r="E149" s="7" t="n">
-        <x:v>335</x:v>
+        <x:v>420</x:v>
       </x:c>
     </x:row>
     <x:row r="150" ht="15" hidden="0" customHeight="1">
@@ -2831,10 +2831,10 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="D150" s="7" t="n">
-        <x:v>245</x:v>
+        <x:v>295</x:v>
       </x:c>
       <x:c r="E150" s="7" t="n">
-        <x:v>335</x:v>
+        <x:v>320</x:v>
       </x:c>
     </x:row>
     <x:row r="151" ht="15" hidden="0" customHeight="1">
@@ -2848,10 +2848,10 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="D151" s="7" t="n">
-        <x:v>95</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="E151" s="7" t="n">
-        <x:v>435</x:v>
+        <x:v>420</x:v>
       </x:c>
     </x:row>
     <x:row r="152" ht="15" hidden="0" customHeight="1">
@@ -2865,10 +2865,10 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="D152" s="7" t="n">
-        <x:v>145</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="E152" s="7" t="n">
-        <x:v>435</x:v>
+        <x:v>470</x:v>
       </x:c>
     </x:row>
     <x:row r="153" ht="15" hidden="0" customHeight="1">
@@ -2882,10 +2882,10 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="D153" s="7" t="n">
-        <x:v>195</x:v>
+        <x:v>245</x:v>
       </x:c>
       <x:c r="E153" s="7" t="n">
-        <x:v>435</x:v>
+        <x:v>420</x:v>
       </x:c>
     </x:row>
     <x:row r="154" ht="15" hidden="0" customHeight="1">
@@ -2899,10 +2899,10 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="D154" s="7" t="n">
-        <x:v>245</x:v>
+        <x:v>295</x:v>
       </x:c>
       <x:c r="E154" s="7" t="n">
-        <x:v>435</x:v>
+        <x:v>420</x:v>
       </x:c>
     </x:row>
     <x:row r="155" ht="15" hidden="0" customHeight="1">
@@ -2919,7 +2919,7 @@
         <x:v>295</x:v>
       </x:c>
       <x:c r="E155" s="7" t="n">
-        <x:v>435</x:v>
+        <x:v>520</x:v>
       </x:c>
     </x:row>
     <x:row r="156" ht="15" hidden="0" customHeight="1">
@@ -2936,7 +2936,7 @@
         <x:v>195</x:v>
       </x:c>
       <x:c r="E156" s="7" t="n">
-        <x:v>535</x:v>
+        <x:v>520</x:v>
       </x:c>
     </x:row>
     <x:row r="157" ht="15" hidden="0" customHeight="1">
@@ -2953,7 +2953,7 @@
         <x:v>245</x:v>
       </x:c>
       <x:c r="E157" s="7" t="n">
-        <x:v>535</x:v>
+        <x:v>520</x:v>
       </x:c>
     </x:row>
     <x:row r="158" ht="15" hidden="0" customHeight="1">
@@ -2967,10 +2967,10 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="D158" s="7" t="n">
-        <x:v>295</x:v>
+        <x:v>345</x:v>
       </x:c>
       <x:c r="E158" s="7" t="n">
-        <x:v>535</x:v>
+        <x:v>520</x:v>
       </x:c>
     </x:row>
     <x:row r="159" ht="15" hidden="0" customHeight="1">
@@ -2984,10 +2984,10 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="D159" s="7" t="n">
-        <x:v>345</x:v>
+        <x:v>215</x:v>
       </x:c>
       <x:c r="E159" s="7" t="n">
-        <x:v>535</x:v>
+        <x:v>575</x:v>
       </x:c>
     </x:row>
     <x:row r="160" ht="15" hidden="0" customHeight="1">
@@ -3004,7 +3004,7 @@
         <x:v>195</x:v>
       </x:c>
       <x:c r="E160" s="7" t="n">
-        <x:v>135</x:v>
+        <x:v>150</x:v>
       </x:c>
     </x:row>
     <x:row r="161" ht="15" hidden="0" customHeight="1">
@@ -3021,7 +3021,7 @@
         <x:v>245</x:v>
       </x:c>
       <x:c r="E161" s="7" t="n">
-        <x:v>135</x:v>
+        <x:v>150</x:v>
       </x:c>
     </x:row>
     <x:row r="162" ht="15" hidden="0" customHeight="1">
@@ -3038,7 +3038,7 @@
         <x:v>295</x:v>
       </x:c>
       <x:c r="E162" s="7" t="n">
-        <x:v>135</x:v>
+        <x:v>150</x:v>
       </x:c>
     </x:row>
     <x:row r="163" ht="15" hidden="0" customHeight="1">
@@ -3055,7 +3055,7 @@
         <x:v>345</x:v>
       </x:c>
       <x:c r="E163" s="7" t="n">
-        <x:v>135</x:v>
+        <x:v>150</x:v>
       </x:c>
     </x:row>
     <x:row r="164" ht="15" hidden="0" customHeight="1">
@@ -3072,7 +3072,7 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="E164" s="7" t="n">
-        <x:v>235</x:v>
+        <x:v>250</x:v>
       </x:c>
     </x:row>
     <x:row r="165" ht="15" hidden="0" customHeight="1">
@@ -3089,7 +3089,7 @@
         <x:v>95</x:v>
       </x:c>
       <x:c r="E165" s="7" t="n">
-        <x:v>235</x:v>
+        <x:v>250</x:v>
       </x:c>
     </x:row>
     <x:row r="166" ht="15" hidden="0" customHeight="1">
@@ -3106,7 +3106,7 @@
         <x:v>145</x:v>
       </x:c>
       <x:c r="E166" s="7" t="n">
-        <x:v>235</x:v>
+        <x:v>250</x:v>
       </x:c>
     </x:row>
     <x:row r="167" ht="15" hidden="0" customHeight="1">
@@ -3123,7 +3123,7 @@
         <x:v>195</x:v>
       </x:c>
       <x:c r="E167" s="7" t="n">
-        <x:v>235</x:v>
+        <x:v>250</x:v>
       </x:c>
     </x:row>
     <x:row r="168" ht="15" hidden="0" customHeight="1">
@@ -3140,7 +3140,7 @@
         <x:v>245</x:v>
       </x:c>
       <x:c r="E168" s="7" t="n">
-        <x:v>235</x:v>
+        <x:v>250</x:v>
       </x:c>
     </x:row>
     <x:row r="169" ht="15" hidden="0" customHeight="1">
@@ -3157,7 +3157,7 @@
         <x:v>95</x:v>
       </x:c>
       <x:c r="E169" s="7" t="n">
-        <x:v>335</x:v>
+        <x:v>360</x:v>
       </x:c>
     </x:row>
     <x:row r="170" ht="15" hidden="0" customHeight="1">
@@ -3174,7 +3174,7 @@
         <x:v>145</x:v>
       </x:c>
       <x:c r="E170" s="7" t="n">
-        <x:v>335</x:v>
+        <x:v>360</x:v>
       </x:c>
     </x:row>
     <x:row r="171" ht="15" hidden="0" customHeight="1">
@@ -3191,7 +3191,7 @@
         <x:v>195</x:v>
       </x:c>
       <x:c r="E171" s="7" t="n">
-        <x:v>335</x:v>
+        <x:v>360</x:v>
       </x:c>
     </x:row>
     <x:row r="172" ht="15" hidden="0" customHeight="1">
@@ -3208,7 +3208,7 @@
         <x:v>245</x:v>
       </x:c>
       <x:c r="E172" s="7" t="n">
-        <x:v>335</x:v>
+        <x:v>360</x:v>
       </x:c>
     </x:row>
     <x:row r="173" ht="15" hidden="0" customHeight="1">
@@ -3225,7 +3225,7 @@
         <x:v>295</x:v>
       </x:c>
       <x:c r="E173" s="7" t="n">
-        <x:v>335</x:v>
+        <x:v>350</x:v>
       </x:c>
     </x:row>
     <x:row r="174" ht="15" hidden="0" customHeight="1">
@@ -3242,7 +3242,7 @@
         <x:v>95</x:v>
       </x:c>
       <x:c r="E174" s="7" t="n">
-        <x:v>385</x:v>
+        <x:v>470</x:v>
       </x:c>
     </x:row>
     <x:row r="175" ht="15" hidden="0" customHeight="1">
@@ -3259,7 +3259,7 @@
         <x:v>145</x:v>
       </x:c>
       <x:c r="E175" s="7" t="n">
-        <x:v>385</x:v>
+        <x:v>470</x:v>
       </x:c>
     </x:row>
     <x:row r="176" ht="15" hidden="0" customHeight="1">
@@ -3276,7 +3276,7 @@
         <x:v>195</x:v>
       </x:c>
       <x:c r="E176" s="7" t="n">
-        <x:v>385</x:v>
+        <x:v>470</x:v>
       </x:c>
     </x:row>
     <x:row r="177" ht="15" hidden="0" customHeight="1">
@@ -3293,7 +3293,7 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="E177" s="7" t="n">
-        <x:v>485</x:v>
+        <x:v>470</x:v>
       </x:c>
     </x:row>
     <x:row r="178" ht="15" hidden="0" customHeight="1">
@@ -3307,10 +3307,10 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="D178" s="7" t="n">
-        <x:v>95</x:v>
+        <x:v>225</x:v>
       </x:c>
       <x:c r="E178" s="7" t="n">
-        <x:v>485</x:v>
+        <x:v>515</x:v>
       </x:c>
     </x:row>
     <x:row r="179" ht="15" hidden="0" customHeight="1">
@@ -3324,10 +3324,10 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="D179" s="7" t="n">
-        <x:v>145</x:v>
+        <x:v>225</x:v>
       </x:c>
       <x:c r="E179" s="7" t="n">
-        <x:v>485</x:v>
+        <x:v>565</x:v>
       </x:c>
     </x:row>
     <x:row r="180" ht="15" hidden="0" customHeight="1">
@@ -3341,10 +3341,10 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="D180" s="7" t="n">
-        <x:v>195</x:v>
+        <x:v>345</x:v>
       </x:c>
       <x:c r="E180" s="7" t="n">
-        <x:v>485</x:v>
+        <x:v>470</x:v>
       </x:c>
     </x:row>
     <x:row r="181" ht="15" hidden="0" customHeight="1">
@@ -3358,10 +3358,10 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="D181" s="7" t="n">
-        <x:v>245</x:v>
+        <x:v>345</x:v>
       </x:c>
       <x:c r="E181" s="7" t="n">
-        <x:v>485</x:v>
+        <x:v>420</x:v>
       </x:c>
     </x:row>
     <x:row r="182" ht="15" hidden="0" customHeight="1">
@@ -3732,10 +3732,10 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="D203" s="7" t="n">
-        <x:v>195</x:v>
+        <x:v>295</x:v>
       </x:c>
       <x:c r="E203" s="7" t="n">
-        <x:v>585</x:v>
+        <x:v>520</x:v>
       </x:c>
     </x:row>
     <x:row r="204" ht="15" hidden="0" customHeight="1">
@@ -3752,7 +3752,7 @@
         <x:v>145</x:v>
       </x:c>
       <x:c r="E204" s="7" t="n">
-        <x:v>185</x:v>
+        <x:v>225</x:v>
       </x:c>
     </x:row>
     <x:row r="205" ht="15" hidden="0" customHeight="1">
@@ -3769,7 +3769,7 @@
         <x:v>195</x:v>
       </x:c>
       <x:c r="E205" s="7" t="n">
-        <x:v>185</x:v>
+        <x:v>225</x:v>
       </x:c>
     </x:row>
     <x:row r="206" ht="15" hidden="0" customHeight="1">
@@ -3786,7 +3786,7 @@
         <x:v>245</x:v>
       </x:c>
       <x:c r="E206" s="7" t="n">
-        <x:v>185</x:v>
+        <x:v>225</x:v>
       </x:c>
     </x:row>
     <x:row r="207" ht="15" hidden="0" customHeight="1">
@@ -3803,7 +3803,7 @@
         <x:v>295</x:v>
       </x:c>
       <x:c r="E207" s="7" t="n">
-        <x:v>185</x:v>
+        <x:v>225</x:v>
       </x:c>
     </x:row>
     <x:row r="208" ht="15" hidden="0" customHeight="1">
@@ -3817,10 +3817,10 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="D208" s="7" t="n">
-        <x:v>145</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="E208" s="7" t="n">
-        <x:v>235</x:v>
+        <x:v>225</x:v>
       </x:c>
     </x:row>
     <x:row r="209" ht="15" hidden="0" customHeight="1">
@@ -3837,7 +3837,7 @@
         <x:v>195</x:v>
       </x:c>
       <x:c r="E209" s="7" t="n">
-        <x:v>235</x:v>
+        <x:v>345</x:v>
       </x:c>
     </x:row>
     <x:row r="210" ht="15" hidden="0" customHeight="1">
@@ -3854,7 +3854,7 @@
         <x:v>245</x:v>
       </x:c>
       <x:c r="E210" s="7" t="n">
-        <x:v>235</x:v>
+        <x:v>345</x:v>
       </x:c>
     </x:row>
     <x:row r="211" ht="15" hidden="0" customHeight="1">
@@ -3871,7 +3871,7 @@
         <x:v>295</x:v>
       </x:c>
       <x:c r="E211" s="7" t="n">
-        <x:v>235</x:v>
+        <x:v>335</x:v>
       </x:c>
     </x:row>
     <x:row r="212" ht="15" hidden="0" customHeight="1">
@@ -3888,7 +3888,7 @@
         <x:v>95</x:v>
       </x:c>
       <x:c r="E212" s="7" t="n">
-        <x:v>335</x:v>
+        <x:v>345</x:v>
       </x:c>
     </x:row>
     <x:row r="213" ht="15" hidden="0" customHeight="1">
@@ -3905,7 +3905,7 @@
         <x:v>145</x:v>
       </x:c>
       <x:c r="E213" s="7" t="n">
-        <x:v>335</x:v>
+        <x:v>345</x:v>
       </x:c>
     </x:row>
     <x:row r="214" ht="15" hidden="0" customHeight="1">
@@ -3922,7 +3922,7 @@
         <x:v>195</x:v>
       </x:c>
       <x:c r="E214" s="7" t="n">
-        <x:v>335</x:v>
+        <x:v>455</x:v>
       </x:c>
     </x:row>
     <x:row r="215" ht="15" hidden="0" customHeight="1">
@@ -3936,10 +3936,10 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="D215" s="7" t="n">
-        <x:v>245</x:v>
+        <x:v>335</x:v>
       </x:c>
       <x:c r="E215" s="7" t="n">
-        <x:v>335</x:v>
+        <x:v>365</x:v>
       </x:c>
     </x:row>
     <x:row r="216" ht="15" hidden="0" customHeight="1">
@@ -3956,7 +3956,7 @@
         <x:v>95</x:v>
       </x:c>
       <x:c r="E216" s="7" t="n">
-        <x:v>385</x:v>
+        <x:v>455</x:v>
       </x:c>
     </x:row>
     <x:row r="217" ht="15" hidden="0" customHeight="1">
@@ -3973,7 +3973,7 @@
         <x:v>145</x:v>
       </x:c>
       <x:c r="E217" s="7" t="n">
-        <x:v>385</x:v>
+        <x:v>455</x:v>
       </x:c>
     </x:row>
     <x:row r="218" ht="15" hidden="0" customHeight="1">
@@ -3987,10 +3987,10 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="D218" s="7" t="n">
-        <x:v>195</x:v>
+        <x:v>245</x:v>
       </x:c>
       <x:c r="E218" s="7" t="n">
-        <x:v>385</x:v>
+        <x:v>455</x:v>
       </x:c>
     </x:row>
     <x:row r="219" ht="15" hidden="0" customHeight="1">
@@ -4004,10 +4004,10 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="D219" s="7" t="n">
-        <x:v>245</x:v>
+        <x:v>345</x:v>
       </x:c>
       <x:c r="E219" s="7" t="n">
-        <x:v>385</x:v>
+        <x:v>415</x:v>
       </x:c>
     </x:row>
     <x:row r="220" ht="15" hidden="0" customHeight="1">
@@ -4024,7 +4024,7 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="E220" s="7" t="n">
-        <x:v>485</x:v>
+        <x:v>455</x:v>
       </x:c>
     </x:row>
     <x:row r="221" ht="15" hidden="0" customHeight="1">
@@ -4038,10 +4038,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="D221" s="7" t="n">
-        <x:v>95</x:v>
+        <x:v>225</x:v>
       </x:c>
       <x:c r="E221" s="7" t="n">
-        <x:v>485</x:v>
+        <x:v>505</x:v>
       </x:c>
     </x:row>
     <x:row r="222" ht="15" hidden="0" customHeight="1">
@@ -4055,10 +4055,10 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="D222" s="7" t="n">
-        <x:v>145</x:v>
+        <x:v>225</x:v>
       </x:c>
       <x:c r="E222" s="7" t="n">
-        <x:v>485</x:v>
+        <x:v>555</x:v>
       </x:c>
     </x:row>
     <x:row r="223" ht="15" hidden="0" customHeight="1">
@@ -4072,10 +4072,10 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="D223" s="7" t="n">
-        <x:v>195</x:v>
+        <x:v>345</x:v>
       </x:c>
       <x:c r="E223" s="7" t="n">
-        <x:v>485</x:v>
+        <x:v>465</x:v>
       </x:c>
     </x:row>
     <x:row r="224" ht="15" hidden="0" customHeight="1">
@@ -4089,432 +4089,432 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="D224" s="7" t="n">
-        <x:v>245</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="E224" s="7" t="n">
-        <x:v>485</x:v>
+        <x:v>235</x:v>
       </x:c>
     </x:row>
     <x:row r="225" ht="15" hidden="0" customHeight="1">
       <x:c r="A225" s="7" t="n">
-        <x:v>1022</x:v>
+        <x:v>1101</x:v>
       </x:c>
       <x:c r="B225" s="7" t="n">
-        <x:v>10</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C225" s="7" t="n">
-        <x:v>21</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D225" s="7" t="n">
-        <x:v>245</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="E225" s="7" t="n">
-        <x:v>535</x:v>
+        <x:v>225</x:v>
       </x:c>
     </x:row>
     <x:row r="226" ht="15" hidden="0" customHeight="1">
       <x:c r="A226" s="7" t="n">
-        <x:v>1101</x:v>
+        <x:v>1102</x:v>
       </x:c>
       <x:c r="B226" s="7" t="n">
         <x:v>11</x:v>
       </x:c>
       <x:c r="C226" s="7" t="n">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="D226" s="7" t="n">
-        <x:v>95</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="E226" s="7" t="n">
-        <x:v>185</x:v>
+        <x:v>225</x:v>
       </x:c>
     </x:row>
     <x:row r="227" ht="15" hidden="0" customHeight="1">
       <x:c r="A227" s="7" t="n">
-        <x:v>1102</x:v>
+        <x:v>1103</x:v>
       </x:c>
       <x:c r="B227" s="7" t="n">
         <x:v>11</x:v>
       </x:c>
       <x:c r="C227" s="7" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="D227" s="7" t="n">
-        <x:v>145</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="E227" s="7" t="n">
-        <x:v>185</x:v>
+        <x:v>225</x:v>
       </x:c>
     </x:row>
     <x:row r="228" ht="15" hidden="0" customHeight="1">
       <x:c r="A228" s="7" t="n">
-        <x:v>1103</x:v>
+        <x:v>1104</x:v>
       </x:c>
       <x:c r="B228" s="7" t="n">
         <x:v>11</x:v>
       </x:c>
       <x:c r="C228" s="7" t="n">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="D228" s="7" t="n">
-        <x:v>195</x:v>
+        <x:v>245</x:v>
       </x:c>
       <x:c r="E228" s="7" t="n">
-        <x:v>185</x:v>
+        <x:v>225</x:v>
       </x:c>
     </x:row>
     <x:row r="229" ht="15" hidden="0" customHeight="1">
       <x:c r="A229" s="7" t="n">
-        <x:v>1104</x:v>
+        <x:v>1105</x:v>
       </x:c>
       <x:c r="B229" s="7" t="n">
         <x:v>11</x:v>
       </x:c>
       <x:c r="C229" s="7" t="n">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="D229" s="7" t="n">
-        <x:v>245</x:v>
+        <x:v>295</x:v>
       </x:c>
       <x:c r="E229" s="7" t="n">
-        <x:v>185</x:v>
+        <x:v>225</x:v>
       </x:c>
     </x:row>
     <x:row r="230" ht="15" hidden="0" customHeight="1">
       <x:c r="A230" s="7" t="n">
-        <x:v>1105</x:v>
+        <x:v>1106</x:v>
       </x:c>
       <x:c r="B230" s="7" t="n">
         <x:v>11</x:v>
       </x:c>
       <x:c r="C230" s="7" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D230" s="7" t="n">
-        <x:v>295</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="E230" s="7" t="n">
-        <x:v>185</x:v>
+        <x:v>235</x:v>
       </x:c>
     </x:row>
     <x:row r="231" ht="15" hidden="0" customHeight="1">
       <x:c r="A231" s="7" t="n">
-        <x:v>1106</x:v>
+        <x:v>1107</x:v>
       </x:c>
       <x:c r="B231" s="7" t="n">
         <x:v>11</x:v>
       </x:c>
       <x:c r="C231" s="7" t="n">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="D231" s="7" t="n">
-        <x:v>45</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="E231" s="7" t="n">
-        <x:v>235</x:v>
+        <x:v>345</x:v>
       </x:c>
     </x:row>
     <x:row r="232" ht="15" hidden="0" customHeight="1">
       <x:c r="A232" s="7" t="n">
-        <x:v>1107</x:v>
+        <x:v>1108</x:v>
       </x:c>
       <x:c r="B232" s="7" t="n">
         <x:v>11</x:v>
       </x:c>
       <x:c r="C232" s="7" t="n">
-        <x:v>6</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="D232" s="7" t="n">
-        <x:v>95</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="E232" s="7" t="n">
-        <x:v>235</x:v>
+        <x:v>345</x:v>
       </x:c>
     </x:row>
     <x:row r="233" ht="15" hidden="0" customHeight="1">
       <x:c r="A233" s="7" t="n">
-        <x:v>1108</x:v>
+        <x:v>1109</x:v>
       </x:c>
       <x:c r="B233" s="7" t="n">
         <x:v>11</x:v>
       </x:c>
       <x:c r="C233" s="7" t="n">
-        <x:v>7</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="D233" s="7" t="n">
-        <x:v>145</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="E233" s="7" t="n">
-        <x:v>235</x:v>
+        <x:v>345</x:v>
       </x:c>
     </x:row>
     <x:row r="234" ht="15" hidden="0" customHeight="1">
       <x:c r="A234" s="7" t="n">
-        <x:v>1109</x:v>
+        <x:v>1110</x:v>
       </x:c>
       <x:c r="B234" s="7" t="n">
         <x:v>11</x:v>
       </x:c>
       <x:c r="C234" s="7" t="n">
-        <x:v>8</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="D234" s="7" t="n">
-        <x:v>195</x:v>
+        <x:v>245</x:v>
       </x:c>
       <x:c r="E234" s="7" t="n">
-        <x:v>235</x:v>
+        <x:v>345</x:v>
       </x:c>
     </x:row>
     <x:row r="235" ht="15" hidden="0" customHeight="1">
       <x:c r="A235" s="7" t="n">
-        <x:v>1110</x:v>
+        <x:v>1111</x:v>
       </x:c>
       <x:c r="B235" s="7" t="n">
         <x:v>11</x:v>
       </x:c>
       <x:c r="C235" s="7" t="n">
-        <x:v>9</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="D235" s="7" t="n">
-        <x:v>245</x:v>
+        <x:v>295</x:v>
       </x:c>
       <x:c r="E235" s="7" t="n">
-        <x:v>235</x:v>
+        <x:v>335</x:v>
       </x:c>
     </x:row>
     <x:row r="236" ht="15" hidden="0" customHeight="1">
       <x:c r="A236" s="7" t="n">
-        <x:v>1111</x:v>
+        <x:v>1112</x:v>
       </x:c>
       <x:c r="B236" s="7" t="n">
         <x:v>11</x:v>
       </x:c>
       <x:c r="C236" s="7" t="n">
-        <x:v>10</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D236" s="7" t="n">
-        <x:v>295</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="E236" s="7" t="n">
-        <x:v>235</x:v>
+        <x:v>455</x:v>
       </x:c>
     </x:row>
     <x:row r="237" ht="15" hidden="0" customHeight="1">
       <x:c r="A237" s="7" t="n">
-        <x:v>1112</x:v>
+        <x:v>1113</x:v>
       </x:c>
       <x:c r="B237" s="7" t="n">
         <x:v>11</x:v>
       </x:c>
       <x:c r="C237" s="7" t="n">
-        <x:v>11</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="D237" s="7" t="n">
-        <x:v>95</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="E237" s="7" t="n">
-        <x:v>335</x:v>
+        <x:v>455</x:v>
       </x:c>
     </x:row>
     <x:row r="238" ht="15" hidden="0" customHeight="1">
       <x:c r="A238" s="7" t="n">
-        <x:v>1113</x:v>
+        <x:v>1114</x:v>
       </x:c>
       <x:c r="B238" s="7" t="n">
         <x:v>11</x:v>
       </x:c>
       <x:c r="C238" s="7" t="n">
-        <x:v>12</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D238" s="7" t="n">
-        <x:v>145</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="E238" s="7" t="n">
-        <x:v>335</x:v>
+        <x:v>455</x:v>
       </x:c>
     </x:row>
     <x:row r="239" ht="15" hidden="0" customHeight="1">
       <x:c r="A239" s="7" t="n">
-        <x:v>1114</x:v>
+        <x:v>1115</x:v>
       </x:c>
       <x:c r="B239" s="7" t="n">
         <x:v>11</x:v>
       </x:c>
       <x:c r="C239" s="7" t="n">
-        <x:v>13</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="D239" s="7" t="n">
-        <x:v>195</x:v>
+        <x:v>335</x:v>
       </x:c>
       <x:c r="E239" s="7" t="n">
-        <x:v>335</x:v>
+        <x:v>365</x:v>
       </x:c>
     </x:row>
     <x:row r="240" ht="15" hidden="0" customHeight="1">
       <x:c r="A240" s="7" t="n">
-        <x:v>1115</x:v>
+        <x:v>1116</x:v>
       </x:c>
       <x:c r="B240" s="7" t="n">
         <x:v>11</x:v>
       </x:c>
       <x:c r="C240" s="7" t="n">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="D240" s="7" t="n">
-        <x:v>245</x:v>
+        <x:v>345</x:v>
       </x:c>
       <x:c r="E240" s="7" t="n">
-        <x:v>335</x:v>
+        <x:v>415</x:v>
       </x:c>
     </x:row>
     <x:row r="241" ht="15" hidden="0" customHeight="1">
       <x:c r="A241" s="7" t="n">
-        <x:v>1116</x:v>
+        <x:v>1117</x:v>
       </x:c>
       <x:c r="B241" s="7" t="n">
         <x:v>11</x:v>
       </x:c>
       <x:c r="C241" s="7" t="n">
-        <x:v>15</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="D241" s="7" t="n">
-        <x:v>295</x:v>
+        <x:v>345</x:v>
       </x:c>
       <x:c r="E241" s="7" t="n">
-        <x:v>335</x:v>
+        <x:v>465</x:v>
       </x:c>
     </x:row>
     <x:row r="242" ht="15" hidden="0" customHeight="1">
       <x:c r="A242" s="7" t="n">
-        <x:v>1117</x:v>
+        <x:v>1118</x:v>
       </x:c>
       <x:c r="B242" s="7" t="n">
         <x:v>11</x:v>
       </x:c>
       <x:c r="C242" s="7" t="n">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="D242" s="7" t="n">
-        <x:v>345</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="E242" s="7" t="n">
-        <x:v>335</x:v>
+        <x:v>455</x:v>
       </x:c>
     </x:row>
     <x:row r="243" ht="15" hidden="0" customHeight="1">
       <x:c r="A243" s="7" t="n">
-        <x:v>1118</x:v>
+        <x:v>1119</x:v>
       </x:c>
       <x:c r="B243" s="7" t="n">
         <x:v>11</x:v>
       </x:c>
       <x:c r="C243" s="7" t="n">
-        <x:v>17</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="D243" s="7" t="n">
-        <x:v>95</x:v>
+        <x:v>245</x:v>
       </x:c>
       <x:c r="E243" s="7" t="n">
-        <x:v>385</x:v>
+        <x:v>455</x:v>
       </x:c>
     </x:row>
     <x:row r="244" ht="15" hidden="0" customHeight="1">
       <x:c r="A244" s="7" t="n">
-        <x:v>1119</x:v>
+        <x:v>1120</x:v>
       </x:c>
       <x:c r="B244" s="7" t="n">
         <x:v>11</x:v>
       </x:c>
       <x:c r="C244" s="7" t="n">
-        <x:v>18</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="D244" s="7" t="n">
-        <x:v>345</x:v>
+        <x:v>225</x:v>
       </x:c>
       <x:c r="E244" s="7" t="n">
-        <x:v>435</x:v>
+        <x:v>505</x:v>
       </x:c>
     </x:row>
     <x:row r="245" ht="15" hidden="0" customHeight="1">
       <x:c r="A245" s="7" t="n">
-        <x:v>1120</x:v>
+        <x:v>1121</x:v>
       </x:c>
       <x:c r="B245" s="7" t="n">
         <x:v>11</x:v>
       </x:c>
       <x:c r="C245" s="7" t="n">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="D245" s="7" t="n">
-        <x:v>45</x:v>
+        <x:v>225</x:v>
       </x:c>
       <x:c r="E245" s="7" t="n">
-        <x:v>485</x:v>
+        <x:v>555</x:v>
       </x:c>
     </x:row>
     <x:row r="246" ht="15" hidden="0" customHeight="1">
       <x:c r="A246" s="7" t="n">
-        <x:v>1121</x:v>
+        <x:v>1201</x:v>
       </x:c>
       <x:c r="B246" s="7" t="n">
-        <x:v>11</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C246" s="7" t="n">
-        <x:v>20</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D246" s="7" t="n">
-        <x:v>95</x:v>
+        <x:v>185</x:v>
       </x:c>
       <x:c r="E246" s="7" t="n">
-        <x:v>485</x:v>
+        <x:v>125</x:v>
       </x:c>
     </x:row>
     <x:row r="247" ht="15" hidden="0" customHeight="1">
       <x:c r="A247" s="7" t="n">
-        <x:v>1122</x:v>
+        <x:v>1202</x:v>
       </x:c>
       <x:c r="B247" s="7" t="n">
-        <x:v>11</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C247" s="7" t="n">
-        <x:v>21</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="D247" s="7" t="n">
-        <x:v>345</x:v>
+        <x:v>155</x:v>
       </x:c>
       <x:c r="E247" s="7" t="n">
-        <x:v>485</x:v>
+        <x:v>175</x:v>
       </x:c>
     </x:row>
     <x:row r="248" ht="15" hidden="0" customHeight="1">
       <x:c r="A248" s="7" t="n">
-        <x:v>1201</x:v>
+        <x:v>1203</x:v>
       </x:c>
       <x:c r="B248" s="7" t="n">
         <x:v>12</x:v>
       </x:c>
       <x:c r="C248" s="7" t="n">
-        <x:v>0</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="D248" s="7" t="n">
-        <x:v>195</x:v>
+        <x:v>170</x:v>
       </x:c>
       <x:c r="E248" s="7" t="n">
-        <x:v>135</x:v>
+        <x:v>235</x:v>
       </x:c>
     </x:row>
     <x:row r="249" ht="15" hidden="0" customHeight="1">
       <x:c r="A249" s="7" t="n">
-        <x:v>1202</x:v>
+        <x:v>1204</x:v>
       </x:c>
       <x:c r="B249" s="7" t="n">
         <x:v>12</x:v>
       </x:c>
       <x:c r="C249" s="7" t="n">
-        <x:v>1</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="D249" s="7" t="n">
-        <x:v>145</x:v>
+        <x:v>280</x:v>
       </x:c>
       <x:c r="E249" s="7" t="n">
         <x:v>185</x:v>
@@ -4522,1223 +4522,1223 @@
     </x:row>
     <x:row r="250" ht="15" hidden="0" customHeight="1">
       <x:c r="A250" s="7" t="n">
-        <x:v>1203</x:v>
+        <x:v>1205</x:v>
       </x:c>
       <x:c r="B250" s="7" t="n">
         <x:v>12</x:v>
       </x:c>
       <x:c r="C250" s="7" t="n">
-        <x:v>2</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="D250" s="7" t="n">
-        <x:v>195</x:v>
+        <x:v>170</x:v>
       </x:c>
       <x:c r="E250" s="7" t="n">
-        <x:v>185</x:v>
+        <x:v>285</x:v>
       </x:c>
     </x:row>
     <x:row r="251" ht="15" hidden="0" customHeight="1">
       <x:c r="A251" s="7" t="n">
-        <x:v>1204</x:v>
+        <x:v>1206</x:v>
       </x:c>
       <x:c r="B251" s="7" t="n">
         <x:v>12</x:v>
       </x:c>
       <x:c r="C251" s="7" t="n">
-        <x:v>3</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D251" s="7" t="n">
-        <x:v>295</x:v>
+        <x:v>280</x:v>
       </x:c>
       <x:c r="E251" s="7" t="n">
-        <x:v>185</x:v>
+        <x:v>235</x:v>
       </x:c>
     </x:row>
     <x:row r="252" ht="15" hidden="0" customHeight="1">
       <x:c r="A252" s="7" t="n">
-        <x:v>1205</x:v>
+        <x:v>1207</x:v>
       </x:c>
       <x:c r="B252" s="7" t="n">
         <x:v>12</x:v>
       </x:c>
       <x:c r="C252" s="7" t="n">
-        <x:v>4</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="D252" s="7" t="n">
-        <x:v>145</x:v>
+        <x:v>280</x:v>
       </x:c>
       <x:c r="E252" s="7" t="n">
-        <x:v>235</x:v>
+        <x:v>285</x:v>
       </x:c>
     </x:row>
     <x:row r="253" ht="15" hidden="0" customHeight="1">
       <x:c r="A253" s="7" t="n">
-        <x:v>1206</x:v>
+        <x:v>1208</x:v>
       </x:c>
       <x:c r="B253" s="7" t="n">
         <x:v>12</x:v>
       </x:c>
       <x:c r="C253" s="7" t="n">
-        <x:v>5</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="D253" s="7" t="n">
-        <x:v>195</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="E253" s="7" t="n">
-        <x:v>235</x:v>
+        <x:v>285</x:v>
       </x:c>
     </x:row>
     <x:row r="254" ht="15" hidden="0" customHeight="1">
       <x:c r="A254" s="7" t="n">
-        <x:v>1207</x:v>
+        <x:v>1209</x:v>
       </x:c>
       <x:c r="B254" s="7" t="n">
         <x:v>12</x:v>
       </x:c>
       <x:c r="C254" s="7" t="n">
-        <x:v>6</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="D254" s="7" t="n">
-        <x:v>295</x:v>
+        <x:v>170</x:v>
       </x:c>
       <x:c r="E254" s="7" t="n">
-        <x:v>235</x:v>
+        <x:v>335</x:v>
       </x:c>
     </x:row>
     <x:row r="255" ht="15" hidden="0" customHeight="1">
       <x:c r="A255" s="7" t="n">
-        <x:v>1208</x:v>
+        <x:v>1210</x:v>
       </x:c>
       <x:c r="B255" s="7" t="n">
         <x:v>12</x:v>
       </x:c>
       <x:c r="C255" s="7" t="n">
-        <x:v>7</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="D255" s="7" t="n">
-        <x:v>45</x:v>
+        <x:v>280</x:v>
       </x:c>
       <x:c r="E255" s="7" t="n">
-        <x:v>285</x:v>
+        <x:v>335</x:v>
       </x:c>
     </x:row>
     <x:row r="256" ht="15" hidden="0" customHeight="1">
       <x:c r="A256" s="7" t="n">
-        <x:v>1209</x:v>
+        <x:v>1211</x:v>
       </x:c>
       <x:c r="B256" s="7" t="n">
         <x:v>12</x:v>
       </x:c>
       <x:c r="C256" s="7" t="n">
-        <x:v>8</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="D256" s="7" t="n">
-        <x:v>145</x:v>
+        <x:v>280</x:v>
       </x:c>
       <x:c r="E256" s="7" t="n">
-        <x:v>285</x:v>
+        <x:v>385</x:v>
       </x:c>
     </x:row>
     <x:row r="257" ht="15" hidden="0" customHeight="1">
       <x:c r="A257" s="7" t="n">
-        <x:v>1210</x:v>
+        <x:v>1212</x:v>
       </x:c>
       <x:c r="B257" s="7" t="n">
         <x:v>12</x:v>
       </x:c>
       <x:c r="C257" s="7" t="n">
-        <x:v>9</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D257" s="7" t="n">
-        <x:v>195</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="E257" s="7" t="n">
-        <x:v>285</x:v>
+        <x:v>335</x:v>
       </x:c>
     </x:row>
     <x:row r="258" ht="15" hidden="0" customHeight="1">
       <x:c r="A258" s="7" t="n">
-        <x:v>1211</x:v>
+        <x:v>1213</x:v>
       </x:c>
       <x:c r="B258" s="7" t="n">
         <x:v>12</x:v>
       </x:c>
       <x:c r="C258" s="7" t="n">
-        <x:v>10</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="D258" s="7" t="n">
-        <x:v>295</x:v>
+        <x:v>170</x:v>
       </x:c>
       <x:c r="E258" s="7" t="n">
-        <x:v>285</x:v>
+        <x:v>385</x:v>
       </x:c>
     </x:row>
     <x:row r="259" ht="15" hidden="0" customHeight="1">
       <x:c r="A259" s="7" t="n">
-        <x:v>1212</x:v>
+        <x:v>1214</x:v>
       </x:c>
       <x:c r="B259" s="7" t="n">
         <x:v>12</x:v>
       </x:c>
       <x:c r="C259" s="7" t="n">
-        <x:v>11</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D259" s="7" t="n">
-        <x:v>45</x:v>
+        <x:v>170</x:v>
       </x:c>
       <x:c r="E259" s="7" t="n">
-        <x:v>335</x:v>
+        <x:v>435</x:v>
       </x:c>
     </x:row>
     <x:row r="260" ht="15" hidden="0" customHeight="1">
       <x:c r="A260" s="7" t="n">
-        <x:v>1213</x:v>
+        <x:v>1215</x:v>
       </x:c>
       <x:c r="B260" s="7" t="n">
         <x:v>12</x:v>
       </x:c>
       <x:c r="C260" s="7" t="n">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="D260" s="7" t="n">
-        <x:v>145</x:v>
+        <x:v>285</x:v>
       </x:c>
       <x:c r="E260" s="7" t="n">
-        <x:v>335</x:v>
+        <x:v>475</x:v>
       </x:c>
     </x:row>
     <x:row r="261" ht="15" hidden="0" customHeight="1">
       <x:c r="A261" s="7" t="n">
-        <x:v>1214</x:v>
+        <x:v>1216</x:v>
       </x:c>
       <x:c r="B261" s="7" t="n">
         <x:v>12</x:v>
       </x:c>
       <x:c r="C261" s="7" t="n">
-        <x:v>13</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="D261" s="7" t="n">
-        <x:v>195</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="E261" s="7" t="n">
-        <x:v>335</x:v>
+        <x:v>385</x:v>
       </x:c>
     </x:row>
     <x:row r="262" ht="15" hidden="0" customHeight="1">
       <x:c r="A262" s="7" t="n">
-        <x:v>1215</x:v>
+        <x:v>1217</x:v>
       </x:c>
       <x:c r="B262" s="7" t="n">
         <x:v>12</x:v>
       </x:c>
       <x:c r="C262" s="7" t="n">
-        <x:v>14</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="D262" s="7" t="n">
-        <x:v>295</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="E262" s="7" t="n">
-        <x:v>335</x:v>
+        <x:v>435</x:v>
       </x:c>
     </x:row>
     <x:row r="263" ht="15" hidden="0" customHeight="1">
       <x:c r="A263" s="7" t="n">
-        <x:v>1216</x:v>
+        <x:v>1218</x:v>
       </x:c>
       <x:c r="B263" s="7" t="n">
         <x:v>12</x:v>
       </x:c>
       <x:c r="C263" s="7" t="n">
-        <x:v>15</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="D263" s="7" t="n">
-        <x:v>45</x:v>
+        <x:v>170</x:v>
       </x:c>
       <x:c r="E263" s="7" t="n">
-        <x:v>385</x:v>
+        <x:v>485</x:v>
       </x:c>
     </x:row>
     <x:row r="264" ht="15" hidden="0" customHeight="1">
       <x:c r="A264" s="7" t="n">
-        <x:v>1217</x:v>
+        <x:v>1219</x:v>
       </x:c>
       <x:c r="B264" s="7" t="n">
         <x:v>12</x:v>
       </x:c>
       <x:c r="C264" s="7" t="n">
-        <x:v>16</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="D264" s="7" t="n">
-        <x:v>145</x:v>
+        <x:v>325</x:v>
       </x:c>
       <x:c r="E264" s="7" t="n">
-        <x:v>385</x:v>
+        <x:v>505</x:v>
       </x:c>
     </x:row>
     <x:row r="265" ht="15" hidden="0" customHeight="1">
       <x:c r="A265" s="7" t="n">
-        <x:v>1218</x:v>
+        <x:v>1220</x:v>
       </x:c>
       <x:c r="B265" s="7" t="n">
         <x:v>12</x:v>
       </x:c>
       <x:c r="C265" s="7" t="n">
-        <x:v>17</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="D265" s="7" t="n">
-        <x:v>195</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="E265" s="7" t="n">
-        <x:v>385</x:v>
+        <x:v>485</x:v>
       </x:c>
     </x:row>
     <x:row r="266" ht="15" hidden="0" customHeight="1">
       <x:c r="A266" s="7" t="n">
-        <x:v>1219</x:v>
+        <x:v>1221</x:v>
       </x:c>
       <x:c r="B266" s="7" t="n">
         <x:v>12</x:v>
       </x:c>
       <x:c r="C266" s="7" t="n">
-        <x:v>18</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="D266" s="7" t="n">
-        <x:v>295</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="E266" s="7" t="n">
-        <x:v>385</x:v>
+        <x:v>535</x:v>
       </x:c>
     </x:row>
     <x:row r="267" ht="15" hidden="0" customHeight="1">
       <x:c r="A267" s="7" t="n">
-        <x:v>1220</x:v>
+        <x:v>1222</x:v>
       </x:c>
       <x:c r="B267" s="7" t="n">
         <x:v>12</x:v>
       </x:c>
       <x:c r="C267" s="7" t="n">
-        <x:v>19</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="D267" s="7" t="n">
-        <x:v>45</x:v>
+        <x:v>280</x:v>
       </x:c>
       <x:c r="E267" s="7" t="n">
-        <x:v>435</x:v>
+        <x:v>535</x:v>
       </x:c>
     </x:row>
     <x:row r="268" ht="15" hidden="0" customHeight="1">
       <x:c r="A268" s="7" t="n">
-        <x:v>1221</x:v>
+        <x:v>1301</x:v>
       </x:c>
       <x:c r="B268" s="7" t="n">
-        <x:v>12</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C268" s="7" t="n">
-        <x:v>20</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D268" s="7" t="n">
-        <x:v>145</x:v>
+        <x:v>245</x:v>
       </x:c>
       <x:c r="E268" s="7" t="n">
-        <x:v>435</x:v>
+        <x:v>165</x:v>
       </x:c>
     </x:row>
     <x:row r="269" ht="15" hidden="0" customHeight="1">
       <x:c r="A269" s="7" t="n">
-        <x:v>1222</x:v>
+        <x:v>1302</x:v>
       </x:c>
       <x:c r="B269" s="7" t="n">
-        <x:v>12</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C269" s="7" t="n">
-        <x:v>21</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="D269" s="7" t="n">
-        <x:v>195</x:v>
+        <x:v>245</x:v>
       </x:c>
       <x:c r="E269" s="7" t="n">
-        <x:v>435</x:v>
+        <x:v>215</x:v>
       </x:c>
     </x:row>
     <x:row r="270" ht="15" hidden="0" customHeight="1">
       <x:c r="A270" s="7" t="n">
-        <x:v>1301</x:v>
+        <x:v>1303</x:v>
       </x:c>
       <x:c r="B270" s="7" t="n">
         <x:v>13</x:v>
       </x:c>
       <x:c r="C270" s="7" t="n">
-        <x:v>0</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="D270" s="7" t="n">
-        <x:v>245</x:v>
+        <x:v>345</x:v>
       </x:c>
       <x:c r="E270" s="7" t="n">
-        <x:v>135</x:v>
+        <x:v>225</x:v>
       </x:c>
     </x:row>
     <x:row r="271" ht="15" hidden="0" customHeight="1">
       <x:c r="A271" s="7" t="n">
-        <x:v>1302</x:v>
+        <x:v>1304</x:v>
       </x:c>
       <x:c r="B271" s="7" t="n">
         <x:v>13</x:v>
       </x:c>
       <x:c r="C271" s="7" t="n">
-        <x:v>1</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="D271" s="7" t="n">
-        <x:v>245</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="E271" s="7" t="n">
-        <x:v>185</x:v>
+        <x:v>230</x:v>
       </x:c>
     </x:row>
     <x:row r="272" ht="15" hidden="0" customHeight="1">
       <x:c r="A272" s="7" t="n">
-        <x:v>1303</x:v>
+        <x:v>1305</x:v>
       </x:c>
       <x:c r="B272" s="7" t="n">
         <x:v>13</x:v>
       </x:c>
       <x:c r="C272" s="7" t="n">
-        <x:v>2</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="D272" s="7" t="n">
-        <x:v>345</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="E272" s="7" t="n">
-        <x:v>185</x:v>
+        <x:v>230</x:v>
       </x:c>
     </x:row>
     <x:row r="273" ht="15" hidden="0" customHeight="1">
       <x:c r="A273" s="7" t="n">
-        <x:v>1304</x:v>
+        <x:v>1306</x:v>
       </x:c>
       <x:c r="B273" s="7" t="n">
         <x:v>13</x:v>
       </x:c>
       <x:c r="C273" s="7" t="n">
-        <x:v>3</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D273" s="7" t="n">
-        <x:v>95</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="E273" s="7" t="n">
-        <x:v>235</x:v>
+        <x:v>230</x:v>
       </x:c>
     </x:row>
     <x:row r="274" ht="15" hidden="0" customHeight="1">
       <x:c r="A274" s="7" t="n">
-        <x:v>1305</x:v>
+        <x:v>1307</x:v>
       </x:c>
       <x:c r="B274" s="7" t="n">
         <x:v>13</x:v>
       </x:c>
       <x:c r="C274" s="7" t="n">
-        <x:v>4</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="D274" s="7" t="n">
-        <x:v>145</x:v>
+        <x:v>245</x:v>
       </x:c>
       <x:c r="E274" s="7" t="n">
-        <x:v>235</x:v>
+        <x:v>340</x:v>
       </x:c>
     </x:row>
     <x:row r="275" ht="15" hidden="0" customHeight="1">
       <x:c r="A275" s="7" t="n">
-        <x:v>1306</x:v>
+        <x:v>1308</x:v>
       </x:c>
       <x:c r="B275" s="7" t="n">
         <x:v>13</x:v>
       </x:c>
       <x:c r="C275" s="7" t="n">
-        <x:v>5</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="D275" s="7" t="n">
-        <x:v>195</x:v>
+        <x:v>345</x:v>
       </x:c>
       <x:c r="E275" s="7" t="n">
-        <x:v>235</x:v>
+        <x:v>275</x:v>
       </x:c>
     </x:row>
     <x:row r="276" ht="15" hidden="0" customHeight="1">
       <x:c r="A276" s="7" t="n">
-        <x:v>1307</x:v>
+        <x:v>1309</x:v>
       </x:c>
       <x:c r="B276" s="7" t="n">
         <x:v>13</x:v>
       </x:c>
       <x:c r="C276" s="7" t="n">
-        <x:v>6</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="D276" s="7" t="n">
-        <x:v>245</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="E276" s="7" t="n">
-        <x:v>235</x:v>
+        <x:v>280</x:v>
       </x:c>
     </x:row>
     <x:row r="277" ht="15" hidden="0" customHeight="1">
       <x:c r="A277" s="7" t="n">
-        <x:v>1308</x:v>
+        <x:v>1310</x:v>
       </x:c>
       <x:c r="B277" s="7" t="n">
         <x:v>13</x:v>
       </x:c>
       <x:c r="C277" s="7" t="n">
-        <x:v>7</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="D277" s="7" t="n">
         <x:v>345</x:v>
       </x:c>
       <x:c r="E277" s="7" t="n">
-        <x:v>235</x:v>
+        <x:v>325</x:v>
       </x:c>
     </x:row>
     <x:row r="278" ht="15" hidden="0" customHeight="1">
       <x:c r="A278" s="7" t="n">
-        <x:v>1309</x:v>
+        <x:v>1311</x:v>
       </x:c>
       <x:c r="B278" s="7" t="n">
         <x:v>13</x:v>
       </x:c>
       <x:c r="C278" s="7" t="n">
-        <x:v>8</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="D278" s="7" t="n">
         <x:v>45</x:v>
       </x:c>
       <x:c r="E278" s="7" t="n">
-        <x:v>285</x:v>
+        <x:v>330</x:v>
       </x:c>
     </x:row>
     <x:row r="279" ht="15" hidden="0" customHeight="1">
       <x:c r="A279" s="7" t="n">
-        <x:v>1310</x:v>
+        <x:v>1312</x:v>
       </x:c>
       <x:c r="B279" s="7" t="n">
         <x:v>13</x:v>
       </x:c>
       <x:c r="C279" s="7" t="n">
-        <x:v>9</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D279" s="7" t="n">
-        <x:v>345</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="E279" s="7" t="n">
-        <x:v>285</x:v>
+        <x:v>340</x:v>
       </x:c>
     </x:row>
     <x:row r="280" ht="15" hidden="0" customHeight="1">
       <x:c r="A280" s="7" t="n">
-        <x:v>1311</x:v>
+        <x:v>1313</x:v>
       </x:c>
       <x:c r="B280" s="7" t="n">
         <x:v>13</x:v>
       </x:c>
       <x:c r="C280" s="7" t="n">
-        <x:v>10</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="D280" s="7" t="n">
-        <x:v>45</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="E280" s="7" t="n">
-        <x:v>335</x:v>
+        <x:v>340</x:v>
       </x:c>
     </x:row>
     <x:row r="281" ht="15" hidden="0" customHeight="1">
       <x:c r="A281" s="7" t="n">
-        <x:v>1312</x:v>
+        <x:v>1314</x:v>
       </x:c>
       <x:c r="B281" s="7" t="n">
         <x:v>13</x:v>
       </x:c>
       <x:c r="C281" s="7" t="n">
-        <x:v>11</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D281" s="7" t="n">
-        <x:v>145</x:v>
+        <x:v>295</x:v>
       </x:c>
       <x:c r="E281" s="7" t="n">
-        <x:v>335</x:v>
+        <x:v>330</x:v>
       </x:c>
     </x:row>
     <x:row r="282" ht="15" hidden="0" customHeight="1">
       <x:c r="A282" s="7" t="n">
-        <x:v>1313</x:v>
+        <x:v>1315</x:v>
       </x:c>
       <x:c r="B282" s="7" t="n">
         <x:v>13</x:v>
       </x:c>
       <x:c r="C282" s="7" t="n">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="D282" s="7" t="n">
-        <x:v>195</x:v>
+        <x:v>335</x:v>
       </x:c>
       <x:c r="E282" s="7" t="n">
-        <x:v>335</x:v>
+        <x:v>375</x:v>
       </x:c>
     </x:row>
     <x:row r="283" ht="15" hidden="0" customHeight="1">
       <x:c r="A283" s="7" t="n">
-        <x:v>1314</x:v>
+        <x:v>1316</x:v>
       </x:c>
       <x:c r="B283" s="7" t="n">
         <x:v>13</x:v>
       </x:c>
       <x:c r="C283" s="7" t="n">
-        <x:v>13</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="D283" s="7" t="n">
-        <x:v>245</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="E283" s="7" t="n">
-        <x:v>335</x:v>
+        <x:v>380</x:v>
       </x:c>
     </x:row>
     <x:row r="284" ht="15" hidden="0" customHeight="1">
       <x:c r="A284" s="7" t="n">
-        <x:v>1315</x:v>
+        <x:v>1317</x:v>
       </x:c>
       <x:c r="B284" s="7" t="n">
         <x:v>13</x:v>
       </x:c>
       <x:c r="C284" s="7" t="n">
-        <x:v>14</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="D284" s="7" t="n">
-        <x:v>295</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="E284" s="7" t="n">
-        <x:v>335</x:v>
+        <x:v>450</x:v>
       </x:c>
     </x:row>
     <x:row r="285" ht="15" hidden="0" customHeight="1">
       <x:c r="A285" s="7" t="n">
-        <x:v>1316</x:v>
+        <x:v>1318</x:v>
       </x:c>
       <x:c r="B285" s="7" t="n">
         <x:v>13</x:v>
       </x:c>
       <x:c r="C285" s="7" t="n">
-        <x:v>15</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="D285" s="7" t="n">
-        <x:v>45</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="E285" s="7" t="n">
-        <x:v>385</x:v>
+        <x:v>450</x:v>
       </x:c>
     </x:row>
     <x:row r="286" ht="15" hidden="0" customHeight="1">
       <x:c r="A286" s="7" t="n">
-        <x:v>1317</x:v>
+        <x:v>1319</x:v>
       </x:c>
       <x:c r="B286" s="7" t="n">
         <x:v>13</x:v>
       </x:c>
       <x:c r="C286" s="7" t="n">
-        <x:v>16</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="D286" s="7" t="n">
-        <x:v>145</x:v>
+        <x:v>345</x:v>
       </x:c>
       <x:c r="E286" s="7" t="n">
-        <x:v>385</x:v>
+        <x:v>425</x:v>
       </x:c>
     </x:row>
     <x:row r="287" ht="15" hidden="0" customHeight="1">
       <x:c r="A287" s="7" t="n">
-        <x:v>1318</x:v>
+        <x:v>1320</x:v>
       </x:c>
       <x:c r="B287" s="7" t="n">
         <x:v>13</x:v>
       </x:c>
       <x:c r="C287" s="7" t="n">
-        <x:v>17</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="D287" s="7" t="n">
-        <x:v>195</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="E287" s="7" t="n">
-        <x:v>385</x:v>
+        <x:v>450</x:v>
       </x:c>
     </x:row>
     <x:row r="288" ht="15" hidden="0" customHeight="1">
       <x:c r="A288" s="7" t="n">
-        <x:v>1319</x:v>
+        <x:v>1321</x:v>
       </x:c>
       <x:c r="B288" s="7" t="n">
         <x:v>13</x:v>
       </x:c>
       <x:c r="C288" s="7" t="n">
-        <x:v>18</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="D288" s="7" t="n">
-        <x:v>345</x:v>
+        <x:v>245</x:v>
       </x:c>
       <x:c r="E288" s="7" t="n">
-        <x:v>435</x:v>
+        <x:v>450</x:v>
       </x:c>
     </x:row>
     <x:row r="289" ht="15" hidden="0" customHeight="1">
       <x:c r="A289" s="7" t="n">
-        <x:v>1320</x:v>
+        <x:v>1322</x:v>
       </x:c>
       <x:c r="B289" s="7" t="n">
         <x:v>13</x:v>
       </x:c>
       <x:c r="C289" s="7" t="n">
-        <x:v>19</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="D289" s="7" t="n">
-        <x:v>95</x:v>
+        <x:v>345</x:v>
       </x:c>
       <x:c r="E289" s="7" t="n">
-        <x:v>485</x:v>
+        <x:v>475</x:v>
       </x:c>
     </x:row>
     <x:row r="290" ht="15" hidden="0" customHeight="1">
       <x:c r="A290" s="7" t="n">
-        <x:v>1321</x:v>
+        <x:v>1401</x:v>
       </x:c>
       <x:c r="B290" s="7" t="n">
-        <x:v>13</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C290" s="7" t="n">
-        <x:v>20</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D290" s="7" t="n">
-        <x:v>145</x:v>
+        <x:v>295</x:v>
       </x:c>
       <x:c r="E290" s="7" t="n">
-        <x:v>485</x:v>
+        <x:v>175</x:v>
       </x:c>
     </x:row>
     <x:row r="291" ht="15" hidden="0" customHeight="1">
       <x:c r="A291" s="7" t="n">
-        <x:v>1322</x:v>
+        <x:v>1402</x:v>
       </x:c>
       <x:c r="B291" s="7" t="n">
-        <x:v>13</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C291" s="7" t="n">
-        <x:v>21</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="D291" s="7" t="n">
-        <x:v>345</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="E291" s="7" t="n">
-        <x:v>485</x:v>
+        <x:v>225</x:v>
       </x:c>
     </x:row>
     <x:row r="292" ht="15" hidden="0" customHeight="1">
       <x:c r="A292" s="7" t="n">
-        <x:v>1401</x:v>
+        <x:v>1403</x:v>
       </x:c>
       <x:c r="B292" s="7" t="n">
         <x:v>14</x:v>
       </x:c>
       <x:c r="C292" s="7" t="n">
-        <x:v>0</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="D292" s="7" t="n">
-        <x:v>295</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="E292" s="7" t="n">
-        <x:v>135</x:v>
+        <x:v>225</x:v>
       </x:c>
     </x:row>
     <x:row r="293" ht="15" hidden="0" customHeight="1">
       <x:c r="A293" s="7" t="n">
-        <x:v>1402</x:v>
+        <x:v>1404</x:v>
       </x:c>
       <x:c r="B293" s="7" t="n">
         <x:v>14</x:v>
       </x:c>
       <x:c r="C293" s="7" t="n">
-        <x:v>1</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="D293" s="7" t="n">
-        <x:v>95</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="E293" s="7" t="n">
-        <x:v>185</x:v>
+        <x:v>225</x:v>
       </x:c>
     </x:row>
     <x:row r="294" ht="15" hidden="0" customHeight="1">
       <x:c r="A294" s="7" t="n">
-        <x:v>1403</x:v>
+        <x:v>1405</x:v>
       </x:c>
       <x:c r="B294" s="7" t="n">
         <x:v>14</x:v>
       </x:c>
       <x:c r="C294" s="7" t="n">
-        <x:v>2</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="D294" s="7" t="n">
-        <x:v>145</x:v>
+        <x:v>295</x:v>
       </x:c>
       <x:c r="E294" s="7" t="n">
-        <x:v>185</x:v>
+        <x:v>225</x:v>
       </x:c>
     </x:row>
     <x:row r="295" ht="15" hidden="0" customHeight="1">
       <x:c r="A295" s="7" t="n">
-        <x:v>1404</x:v>
+        <x:v>1406</x:v>
       </x:c>
       <x:c r="B295" s="7" t="n">
         <x:v>14</x:v>
       </x:c>
       <x:c r="C295" s="7" t="n">
-        <x:v>3</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D295" s="7" t="n">
-        <x:v>195</x:v>
+        <x:v>295</x:v>
       </x:c>
       <x:c r="E295" s="7" t="n">
-        <x:v>185</x:v>
+        <x:v>275</x:v>
       </x:c>
     </x:row>
     <x:row r="296" ht="15" hidden="0" customHeight="1">
       <x:c r="A296" s="7" t="n">
-        <x:v>1405</x:v>
+        <x:v>1407</x:v>
       </x:c>
       <x:c r="B296" s="7" t="n">
         <x:v>14</x:v>
       </x:c>
       <x:c r="C296" s="7" t="n">
-        <x:v>4</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="D296" s="7" t="n">
-        <x:v>295</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="E296" s="7" t="n">
-        <x:v>185</x:v>
+        <x:v>335</x:v>
       </x:c>
     </x:row>
     <x:row r="297" ht="15" hidden="0" customHeight="1">
       <x:c r="A297" s="7" t="n">
-        <x:v>1406</x:v>
+        <x:v>1408</x:v>
       </x:c>
       <x:c r="B297" s="7" t="n">
         <x:v>14</x:v>
       </x:c>
       <x:c r="C297" s="7" t="n">
-        <x:v>5</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="D297" s="7" t="n">
-        <x:v>295</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="E297" s="7" t="n">
-        <x:v>235</x:v>
+        <x:v>335</x:v>
       </x:c>
     </x:row>
     <x:row r="298" ht="15" hidden="0" customHeight="1">
       <x:c r="A298" s="7" t="n">
-        <x:v>1407</x:v>
+        <x:v>1409</x:v>
       </x:c>
       <x:c r="B298" s="7" t="n">
         <x:v>14</x:v>
       </x:c>
       <x:c r="C298" s="7" t="n">
-        <x:v>6</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="D298" s="7" t="n">
-        <x:v>95</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="E298" s="7" t="n">
-        <x:v>285</x:v>
+        <x:v>335</x:v>
       </x:c>
     </x:row>
     <x:row r="299" ht="15" hidden="0" customHeight="1">
       <x:c r="A299" s="7" t="n">
-        <x:v>1408</x:v>
+        <x:v>1410</x:v>
       </x:c>
       <x:c r="B299" s="7" t="n">
         <x:v>14</x:v>
       </x:c>
       <x:c r="C299" s="7" t="n">
-        <x:v>7</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="D299" s="7" t="n">
-        <x:v>145</x:v>
+        <x:v>245</x:v>
       </x:c>
       <x:c r="E299" s="7" t="n">
-        <x:v>285</x:v>
+        <x:v>325</x:v>
       </x:c>
     </x:row>
     <x:row r="300" ht="15" hidden="0" customHeight="1">
       <x:c r="A300" s="7" t="n">
-        <x:v>1409</x:v>
+        <x:v>1411</x:v>
       </x:c>
       <x:c r="B300" s="7" t="n">
         <x:v>14</x:v>
       </x:c>
       <x:c r="C300" s="7" t="n">
-        <x:v>8</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="D300" s="7" t="n">
-        <x:v>195</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="E300" s="7" t="n">
-        <x:v>285</x:v>
+        <x:v>445</x:v>
       </x:c>
     </x:row>
     <x:row r="301" ht="15" hidden="0" customHeight="1">
       <x:c r="A301" s="7" t="n">
-        <x:v>1410</x:v>
+        <x:v>1412</x:v>
       </x:c>
       <x:c r="B301" s="7" t="n">
         <x:v>14</x:v>
       </x:c>
       <x:c r="C301" s="7" t="n">
-        <x:v>9</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D301" s="7" t="n">
-        <x:v>245</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="E301" s="7" t="n">
-        <x:v>285</x:v>
+        <x:v>445</x:v>
       </x:c>
     </x:row>
     <x:row r="302" ht="15" hidden="0" customHeight="1">
       <x:c r="A302" s="7" t="n">
-        <x:v>1411</x:v>
+        <x:v>1413</x:v>
       </x:c>
       <x:c r="B302" s="7" t="n">
         <x:v>14</x:v>
       </x:c>
       <x:c r="C302" s="7" t="n">
-        <x:v>10</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="D302" s="7" t="n">
-        <x:v>95</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="E302" s="7" t="n">
-        <x:v>335</x:v>
+        <x:v>445</x:v>
       </x:c>
     </x:row>
     <x:row r="303" ht="15" hidden="0" customHeight="1">
       <x:c r="A303" s="7" t="n">
-        <x:v>1412</x:v>
+        <x:v>1414</x:v>
       </x:c>
       <x:c r="B303" s="7" t="n">
         <x:v>14</x:v>
       </x:c>
       <x:c r="C303" s="7" t="n">
-        <x:v>11</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D303" s="7" t="n">
-        <x:v>95</x:v>
+        <x:v>235</x:v>
       </x:c>
       <x:c r="E303" s="7" t="n">
-        <x:v>385</x:v>
+        <x:v>445</x:v>
       </x:c>
     </x:row>
     <x:row r="304" ht="15" hidden="0" customHeight="1">
       <x:c r="A304" s="7" t="n">
-        <x:v>1413</x:v>
+        <x:v>1415</x:v>
       </x:c>
       <x:c r="B304" s="7" t="n">
         <x:v>14</x:v>
       </x:c>
       <x:c r="C304" s="7" t="n">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="D304" s="7" t="n">
-        <x:v>145</x:v>
+        <x:v>295</x:v>
       </x:c>
       <x:c r="E304" s="7" t="n">
-        <x:v>385</x:v>
+        <x:v>345</x:v>
       </x:c>
     </x:row>
     <x:row r="305" ht="15" hidden="0" customHeight="1">
       <x:c r="A305" s="7" t="n">
-        <x:v>1414</x:v>
+        <x:v>1416</x:v>
       </x:c>
       <x:c r="B305" s="7" t="n">
         <x:v>14</x:v>
       </x:c>
       <x:c r="C305" s="7" t="n">
-        <x:v>13</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="D305" s="7" t="n">
-        <x:v>195</x:v>
+        <x:v>345</x:v>
       </x:c>
       <x:c r="E305" s="7" t="n">
-        <x:v>385</x:v>
+        <x:v>345</x:v>
       </x:c>
     </x:row>
     <x:row r="306" ht="15" hidden="0" customHeight="1">
       <x:c r="A306" s="7" t="n">
-        <x:v>1415</x:v>
+        <x:v>1417</x:v>
       </x:c>
       <x:c r="B306" s="7" t="n">
         <x:v>14</x:v>
       </x:c>
       <x:c r="C306" s="7" t="n">
-        <x:v>14</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="D306" s="7" t="n">
-        <x:v>245</x:v>
+        <x:v>295</x:v>
       </x:c>
       <x:c r="E306" s="7" t="n">
-        <x:v>385</x:v>
+        <x:v>445</x:v>
       </x:c>
     </x:row>
     <x:row r="307" ht="15" hidden="0" customHeight="1">
       <x:c r="A307" s="7" t="n">
-        <x:v>1416</x:v>
+        <x:v>1418</x:v>
       </x:c>
       <x:c r="B307" s="7" t="n">
         <x:v>14</x:v>
       </x:c>
       <x:c r="C307" s="7" t="n">
-        <x:v>15</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="D307" s="7" t="n">
-        <x:v>295</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="E307" s="7" t="n">
-        <x:v>385</x:v>
+        <x:v>495</x:v>
       </x:c>
     </x:row>
     <x:row r="308" ht="15" hidden="0" customHeight="1">
       <x:c r="A308" s="7" t="n">
-        <x:v>1417</x:v>
+        <x:v>1419</x:v>
       </x:c>
       <x:c r="B308" s="7" t="n">
         <x:v>14</x:v>
       </x:c>
       <x:c r="C308" s="7" t="n">
-        <x:v>16</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="D308" s="7" t="n">
-        <x:v>345</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="E308" s="7" t="n">
-        <x:v>385</x:v>
+        <x:v>545</x:v>
       </x:c>
     </x:row>
     <x:row r="309" ht="15" hidden="0" customHeight="1">
       <x:c r="A309" s="7" t="n">
-        <x:v>1418</x:v>
+        <x:v>1420</x:v>
       </x:c>
       <x:c r="B309" s="7" t="n">
         <x:v>14</x:v>
       </x:c>
       <x:c r="C309" s="7" t="n">
-        <x:v>17</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="D309" s="7" t="n">
-        <x:v>45</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="E309" s="7" t="n">
-        <x:v>485</x:v>
+        <x:v>565</x:v>
       </x:c>
     </x:row>
     <x:row r="310" ht="15" hidden="0" customHeight="1">
       <x:c r="A310" s="7" t="n">
-        <x:v>1419</x:v>
+        <x:v>1421</x:v>
       </x:c>
       <x:c r="B310" s="7" t="n">
         <x:v>14</x:v>
       </x:c>
       <x:c r="C310" s="7" t="n">
-        <x:v>18</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="D310" s="7" t="n">
-        <x:v>95</x:v>
+        <x:v>245</x:v>
       </x:c>
       <x:c r="E310" s="7" t="n">
-        <x:v>485</x:v>
+        <x:v>545</x:v>
       </x:c>
     </x:row>
     <x:row r="311" ht="15" hidden="0" customHeight="1">
       <x:c r="A311" s="7" t="n">
-        <x:v>1420</x:v>
+        <x:v>1422</x:v>
       </x:c>
       <x:c r="B311" s="7" t="n">
         <x:v>14</x:v>
       </x:c>
       <x:c r="C311" s="7" t="n">
-        <x:v>19</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="D311" s="7" t="n">
-        <x:v>145</x:v>
+        <x:v>295</x:v>
       </x:c>
       <x:c r="E311" s="7" t="n">
-        <x:v>485</x:v>
+        <x:v>545</x:v>
       </x:c>
     </x:row>
     <x:row r="312" ht="15" hidden="0" customHeight="1">
       <x:c r="A312" s="7" t="n">
-        <x:v>1421</x:v>
+        <x:v>1501</x:v>
       </x:c>
       <x:c r="B312" s="7" t="n">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="C312" s="7" t="n">
-        <x:v>20</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D312" s="7" t="n">
-        <x:v>195</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="E312" s="7" t="n">
-        <x:v>485</x:v>
+        <x:v>210</x:v>
       </x:c>
     </x:row>
     <x:row r="313" ht="15" hidden="0" customHeight="1">
       <x:c r="A313" s="7" t="n">
-        <x:v>1422</x:v>
+        <x:v>1502</x:v>
       </x:c>
       <x:c r="B313" s="7" t="n">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="C313" s="7" t="n">
-        <x:v>21</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="D313" s="7" t="n">
-        <x:v>245</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="E313" s="7" t="n">
-        <x:v>485</x:v>
+        <x:v>210</x:v>
       </x:c>
     </x:row>
     <x:row r="314" ht="15" hidden="0" customHeight="1">
       <x:c r="A314" s="7" t="n">
-        <x:v>1501</x:v>
+        <x:v>1503</x:v>
       </x:c>
       <x:c r="B314" s="7" t="n">
         <x:v>15</x:v>
       </x:c>
       <x:c r="C314" s="7" t="n">
-        <x:v>0</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="D314" s="7" t="n">
-        <x:v>95</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="E314" s="7" t="n">
-        <x:v>185</x:v>
+        <x:v>210</x:v>
       </x:c>
     </x:row>
     <x:row r="315" ht="15" hidden="0" customHeight="1">
       <x:c r="A315" s="7" t="n">
-        <x:v>1502</x:v>
+        <x:v>1504</x:v>
       </x:c>
       <x:c r="B315" s="7" t="n">
         <x:v>15</x:v>
       </x:c>
       <x:c r="C315" s="7" t="n">
-        <x:v>1</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="D315" s="7" t="n">
-        <x:v>145</x:v>
+        <x:v>245</x:v>
       </x:c>
       <x:c r="E315" s="7" t="n">
-        <x:v>185</x:v>
+        <x:v>210</x:v>
       </x:c>
     </x:row>
     <x:row r="316" ht="15" hidden="0" customHeight="1">
       <x:c r="A316" s="7" t="n">
-        <x:v>1503</x:v>
+        <x:v>1505</x:v>
       </x:c>
       <x:c r="B316" s="7" t="n">
         <x:v>15</x:v>
       </x:c>
       <x:c r="C316" s="7" t="n">
-        <x:v>2</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="D316" s="7" t="n">
-        <x:v>195</x:v>
+        <x:v>295</x:v>
       </x:c>
       <x:c r="E316" s="7" t="n">
-        <x:v>185</x:v>
+        <x:v>200</x:v>
       </x:c>
     </x:row>
     <x:row r="317" ht="15" hidden="0" customHeight="1">
       <x:c r="A317" s="7" t="n">
-        <x:v>1504</x:v>
+        <x:v>1506</x:v>
       </x:c>
       <x:c r="B317" s="7" t="n">
         <x:v>15</x:v>
       </x:c>
       <x:c r="C317" s="7" t="n">
-        <x:v>3</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D317" s="7" t="n">
-        <x:v>245</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="E317" s="7" t="n">
-        <x:v>185</x:v>
+        <x:v>320</x:v>
       </x:c>
     </x:row>
     <x:row r="318" ht="15" hidden="0" customHeight="1">
       <x:c r="A318" s="7" t="n">
-        <x:v>1505</x:v>
+        <x:v>1507</x:v>
       </x:c>
       <x:c r="B318" s="7" t="n">
         <x:v>15</x:v>
       </x:c>
       <x:c r="C318" s="7" t="n">
-        <x:v>4</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="D318" s="7" t="n">
-        <x:v>295</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="E318" s="7" t="n">
-        <x:v>185</x:v>
+        <x:v>320</x:v>
       </x:c>
     </x:row>
     <x:row r="319" ht="15" hidden="0" customHeight="1">
       <x:c r="A319" s="7" t="n">
-        <x:v>1506</x:v>
+        <x:v>1508</x:v>
       </x:c>
       <x:c r="B319" s="7" t="n">
         <x:v>15</x:v>
       </x:c>
       <x:c r="C319" s="7" t="n">
-        <x:v>5</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="D319" s="7" t="n">
-        <x:v>95</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="E319" s="7" t="n">
-        <x:v>235</x:v>
+        <x:v>320</x:v>
       </x:c>
     </x:row>
     <x:row r="320" ht="15" hidden="0" customHeight="1">
       <x:c r="A320" s="7" t="n">
-        <x:v>1507</x:v>
+        <x:v>1509</x:v>
       </x:c>
       <x:c r="B320" s="7" t="n">
         <x:v>15</x:v>
       </x:c>
       <x:c r="C320" s="7" t="n">
-        <x:v>6</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="D320" s="7" t="n">
-        <x:v>145</x:v>
+        <x:v>245</x:v>
       </x:c>
       <x:c r="E320" s="7" t="n">
-        <x:v>235</x:v>
+        <x:v>320</x:v>
       </x:c>
     </x:row>
     <x:row r="321" ht="15" hidden="0" customHeight="1">
       <x:c r="A321" s="7" t="n">
-        <x:v>1508</x:v>
+        <x:v>1510</x:v>
       </x:c>
       <x:c r="B321" s="7" t="n">
         <x:v>15</x:v>
       </x:c>
       <x:c r="C321" s="7" t="n">
-        <x:v>7</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="D321" s="7" t="n">
-        <x:v>195</x:v>
+        <x:v>335</x:v>
       </x:c>
       <x:c r="E321" s="7" t="n">
         <x:v>235</x:v>
@@ -5746,118 +5746,118 @@
     </x:row>
     <x:row r="322" ht="15" hidden="0" customHeight="1">
       <x:c r="A322" s="7" t="n">
-        <x:v>1509</x:v>
+        <x:v>1511</x:v>
       </x:c>
       <x:c r="B322" s="7" t="n">
         <x:v>15</x:v>
       </x:c>
       <x:c r="C322" s="7" t="n">
-        <x:v>8</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="D322" s="7" t="n">
-        <x:v>245</x:v>
+        <x:v>345</x:v>
       </x:c>
       <x:c r="E322" s="7" t="n">
-        <x:v>235</x:v>
+        <x:v>285</x:v>
       </x:c>
     </x:row>
     <x:row r="323" ht="15" hidden="0" customHeight="1">
       <x:c r="A323" s="7" t="n">
-        <x:v>1510</x:v>
+        <x:v>1512</x:v>
       </x:c>
       <x:c r="B323" s="7" t="n">
         <x:v>15</x:v>
       </x:c>
       <x:c r="C323" s="7" t="n">
-        <x:v>9</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D323" s="7" t="n">
-        <x:v>295</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="E323" s="7" t="n">
-        <x:v>235</x:v>
+        <x:v>320</x:v>
       </x:c>
     </x:row>
     <x:row r="324" ht="15" hidden="0" customHeight="1">
       <x:c r="A324" s="7" t="n">
-        <x:v>1511</x:v>
+        <x:v>1513</x:v>
       </x:c>
       <x:c r="B324" s="7" t="n">
         <x:v>15</x:v>
       </x:c>
       <x:c r="C324" s="7" t="n">
-        <x:v>10</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="D324" s="7" t="n">
-        <x:v>345</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="E324" s="7" t="n">
-        <x:v>285</x:v>
+        <x:v>370</x:v>
       </x:c>
     </x:row>
     <x:row r="325" ht="15" hidden="0" customHeight="1">
       <x:c r="A325" s="7" t="n">
-        <x:v>1512</x:v>
+        <x:v>1514</x:v>
       </x:c>
       <x:c r="B325" s="7" t="n">
         <x:v>15</x:v>
       </x:c>
       <x:c r="C325" s="7" t="n">
-        <x:v>11</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D325" s="7" t="n">
-        <x:v>45</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="E325" s="7" t="n">
-        <x:v>335</x:v>
+        <x:v>420</x:v>
       </x:c>
     </x:row>
     <x:row r="326" ht="15" hidden="0" customHeight="1">
       <x:c r="A326" s="7" t="n">
-        <x:v>1513</x:v>
+        <x:v>1515</x:v>
       </x:c>
       <x:c r="B326" s="7" t="n">
         <x:v>15</x:v>
       </x:c>
       <x:c r="C326" s="7" t="n">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="D326" s="7" t="n">
-        <x:v>95</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="E326" s="7" t="n">
-        <x:v>335</x:v>
+        <x:v>420</x:v>
       </x:c>
     </x:row>
     <x:row r="327" ht="15" hidden="0" customHeight="1">
       <x:c r="A327" s="7" t="n">
-        <x:v>1514</x:v>
+        <x:v>1516</x:v>
       </x:c>
       <x:c r="B327" s="7" t="n">
         <x:v>15</x:v>
       </x:c>
       <x:c r="C327" s="7" t="n">
-        <x:v>13</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="D327" s="7" t="n">
-        <x:v>145</x:v>
+        <x:v>245</x:v>
       </x:c>
       <x:c r="E327" s="7" t="n">
-        <x:v>335</x:v>
+        <x:v>420</x:v>
       </x:c>
     </x:row>
     <x:row r="328" ht="15" hidden="0" customHeight="1">
       <x:c r="A328" s="7" t="n">
-        <x:v>1515</x:v>
+        <x:v>1517</x:v>
       </x:c>
       <x:c r="B328" s="7" t="n">
         <x:v>15</x:v>
       </x:c>
       <x:c r="C328" s="7" t="n">
-        <x:v>14</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="D328" s="7" t="n">
-        <x:v>195</x:v>
+        <x:v>345</x:v>
       </x:c>
       <x:c r="E328" s="7" t="n">
         <x:v>335</x:v>
@@ -5865,2277 +5865,2277 @@
     </x:row>
     <x:row r="329" ht="15" hidden="0" customHeight="1">
       <x:c r="A329" s="7" t="n">
-        <x:v>1516</x:v>
+        <x:v>1518</x:v>
       </x:c>
       <x:c r="B329" s="7" t="n">
         <x:v>15</x:v>
       </x:c>
       <x:c r="C329" s="7" t="n">
-        <x:v>15</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="D329" s="7" t="n">
-        <x:v>245</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="E329" s="7" t="n">
-        <x:v>335</x:v>
+        <x:v>420</x:v>
       </x:c>
     </x:row>
     <x:row r="330" ht="15" hidden="0" customHeight="1">
       <x:c r="A330" s="7" t="n">
-        <x:v>1517</x:v>
+        <x:v>1519</x:v>
       </x:c>
       <x:c r="B330" s="7" t="n">
         <x:v>15</x:v>
       </x:c>
       <x:c r="C330" s="7" t="n">
-        <x:v>16</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="D330" s="7" t="n">
         <x:v>345</x:v>
       </x:c>
       <x:c r="E330" s="7" t="n">
-        <x:v>335</x:v>
+        <x:v>385</x:v>
       </x:c>
     </x:row>
     <x:row r="331" ht="15" hidden="0" customHeight="1">
       <x:c r="A331" s="7" t="n">
-        <x:v>1518</x:v>
+        <x:v>1520</x:v>
       </x:c>
       <x:c r="B331" s="7" t="n">
         <x:v>15</x:v>
       </x:c>
       <x:c r="C331" s="7" t="n">
-        <x:v>17</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="D331" s="7" t="n">
         <x:v>45</x:v>
       </x:c>
       <x:c r="E331" s="7" t="n">
-        <x:v>385</x:v>
+        <x:v>470</x:v>
       </x:c>
     </x:row>
     <x:row r="332" ht="15" hidden="0" customHeight="1">
       <x:c r="A332" s="7" t="n">
-        <x:v>1519</x:v>
+        <x:v>1521</x:v>
       </x:c>
       <x:c r="B332" s="7" t="n">
         <x:v>15</x:v>
       </x:c>
       <x:c r="C332" s="7" t="n">
-        <x:v>18</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="D332" s="7" t="n">
-        <x:v>345</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="E332" s="7" t="n">
-        <x:v>385</x:v>
+        <x:v>520</x:v>
       </x:c>
     </x:row>
     <x:row r="333" ht="15" hidden="0" customHeight="1">
       <x:c r="A333" s="7" t="n">
-        <x:v>1520</x:v>
+        <x:v>1522</x:v>
       </x:c>
       <x:c r="B333" s="7" t="n">
         <x:v>15</x:v>
       </x:c>
       <x:c r="C333" s="7" t="n">
-        <x:v>19</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="D333" s="7" t="n">
-        <x:v>45</x:v>
+        <x:v>295</x:v>
       </x:c>
       <x:c r="E333" s="7" t="n">
-        <x:v>435</x:v>
+        <x:v>420</x:v>
       </x:c>
     </x:row>
     <x:row r="334" ht="15" hidden="0" customHeight="1">
       <x:c r="A334" s="7" t="n">
-        <x:v>1521</x:v>
+        <x:v>1601</x:v>
       </x:c>
       <x:c r="B334" s="7" t="n">
-        <x:v>15</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C334" s="7" t="n">
-        <x:v>20</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D334" s="7" t="n">
-        <x:v>145</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="E334" s="7" t="n">
-        <x:v>435</x:v>
+        <x:v>150</x:v>
       </x:c>
     </x:row>
     <x:row r="335" ht="15" hidden="0" customHeight="1">
       <x:c r="A335" s="7" t="n">
-        <x:v>1522</x:v>
+        <x:v>1602</x:v>
       </x:c>
       <x:c r="B335" s="7" t="n">
-        <x:v>15</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C335" s="7" t="n">
-        <x:v>21</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="D335" s="7" t="n">
-        <x:v>195</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="E335" s="7" t="n">
-        <x:v>435</x:v>
+        <x:v>200</x:v>
       </x:c>
     </x:row>
     <x:row r="336" ht="15" hidden="0" customHeight="1">
       <x:c r="A336" s="7" t="n">
-        <x:v>1601</x:v>
+        <x:v>1603</x:v>
       </x:c>
       <x:c r="B336" s="7" t="n">
         <x:v>16</x:v>
       </x:c>
       <x:c r="C336" s="7" t="n">
-        <x:v>0</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="D336" s="7" t="n">
         <x:v>195</x:v>
       </x:c>
       <x:c r="E336" s="7" t="n">
-        <x:v>135</x:v>
+        <x:v>200</x:v>
       </x:c>
     </x:row>
     <x:row r="337" ht="15" hidden="0" customHeight="1">
       <x:c r="A337" s="7" t="n">
-        <x:v>1602</x:v>
+        <x:v>1604</x:v>
       </x:c>
       <x:c r="B337" s="7" t="n">
         <x:v>16</x:v>
       </x:c>
       <x:c r="C337" s="7" t="n">
-        <x:v>1</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="D337" s="7" t="n">
-        <x:v>95</x:v>
+        <x:v>245</x:v>
       </x:c>
       <x:c r="E337" s="7" t="n">
-        <x:v>185</x:v>
+        <x:v>200</x:v>
       </x:c>
     </x:row>
     <x:row r="338" ht="15" hidden="0" customHeight="1">
       <x:c r="A338" s="7" t="n">
-        <x:v>1603</x:v>
+        <x:v>1605</x:v>
       </x:c>
       <x:c r="B338" s="7" t="n">
         <x:v>16</x:v>
       </x:c>
       <x:c r="C338" s="7" t="n">
-        <x:v>2</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="D338" s="7" t="n">
-        <x:v>195</x:v>
+        <x:v>295</x:v>
       </x:c>
       <x:c r="E338" s="7" t="n">
-        <x:v>185</x:v>
+        <x:v>200</x:v>
       </x:c>
     </x:row>
     <x:row r="339" ht="15" hidden="0" customHeight="1">
       <x:c r="A339" s="7" t="n">
-        <x:v>1604</x:v>
+        <x:v>1606</x:v>
       </x:c>
       <x:c r="B339" s="7" t="n">
         <x:v>16</x:v>
       </x:c>
       <x:c r="C339" s="7" t="n">
-        <x:v>3</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D339" s="7" t="n">
-        <x:v>245</x:v>
+        <x:v>345</x:v>
       </x:c>
       <x:c r="E339" s="7" t="n">
-        <x:v>185</x:v>
+        <x:v>200</x:v>
       </x:c>
     </x:row>
     <x:row r="340" ht="15" hidden="0" customHeight="1">
       <x:c r="A340" s="7" t="n">
-        <x:v>1605</x:v>
+        <x:v>1607</x:v>
       </x:c>
       <x:c r="B340" s="7" t="n">
         <x:v>16</x:v>
       </x:c>
       <x:c r="C340" s="7" t="n">
-        <x:v>4</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="D340" s="7" t="n">
-        <x:v>295</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="E340" s="7" t="n">
-        <x:v>185</x:v>
+        <x:v>250</x:v>
       </x:c>
     </x:row>
     <x:row r="341" ht="15" hidden="0" customHeight="1">
       <x:c r="A341" s="7" t="n">
-        <x:v>1606</x:v>
+        <x:v>1608</x:v>
       </x:c>
       <x:c r="B341" s="7" t="n">
         <x:v>16</x:v>
       </x:c>
       <x:c r="C341" s="7" t="n">
-        <x:v>5</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="D341" s="7" t="n">
-        <x:v>345</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="E341" s="7" t="n">
-        <x:v>185</x:v>
+        <x:v>300</x:v>
       </x:c>
     </x:row>
     <x:row r="342" ht="15" hidden="0" customHeight="1">
       <x:c r="A342" s="7" t="n">
-        <x:v>1607</x:v>
+        <x:v>1609</x:v>
       </x:c>
       <x:c r="B342" s="7" t="n">
         <x:v>16</x:v>
       </x:c>
       <x:c r="C342" s="7" t="n">
-        <x:v>6</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="D342" s="7" t="n">
-        <x:v>95</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="E342" s="7" t="n">
-        <x:v>235</x:v>
+        <x:v>310</x:v>
       </x:c>
     </x:row>
     <x:row r="343" ht="15" hidden="0" customHeight="1">
       <x:c r="A343" s="7" t="n">
-        <x:v>1608</x:v>
+        <x:v>1610</x:v>
       </x:c>
       <x:c r="B343" s="7" t="n">
         <x:v>16</x:v>
       </x:c>
       <x:c r="C343" s="7" t="n">
-        <x:v>7</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="D343" s="7" t="n">
-        <x:v>145</x:v>
+        <x:v>245</x:v>
       </x:c>
       <x:c r="E343" s="7" t="n">
-        <x:v>285</x:v>
+        <x:v>310</x:v>
       </x:c>
     </x:row>
     <x:row r="344" ht="15" hidden="0" customHeight="1">
       <x:c r="A344" s="7" t="n">
-        <x:v>1609</x:v>
+        <x:v>1611</x:v>
       </x:c>
       <x:c r="B344" s="7" t="n">
         <x:v>16</x:v>
       </x:c>
       <x:c r="C344" s="7" t="n">
-        <x:v>8</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="D344" s="7" t="n">
-        <x:v>195</x:v>
+        <x:v>295</x:v>
       </x:c>
       <x:c r="E344" s="7" t="n">
-        <x:v>285</x:v>
+        <x:v>310</x:v>
       </x:c>
     </x:row>
     <x:row r="345" ht="15" hidden="0" customHeight="1">
       <x:c r="A345" s="7" t="n">
-        <x:v>1610</x:v>
+        <x:v>1612</x:v>
       </x:c>
       <x:c r="B345" s="7" t="n">
         <x:v>16</x:v>
       </x:c>
       <x:c r="C345" s="7" t="n">
-        <x:v>9</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D345" s="7" t="n">
-        <x:v>245</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="E345" s="7" t="n">
-        <x:v>285</x:v>
+        <x:v>320</x:v>
       </x:c>
     </x:row>
     <x:row r="346" ht="15" hidden="0" customHeight="1">
       <x:c r="A346" s="7" t="n">
-        <x:v>1611</x:v>
+        <x:v>1613</x:v>
       </x:c>
       <x:c r="B346" s="7" t="n">
         <x:v>16</x:v>
       </x:c>
       <x:c r="C346" s="7" t="n">
-        <x:v>10</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="D346" s="7" t="n">
-        <x:v>295</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="E346" s="7" t="n">
-        <x:v>285</x:v>
+        <x:v>320</x:v>
       </x:c>
     </x:row>
     <x:row r="347" ht="15" hidden="0" customHeight="1">
       <x:c r="A347" s="7" t="n">
-        <x:v>1612</x:v>
+        <x:v>1614</x:v>
       </x:c>
       <x:c r="B347" s="7" t="n">
         <x:v>16</x:v>
       </x:c>
       <x:c r="C347" s="7" t="n">
-        <x:v>11</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D347" s="7" t="n">
-        <x:v>45</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="E347" s="7" t="n">
-        <x:v>335</x:v>
+        <x:v>420</x:v>
       </x:c>
     </x:row>
     <x:row r="348" ht="15" hidden="0" customHeight="1">
       <x:c r="A348" s="7" t="n">
-        <x:v>1613</x:v>
+        <x:v>1615</x:v>
       </x:c>
       <x:c r="B348" s="7" t="n">
         <x:v>16</x:v>
       </x:c>
       <x:c r="C348" s="7" t="n">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="D348" s="7" t="n">
-        <x:v>95</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="E348" s="7" t="n">
-        <x:v>335</x:v>
+        <x:v>420</x:v>
       </x:c>
     </x:row>
     <x:row r="349" ht="15" hidden="0" customHeight="1">
       <x:c r="A349" s="7" t="n">
-        <x:v>1614</x:v>
+        <x:v>1616</x:v>
       </x:c>
       <x:c r="B349" s="7" t="n">
         <x:v>16</x:v>
       </x:c>
       <x:c r="C349" s="7" t="n">
-        <x:v>13</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="D349" s="7" t="n">
-        <x:v>145</x:v>
+        <x:v>245</x:v>
       </x:c>
       <x:c r="E349" s="7" t="n">
-        <x:v>335</x:v>
+        <x:v>420</x:v>
       </x:c>
     </x:row>
     <x:row r="350" ht="15" hidden="0" customHeight="1">
       <x:c r="A350" s="7" t="n">
-        <x:v>1615</x:v>
+        <x:v>1617</x:v>
       </x:c>
       <x:c r="B350" s="7" t="n">
         <x:v>16</x:v>
       </x:c>
       <x:c r="C350" s="7" t="n">
-        <x:v>14</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="D350" s="7" t="n">
-        <x:v>195</x:v>
+        <x:v>295</x:v>
       </x:c>
       <x:c r="E350" s="7" t="n">
-        <x:v>335</x:v>
+        <x:v>420</x:v>
       </x:c>
     </x:row>
     <x:row r="351" ht="15" hidden="0" customHeight="1">
       <x:c r="A351" s="7" t="n">
-        <x:v>1616</x:v>
+        <x:v>1618</x:v>
       </x:c>
       <x:c r="B351" s="7" t="n">
         <x:v>16</x:v>
       </x:c>
       <x:c r="C351" s="7" t="n">
-        <x:v>15</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="D351" s="7" t="n">
-        <x:v>245</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="E351" s="7" t="n">
-        <x:v>335</x:v>
+        <x:v>420</x:v>
       </x:c>
     </x:row>
     <x:row r="352" ht="15" hidden="0" customHeight="1">
       <x:c r="A352" s="7" t="n">
-        <x:v>1617</x:v>
+        <x:v>1619</x:v>
       </x:c>
       <x:c r="B352" s="7" t="n">
         <x:v>16</x:v>
       </x:c>
       <x:c r="C352" s="7" t="n">
-        <x:v>16</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="D352" s="7" t="n">
-        <x:v>295</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="E352" s="7" t="n">
-        <x:v>335</x:v>
+        <x:v>520</x:v>
       </x:c>
     </x:row>
     <x:row r="353" ht="15" hidden="0" customHeight="1">
       <x:c r="A353" s="7" t="n">
-        <x:v>1618</x:v>
+        <x:v>1620</x:v>
       </x:c>
       <x:c r="B353" s="7" t="n">
         <x:v>16</x:v>
       </x:c>
       <x:c r="C353" s="7" t="n">
-        <x:v>17</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="D353" s="7" t="n">
-        <x:v>95</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="E353" s="7" t="n">
-        <x:v>435</x:v>
+        <x:v>520</x:v>
       </x:c>
     </x:row>
     <x:row r="354" ht="15" hidden="0" customHeight="1">
       <x:c r="A354" s="7" t="n">
-        <x:v>1619</x:v>
+        <x:v>1621</x:v>
       </x:c>
       <x:c r="B354" s="7" t="n">
         <x:v>16</x:v>
       </x:c>
       <x:c r="C354" s="7" t="n">
-        <x:v>18</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="D354" s="7" t="n">
-        <x:v>145</x:v>
+        <x:v>245</x:v>
       </x:c>
       <x:c r="E354" s="7" t="n">
-        <x:v>435</x:v>
+        <x:v>520</x:v>
       </x:c>
     </x:row>
     <x:row r="355" ht="15" hidden="0" customHeight="1">
       <x:c r="A355" s="7" t="n">
-        <x:v>1620</x:v>
+        <x:v>1622</x:v>
       </x:c>
       <x:c r="B355" s="7" t="n">
         <x:v>16</x:v>
       </x:c>
       <x:c r="C355" s="7" t="n">
-        <x:v>19</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="D355" s="7" t="n">
-        <x:v>195</x:v>
+        <x:v>295</x:v>
       </x:c>
       <x:c r="E355" s="7" t="n">
-        <x:v>435</x:v>
+        <x:v>520</x:v>
       </x:c>
     </x:row>
     <x:row r="356" ht="15" hidden="0" customHeight="1">
       <x:c r="A356" s="7" t="n">
-        <x:v>1621</x:v>
+        <x:v>1701</x:v>
       </x:c>
       <x:c r="B356" s="7" t="n">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C356" s="7" t="n">
-        <x:v>20</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D356" s="7" t="n">
         <x:v>245</x:v>
       </x:c>
       <x:c r="E356" s="7" t="n">
-        <x:v>435</x:v>
+        <x:v>150</x:v>
       </x:c>
     </x:row>
     <x:row r="357" ht="15" hidden="0" customHeight="1">
       <x:c r="A357" s="7" t="n">
-        <x:v>1622</x:v>
+        <x:v>1702</x:v>
       </x:c>
       <x:c r="B357" s="7" t="n">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C357" s="7" t="n">
-        <x:v>21</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="D357" s="7" t="n">
         <x:v>295</x:v>
       </x:c>
       <x:c r="E357" s="7" t="n">
-        <x:v>435</x:v>
+        <x:v>150</x:v>
       </x:c>
     </x:row>
     <x:row r="358" ht="15" hidden="0" customHeight="1">
       <x:c r="A358" s="7" t="n">
-        <x:v>1701</x:v>
+        <x:v>1703</x:v>
       </x:c>
       <x:c r="B358" s="7" t="n">
         <x:v>17</x:v>
       </x:c>
       <x:c r="C358" s="7" t="n">
-        <x:v>0</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="D358" s="7" t="n">
-        <x:v>245</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="E358" s="7" t="n">
-        <x:v>135</x:v>
+        <x:v>200</x:v>
       </x:c>
     </x:row>
     <x:row r="359" ht="15" hidden="0" customHeight="1">
       <x:c r="A359" s="7" t="n">
-        <x:v>1702</x:v>
+        <x:v>1704</x:v>
       </x:c>
       <x:c r="B359" s="7" t="n">
         <x:v>17</x:v>
       </x:c>
       <x:c r="C359" s="7" t="n">
-        <x:v>1</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="D359" s="7" t="n">
-        <x:v>295</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="E359" s="7" t="n">
-        <x:v>135</x:v>
+        <x:v>250</x:v>
       </x:c>
     </x:row>
     <x:row r="360" ht="15" hidden="0" customHeight="1">
       <x:c r="A360" s="7" t="n">
-        <x:v>1703</x:v>
+        <x:v>1705</x:v>
       </x:c>
       <x:c r="B360" s="7" t="n">
         <x:v>17</x:v>
       </x:c>
       <x:c r="C360" s="7" t="n">
-        <x:v>2</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="D360" s="7" t="n">
-        <x:v>195</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="E360" s="7" t="n">
-        <x:v>185</x:v>
+        <x:v>250</x:v>
       </x:c>
     </x:row>
     <x:row r="361" ht="15" hidden="0" customHeight="1">
       <x:c r="A361" s="7" t="n">
-        <x:v>1704</x:v>
+        <x:v>1706</x:v>
       </x:c>
       <x:c r="B361" s="7" t="n">
         <x:v>17</x:v>
       </x:c>
       <x:c r="C361" s="7" t="n">
-        <x:v>3</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D361" s="7" t="n">
-        <x:v>45</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="E361" s="7" t="n">
-        <x:v>235</x:v>
+        <x:v>250</x:v>
       </x:c>
     </x:row>
     <x:row r="362" ht="15" hidden="0" customHeight="1">
       <x:c r="A362" s="7" t="n">
-        <x:v>1705</x:v>
+        <x:v>1707</x:v>
       </x:c>
       <x:c r="B362" s="7" t="n">
         <x:v>17</x:v>
       </x:c>
       <x:c r="C362" s="7" t="n">
-        <x:v>4</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="D362" s="7" t="n">
-        <x:v>95</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="E362" s="7" t="n">
-        <x:v>235</x:v>
+        <x:v>250</x:v>
       </x:c>
     </x:row>
     <x:row r="363" ht="15" hidden="0" customHeight="1">
       <x:c r="A363" s="7" t="n">
-        <x:v>1706</x:v>
+        <x:v>1708</x:v>
       </x:c>
       <x:c r="B363" s="7" t="n">
         <x:v>17</x:v>
       </x:c>
       <x:c r="C363" s="7" t="n">
-        <x:v>5</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="D363" s="7" t="n">
-        <x:v>145</x:v>
+        <x:v>295</x:v>
       </x:c>
       <x:c r="E363" s="7" t="n">
-        <x:v>235</x:v>
+        <x:v>250</x:v>
       </x:c>
     </x:row>
     <x:row r="364" ht="15" hidden="0" customHeight="1">
       <x:c r="A364" s="7" t="n">
-        <x:v>1707</x:v>
+        <x:v>1709</x:v>
       </x:c>
       <x:c r="B364" s="7" t="n">
         <x:v>17</x:v>
       </x:c>
       <x:c r="C364" s="7" t="n">
-        <x:v>6</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="D364" s="7" t="n">
-        <x:v>195</x:v>
+        <x:v>295</x:v>
       </x:c>
       <x:c r="E364" s="7" t="n">
-        <x:v>235</x:v>
+        <x:v>300</x:v>
       </x:c>
     </x:row>
     <x:row r="365" ht="15" hidden="0" customHeight="1">
       <x:c r="A365" s="7" t="n">
-        <x:v>1708</x:v>
+        <x:v>1710</x:v>
       </x:c>
       <x:c r="B365" s="7" t="n">
         <x:v>17</x:v>
       </x:c>
       <x:c r="C365" s="7" t="n">
-        <x:v>7</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="D365" s="7" t="n">
-        <x:v>295</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="E365" s="7" t="n">
-        <x:v>235</x:v>
+        <x:v>360</x:v>
       </x:c>
     </x:row>
     <x:row r="366" ht="15" hidden="0" customHeight="1">
       <x:c r="A366" s="7" t="n">
-        <x:v>1709</x:v>
+        <x:v>1711</x:v>
       </x:c>
       <x:c r="B366" s="7" t="n">
         <x:v>17</x:v>
       </x:c>
       <x:c r="C366" s="7" t="n">
-        <x:v>8</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="D366" s="7" t="n">
-        <x:v>295</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="E366" s="7" t="n">
-        <x:v>285</x:v>
+        <x:v>360</x:v>
       </x:c>
     </x:row>
     <x:row r="367" ht="15" hidden="0" customHeight="1">
       <x:c r="A367" s="7" t="n">
-        <x:v>1710</x:v>
+        <x:v>1712</x:v>
       </x:c>
       <x:c r="B367" s="7" t="n">
         <x:v>17</x:v>
       </x:c>
       <x:c r="C367" s="7" t="n">
-        <x:v>9</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D367" s="7" t="n">
-        <x:v>95</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="E367" s="7" t="n">
-        <x:v>335</x:v>
+        <x:v>360</x:v>
       </x:c>
     </x:row>
     <x:row r="368" ht="15" hidden="0" customHeight="1">
       <x:c r="A368" s="7" t="n">
-        <x:v>1711</x:v>
+        <x:v>1713</x:v>
       </x:c>
       <x:c r="B368" s="7" t="n">
         <x:v>17</x:v>
       </x:c>
       <x:c r="C368" s="7" t="n">
-        <x:v>10</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="D368" s="7" t="n">
-        <x:v>145</x:v>
+        <x:v>245</x:v>
       </x:c>
       <x:c r="E368" s="7" t="n">
-        <x:v>335</x:v>
+        <x:v>350</x:v>
       </x:c>
     </x:row>
     <x:row r="369" ht="15" hidden="0" customHeight="1">
       <x:c r="A369" s="7" t="n">
-        <x:v>1712</x:v>
+        <x:v>1714</x:v>
       </x:c>
       <x:c r="B369" s="7" t="n">
         <x:v>17</x:v>
       </x:c>
       <x:c r="C369" s="7" t="n">
-        <x:v>11</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D369" s="7" t="n">
-        <x:v>195</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="E369" s="7" t="n">
-        <x:v>335</x:v>
+        <x:v>470</x:v>
       </x:c>
     </x:row>
     <x:row r="370" ht="15" hidden="0" customHeight="1">
       <x:c r="A370" s="7" t="n">
-        <x:v>1713</x:v>
+        <x:v>1715</x:v>
       </x:c>
       <x:c r="B370" s="7" t="n">
         <x:v>17</x:v>
       </x:c>
       <x:c r="C370" s="7" t="n">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="D370" s="7" t="n">
-        <x:v>245</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="E370" s="7" t="n">
-        <x:v>335</x:v>
+        <x:v>470</x:v>
       </x:c>
     </x:row>
     <x:row r="371" ht="15" hidden="0" customHeight="1">
       <x:c r="A371" s="7" t="n">
-        <x:v>1714</x:v>
+        <x:v>1716</x:v>
       </x:c>
       <x:c r="B371" s="7" t="n">
         <x:v>17</x:v>
       </x:c>
       <x:c r="C371" s="7" t="n">
-        <x:v>13</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="D371" s="7" t="n">
-        <x:v>95</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="E371" s="7" t="n">
-        <x:v>385</x:v>
+        <x:v>470</x:v>
       </x:c>
     </x:row>
     <x:row r="372" ht="15" hidden="0" customHeight="1">
       <x:c r="A372" s="7" t="n">
-        <x:v>1715</x:v>
+        <x:v>1717</x:v>
       </x:c>
       <x:c r="B372" s="7" t="n">
         <x:v>17</x:v>
       </x:c>
       <x:c r="C372" s="7" t="n">
-        <x:v>14</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="D372" s="7" t="n">
-        <x:v>145</x:v>
+        <x:v>295</x:v>
       </x:c>
       <x:c r="E372" s="7" t="n">
-        <x:v>385</x:v>
+        <x:v>370</x:v>
       </x:c>
     </x:row>
     <x:row r="373" ht="15" hidden="0" customHeight="1">
       <x:c r="A373" s="7" t="n">
-        <x:v>1716</x:v>
+        <x:v>1718</x:v>
       </x:c>
       <x:c r="B373" s="7" t="n">
         <x:v>17</x:v>
       </x:c>
       <x:c r="C373" s="7" t="n">
-        <x:v>15</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="D373" s="7" t="n">
-        <x:v>195</x:v>
+        <x:v>345</x:v>
       </x:c>
       <x:c r="E373" s="7" t="n">
-        <x:v>385</x:v>
+        <x:v>370</x:v>
       </x:c>
     </x:row>
     <x:row r="374" ht="15" hidden="0" customHeight="1">
       <x:c r="A374" s="7" t="n">
-        <x:v>1717</x:v>
+        <x:v>1719</x:v>
       </x:c>
       <x:c r="B374" s="7" t="n">
         <x:v>17</x:v>
       </x:c>
       <x:c r="C374" s="7" t="n">
-        <x:v>16</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="D374" s="7" t="n">
-        <x:v>245</x:v>
+        <x:v>295</x:v>
       </x:c>
       <x:c r="E374" s="7" t="n">
-        <x:v>385</x:v>
+        <x:v>470</x:v>
       </x:c>
     </x:row>
     <x:row r="375" ht="15" hidden="0" customHeight="1">
       <x:c r="A375" s="7" t="n">
-        <x:v>1718</x:v>
+        <x:v>1720</x:v>
       </x:c>
       <x:c r="B375" s="7" t="n">
         <x:v>17</x:v>
       </x:c>
       <x:c r="C375" s="7" t="n">
-        <x:v>17</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="D375" s="7" t="n">
-        <x:v>295</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="E375" s="7" t="n">
-        <x:v>385</x:v>
+        <x:v>575</x:v>
       </x:c>
     </x:row>
     <x:row r="376" ht="15" hidden="0" customHeight="1">
       <x:c r="A376" s="7" t="n">
-        <x:v>1719</x:v>
+        <x:v>1721</x:v>
       </x:c>
       <x:c r="B376" s="7" t="n">
         <x:v>17</x:v>
       </x:c>
       <x:c r="C376" s="7" t="n">
-        <x:v>18</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="D376" s="7" t="n">
-        <x:v>345</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="E376" s="7" t="n">
-        <x:v>385</x:v>
+        <x:v>575</x:v>
       </x:c>
     </x:row>
     <x:row r="377" ht="15" hidden="0" customHeight="1">
       <x:c r="A377" s="7" t="n">
-        <x:v>1720</x:v>
+        <x:v>1722</x:v>
       </x:c>
       <x:c r="B377" s="7" t="n">
         <x:v>17</x:v>
       </x:c>
       <x:c r="C377" s="7" t="n">
-        <x:v>19</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="D377" s="7" t="n">
-        <x:v>45</x:v>
+        <x:v>245</x:v>
       </x:c>
       <x:c r="E377" s="7" t="n">
-        <x:v>485</x:v>
+        <x:v>470</x:v>
       </x:c>
     </x:row>
     <x:row r="378" ht="15" hidden="0" customHeight="1">
       <x:c r="A378" s="7" t="n">
-        <x:v>1721</x:v>
+        <x:v>1801</x:v>
       </x:c>
       <x:c r="B378" s="7" t="n">
-        <x:v>17</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C378" s="7" t="n">
-        <x:v>20</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D378" s="7" t="n">
-        <x:v>95</x:v>
+        <x:v>160</x:v>
       </x:c>
       <x:c r="E378" s="7" t="n">
-        <x:v>485</x:v>
+        <x:v>155</x:v>
       </x:c>
     </x:row>
     <x:row r="379" ht="15" hidden="0" customHeight="1">
       <x:c r="A379" s="7" t="n">
-        <x:v>1722</x:v>
+        <x:v>1802</x:v>
       </x:c>
       <x:c r="B379" s="7" t="n">
-        <x:v>17</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C379" s="7" t="n">
-        <x:v>21</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="D379" s="7" t="n">
-        <x:v>145</x:v>
+        <x:v>245</x:v>
       </x:c>
       <x:c r="E379" s="7" t="n">
-        <x:v>485</x:v>
+        <x:v>165</x:v>
       </x:c>
     </x:row>
     <x:row r="380" ht="15" hidden="0" customHeight="1">
       <x:c r="A380" s="7" t="n">
-        <x:v>1801</x:v>
+        <x:v>1803</x:v>
       </x:c>
       <x:c r="B380" s="7" t="n">
         <x:v>18</x:v>
       </x:c>
       <x:c r="C380" s="7" t="n">
-        <x:v>0</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="D380" s="7" t="n">
-        <x:v>145</x:v>
+        <x:v>345</x:v>
       </x:c>
       <x:c r="E380" s="7" t="n">
-        <x:v>135</x:v>
+        <x:v>165</x:v>
       </x:c>
     </x:row>
     <x:row r="381" ht="15" hidden="0" customHeight="1">
       <x:c r="A381" s="7" t="n">
-        <x:v>1802</x:v>
+        <x:v>1804</x:v>
       </x:c>
       <x:c r="B381" s="7" t="n">
         <x:v>18</x:v>
       </x:c>
       <x:c r="C381" s="7" t="n">
-        <x:v>1</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="D381" s="7" t="n">
-        <x:v>245</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="E381" s="7" t="n">
-        <x:v>135</x:v>
+        <x:v>225</x:v>
       </x:c>
     </x:row>
     <x:row r="382" ht="15" hidden="0" customHeight="1">
       <x:c r="A382" s="7" t="n">
-        <x:v>1803</x:v>
+        <x:v>1805</x:v>
       </x:c>
       <x:c r="B382" s="7" t="n">
         <x:v>18</x:v>
       </x:c>
       <x:c r="C382" s="7" t="n">
-        <x:v>2</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="D382" s="7" t="n">
-        <x:v>295</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="E382" s="7" t="n">
-        <x:v>135</x:v>
+        <x:v>325</x:v>
       </x:c>
     </x:row>
     <x:row r="383" ht="15" hidden="0" customHeight="1">
       <x:c r="A383" s="7" t="n">
-        <x:v>1804</x:v>
+        <x:v>1806</x:v>
       </x:c>
       <x:c r="B383" s="7" t="n">
         <x:v>18</x:v>
       </x:c>
       <x:c r="C383" s="7" t="n">
-        <x:v>3</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D383" s="7" t="n">
-        <x:v>345</x:v>
+        <x:v>280</x:v>
       </x:c>
       <x:c r="E383" s="7" t="n">
-        <x:v>135</x:v>
+        <x:v>265</x:v>
       </x:c>
     </x:row>
     <x:row r="384" ht="15" hidden="0" customHeight="1">
       <x:c r="A384" s="7" t="n">
-        <x:v>1805</x:v>
+        <x:v>1807</x:v>
       </x:c>
       <x:c r="B384" s="7" t="n">
         <x:v>18</x:v>
       </x:c>
       <x:c r="C384" s="7" t="n">
-        <x:v>4</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="D384" s="7" t="n">
         <x:v>45</x:v>
       </x:c>
       <x:c r="E384" s="7" t="n">
-        <x:v>185</x:v>
+        <x:v>275</x:v>
       </x:c>
     </x:row>
     <x:row r="385" ht="15" hidden="0" customHeight="1">
       <x:c r="A385" s="7" t="n">
-        <x:v>1806</x:v>
+        <x:v>1808</x:v>
       </x:c>
       <x:c r="B385" s="7" t="n">
         <x:v>18</x:v>
       </x:c>
       <x:c r="C385" s="7" t="n">
-        <x:v>5</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="D385" s="7" t="n">
-        <x:v>145</x:v>
+        <x:v>165</x:v>
       </x:c>
       <x:c r="E385" s="7" t="n">
-        <x:v>185</x:v>
+        <x:v>215</x:v>
       </x:c>
     </x:row>
     <x:row r="386" ht="15" hidden="0" customHeight="1">
       <x:c r="A386" s="7" t="n">
-        <x:v>1807</x:v>
+        <x:v>1809</x:v>
       </x:c>
       <x:c r="B386" s="7" t="n">
         <x:v>18</x:v>
       </x:c>
       <x:c r="C386" s="7" t="n">
-        <x:v>6</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="D386" s="7" t="n">
-        <x:v>195</x:v>
+        <x:v>170</x:v>
       </x:c>
       <x:c r="E386" s="7" t="n">
-        <x:v>185</x:v>
+        <x:v>265</x:v>
       </x:c>
     </x:row>
     <x:row r="387" ht="15" hidden="0" customHeight="1">
       <x:c r="A387" s="7" t="n">
-        <x:v>1808</x:v>
+        <x:v>1810</x:v>
       </x:c>
       <x:c r="B387" s="7" t="n">
         <x:v>18</x:v>
       </x:c>
       <x:c r="C387" s="7" t="n">
-        <x:v>7</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="D387" s="7" t="n">
-        <x:v>45</x:v>
+        <x:v>295</x:v>
       </x:c>
       <x:c r="E387" s="7" t="n">
-        <x:v>235</x:v>
+        <x:v>165</x:v>
       </x:c>
     </x:row>
     <x:row r="388" ht="15" hidden="0" customHeight="1">
       <x:c r="A388" s="7" t="n">
-        <x:v>1809</x:v>
+        <x:v>1811</x:v>
       </x:c>
       <x:c r="B388" s="7" t="n">
         <x:v>18</x:v>
       </x:c>
       <x:c r="C388" s="7" t="n">
-        <x:v>8</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="D388" s="7" t="n">
-        <x:v>145</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="E388" s="7" t="n">
-        <x:v>235</x:v>
+        <x:v>425</x:v>
       </x:c>
     </x:row>
     <x:row r="389" ht="15" hidden="0" customHeight="1">
       <x:c r="A389" s="7" t="n">
-        <x:v>1810</x:v>
+        <x:v>1812</x:v>
       </x:c>
       <x:c r="B389" s="7" t="n">
         <x:v>18</x:v>
       </x:c>
       <x:c r="C389" s="7" t="n">
-        <x:v>9</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D389" s="7" t="n">
-        <x:v>195</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="E389" s="7" t="n">
-        <x:v>235</x:v>
+        <x:v>405</x:v>
       </x:c>
     </x:row>
     <x:row r="390" ht="15" hidden="0" customHeight="1">
       <x:c r="A390" s="7" t="n">
-        <x:v>1811</x:v>
+        <x:v>1813</x:v>
       </x:c>
       <x:c r="B390" s="7" t="n">
         <x:v>18</x:v>
       </x:c>
       <x:c r="C390" s="7" t="n">
-        <x:v>10</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="D390" s="7" t="n">
-        <x:v>295</x:v>
+        <x:v>245</x:v>
       </x:c>
       <x:c r="E390" s="7" t="n">
-        <x:v>235</x:v>
+        <x:v>405</x:v>
       </x:c>
     </x:row>
     <x:row r="391" ht="15" hidden="0" customHeight="1">
       <x:c r="A391" s="7" t="n">
-        <x:v>1812</x:v>
+        <x:v>1814</x:v>
       </x:c>
       <x:c r="B391" s="7" t="n">
         <x:v>18</x:v>
       </x:c>
       <x:c r="C391" s="7" t="n">
-        <x:v>11</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D391" s="7" t="n">
-        <x:v>45</x:v>
+        <x:v>280</x:v>
       </x:c>
       <x:c r="E391" s="7" t="n">
-        <x:v>285</x:v>
+        <x:v>315</x:v>
       </x:c>
     </x:row>
     <x:row r="392" ht="15" hidden="0" customHeight="1">
       <x:c r="A392" s="7" t="n">
-        <x:v>1813</x:v>
+        <x:v>1815</x:v>
       </x:c>
       <x:c r="B392" s="7" t="n">
         <x:v>18</x:v>
       </x:c>
       <x:c r="C392" s="7" t="n">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="D392" s="7" t="n">
-        <x:v>145</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="E392" s="7" t="n">
-        <x:v>285</x:v>
+        <x:v>375</x:v>
       </x:c>
     </x:row>
     <x:row r="393" ht="15" hidden="0" customHeight="1">
       <x:c r="A393" s="7" t="n">
-        <x:v>1814</x:v>
+        <x:v>1816</x:v>
       </x:c>
       <x:c r="B393" s="7" t="n">
         <x:v>18</x:v>
       </x:c>
       <x:c r="C393" s="7" t="n">
-        <x:v>13</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="D393" s="7" t="n">
-        <x:v>195</x:v>
+        <x:v>280</x:v>
       </x:c>
       <x:c r="E393" s="7" t="n">
-        <x:v>285</x:v>
+        <x:v>365</x:v>
       </x:c>
     </x:row>
     <x:row r="394" ht="15" hidden="0" customHeight="1">
       <x:c r="A394" s="7" t="n">
-        <x:v>1815</x:v>
+        <x:v>1817</x:v>
       </x:c>
       <x:c r="B394" s="7" t="n">
         <x:v>18</x:v>
       </x:c>
       <x:c r="C394" s="7" t="n">
-        <x:v>14</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="D394" s="7" t="n">
-        <x:v>295</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="E394" s="7" t="n">
-        <x:v>285</x:v>
+        <x:v>555</x:v>
       </x:c>
     </x:row>
     <x:row r="395" ht="15" hidden="0" customHeight="1">
       <x:c r="A395" s="7" t="n">
-        <x:v>1816</x:v>
+        <x:v>1818</x:v>
       </x:c>
       <x:c r="B395" s="7" t="n">
         <x:v>18</x:v>
       </x:c>
       <x:c r="C395" s="7" t="n">
-        <x:v>15</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="D395" s="7" t="n">
-        <x:v>45</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="E395" s="7" t="n">
-        <x:v>335</x:v>
+        <x:v>395</x:v>
       </x:c>
     </x:row>
     <x:row r="396" ht="15" hidden="0" customHeight="1">
       <x:c r="A396" s="7" t="n">
-        <x:v>1817</x:v>
+        <x:v>1819</x:v>
       </x:c>
       <x:c r="B396" s="7" t="n">
         <x:v>18</x:v>
       </x:c>
       <x:c r="C396" s="7" t="n">
-        <x:v>16</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="D396" s="7" t="n">
-        <x:v>295</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="E396" s="7" t="n">
-        <x:v>335</x:v>
+        <x:v>395</x:v>
       </x:c>
     </x:row>
     <x:row r="397" ht="15" hidden="0" customHeight="1">
       <x:c r="A397" s="7" t="n">
-        <x:v>1818</x:v>
+        <x:v>1820</x:v>
       </x:c>
       <x:c r="B397" s="7" t="n">
         <x:v>18</x:v>
       </x:c>
       <x:c r="C397" s="7" t="n">
-        <x:v>17</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="D397" s="7" t="n">
-        <x:v>95</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="E397" s="7" t="n">
-        <x:v>410</x:v>
+        <x:v>505</x:v>
       </x:c>
     </x:row>
     <x:row r="398" ht="15" hidden="0" customHeight="1">
       <x:c r="A398" s="7" t="n">
-        <x:v>1819</x:v>
+        <x:v>1901</x:v>
       </x:c>
       <x:c r="B398" s="7" t="n">
-        <x:v>18</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C398" s="7" t="n">
-        <x:v>18</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D398" s="7" t="n">
-        <x:v>145</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="E398" s="7" t="n">
-        <x:v>410</x:v>
+        <x:v>200</x:v>
       </x:c>
     </x:row>
     <x:row r="399" ht="15" hidden="0" customHeight="1">
       <x:c r="A399" s="7" t="n">
-        <x:v>1820</x:v>
+        <x:v>1902</x:v>
       </x:c>
       <x:c r="B399" s="7" t="n">
-        <x:v>18</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C399" s="7" t="n">
-        <x:v>19</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="D399" s="7" t="n">
-        <x:v>195</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="E399" s="7" t="n">
-        <x:v>410</x:v>
+        <x:v>200</x:v>
       </x:c>
     </x:row>
     <x:row r="400" ht="15" hidden="0" customHeight="1">
       <x:c r="A400" s="7" t="n">
-        <x:v>1821</x:v>
+        <x:v>1903</x:v>
       </x:c>
       <x:c r="B400" s="7" t="n">
-        <x:v>18</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C400" s="7" t="n">
-        <x:v>20</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="D400" s="7" t="n">
-        <x:v>45</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="E400" s="7" t="n">
-        <x:v>485</x:v>
+        <x:v>200</x:v>
       </x:c>
     </x:row>
     <x:row r="401" ht="15" hidden="0" customHeight="1">
       <x:c r="A401" s="7" t="n">
-        <x:v>1822</x:v>
+        <x:v>1904</x:v>
       </x:c>
       <x:c r="B401" s="7" t="n">
-        <x:v>18</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C401" s="7" t="n">
-        <x:v>21</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="D401" s="7" t="n">
-        <x:v>45</x:v>
+        <x:v>245</x:v>
       </x:c>
       <x:c r="E401" s="7" t="n">
-        <x:v>535</x:v>
+        <x:v>200</x:v>
       </x:c>
     </x:row>
     <x:row r="402" ht="15" hidden="0" customHeight="1">
       <x:c r="A402" s="7" t="n">
-        <x:v>1901</x:v>
+        <x:v>1905</x:v>
       </x:c>
       <x:c r="B402" s="7" t="n">
         <x:v>19</x:v>
       </x:c>
       <x:c r="C402" s="7" t="n">
-        <x:v>0</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="D402" s="7" t="n">
-        <x:v>95</x:v>
+        <x:v>295</x:v>
       </x:c>
       <x:c r="E402" s="7" t="n">
-        <x:v>185</x:v>
+        <x:v>200</x:v>
       </x:c>
     </x:row>
     <x:row r="403" ht="15" hidden="0" customHeight="1">
       <x:c r="A403" s="7" t="n">
-        <x:v>1902</x:v>
+        <x:v>1906</x:v>
       </x:c>
       <x:c r="B403" s="7" t="n">
         <x:v>19</x:v>
       </x:c>
       <x:c r="C403" s="7" t="n">
-        <x:v>1</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D403" s="7" t="n">
-        <x:v>145</x:v>
+        <x:v>295</x:v>
       </x:c>
       <x:c r="E403" s="7" t="n">
-        <x:v>185</x:v>
+        <x:v>250</x:v>
       </x:c>
     </x:row>
     <x:row r="404" ht="15" hidden="0" customHeight="1">
       <x:c r="A404" s="7" t="n">
-        <x:v>1903</x:v>
+        <x:v>1907</x:v>
       </x:c>
       <x:c r="B404" s="7" t="n">
         <x:v>19</x:v>
       </x:c>
       <x:c r="C404" s="7" t="n">
-        <x:v>2</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="D404" s="7" t="n">
-        <x:v>195</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="E404" s="7" t="n">
-        <x:v>185</x:v>
+        <x:v>300</x:v>
       </x:c>
     </x:row>
     <x:row r="405" ht="15" hidden="0" customHeight="1">
       <x:c r="A405" s="7" t="n">
-        <x:v>1904</x:v>
+        <x:v>1908</x:v>
       </x:c>
       <x:c r="B405" s="7" t="n">
         <x:v>19</x:v>
       </x:c>
       <x:c r="C405" s="7" t="n">
-        <x:v>3</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="D405" s="7" t="n">
-        <x:v>245</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="E405" s="7" t="n">
-        <x:v>185</x:v>
+        <x:v>300</x:v>
       </x:c>
     </x:row>
     <x:row r="406" ht="15" hidden="0" customHeight="1">
       <x:c r="A406" s="7" t="n">
-        <x:v>1905</x:v>
+        <x:v>1909</x:v>
       </x:c>
       <x:c r="B406" s="7" t="n">
         <x:v>19</x:v>
       </x:c>
       <x:c r="C406" s="7" t="n">
-        <x:v>4</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="D406" s="7" t="n">
-        <x:v>295</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="E406" s="7" t="n">
-        <x:v>185</x:v>
+        <x:v>310</x:v>
       </x:c>
     </x:row>
     <x:row r="407" ht="15" hidden="0" customHeight="1">
       <x:c r="A407" s="7" t="n">
-        <x:v>1906</x:v>
+        <x:v>1910</x:v>
       </x:c>
       <x:c r="B407" s="7" t="n">
         <x:v>19</x:v>
       </x:c>
       <x:c r="C407" s="7" t="n">
-        <x:v>5</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="D407" s="7" t="n">
-        <x:v>295</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="E407" s="7" t="n">
-        <x:v>235</x:v>
+        <x:v>310</x:v>
       </x:c>
     </x:row>
     <x:row r="408" ht="15" hidden="0" customHeight="1">
       <x:c r="A408" s="7" t="n">
-        <x:v>1907</x:v>
+        <x:v>1911</x:v>
       </x:c>
       <x:c r="B408" s="7" t="n">
         <x:v>19</x:v>
       </x:c>
       <x:c r="C408" s="7" t="n">
-        <x:v>6</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="D408" s="7" t="n">
-        <x:v>45</x:v>
+        <x:v>295</x:v>
       </x:c>
       <x:c r="E408" s="7" t="n">
-        <x:v>285</x:v>
+        <x:v>300</x:v>
       </x:c>
     </x:row>
     <x:row r="409" ht="15" hidden="0" customHeight="1">
       <x:c r="A409" s="7" t="n">
-        <x:v>1908</x:v>
+        <x:v>1912</x:v>
       </x:c>
       <x:c r="B409" s="7" t="n">
         <x:v>19</x:v>
       </x:c>
       <x:c r="C409" s="7" t="n">
-        <x:v>7</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D409" s="7" t="n">
-        <x:v>95</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="E409" s="7" t="n">
-        <x:v>285</x:v>
+        <x:v>355</x:v>
       </x:c>
     </x:row>
     <x:row r="410" ht="15" hidden="0" customHeight="1">
       <x:c r="A410" s="7" t="n">
-        <x:v>1909</x:v>
+        <x:v>1913</x:v>
       </x:c>
       <x:c r="B410" s="7" t="n">
         <x:v>19</x:v>
       </x:c>
       <x:c r="C410" s="7" t="n">
-        <x:v>8</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="D410" s="7" t="n">
         <x:v>145</x:v>
       </x:c>
       <x:c r="E410" s="7" t="n">
-        <x:v>285</x:v>
+        <x:v>420</x:v>
       </x:c>
     </x:row>
     <x:row r="411" ht="15" hidden="0" customHeight="1">
       <x:c r="A411" s="7" t="n">
-        <x:v>1910</x:v>
+        <x:v>1914</x:v>
       </x:c>
       <x:c r="B411" s="7" t="n">
         <x:v>19</x:v>
       </x:c>
       <x:c r="C411" s="7" t="n">
-        <x:v>9</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D411" s="7" t="n">
         <x:v>195</x:v>
       </x:c>
       <x:c r="E411" s="7" t="n">
-        <x:v>285</x:v>
+        <x:v>420</x:v>
       </x:c>
     </x:row>
     <x:row r="412" ht="15" hidden="0" customHeight="1">
       <x:c r="A412" s="7" t="n">
-        <x:v>1911</x:v>
+        <x:v>1915</x:v>
       </x:c>
       <x:c r="B412" s="7" t="n">
         <x:v>19</x:v>
       </x:c>
       <x:c r="C412" s="7" t="n">
-        <x:v>10</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="D412" s="7" t="n">
         <x:v>295</x:v>
       </x:c>
       <x:c r="E412" s="7" t="n">
-        <x:v>285</x:v>
+        <x:v>350</x:v>
       </x:c>
     </x:row>
     <x:row r="413" ht="15" hidden="0" customHeight="1">
       <x:c r="A413" s="7" t="n">
-        <x:v>1912</x:v>
+        <x:v>1916</x:v>
       </x:c>
       <x:c r="B413" s="7" t="n">
         <x:v>19</x:v>
       </x:c>
       <x:c r="C413" s="7" t="n">
-        <x:v>11</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="D413" s="7" t="n">
-        <x:v>95</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="E413" s="7" t="n">
-        <x:v>335</x:v>
+        <x:v>405</x:v>
       </x:c>
     </x:row>
     <x:row r="414" ht="15" hidden="0" customHeight="1">
       <x:c r="A414" s="7" t="n">
-        <x:v>1913</x:v>
+        <x:v>1917</x:v>
       </x:c>
       <x:c r="B414" s="7" t="n">
         <x:v>19</x:v>
       </x:c>
       <x:c r="C414" s="7" t="n">
-        <x:v>12</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="D414" s="7" t="n">
-        <x:v>145</x:v>
+        <x:v>295</x:v>
       </x:c>
       <x:c r="E414" s="7" t="n">
-        <x:v>335</x:v>
+        <x:v>405</x:v>
       </x:c>
     </x:row>
     <x:row r="415" ht="15" hidden="0" customHeight="1">
       <x:c r="A415" s="7" t="n">
-        <x:v>1914</x:v>
+        <x:v>1918</x:v>
       </x:c>
       <x:c r="B415" s="7" t="n">
         <x:v>19</x:v>
       </x:c>
       <x:c r="C415" s="7" t="n">
-        <x:v>13</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="D415" s="7" t="n">
-        <x:v>195</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="E415" s="7" t="n">
-        <x:v>335</x:v>
+        <x:v>455</x:v>
       </x:c>
     </x:row>
     <x:row r="416" ht="15" hidden="0" customHeight="1">
       <x:c r="A416" s="7" t="n">
-        <x:v>1915</x:v>
+        <x:v>1919</x:v>
       </x:c>
       <x:c r="B416" s="7" t="n">
         <x:v>19</x:v>
       </x:c>
       <x:c r="C416" s="7" t="n">
-        <x:v>14</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="D416" s="7" t="n">
-        <x:v>295</x:v>
+        <x:v>245</x:v>
       </x:c>
       <x:c r="E416" s="7" t="n">
-        <x:v>335</x:v>
+        <x:v>420</x:v>
       </x:c>
     </x:row>
     <x:row r="417" ht="15" hidden="0" customHeight="1">
       <x:c r="A417" s="7" t="n">
-        <x:v>1916</x:v>
+        <x:v>1920</x:v>
       </x:c>
       <x:c r="B417" s="7" t="n">
         <x:v>19</x:v>
       </x:c>
       <x:c r="C417" s="7" t="n">
-        <x:v>15</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="D417" s="7" t="n">
-        <x:v>45</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="E417" s="7" t="n">
-        <x:v>385</x:v>
+        <x:v>520</x:v>
       </x:c>
     </x:row>
     <x:row r="418" ht="15" hidden="0" customHeight="1">
       <x:c r="A418" s="7" t="n">
-        <x:v>1917</x:v>
+        <x:v>1921</x:v>
       </x:c>
       <x:c r="B418" s="7" t="n">
         <x:v>19</x:v>
       </x:c>
       <x:c r="C418" s="7" t="n">
-        <x:v>16</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="D418" s="7" t="n">
-        <x:v>295</x:v>
+        <x:v>245</x:v>
       </x:c>
       <x:c r="E418" s="7" t="n">
-        <x:v>385</x:v>
+        <x:v>520</x:v>
       </x:c>
     </x:row>
     <x:row r="419" ht="15" hidden="0" customHeight="1">
       <x:c r="A419" s="7" t="n">
-        <x:v>1918</x:v>
+        <x:v>1922</x:v>
       </x:c>
       <x:c r="B419" s="7" t="n">
         <x:v>19</x:v>
       </x:c>
       <x:c r="C419" s="7" t="n">
-        <x:v>17</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="D419" s="7" t="n">
         <x:v>45</x:v>
       </x:c>
       <x:c r="E419" s="7" t="n">
-        <x:v>435</x:v>
+        <x:v>505</x:v>
       </x:c>
     </x:row>
     <x:row r="420" ht="15" hidden="0" customHeight="1">
       <x:c r="A420" s="7" t="n">
-        <x:v>1919</x:v>
+        <x:v>2001</x:v>
       </x:c>
       <x:c r="B420" s="7" t="n">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="C420" s="7" t="n">
-        <x:v>18</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D420" s="7" t="n">
-        <x:v>145</x:v>
+        <x:v>345</x:v>
       </x:c>
       <x:c r="E420" s="7" t="n">
-        <x:v>435</x:v>
+        <x:v>150</x:v>
       </x:c>
     </x:row>
     <x:row r="421" ht="15" hidden="0" customHeight="1">
       <x:c r="A421" s="7" t="n">
-        <x:v>1920</x:v>
+        <x:v>2002</x:v>
       </x:c>
       <x:c r="B421" s="7" t="n">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="C421" s="7" t="n">
-        <x:v>19</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="D421" s="7" t="n">
-        <x:v>195</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="E421" s="7" t="n">
-        <x:v>435</x:v>
+        <x:v>215</x:v>
       </x:c>
     </x:row>
     <x:row r="422" ht="15" hidden="0" customHeight="1">
       <x:c r="A422" s="7" t="n">
-        <x:v>1921</x:v>
+        <x:v>2003</x:v>
       </x:c>
       <x:c r="B422" s="7" t="n">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="C422" s="7" t="n">
-        <x:v>20</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="D422" s="7" t="n">
-        <x:v>245</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="E422" s="7" t="n">
-        <x:v>435</x:v>
+        <x:v>200</x:v>
       </x:c>
     </x:row>
     <x:row r="423" ht="15" hidden="0" customHeight="1">
       <x:c r="A423" s="7" t="n">
-        <x:v>1922</x:v>
+        <x:v>2004</x:v>
       </x:c>
       <x:c r="B423" s="7" t="n">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="C423" s="7" t="n">
-        <x:v>21</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="D423" s="7" t="n">
-        <x:v>45</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="E423" s="7" t="n">
-        <x:v>485</x:v>
+        <x:v>200</x:v>
       </x:c>
     </x:row>
     <x:row r="424" ht="15" hidden="0" customHeight="1">
       <x:c r="A424" s="7" t="n">
-        <x:v>2001</x:v>
+        <x:v>2005</x:v>
       </x:c>
       <x:c r="B424" s="7" t="n">
         <x:v>20</x:v>
       </x:c>
       <x:c r="C424" s="7" t="n">
-        <x:v>0</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="D424" s="7" t="n">
-        <x:v>345</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="E424" s="7" t="n">
-        <x:v>135</x:v>
+        <x:v>200</x:v>
       </x:c>
     </x:row>
     <x:row r="425" ht="15" hidden="0" customHeight="1">
       <x:c r="A425" s="7" t="n">
-        <x:v>2002</x:v>
+        <x:v>2006</x:v>
       </x:c>
       <x:c r="B425" s="7" t="n">
         <x:v>20</x:v>
       </x:c>
       <x:c r="C425" s="7" t="n">
-        <x:v>1</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D425" s="7" t="n">
-        <x:v>45</x:v>
+        <x:v>245</x:v>
       </x:c>
       <x:c r="E425" s="7" t="n">
-        <x:v>185</x:v>
+        <x:v>200</x:v>
       </x:c>
     </x:row>
     <x:row r="426" ht="15" hidden="0" customHeight="1">
       <x:c r="A426" s="7" t="n">
-        <x:v>2003</x:v>
+        <x:v>2007</x:v>
       </x:c>
       <x:c r="B426" s="7" t="n">
         <x:v>20</x:v>
       </x:c>
       <x:c r="C426" s="7" t="n">
-        <x:v>2</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="D426" s="7" t="n">
-        <x:v>95</x:v>
+        <x:v>345</x:v>
       </x:c>
       <x:c r="E426" s="7" t="n">
-        <x:v>185</x:v>
+        <x:v>200</x:v>
       </x:c>
     </x:row>
     <x:row r="427" ht="15" hidden="0" customHeight="1">
       <x:c r="A427" s="7" t="n">
-        <x:v>2004</x:v>
+        <x:v>2008</x:v>
       </x:c>
       <x:c r="B427" s="7" t="n">
         <x:v>20</x:v>
       </x:c>
       <x:c r="C427" s="7" t="n">
-        <x:v>3</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="D427" s="7" t="n">
-        <x:v>145</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="E427" s="7" t="n">
-        <x:v>185</x:v>
+        <x:v>265</x:v>
       </x:c>
     </x:row>
     <x:row r="428" ht="15" hidden="0" customHeight="1">
       <x:c r="A428" s="7" t="n">
-        <x:v>2005</x:v>
+        <x:v>2009</x:v>
       </x:c>
       <x:c r="B428" s="7" t="n">
         <x:v>20</x:v>
       </x:c>
       <x:c r="C428" s="7" t="n">
-        <x:v>4</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="D428" s="7" t="n">
-        <x:v>195</x:v>
+        <x:v>345</x:v>
       </x:c>
       <x:c r="E428" s="7" t="n">
-        <x:v>185</x:v>
+        <x:v>250</x:v>
       </x:c>
     </x:row>
     <x:row r="429" ht="15" hidden="0" customHeight="1">
       <x:c r="A429" s="7" t="n">
-        <x:v>2006</x:v>
+        <x:v>2010</x:v>
       </x:c>
       <x:c r="B429" s="7" t="n">
         <x:v>20</x:v>
       </x:c>
       <x:c r="C429" s="7" t="n">
-        <x:v>5</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="D429" s="7" t="n">
-        <x:v>245</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="E429" s="7" t="n">
-        <x:v>185</x:v>
+        <x:v>315</x:v>
       </x:c>
     </x:row>
     <x:row r="430" ht="15" hidden="0" customHeight="1">
       <x:c r="A430" s="7" t="n">
-        <x:v>2007</x:v>
+        <x:v>2011</x:v>
       </x:c>
       <x:c r="B430" s="7" t="n">
         <x:v>20</x:v>
       </x:c>
       <x:c r="C430" s="7" t="n">
-        <x:v>6</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="D430" s="7" t="n">
-        <x:v>345</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="E430" s="7" t="n">
-        <x:v>185</x:v>
+        <x:v>310</x:v>
       </x:c>
     </x:row>
     <x:row r="431" ht="15" hidden="0" customHeight="1">
       <x:c r="A431" s="7" t="n">
-        <x:v>2008</x:v>
+        <x:v>2012</x:v>
       </x:c>
       <x:c r="B431" s="7" t="n">
         <x:v>20</x:v>
       </x:c>
       <x:c r="C431" s="7" t="n">
-        <x:v>7</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D431" s="7" t="n">
-        <x:v>45</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="E431" s="7" t="n">
-        <x:v>235</x:v>
+        <x:v>310</x:v>
       </x:c>
     </x:row>
     <x:row r="432" ht="15" hidden="0" customHeight="1">
       <x:c r="A432" s="7" t="n">
-        <x:v>2009</x:v>
+        <x:v>2013</x:v>
       </x:c>
       <x:c r="B432" s="7" t="n">
         <x:v>20</x:v>
       </x:c>
       <x:c r="C432" s="7" t="n">
-        <x:v>8</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="D432" s="7" t="n">
-        <x:v>345</x:v>
+        <x:v>245</x:v>
       </x:c>
       <x:c r="E432" s="7" t="n">
-        <x:v>235</x:v>
+        <x:v>310</x:v>
       </x:c>
     </x:row>
     <x:row r="433" ht="15" hidden="0" customHeight="1">
       <x:c r="A433" s="7" t="n">
-        <x:v>2010</x:v>
+        <x:v>2014</x:v>
       </x:c>
       <x:c r="B433" s="7" t="n">
         <x:v>20</x:v>
       </x:c>
       <x:c r="C433" s="7" t="n">
-        <x:v>9</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D433" s="7" t="n">
-        <x:v>45</x:v>
+        <x:v>295</x:v>
       </x:c>
       <x:c r="E433" s="7" t="n">
-        <x:v>285</x:v>
+        <x:v>300</x:v>
       </x:c>
     </x:row>
     <x:row r="434" ht="15" hidden="0" customHeight="1">
       <x:c r="A434" s="7" t="n">
-        <x:v>2011</x:v>
+        <x:v>2015</x:v>
       </x:c>
       <x:c r="B434" s="7" t="n">
         <x:v>20</x:v>
       </x:c>
       <x:c r="C434" s="7" t="n">
-        <x:v>10</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="D434" s="7" t="n">
-        <x:v>145</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="E434" s="7" t="n">
-        <x:v>285</x:v>
+        <x:v>365</x:v>
       </x:c>
     </x:row>
     <x:row r="435" ht="15" hidden="0" customHeight="1">
       <x:c r="A435" s="7" t="n">
-        <x:v>2012</x:v>
+        <x:v>2016</x:v>
       </x:c>
       <x:c r="B435" s="7" t="n">
         <x:v>20</x:v>
       </x:c>
       <x:c r="C435" s="7" t="n">
-        <x:v>11</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="D435" s="7" t="n">
-        <x:v>195</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="E435" s="7" t="n">
-        <x:v>285</x:v>
+        <x:v>420</x:v>
       </x:c>
     </x:row>
     <x:row r="436" ht="15" hidden="0" customHeight="1">
       <x:c r="A436" s="7" t="n">
-        <x:v>2013</x:v>
+        <x:v>2017</x:v>
       </x:c>
       <x:c r="B436" s="7" t="n">
         <x:v>20</x:v>
       </x:c>
       <x:c r="C436" s="7" t="n">
-        <x:v>12</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="D436" s="7" t="n">
-        <x:v>245</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="E436" s="7" t="n">
-        <x:v>285</x:v>
+        <x:v>420</x:v>
       </x:c>
     </x:row>
     <x:row r="437" ht="15" hidden="0" customHeight="1">
       <x:c r="A437" s="7" t="n">
-        <x:v>2014</x:v>
+        <x:v>2018</x:v>
       </x:c>
       <x:c r="B437" s="7" t="n">
         <x:v>20</x:v>
       </x:c>
       <x:c r="C437" s="7" t="n">
-        <x:v>13</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="D437" s="7" t="n">
-        <x:v>295</x:v>
+        <x:v>245</x:v>
       </x:c>
       <x:c r="E437" s="7" t="n">
-        <x:v>285</x:v>
+        <x:v>420</x:v>
       </x:c>
     </x:row>
     <x:row r="438" ht="15" hidden="0" customHeight="1">
       <x:c r="A438" s="7" t="n">
-        <x:v>2015</x:v>
+        <x:v>2019</x:v>
       </x:c>
       <x:c r="B438" s="7" t="n">
         <x:v>20</x:v>
       </x:c>
       <x:c r="C438" s="7" t="n">
-        <x:v>14</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="D438" s="7" t="n">
-        <x:v>45</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="E438" s="7" t="n">
-        <x:v>335</x:v>
+        <x:v>420</x:v>
       </x:c>
     </x:row>
     <x:row r="439" ht="15" hidden="0" customHeight="1">
       <x:c r="A439" s="7" t="n">
-        <x:v>2016</x:v>
+        <x:v>2020</x:v>
       </x:c>
       <x:c r="B439" s="7" t="n">
         <x:v>20</x:v>
       </x:c>
       <x:c r="C439" s="7" t="n">
-        <x:v>15</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="D439" s="7" t="n">
-        <x:v>145</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="E439" s="7" t="n">
-        <x:v>335</x:v>
+        <x:v>470</x:v>
       </x:c>
     </x:row>
     <x:row r="440" ht="15" hidden="0" customHeight="1">
       <x:c r="A440" s="7" t="n">
-        <x:v>2017</x:v>
+        <x:v>2021</x:v>
       </x:c>
       <x:c r="B440" s="7" t="n">
         <x:v>20</x:v>
       </x:c>
       <x:c r="C440" s="7" t="n">
-        <x:v>16</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="D440" s="7" t="n">
         <x:v>195</x:v>
       </x:c>
       <x:c r="E440" s="7" t="n">
-        <x:v>335</x:v>
+        <x:v>520</x:v>
       </x:c>
     </x:row>
     <x:row r="441" ht="15" hidden="0" customHeight="1">
       <x:c r="A441" s="7" t="n">
-        <x:v>2018</x:v>
+        <x:v>2022</x:v>
       </x:c>
       <x:c r="B441" s="7" t="n">
         <x:v>20</x:v>
       </x:c>
       <x:c r="C441" s="7" t="n">
-        <x:v>17</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="D441" s="7" t="n">
         <x:v>245</x:v>
       </x:c>
       <x:c r="E441" s="7" t="n">
-        <x:v>335</x:v>
+        <x:v>520</x:v>
       </x:c>
     </x:row>
     <x:row r="442" ht="15" hidden="0" customHeight="1">
       <x:c r="A442" s="7" t="n">
-        <x:v>2019</x:v>
+        <x:v>2023</x:v>
       </x:c>
       <x:c r="B442" s="7" t="n">
-        <x:v>20</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C442" s="7" t="n">
-        <x:v>18</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D442" s="7" t="n">
-        <x:v>95</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="E442" s="7" t="n">
-        <x:v>435</x:v>
+        <x:v>185</x:v>
       </x:c>
     </x:row>
     <x:row r="443" ht="15" hidden="0" customHeight="1">
       <x:c r="A443" s="7" t="n">
-        <x:v>2020</x:v>
+        <x:v>2024</x:v>
       </x:c>
       <x:c r="B443" s="7" t="n">
-        <x:v>20</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C443" s="7" t="n">
-        <x:v>19</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="D443" s="7" t="n">
-        <x:v>145</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="E443" s="7" t="n">
-        <x:v>435</x:v>
+        <x:v>185</x:v>
       </x:c>
     </x:row>
     <x:row r="444" ht="15" hidden="0" customHeight="1">
       <x:c r="A444" s="7" t="n">
-        <x:v>2021</x:v>
+        <x:v>2025</x:v>
       </x:c>
       <x:c r="B444" s="7" t="n">
-        <x:v>20</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C444" s="7" t="n">
-        <x:v>20</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="D444" s="7" t="n">
-        <x:v>195</x:v>
+        <x:v>245</x:v>
       </x:c>
       <x:c r="E444" s="7" t="n">
-        <x:v>535</x:v>
+        <x:v>185</x:v>
       </x:c>
     </x:row>
     <x:row r="445" ht="15" hidden="0" customHeight="1">
       <x:c r="A445" s="7" t="n">
-        <x:v>2022</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="B445" s="7" t="n">
-        <x:v>20</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C445" s="7" t="n">
-        <x:v>21</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="D445" s="7" t="n">
-        <x:v>245</x:v>
+        <x:v>295</x:v>
       </x:c>
       <x:c r="E445" s="7" t="n">
-        <x:v>535</x:v>
+        <x:v>185</x:v>
       </x:c>
     </x:row>
     <x:row r="446">
       <x:c r="A446" t="n">
-        <x:v>2023</x:v>
+        <x:v>2027</x:v>
       </x:c>
       <x:c r="B446" t="n">
         <x:v>21</x:v>
       </x:c>
       <x:c r="C446" t="n">
-        <x:v>0</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="D446" t="n">
         <x:v>145</x:v>
       </x:c>
       <x:c r="E446" t="n">
-        <x:v>185</x:v>
+        <x:v>235</x:v>
       </x:c>
     </x:row>
     <x:row r="447">
       <x:c r="A447" t="n">
-        <x:v>2024</x:v>
+        <x:v>2028</x:v>
       </x:c>
       <x:c r="B447" t="n">
         <x:v>21</x:v>
       </x:c>
       <x:c r="C447" t="n">
-        <x:v>1</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D447" t="n">
         <x:v>195</x:v>
       </x:c>
       <x:c r="E447" t="n">
-        <x:v>185</x:v>
+        <x:v>235</x:v>
       </x:c>
     </x:row>
     <x:row r="448">
       <x:c r="A448" t="n">
-        <x:v>2025</x:v>
+        <x:v>2029</x:v>
       </x:c>
       <x:c r="B448" t="n">
         <x:v>21</x:v>
       </x:c>
       <x:c r="C448" t="n">
-        <x:v>2</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="D448" t="n">
         <x:v>245</x:v>
       </x:c>
       <x:c r="E448" t="n">
-        <x:v>185</x:v>
+        <x:v>235</x:v>
       </x:c>
     </x:row>
     <x:row r="449">
       <x:c r="A449" t="n">
-        <x:v>2026</x:v>
+        <x:v>2030</x:v>
       </x:c>
       <x:c r="B449" t="n">
         <x:v>21</x:v>
       </x:c>
       <x:c r="C449" t="n">
-        <x:v>3</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="D449" t="n">
         <x:v>295</x:v>
       </x:c>
       <x:c r="E449" t="n">
-        <x:v>185</x:v>
+        <x:v>235</x:v>
       </x:c>
     </x:row>
     <x:row r="450">
       <x:c r="A450" t="n">
-        <x:v>2027</x:v>
+        <x:v>2031</x:v>
       </x:c>
       <x:c r="B450" t="n">
         <x:v>21</x:v>
       </x:c>
       <x:c r="C450" t="n">
-        <x:v>4</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="D450" t="n">
-        <x:v>145</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="E450" t="n">
-        <x:v>235</x:v>
+        <x:v>335</x:v>
       </x:c>
     </x:row>
     <x:row r="451">
       <x:c r="A451" t="n">
-        <x:v>2028</x:v>
+        <x:v>2032</x:v>
       </x:c>
       <x:c r="B451" t="n">
         <x:v>21</x:v>
       </x:c>
       <x:c r="C451" t="n">
-        <x:v>5</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="D451" t="n">
-        <x:v>195</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="E451" t="n">
-        <x:v>235</x:v>
+        <x:v>335</x:v>
       </x:c>
     </x:row>
     <x:row r="452">
       <x:c r="A452" t="n">
-        <x:v>2029</x:v>
+        <x:v>2033</x:v>
       </x:c>
       <x:c r="B452" t="n">
         <x:v>21</x:v>
       </x:c>
       <x:c r="C452" t="n">
-        <x:v>6</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="D452" t="n">
-        <x:v>245</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="E452" t="n">
-        <x:v>235</x:v>
+        <x:v>335</x:v>
       </x:c>
     </x:row>
     <x:row r="453">
       <x:c r="A453" t="n">
-        <x:v>2030</x:v>
+        <x:v>2034</x:v>
       </x:c>
       <x:c r="B453" t="n">
         <x:v>21</x:v>
       </x:c>
       <x:c r="C453" t="n">
-        <x:v>7</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D453" t="n">
-        <x:v>295</x:v>
+        <x:v>245</x:v>
       </x:c>
       <x:c r="E453" t="n">
-        <x:v>235</x:v>
+        <x:v>335</x:v>
       </x:c>
     </x:row>
     <x:row r="454">
       <x:c r="A454" t="n">
-        <x:v>2031</x:v>
+        <x:v>2035</x:v>
       </x:c>
       <x:c r="B454" t="n">
         <x:v>21</x:v>
       </x:c>
       <x:c r="C454" t="n">
-        <x:v>8</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="D454" t="n">
         <x:v>95</x:v>
       </x:c>
       <x:c r="E454" t="n">
-        <x:v>335</x:v>
+        <x:v>385</x:v>
       </x:c>
     </x:row>
     <x:row r="455">
       <x:c r="A455" t="n">
-        <x:v>2032</x:v>
+        <x:v>2036</x:v>
       </x:c>
       <x:c r="B455" t="n">
         <x:v>21</x:v>
       </x:c>
       <x:c r="C455" t="n">
-        <x:v>9</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D455" t="n">
         <x:v>145</x:v>
       </x:c>
       <x:c r="E455" t="n">
-        <x:v>335</x:v>
+        <x:v>385</x:v>
       </x:c>
     </x:row>
     <x:row r="456">
       <x:c r="A456" t="n">
-        <x:v>2033</x:v>
+        <x:v>2037</x:v>
       </x:c>
       <x:c r="B456" t="n">
         <x:v>21</x:v>
       </x:c>
       <x:c r="C456" t="n">
-        <x:v>10</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="D456" t="n">
         <x:v>195</x:v>
       </x:c>
       <x:c r="E456" t="n">
-        <x:v>335</x:v>
+        <x:v>385</x:v>
       </x:c>
     </x:row>
     <x:row r="457">
       <x:c r="A457" t="n">
-        <x:v>2034</x:v>
+        <x:v>2038</x:v>
       </x:c>
       <x:c r="B457" t="n">
         <x:v>21</x:v>
       </x:c>
       <x:c r="C457" t="n">
-        <x:v>11</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="D457" t="n">
         <x:v>245</x:v>
       </x:c>
       <x:c r="E457" t="n">
-        <x:v>335</x:v>
+        <x:v>385</x:v>
       </x:c>
     </x:row>
     <x:row r="458">
       <x:c r="A458" t="n">
-        <x:v>2035</x:v>
+        <x:v>2039</x:v>
       </x:c>
       <x:c r="B458" t="n">
         <x:v>21</x:v>
       </x:c>
       <x:c r="C458" t="n">
-        <x:v>12</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="D458" t="n">
-        <x:v>95</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="E458" t="n">
-        <x:v>385</x:v>
+        <x:v>485</x:v>
       </x:c>
     </x:row>
     <x:row r="459">
       <x:c r="A459" t="n">
-        <x:v>2036</x:v>
+        <x:v>2040</x:v>
       </x:c>
       <x:c r="B459" t="n">
         <x:v>21</x:v>
       </x:c>
       <x:c r="C459" t="n">
-        <x:v>13</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="D459" t="n">
-        <x:v>145</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="E459" t="n">
-        <x:v>385</x:v>
+        <x:v>485</x:v>
       </x:c>
     </x:row>
     <x:row r="460">
       <x:c r="A460" t="n">
-        <x:v>2037</x:v>
+        <x:v>2041</x:v>
       </x:c>
       <x:c r="B460" t="n">
         <x:v>21</x:v>
       </x:c>
       <x:c r="C460" t="n">
-        <x:v>14</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="D460" t="n">
-        <x:v>195</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="E460" t="n">
-        <x:v>385</x:v>
+        <x:v>485</x:v>
       </x:c>
     </x:row>
     <x:row r="461">
       <x:c r="A461" t="n">
-        <x:v>2038</x:v>
+        <x:v>2042</x:v>
       </x:c>
       <x:c r="B461" t="n">
         <x:v>21</x:v>
       </x:c>
       <x:c r="C461" t="n">
-        <x:v>15</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="D461" t="n">
-        <x:v>245</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="E461" t="n">
-        <x:v>385</x:v>
+        <x:v>485</x:v>
       </x:c>
     </x:row>
     <x:row r="462">
       <x:c r="A462" t="n">
-        <x:v>2039</x:v>
+        <x:v>2043</x:v>
       </x:c>
       <x:c r="B462" t="n">
         <x:v>21</x:v>
       </x:c>
       <x:c r="C462" t="n">
-        <x:v>16</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="D462" t="n">
-        <x:v>45</x:v>
+        <x:v>245</x:v>
       </x:c>
       <x:c r="E462" t="n">
         <x:v>485</x:v>
@@ -8143,88 +8143,48 @@
     </x:row>
     <x:row r="463">
       <x:c r="A463" t="n">
-        <x:v>2040</x:v>
+        <x:v>2044</x:v>
       </x:c>
       <x:c r="B463" t="n">
         <x:v>21</x:v>
       </x:c>
       <x:c r="C463" t="n">
-        <x:v>17</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="D463" t="n">
-        <x:v>95</x:v>
+        <x:v>245</x:v>
       </x:c>
       <x:c r="E463" t="n">
-        <x:v>485</x:v>
+        <x:v>535</x:v>
       </x:c>
     </x:row>
     <x:row r="464">
-      <x:c r="A464" t="n">
-        <x:v>2041</x:v>
-      </x:c>
-      <x:c r="B464" t="n">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="C464" t="n">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="D464" t="n">
-        <x:v>145</x:v>
-      </x:c>
-      <x:c r="E464" t="n">
-        <x:v>485</x:v>
-      </x:c>
+      <x:c r="A464"/>
+      <x:c r="B464"/>
+      <x:c r="C464"/>
+      <x:c r="D464"/>
+      <x:c r="E464"/>
     </x:row>
     <x:row r="465">
-      <x:c r="A465" t="n">
-        <x:v>2042</x:v>
-      </x:c>
-      <x:c r="B465" t="n">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="C465" t="n">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="D465" t="n">
-        <x:v>195</x:v>
-      </x:c>
-      <x:c r="E465" t="n">
-        <x:v>485</x:v>
-      </x:c>
+      <x:c r="A465"/>
+      <x:c r="B465"/>
+      <x:c r="C465"/>
+      <x:c r="D465"/>
+      <x:c r="E465"/>
     </x:row>
     <x:row r="466">
-      <x:c r="A466" t="n">
-        <x:v>2043</x:v>
-      </x:c>
-      <x:c r="B466" t="n">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="C466" t="n">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="D466" t="n">
-        <x:v>245</x:v>
-      </x:c>
-      <x:c r="E466" t="n">
-        <x:v>485</x:v>
-      </x:c>
+      <x:c r="A466"/>
+      <x:c r="B466"/>
+      <x:c r="C466"/>
+      <x:c r="D466"/>
+      <x:c r="E466"/>
     </x:row>
     <x:row r="467">
-      <x:c r="A467" t="n">
-        <x:v>2044</x:v>
-      </x:c>
-      <x:c r="B467" t="n">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="C467" t="n">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="D467" t="n">
-        <x:v>245</x:v>
-      </x:c>
-      <x:c r="E467" t="n">
-        <x:v>535</x:v>
-      </x:c>
+      <x:c r="A467"/>
+      <x:c r="B467"/>
+      <x:c r="C467"/>
+      <x:c r="D467"/>
+      <x:c r="E467"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/design/tables/Spot.xlsx
+++ b/design/tables/Spot.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Spot" sheetId="1" r:id="R8ac7c0800b2e4cee"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Spot" sheetId="1" r:id="R7c9b13a390984a02"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -386,7 +386,7 @@
         <x:v>145</x:v>
       </x:c>
       <x:c r="E6" s="7" t="n">
-        <x:v>250</x:v>
+        <x:v>235</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="15" hidden="0" customHeight="1">
@@ -403,7 +403,7 @@
         <x:v>195</x:v>
       </x:c>
       <x:c r="E7" s="7" t="n">
-        <x:v>250</x:v>
+        <x:v>235</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="15" hidden="0" customHeight="1">
@@ -420,7 +420,7 @@
         <x:v>245</x:v>
       </x:c>
       <x:c r="E8" s="7" t="n">
-        <x:v>250</x:v>
+        <x:v>235</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="15" hidden="0" customHeight="1">
@@ -437,7 +437,7 @@
         <x:v>295</x:v>
       </x:c>
       <x:c r="E9" s="7" t="n">
-        <x:v>250</x:v>
+        <x:v>235</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="15" hidden="0" customHeight="1">
@@ -454,7 +454,7 @@
         <x:v>95</x:v>
       </x:c>
       <x:c r="E10" s="7" t="n">
-        <x:v>350</x:v>
+        <x:v>335</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="15" hidden="0" customHeight="1">
@@ -471,7 +471,7 @@
         <x:v>145</x:v>
       </x:c>
       <x:c r="E11" s="7" t="n">
-        <x:v>360</x:v>
+        <x:v>335</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="15" hidden="0" customHeight="1">
@@ -488,7 +488,7 @@
         <x:v>195</x:v>
       </x:c>
       <x:c r="E12" s="7" t="n">
-        <x:v>360</x:v>
+        <x:v>335</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="15" hidden="0" customHeight="1">
@@ -505,7 +505,7 @@
         <x:v>245</x:v>
       </x:c>
       <x:c r="E13" s="7" t="n">
-        <x:v>360</x:v>
+        <x:v>335</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="15" hidden="0" customHeight="1">
@@ -519,7 +519,7 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="D14" s="7" t="n">
-        <x:v>55</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="E14" s="7" t="n">
         <x:v>385</x:v>
@@ -539,7 +539,7 @@
         <x:v>145</x:v>
       </x:c>
       <x:c r="E15" s="7" t="n">
-        <x:v>470</x:v>
+        <x:v>435</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="15" hidden="0" customHeight="1">
@@ -556,7 +556,7 @@
         <x:v>195</x:v>
       </x:c>
       <x:c r="E16" s="7" t="n">
-        <x:v>470</x:v>
+        <x:v>435</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="15" hidden="0" customHeight="1">
@@ -573,7 +573,7 @@
         <x:v>245</x:v>
       </x:c>
       <x:c r="E17" s="7" t="n">
-        <x:v>470</x:v>
+        <x:v>435</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="15" hidden="0" customHeight="1">
@@ -621,10 +621,10 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="D20" s="7" t="n">
-        <x:v>345</x:v>
+        <x:v>245</x:v>
       </x:c>
       <x:c r="E20" s="7" t="n">
-        <x:v>435</x:v>
+        <x:v>535</x:v>
       </x:c>
     </x:row>
     <x:row r="21" ht="15" hidden="0" customHeight="1">
@@ -672,7 +672,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="D23" s="7" t="n">
-        <x:v>45</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="E23" s="7" t="n">
         <x:v>535</x:v>
@@ -692,7 +692,7 @@
         <x:v>145</x:v>
       </x:c>
       <x:c r="E24" s="7" t="n">
-        <x:v>570</x:v>
+        <x:v>535</x:v>
       </x:c>
     </x:row>
     <x:row r="25" ht="15" hidden="0" customHeight="1">
@@ -706,10 +706,10 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="D25" s="7" t="n">
-        <x:v>295</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="E25" s="7" t="n">
-        <x:v>470</x:v>
+        <x:v>535</x:v>
       </x:c>
     </x:row>
     <x:row r="26" ht="15" hidden="0" customHeight="1">
@@ -723,10 +723,10 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="D26" s="7" t="n">
-        <x:v>245</x:v>
+        <x:v>345</x:v>
       </x:c>
       <x:c r="E26" s="7" t="n">
-        <x:v>570</x:v>
+        <x:v>285</x:v>
       </x:c>
     </x:row>
     <x:row r="27" ht="15" hidden="0" customHeight="1">
@@ -740,10 +740,10 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="D27" s="7" t="n">
-        <x:v>295</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="E27" s="7" t="n">
-        <x:v>570</x:v>
+        <x:v>185</x:v>
       </x:c>
     </x:row>
     <x:row r="28" ht="15" hidden="0" customHeight="1">
@@ -760,7 +760,7 @@
         <x:v>145</x:v>
       </x:c>
       <x:c r="E28" s="7" t="n">
-        <x:v>215</x:v>
+        <x:v>235</x:v>
       </x:c>
     </x:row>
     <x:row r="29" ht="15" hidden="0" customHeight="1">
@@ -777,7 +777,7 @@
         <x:v>195</x:v>
       </x:c>
       <x:c r="E29" s="7" t="n">
-        <x:v>215</x:v>
+        <x:v>235</x:v>
       </x:c>
     </x:row>
     <x:row r="30" ht="15" hidden="0" customHeight="1">
@@ -794,7 +794,7 @@
         <x:v>245</x:v>
       </x:c>
       <x:c r="E30" s="7" t="n">
-        <x:v>215</x:v>
+        <x:v>235</x:v>
       </x:c>
     </x:row>
     <x:row r="31" ht="15" hidden="0" customHeight="1">
@@ -811,7 +811,7 @@
         <x:v>295</x:v>
       </x:c>
       <x:c r="E31" s="7" t="n">
-        <x:v>215</x:v>
+        <x:v>235</x:v>
       </x:c>
     </x:row>
     <x:row r="32" ht="15" hidden="0" customHeight="1">
@@ -828,7 +828,7 @@
         <x:v>95</x:v>
       </x:c>
       <x:c r="E32" s="7" t="n">
-        <x:v>325</x:v>
+        <x:v>335</x:v>
       </x:c>
     </x:row>
     <x:row r="33" ht="15" hidden="0" customHeight="1">
@@ -845,7 +845,7 @@
         <x:v>145</x:v>
       </x:c>
       <x:c r="E33" s="7" t="n">
-        <x:v>325</x:v>
+        <x:v>335</x:v>
       </x:c>
     </x:row>
     <x:row r="34" ht="15" hidden="0" customHeight="1">
@@ -862,7 +862,7 @@
         <x:v>195</x:v>
       </x:c>
       <x:c r="E34" s="7" t="n">
-        <x:v>325</x:v>
+        <x:v>335</x:v>
       </x:c>
     </x:row>
     <x:row r="35" ht="15" hidden="0" customHeight="1">
@@ -879,7 +879,7 @@
         <x:v>245</x:v>
       </x:c>
       <x:c r="E35" s="7" t="n">
-        <x:v>325</x:v>
+        <x:v>335</x:v>
       </x:c>
     </x:row>
     <x:row r="36" ht="15" hidden="0" customHeight="1">
@@ -896,7 +896,7 @@
         <x:v>295</x:v>
       </x:c>
       <x:c r="E36" s="7" t="n">
-        <x:v>315</x:v>
+        <x:v>335</x:v>
       </x:c>
     </x:row>
     <x:row r="37" ht="15" hidden="0" customHeight="1">
@@ -913,7 +913,7 @@
         <x:v>345</x:v>
       </x:c>
       <x:c r="E37" s="7" t="n">
-        <x:v>315</x:v>
+        <x:v>335</x:v>
       </x:c>
     </x:row>
     <x:row r="38" ht="15" hidden="0" customHeight="1">
@@ -998,7 +998,7 @@
         <x:v>345</x:v>
       </x:c>
       <x:c r="E42" s="7" t="n">
-        <x:v>365</x:v>
+        <x:v>385</x:v>
       </x:c>
     </x:row>
     <x:row r="43" ht="15" hidden="0" customHeight="1">
@@ -1029,7 +1029,7 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="D44" s="7" t="n">
-        <x:v>225</x:v>
+        <x:v>245</x:v>
       </x:c>
       <x:c r="E44" s="7" t="n">
         <x:v>485</x:v>
@@ -1046,10 +1046,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="D45" s="7" t="n">
-        <x:v>235</x:v>
+        <x:v>245</x:v>
       </x:c>
       <x:c r="E45" s="7" t="n">
-        <x:v>535</x:v>
+        <x:v>135</x:v>
       </x:c>
     </x:row>
     <x:row r="46" ht="15" hidden="0" customHeight="1">
@@ -1066,7 +1066,7 @@
         <x:v>345</x:v>
       </x:c>
       <x:c r="E46" s="7" t="n">
-        <x:v>425</x:v>
+        <x:v>135</x:v>
       </x:c>
     </x:row>
     <x:row r="47" ht="15" hidden="0" customHeight="1">
@@ -1080,10 +1080,10 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="D47" s="7" t="n">
-        <x:v>285</x:v>
+        <x:v>295</x:v>
       </x:c>
       <x:c r="E47" s="7" t="n">
-        <x:v>555</x:v>
+        <x:v>135</x:v>
       </x:c>
     </x:row>
     <x:row r="48" ht="15" hidden="0" customHeight="1">
@@ -1097,10 +1097,10 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="D48" s="7" t="n">
-        <x:v>335</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="E48" s="7" t="n">
-        <x:v>575</x:v>
+        <x:v>135</x:v>
       </x:c>
     </x:row>
     <x:row r="49" ht="15" hidden="0" customHeight="1">
@@ -1114,10 +1114,10 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="D49" s="7" t="n">
-        <x:v>95</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="E49" s="7" t="n">
-        <x:v>215</x:v>
+        <x:v>135</x:v>
       </x:c>
     </x:row>
     <x:row r="50" ht="15" hidden="0" customHeight="1">
@@ -1131,7 +1131,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D50" s="7" t="n">
-        <x:v>45</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="E50" s="7" t="n">
         <x:v>235</x:v>
@@ -1148,7 +1148,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="D51" s="7" t="n">
-        <x:v>45</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="E51" s="7" t="n">
         <x:v>285</x:v>
@@ -1165,7 +1165,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="D52" s="7" t="n">
-        <x:v>45</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="E52" s="7" t="n">
         <x:v>335</x:v>
@@ -1185,7 +1185,7 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="E53" s="7" t="n">
-        <x:v>385</x:v>
+        <x:v>435</x:v>
       </x:c>
     </x:row>
     <x:row r="54" ht="15" hidden="0" customHeight="1">
@@ -1202,7 +1202,7 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="E54" s="7" t="n">
-        <x:v>435</x:v>
+        <x:v>485</x:v>
       </x:c>
     </x:row>
     <x:row r="55" ht="15" hidden="0" customHeight="1">
@@ -1219,7 +1219,7 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="E55" s="7" t="n">
-        <x:v>485</x:v>
+        <x:v>535</x:v>
       </x:c>
     </x:row>
     <x:row r="56" ht="15" hidden="0" customHeight="1">
@@ -1233,10 +1233,10 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="D56" s="7" t="n">
-        <x:v>45</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="E56" s="7" t="n">
-        <x:v>535</x:v>
+        <x:v>485</x:v>
       </x:c>
     </x:row>
     <x:row r="57" ht="15" hidden="0" customHeight="1">
@@ -1284,7 +1284,7 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D59" s="7" t="n">
-        <x:v>145</x:v>
+        <x:v>245</x:v>
       </x:c>
       <x:c r="E59" s="7" t="n">
         <x:v>235</x:v>
@@ -1301,7 +1301,7 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="D60" s="7" t="n">
-        <x:v>145</x:v>
+        <x:v>245</x:v>
       </x:c>
       <x:c r="E60" s="7" t="n">
         <x:v>285</x:v>
@@ -1321,7 +1321,7 @@
         <x:v>145</x:v>
       </x:c>
       <x:c r="E61" s="7" t="n">
-        <x:v>335</x:v>
+        <x:v>385</x:v>
       </x:c>
     </x:row>
     <x:row r="62" ht="15" hidden="0" customHeight="1">
@@ -1338,7 +1338,7 @@
         <x:v>145</x:v>
       </x:c>
       <x:c r="E62" s="7" t="n">
-        <x:v>385</x:v>
+        <x:v>435</x:v>
       </x:c>
     </x:row>
     <x:row r="63" ht="15" hidden="0" customHeight="1">
@@ -1352,7 +1352,7 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="D63" s="7" t="n">
-        <x:v>145</x:v>
+        <x:v>245</x:v>
       </x:c>
       <x:c r="E63" s="7" t="n">
         <x:v>435</x:v>
@@ -1369,7 +1369,7 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="D64" s="7" t="n">
-        <x:v>145</x:v>
+        <x:v>245</x:v>
       </x:c>
       <x:c r="E64" s="7" t="n">
         <x:v>485</x:v>
@@ -1403,7 +1403,7 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="D66" s="7" t="n">
-        <x:v>245</x:v>
+        <x:v>345</x:v>
       </x:c>
       <x:c r="E66" s="7" t="n">
         <x:v>235</x:v>
@@ -1423,7 +1423,7 @@
         <x:v>245</x:v>
       </x:c>
       <x:c r="E67" s="7" t="n">
-        <x:v>285</x:v>
+        <x:v>335</x:v>
       </x:c>
     </x:row>
     <x:row r="68" ht="15" hidden="0" customHeight="1">
@@ -1440,7 +1440,7 @@
         <x:v>245</x:v>
       </x:c>
       <x:c r="E68" s="7" t="n">
-        <x:v>335</x:v>
+        <x:v>385</x:v>
       </x:c>
     </x:row>
     <x:row r="69" ht="15" hidden="0" customHeight="1">
@@ -1457,7 +1457,7 @@
         <x:v>245</x:v>
       </x:c>
       <x:c r="E69" s="7" t="n">
-        <x:v>385</x:v>
+        <x:v>535</x:v>
       </x:c>
     </x:row>
     <x:row r="70" ht="15" hidden="0" customHeight="1">
@@ -1471,10 +1471,10 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="D70" s="7" t="n">
-        <x:v>245</x:v>
+        <x:v>345</x:v>
       </x:c>
       <x:c r="E70" s="7" t="n">
-        <x:v>435</x:v>
+        <x:v>185</x:v>
       </x:c>
     </x:row>
     <x:row r="71" ht="15" hidden="0" customHeight="1">
@@ -1488,10 +1488,10 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="D71" s="7" t="n">
-        <x:v>245</x:v>
+        <x:v>345</x:v>
       </x:c>
       <x:c r="E71" s="7" t="n">
-        <x:v>485</x:v>
+        <x:v>135</x:v>
       </x:c>
     </x:row>
     <x:row r="72" ht="15" hidden="0" customHeight="1">
@@ -1508,7 +1508,7 @@
         <x:v>145</x:v>
       </x:c>
       <x:c r="E72" s="7" t="n">
-        <x:v>240</x:v>
+        <x:v>235</x:v>
       </x:c>
     </x:row>
     <x:row r="73" ht="15" hidden="0" customHeight="1">
@@ -1525,7 +1525,7 @@
         <x:v>195</x:v>
       </x:c>
       <x:c r="E73" s="7" t="n">
-        <x:v>240</x:v>
+        <x:v>235</x:v>
       </x:c>
     </x:row>
     <x:row r="74" ht="15" hidden="0" customHeight="1">
@@ -1542,7 +1542,7 @@
         <x:v>245</x:v>
       </x:c>
       <x:c r="E74" s="7" t="n">
-        <x:v>240</x:v>
+        <x:v>235</x:v>
       </x:c>
     </x:row>
     <x:row r="75" ht="15" hidden="0" customHeight="1">
@@ -1559,7 +1559,7 @@
         <x:v>295</x:v>
       </x:c>
       <x:c r="E75" s="7" t="n">
-        <x:v>240</x:v>
+        <x:v>235</x:v>
       </x:c>
     </x:row>
     <x:row r="76" ht="15" hidden="0" customHeight="1">
@@ -1573,10 +1573,10 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="D76" s="7" t="n">
-        <x:v>45</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="E76" s="7" t="n">
-        <x:v>250</x:v>
+        <x:v>335</x:v>
       </x:c>
     </x:row>
     <x:row r="77" ht="15" hidden="0" customHeight="1">
@@ -1590,10 +1590,10 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="D77" s="7" t="n">
-        <x:v>95</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="E77" s="7" t="n">
-        <x:v>240</x:v>
+        <x:v>335</x:v>
       </x:c>
     </x:row>
     <x:row r="78" ht="15" hidden="0" customHeight="1">
@@ -1607,10 +1607,10 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="D78" s="7" t="n">
-        <x:v>145</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="E78" s="7" t="n">
-        <x:v>350</x:v>
+        <x:v>335</x:v>
       </x:c>
     </x:row>
     <x:row r="79" ht="15" hidden="0" customHeight="1">
@@ -1624,10 +1624,10 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="D79" s="7" t="n">
-        <x:v>195</x:v>
+        <x:v>245</x:v>
       </x:c>
       <x:c r="E79" s="7" t="n">
-        <x:v>350</x:v>
+        <x:v>335</x:v>
       </x:c>
     </x:row>
     <x:row r="80" ht="15" hidden="0" customHeight="1">
@@ -1641,10 +1641,10 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="D80" s="7" t="n">
-        <x:v>245</x:v>
+        <x:v>295</x:v>
       </x:c>
       <x:c r="E80" s="7" t="n">
-        <x:v>350</x:v>
+        <x:v>335</x:v>
       </x:c>
     </x:row>
     <x:row r="81" ht="15" hidden="0" customHeight="1">
@@ -1658,10 +1658,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D81" s="7" t="n">
-        <x:v>295</x:v>
+        <x:v>345</x:v>
       </x:c>
       <x:c r="E81" s="7" t="n">
-        <x:v>350</x:v>
+        <x:v>335</x:v>
       </x:c>
     </x:row>
     <x:row r="82" ht="15" hidden="0" customHeight="1">
@@ -1678,7 +1678,7 @@
         <x:v>95</x:v>
       </x:c>
       <x:c r="E82" s="7" t="n">
-        <x:v>350</x:v>
+        <x:v>435</x:v>
       </x:c>
     </x:row>
     <x:row r="83" ht="15" hidden="0" customHeight="1">
@@ -1695,7 +1695,7 @@
         <x:v>145</x:v>
       </x:c>
       <x:c r="E83" s="7" t="n">
-        <x:v>450</x:v>
+        <x:v>435</x:v>
       </x:c>
     </x:row>
     <x:row r="84" ht="15" hidden="0" customHeight="1">
@@ -1712,7 +1712,7 @@
         <x:v>195</x:v>
       </x:c>
       <x:c r="E84" s="7" t="n">
-        <x:v>450</x:v>
+        <x:v>435</x:v>
       </x:c>
     </x:row>
     <x:row r="85" ht="15" hidden="0" customHeight="1">
@@ -1729,7 +1729,7 @@
         <x:v>345</x:v>
       </x:c>
       <x:c r="E85" s="7" t="n">
-        <x:v>350</x:v>
+        <x:v>385</x:v>
       </x:c>
     </x:row>
     <x:row r="86" ht="15" hidden="0" customHeight="1">
@@ -1746,7 +1746,7 @@
         <x:v>345</x:v>
       </x:c>
       <x:c r="E86" s="7" t="n">
-        <x:v>400</x:v>
+        <x:v>435</x:v>
       </x:c>
     </x:row>
     <x:row r="87" ht="15" hidden="0" customHeight="1">
@@ -1760,10 +1760,10 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="D87" s="7" t="n">
-        <x:v>35</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="E87" s="7" t="n">
-        <x:v>445</x:v>
+        <x:v>435</x:v>
       </x:c>
     </x:row>
     <x:row r="88" ht="15" hidden="0" customHeight="1">
@@ -1777,10 +1777,10 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="D88" s="7" t="n">
-        <x:v>95</x:v>
+        <x:v>245</x:v>
       </x:c>
       <x:c r="E88" s="7" t="n">
-        <x:v>450</x:v>
+        <x:v>435</x:v>
       </x:c>
     </x:row>
     <x:row r="89" ht="15" hidden="0" customHeight="1">
@@ -1794,10 +1794,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="D89" s="7" t="n">
-        <x:v>225</x:v>
+        <x:v>245</x:v>
       </x:c>
       <x:c r="E89" s="7" t="n">
-        <x:v>495</x:v>
+        <x:v>485</x:v>
       </x:c>
     </x:row>
     <x:row r="90" ht="15" hidden="0" customHeight="1">
@@ -1811,10 +1811,10 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="D90" s="7" t="n">
-        <x:v>225</x:v>
+        <x:v>245</x:v>
       </x:c>
       <x:c r="E90" s="7" t="n">
-        <x:v>545</x:v>
+        <x:v>535</x:v>
       </x:c>
     </x:row>
     <x:row r="91" ht="15" hidden="0" customHeight="1">
@@ -1831,7 +1831,7 @@
         <x:v>345</x:v>
       </x:c>
       <x:c r="E91" s="7" t="n">
-        <x:v>450</x:v>
+        <x:v>135</x:v>
       </x:c>
     </x:row>
     <x:row r="92" ht="15" hidden="0" customHeight="1">
@@ -1845,10 +1845,10 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="D92" s="7" t="n">
-        <x:v>275</x:v>
+        <x:v>295</x:v>
       </x:c>
       <x:c r="E92" s="7" t="n">
-        <x:v>565</x:v>
+        <x:v>135</x:v>
       </x:c>
     </x:row>
     <x:row r="93" ht="15" hidden="0" customHeight="1">
@@ -1862,10 +1862,10 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="D93" s="7" t="n">
-        <x:v>240</x:v>
+        <x:v>245</x:v>
       </x:c>
       <x:c r="E93" s="7" t="n">
-        <x:v>130</x:v>
+        <x:v>135</x:v>
       </x:c>
     </x:row>
     <x:row r="94" ht="15" hidden="0" customHeight="1">
@@ -2151,7 +2151,7 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="D110" s="7" t="n">
-        <x:v>45</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="E110" s="7" t="n">
         <x:v>485</x:v>
@@ -2168,7 +2168,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="D111" s="7" t="n">
-        <x:v>95</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="E111" s="7" t="n">
         <x:v>485</x:v>
@@ -2185,7 +2185,7 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="D112" s="7" t="n">
-        <x:v>145</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="E112" s="7" t="n">
         <x:v>485</x:v>
@@ -2202,7 +2202,7 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="D113" s="7" t="n">
-        <x:v>195</x:v>
+        <x:v>245</x:v>
       </x:c>
       <x:c r="E113" s="7" t="n">
         <x:v>485</x:v>
@@ -2222,7 +2222,7 @@
         <x:v>245</x:v>
       </x:c>
       <x:c r="E114" s="7" t="n">
-        <x:v>485</x:v>
+        <x:v>535</x:v>
       </x:c>
     </x:row>
     <x:row r="115" ht="15" hidden="0" customHeight="1">
@@ -2236,10 +2236,10 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="D115" s="7" t="n">
-        <x:v>245</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="E115" s="7" t="n">
-        <x:v>535</x:v>
+        <x:v>135</x:v>
       </x:c>
     </x:row>
     <x:row r="116" ht="15" hidden="0" customHeight="1">
@@ -2256,7 +2256,7 @@
         <x:v>95</x:v>
       </x:c>
       <x:c r="E116" s="7" t="n">
-        <x:v>250</x:v>
+        <x:v>235</x:v>
       </x:c>
     </x:row>
     <x:row r="117" ht="15" hidden="0" customHeight="1">
@@ -2273,7 +2273,7 @@
         <x:v>145</x:v>
       </x:c>
       <x:c r="E117" s="7" t="n">
-        <x:v>250</x:v>
+        <x:v>235</x:v>
       </x:c>
     </x:row>
     <x:row r="118" ht="15" hidden="0" customHeight="1">
@@ -2290,7 +2290,7 @@
         <x:v>195</x:v>
       </x:c>
       <x:c r="E118" s="7" t="n">
-        <x:v>250</x:v>
+        <x:v>235</x:v>
       </x:c>
     </x:row>
     <x:row r="119" ht="15" hidden="0" customHeight="1">
@@ -2307,7 +2307,7 @@
         <x:v>245</x:v>
       </x:c>
       <x:c r="E119" s="7" t="n">
-        <x:v>250</x:v>
+        <x:v>235</x:v>
       </x:c>
     </x:row>
     <x:row r="120" ht="15" hidden="0" customHeight="1">
@@ -2324,7 +2324,7 @@
         <x:v>295</x:v>
       </x:c>
       <x:c r="E120" s="7" t="n">
-        <x:v>250</x:v>
+        <x:v>235</x:v>
       </x:c>
     </x:row>
     <x:row r="121" ht="15" hidden="0" customHeight="1">
@@ -2341,7 +2341,7 @@
         <x:v>345</x:v>
       </x:c>
       <x:c r="E121" s="7" t="n">
-        <x:v>250</x:v>
+        <x:v>235</x:v>
       </x:c>
     </x:row>
     <x:row r="122" ht="15" hidden="0" customHeight="1">
@@ -2358,7 +2358,7 @@
         <x:v>95</x:v>
       </x:c>
       <x:c r="E122" s="7" t="n">
-        <x:v>360</x:v>
+        <x:v>335</x:v>
       </x:c>
     </x:row>
     <x:row r="123" ht="15" hidden="0" customHeight="1">
@@ -2375,7 +2375,7 @@
         <x:v>145</x:v>
       </x:c>
       <x:c r="E123" s="7" t="n">
-        <x:v>360</x:v>
+        <x:v>335</x:v>
       </x:c>
     </x:row>
     <x:row r="124" ht="15" hidden="0" customHeight="1">
@@ -2392,7 +2392,7 @@
         <x:v>195</x:v>
       </x:c>
       <x:c r="E124" s="7" t="n">
-        <x:v>360</x:v>
+        <x:v>335</x:v>
       </x:c>
     </x:row>
     <x:row r="125" ht="15" hidden="0" customHeight="1">
@@ -2409,7 +2409,7 @@
         <x:v>245</x:v>
       </x:c>
       <x:c r="E125" s="7" t="n">
-        <x:v>360</x:v>
+        <x:v>335</x:v>
       </x:c>
     </x:row>
     <x:row r="126" ht="15" hidden="0" customHeight="1">
@@ -2426,7 +2426,7 @@
         <x:v>295</x:v>
       </x:c>
       <x:c r="E126" s="7" t="n">
-        <x:v>360</x:v>
+        <x:v>335</x:v>
       </x:c>
     </x:row>
     <x:row r="127" ht="15" hidden="0" customHeight="1">
@@ -2443,7 +2443,7 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="E127" s="7" t="n">
-        <x:v>370</x:v>
+        <x:v>335</x:v>
       </x:c>
     </x:row>
     <x:row r="128" ht="15" hidden="0" customHeight="1">
@@ -2460,7 +2460,7 @@
         <x:v>145</x:v>
       </x:c>
       <x:c r="E128" s="7" t="n">
-        <x:v>470</x:v>
+        <x:v>435</x:v>
       </x:c>
     </x:row>
     <x:row r="129" ht="15" hidden="0" customHeight="1">
@@ -2477,7 +2477,7 @@
         <x:v>195</x:v>
       </x:c>
       <x:c r="E129" s="7" t="n">
-        <x:v>470</x:v>
+        <x:v>435</x:v>
       </x:c>
     </x:row>
     <x:row r="130" ht="15" hidden="0" customHeight="1">
@@ -2494,7 +2494,7 @@
         <x:v>245</x:v>
       </x:c>
       <x:c r="E130" s="7" t="n">
-        <x:v>470</x:v>
+        <x:v>435</x:v>
       </x:c>
     </x:row>
     <x:row r="131" ht="15" hidden="0" customHeight="1">
@@ -2508,10 +2508,10 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="D131" s="7" t="n">
-        <x:v>295</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="E131" s="7" t="n">
-        <x:v>470</x:v>
+        <x:v>535</x:v>
       </x:c>
     </x:row>
     <x:row r="132" ht="15" hidden="0" customHeight="1">
@@ -2528,7 +2528,7 @@
         <x:v>95</x:v>
       </x:c>
       <x:c r="E132" s="7" t="n">
-        <x:v>470</x:v>
+        <x:v>435</x:v>
       </x:c>
     </x:row>
     <x:row r="133" ht="15" hidden="0" customHeight="1">
@@ -2545,7 +2545,7 @@
         <x:v>145</x:v>
       </x:c>
       <x:c r="E133" s="7" t="n">
-        <x:v>570</x:v>
+        <x:v>535</x:v>
       </x:c>
     </x:row>
     <x:row r="134" ht="15" hidden="0" customHeight="1">
@@ -2559,10 +2559,10 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="D134" s="7" t="n">
-        <x:v>195</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="E134" s="7" t="n">
-        <x:v>570</x:v>
+        <x:v>535</x:v>
       </x:c>
     </x:row>
     <x:row r="135" ht="15" hidden="0" customHeight="1">
@@ -2576,10 +2576,10 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="D135" s="7" t="n">
-        <x:v>245</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="E135" s="7" t="n">
-        <x:v>570</x:v>
+        <x:v>535</x:v>
       </x:c>
     </x:row>
     <x:row r="136" ht="15" hidden="0" customHeight="1">
@@ -2593,10 +2593,10 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="D136" s="7" t="n">
-        <x:v>295</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="E136" s="7" t="n">
-        <x:v>570</x:v>
+        <x:v>135</x:v>
       </x:c>
     </x:row>
     <x:row r="137" ht="15" hidden="0" customHeight="1">
@@ -2610,10 +2610,10 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="D137" s="7" t="n">
-        <x:v>95</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="E137" s="7" t="n">
-        <x:v>570</x:v>
+        <x:v>135</x:v>
       </x:c>
     </x:row>
     <x:row r="138" ht="15" hidden="0" customHeight="1">
@@ -2630,7 +2630,7 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="E138" s="7" t="n">
-        <x:v>200</x:v>
+        <x:v>185</x:v>
       </x:c>
     </x:row>
     <x:row r="139" ht="15" hidden="0" customHeight="1">
@@ -2647,7 +2647,7 @@
         <x:v>95</x:v>
       </x:c>
       <x:c r="E139" s="7" t="n">
-        <x:v>200</x:v>
+        <x:v>185</x:v>
       </x:c>
     </x:row>
     <x:row r="140" ht="15" hidden="0" customHeight="1">
@@ -2664,7 +2664,7 @@
         <x:v>145</x:v>
       </x:c>
       <x:c r="E140" s="7" t="n">
-        <x:v>200</x:v>
+        <x:v>185</x:v>
       </x:c>
     </x:row>
     <x:row r="141" ht="15" hidden="0" customHeight="1">
@@ -2681,7 +2681,7 @@
         <x:v>195</x:v>
       </x:c>
       <x:c r="E141" s="7" t="n">
-        <x:v>200</x:v>
+        <x:v>185</x:v>
       </x:c>
     </x:row>
     <x:row r="142" ht="15" hidden="0" customHeight="1">
@@ -2698,7 +2698,7 @@
         <x:v>245</x:v>
       </x:c>
       <x:c r="E142" s="7" t="n">
-        <x:v>200</x:v>
+        <x:v>185</x:v>
       </x:c>
     </x:row>
     <x:row r="143" ht="15" hidden="0" customHeight="1">
@@ -2715,7 +2715,7 @@
         <x:v>95</x:v>
       </x:c>
       <x:c r="E143" s="7" t="n">
-        <x:v>310</x:v>
+        <x:v>285</x:v>
       </x:c>
     </x:row>
     <x:row r="144" ht="15" hidden="0" customHeight="1">
@@ -2732,7 +2732,7 @@
         <x:v>145</x:v>
       </x:c>
       <x:c r="E144" s="7" t="n">
-        <x:v>310</x:v>
+        <x:v>285</x:v>
       </x:c>
     </x:row>
     <x:row r="145" ht="15" hidden="0" customHeight="1">
@@ -2749,7 +2749,7 @@
         <x:v>195</x:v>
       </x:c>
       <x:c r="E145" s="7" t="n">
-        <x:v>310</x:v>
+        <x:v>285</x:v>
       </x:c>
     </x:row>
     <x:row r="146" ht="15" hidden="0" customHeight="1">
@@ -2766,7 +2766,7 @@
         <x:v>245</x:v>
       </x:c>
       <x:c r="E146" s="7" t="n">
-        <x:v>310</x:v>
+        <x:v>285</x:v>
       </x:c>
     </x:row>
     <x:row r="147" ht="15" hidden="0" customHeight="1">
@@ -2783,7 +2783,7 @@
         <x:v>95</x:v>
       </x:c>
       <x:c r="E147" s="7" t="n">
-        <x:v>420</x:v>
+        <x:v>435</x:v>
       </x:c>
     </x:row>
     <x:row r="148" ht="15" hidden="0" customHeight="1">
@@ -2800,7 +2800,7 @@
         <x:v>145</x:v>
       </x:c>
       <x:c r="E148" s="7" t="n">
-        <x:v>420</x:v>
+        <x:v>385</x:v>
       </x:c>
     </x:row>
     <x:row r="149" ht="15" hidden="0" customHeight="1">
@@ -2817,7 +2817,7 @@
         <x:v>195</x:v>
       </x:c>
       <x:c r="E149" s="7" t="n">
-        <x:v>420</x:v>
+        <x:v>385</x:v>
       </x:c>
     </x:row>
     <x:row r="150" ht="15" hidden="0" customHeight="1">
@@ -2834,7 +2834,7 @@
         <x:v>295</x:v>
       </x:c>
       <x:c r="E150" s="7" t="n">
-        <x:v>320</x:v>
+        <x:v>285</x:v>
       </x:c>
     </x:row>
     <x:row r="151" ht="15" hidden="0" customHeight="1">
@@ -2848,10 +2848,10 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="D151" s="7" t="n">
-        <x:v>45</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="E151" s="7" t="n">
-        <x:v>420</x:v>
+        <x:v>385</x:v>
       </x:c>
     </x:row>
     <x:row r="152" ht="15" hidden="0" customHeight="1">
@@ -2865,10 +2865,10 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="D152" s="7" t="n">
-        <x:v>95</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="E152" s="7" t="n">
-        <x:v>470</x:v>
+        <x:v>485</x:v>
       </x:c>
     </x:row>
     <x:row r="153" ht="15" hidden="0" customHeight="1">
@@ -2885,7 +2885,7 @@
         <x:v>245</x:v>
       </x:c>
       <x:c r="E153" s="7" t="n">
-        <x:v>420</x:v>
+        <x:v>385</x:v>
       </x:c>
     </x:row>
     <x:row r="154" ht="15" hidden="0" customHeight="1">
@@ -2902,7 +2902,7 @@
         <x:v>295</x:v>
       </x:c>
       <x:c r="E154" s="7" t="n">
-        <x:v>420</x:v>
+        <x:v>385</x:v>
       </x:c>
     </x:row>
     <x:row r="155" ht="15" hidden="0" customHeight="1">
@@ -2919,7 +2919,7 @@
         <x:v>295</x:v>
       </x:c>
       <x:c r="E155" s="7" t="n">
-        <x:v>520</x:v>
+        <x:v>485</x:v>
       </x:c>
     </x:row>
     <x:row r="156" ht="15" hidden="0" customHeight="1">
@@ -2936,7 +2936,7 @@
         <x:v>195</x:v>
       </x:c>
       <x:c r="E156" s="7" t="n">
-        <x:v>520</x:v>
+        <x:v>535</x:v>
       </x:c>
     </x:row>
     <x:row r="157" ht="15" hidden="0" customHeight="1">
@@ -2953,7 +2953,7 @@
         <x:v>245</x:v>
       </x:c>
       <x:c r="E157" s="7" t="n">
-        <x:v>520</x:v>
+        <x:v>485</x:v>
       </x:c>
     </x:row>
     <x:row r="158" ht="15" hidden="0" customHeight="1">
@@ -2970,7 +2970,7 @@
         <x:v>345</x:v>
       </x:c>
       <x:c r="E158" s="7" t="n">
-        <x:v>520</x:v>
+        <x:v>285</x:v>
       </x:c>
     </x:row>
     <x:row r="159" ht="15" hidden="0" customHeight="1">
@@ -2984,10 +2984,10 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="D159" s="7" t="n">
-        <x:v>215</x:v>
+        <x:v>245</x:v>
       </x:c>
       <x:c r="E159" s="7" t="n">
-        <x:v>575</x:v>
+        <x:v>135</x:v>
       </x:c>
     </x:row>
     <x:row r="160" ht="15" hidden="0" customHeight="1">
@@ -3004,7 +3004,7 @@
         <x:v>195</x:v>
       </x:c>
       <x:c r="E160" s="7" t="n">
-        <x:v>150</x:v>
+        <x:v>235</x:v>
       </x:c>
     </x:row>
     <x:row r="161" ht="15" hidden="0" customHeight="1">
@@ -3018,10 +3018,10 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="D161" s="7" t="n">
-        <x:v>245</x:v>
+        <x:v>295</x:v>
       </x:c>
       <x:c r="E161" s="7" t="n">
-        <x:v>150</x:v>
+        <x:v>135</x:v>
       </x:c>
     </x:row>
     <x:row r="162" ht="15" hidden="0" customHeight="1">
@@ -3035,10 +3035,10 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="D162" s="7" t="n">
-        <x:v>295</x:v>
+        <x:v>345</x:v>
       </x:c>
       <x:c r="E162" s="7" t="n">
-        <x:v>150</x:v>
+        <x:v>135</x:v>
       </x:c>
     </x:row>
     <x:row r="163" ht="15" hidden="0" customHeight="1">
@@ -3052,10 +3052,10 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="D163" s="7" t="n">
-        <x:v>345</x:v>
+        <x:v>295</x:v>
       </x:c>
       <x:c r="E163" s="7" t="n">
-        <x:v>150</x:v>
+        <x:v>235</x:v>
       </x:c>
     </x:row>
     <x:row r="164" ht="15" hidden="0" customHeight="1">
@@ -3072,7 +3072,7 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="E164" s="7" t="n">
-        <x:v>250</x:v>
+        <x:v>235</x:v>
       </x:c>
     </x:row>
     <x:row r="165" ht="15" hidden="0" customHeight="1">
@@ -3089,7 +3089,7 @@
         <x:v>95</x:v>
       </x:c>
       <x:c r="E165" s="7" t="n">
-        <x:v>250</x:v>
+        <x:v>235</x:v>
       </x:c>
     </x:row>
     <x:row r="166" ht="15" hidden="0" customHeight="1">
@@ -3106,7 +3106,7 @@
         <x:v>145</x:v>
       </x:c>
       <x:c r="E166" s="7" t="n">
-        <x:v>250</x:v>
+        <x:v>235</x:v>
       </x:c>
     </x:row>
     <x:row r="167" ht="15" hidden="0" customHeight="1">
@@ -3120,10 +3120,10 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="D167" s="7" t="n">
-        <x:v>195</x:v>
+        <x:v>245</x:v>
       </x:c>
       <x:c r="E167" s="7" t="n">
-        <x:v>250</x:v>
+        <x:v>235</x:v>
       </x:c>
     </x:row>
     <x:row r="168" ht="15" hidden="0" customHeight="1">
@@ -3140,7 +3140,7 @@
         <x:v>245</x:v>
       </x:c>
       <x:c r="E168" s="7" t="n">
-        <x:v>250</x:v>
+        <x:v>335</x:v>
       </x:c>
     </x:row>
     <x:row r="169" ht="15" hidden="0" customHeight="1">
@@ -3157,7 +3157,7 @@
         <x:v>95</x:v>
       </x:c>
       <x:c r="E169" s="7" t="n">
-        <x:v>360</x:v>
+        <x:v>335</x:v>
       </x:c>
     </x:row>
     <x:row r="170" ht="15" hidden="0" customHeight="1">
@@ -3174,7 +3174,7 @@
         <x:v>145</x:v>
       </x:c>
       <x:c r="E170" s="7" t="n">
-        <x:v>360</x:v>
+        <x:v>335</x:v>
       </x:c>
     </x:row>
     <x:row r="171" ht="15" hidden="0" customHeight="1">
@@ -3191,7 +3191,7 @@
         <x:v>195</x:v>
       </x:c>
       <x:c r="E171" s="7" t="n">
-        <x:v>360</x:v>
+        <x:v>335</x:v>
       </x:c>
     </x:row>
     <x:row r="172" ht="15" hidden="0" customHeight="1">
@@ -3205,10 +3205,10 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="D172" s="7" t="n">
-        <x:v>245</x:v>
+        <x:v>295</x:v>
       </x:c>
       <x:c r="E172" s="7" t="n">
-        <x:v>360</x:v>
+        <x:v>335</x:v>
       </x:c>
     </x:row>
     <x:row r="173" ht="15" hidden="0" customHeight="1">
@@ -3222,10 +3222,10 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="D173" s="7" t="n">
-        <x:v>295</x:v>
+        <x:v>345</x:v>
       </x:c>
       <x:c r="E173" s="7" t="n">
-        <x:v>350</x:v>
+        <x:v>335</x:v>
       </x:c>
     </x:row>
     <x:row r="174" ht="15" hidden="0" customHeight="1">
@@ -3242,7 +3242,7 @@
         <x:v>95</x:v>
       </x:c>
       <x:c r="E174" s="7" t="n">
-        <x:v>470</x:v>
+        <x:v>435</x:v>
       </x:c>
     </x:row>
     <x:row r="175" ht="15" hidden="0" customHeight="1">
@@ -3259,7 +3259,7 @@
         <x:v>145</x:v>
       </x:c>
       <x:c r="E175" s="7" t="n">
-        <x:v>470</x:v>
+        <x:v>435</x:v>
       </x:c>
     </x:row>
     <x:row r="176" ht="15" hidden="0" customHeight="1">
@@ -3276,7 +3276,7 @@
         <x:v>195</x:v>
       </x:c>
       <x:c r="E176" s="7" t="n">
-        <x:v>470</x:v>
+        <x:v>435</x:v>
       </x:c>
     </x:row>
     <x:row r="177" ht="15" hidden="0" customHeight="1">
@@ -3290,10 +3290,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="D177" s="7" t="n">
-        <x:v>45</x:v>
+        <x:v>245</x:v>
       </x:c>
       <x:c r="E177" s="7" t="n">
-        <x:v>470</x:v>
+        <x:v>485</x:v>
       </x:c>
     </x:row>
     <x:row r="178" ht="15" hidden="0" customHeight="1">
@@ -3307,10 +3307,10 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="D178" s="7" t="n">
-        <x:v>225</x:v>
+        <x:v>245</x:v>
       </x:c>
       <x:c r="E178" s="7" t="n">
-        <x:v>515</x:v>
+        <x:v>535</x:v>
       </x:c>
     </x:row>
     <x:row r="179" ht="15" hidden="0" customHeight="1">
@@ -3324,10 +3324,10 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="D179" s="7" t="n">
-        <x:v>225</x:v>
+        <x:v>245</x:v>
       </x:c>
       <x:c r="E179" s="7" t="n">
-        <x:v>565</x:v>
+        <x:v>435</x:v>
       </x:c>
     </x:row>
     <x:row r="180" ht="15" hidden="0" customHeight="1">
@@ -3344,7 +3344,7 @@
         <x:v>345</x:v>
       </x:c>
       <x:c r="E180" s="7" t="n">
-        <x:v>470</x:v>
+        <x:v>435</x:v>
       </x:c>
     </x:row>
     <x:row r="181" ht="15" hidden="0" customHeight="1">
@@ -3361,7 +3361,7 @@
         <x:v>345</x:v>
       </x:c>
       <x:c r="E181" s="7" t="n">
-        <x:v>420</x:v>
+        <x:v>385</x:v>
       </x:c>
     </x:row>
     <x:row r="182" ht="15" hidden="0" customHeight="1">
@@ -3723,152 +3723,152 @@
     </x:row>
     <x:row r="203" ht="15" hidden="0" customHeight="1">
       <x:c r="A203" s="7" t="n">
-        <x:v>922</x:v>
+        <x:v>1001</x:v>
       </x:c>
       <x:c r="B203" s="7" t="n">
-        <x:v>9</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C203" s="7" t="n">
-        <x:v>21</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D203" s="7" t="n">
-        <x:v>295</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="E203" s="7" t="n">
-        <x:v>520</x:v>
+        <x:v>235</x:v>
       </x:c>
     </x:row>
     <x:row r="204" ht="15" hidden="0" customHeight="1">
       <x:c r="A204" s="7" t="n">
-        <x:v>1001</x:v>
+        <x:v>1002</x:v>
       </x:c>
       <x:c r="B204" s="7" t="n">
         <x:v>10</x:v>
       </x:c>
       <x:c r="C204" s="7" t="n">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="D204" s="7" t="n">
-        <x:v>145</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="E204" s="7" t="n">
-        <x:v>225</x:v>
+        <x:v>235</x:v>
       </x:c>
     </x:row>
     <x:row r="205" ht="15" hidden="0" customHeight="1">
       <x:c r="A205" s="7" t="n">
-        <x:v>1002</x:v>
+        <x:v>1003</x:v>
       </x:c>
       <x:c r="B205" s="7" t="n">
         <x:v>10</x:v>
       </x:c>
       <x:c r="C205" s="7" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="D205" s="7" t="n">
-        <x:v>195</x:v>
+        <x:v>245</x:v>
       </x:c>
       <x:c r="E205" s="7" t="n">
-        <x:v>225</x:v>
+        <x:v>235</x:v>
       </x:c>
     </x:row>
     <x:row r="206" ht="15" hidden="0" customHeight="1">
       <x:c r="A206" s="7" t="n">
-        <x:v>1003</x:v>
+        <x:v>1004</x:v>
       </x:c>
       <x:c r="B206" s="7" t="n">
         <x:v>10</x:v>
       </x:c>
       <x:c r="C206" s="7" t="n">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="D206" s="7" t="n">
-        <x:v>245</x:v>
+        <x:v>295</x:v>
       </x:c>
       <x:c r="E206" s="7" t="n">
-        <x:v>225</x:v>
+        <x:v>235</x:v>
       </x:c>
     </x:row>
     <x:row r="207" ht="15" hidden="0" customHeight="1">
       <x:c r="A207" s="7" t="n">
-        <x:v>1004</x:v>
+        <x:v>1005</x:v>
       </x:c>
       <x:c r="B207" s="7" t="n">
         <x:v>10</x:v>
       </x:c>
       <x:c r="C207" s="7" t="n">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="D207" s="7" t="n">
-        <x:v>295</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="E207" s="7" t="n">
-        <x:v>225</x:v>
+        <x:v>335</x:v>
       </x:c>
     </x:row>
     <x:row r="208" ht="15" hidden="0" customHeight="1">
       <x:c r="A208" s="7" t="n">
-        <x:v>1005</x:v>
+        <x:v>1006</x:v>
       </x:c>
       <x:c r="B208" s="7" t="n">
         <x:v>10</x:v>
       </x:c>
       <x:c r="C208" s="7" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D208" s="7" t="n">
-        <x:v>95</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="E208" s="7" t="n">
-        <x:v>225</x:v>
+        <x:v>335</x:v>
       </x:c>
     </x:row>
     <x:row r="209" ht="15" hidden="0" customHeight="1">
       <x:c r="A209" s="7" t="n">
-        <x:v>1006</x:v>
+        <x:v>1007</x:v>
       </x:c>
       <x:c r="B209" s="7" t="n">
         <x:v>10</x:v>
       </x:c>
       <x:c r="C209" s="7" t="n">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="D209" s="7" t="n">
-        <x:v>195</x:v>
+        <x:v>245</x:v>
       </x:c>
       <x:c r="E209" s="7" t="n">
-        <x:v>345</x:v>
+        <x:v>335</x:v>
       </x:c>
     </x:row>
     <x:row r="210" ht="15" hidden="0" customHeight="1">
       <x:c r="A210" s="7" t="n">
-        <x:v>1007</x:v>
+        <x:v>1008</x:v>
       </x:c>
       <x:c r="B210" s="7" t="n">
         <x:v>10</x:v>
       </x:c>
       <x:c r="C210" s="7" t="n">
-        <x:v>6</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="D210" s="7" t="n">
-        <x:v>245</x:v>
+        <x:v>295</x:v>
       </x:c>
       <x:c r="E210" s="7" t="n">
-        <x:v>345</x:v>
+        <x:v>335</x:v>
       </x:c>
     </x:row>
     <x:row r="211" ht="15" hidden="0" customHeight="1">
       <x:c r="A211" s="7" t="n">
-        <x:v>1008</x:v>
+        <x:v>1009</x:v>
       </x:c>
       <x:c r="B211" s="7" t="n">
         <x:v>10</x:v>
       </x:c>
       <x:c r="C211" s="7" t="n">
-        <x:v>7</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="D211" s="7" t="n">
-        <x:v>295</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="E211" s="7" t="n">
         <x:v>335</x:v>
@@ -3876,223 +3876,223 @@
     </x:row>
     <x:row r="212" ht="15" hidden="0" customHeight="1">
       <x:c r="A212" s="7" t="n">
-        <x:v>1009</x:v>
+        <x:v>1010</x:v>
       </x:c>
       <x:c r="B212" s="7" t="n">
         <x:v>10</x:v>
       </x:c>
       <x:c r="C212" s="7" t="n">
-        <x:v>8</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="D212" s="7" t="n">
-        <x:v>95</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="E212" s="7" t="n">
-        <x:v>345</x:v>
+        <x:v>435</x:v>
       </x:c>
     </x:row>
     <x:row r="213" ht="15" hidden="0" customHeight="1">
       <x:c r="A213" s="7" t="n">
-        <x:v>1010</x:v>
+        <x:v>1011</x:v>
       </x:c>
       <x:c r="B213" s="7" t="n">
         <x:v>10</x:v>
       </x:c>
       <x:c r="C213" s="7" t="n">
-        <x:v>9</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="D213" s="7" t="n">
-        <x:v>145</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="E213" s="7" t="n">
-        <x:v>345</x:v>
+        <x:v>435</x:v>
       </x:c>
     </x:row>
     <x:row r="214" ht="15" hidden="0" customHeight="1">
       <x:c r="A214" s="7" t="n">
-        <x:v>1011</x:v>
+        <x:v>1012</x:v>
       </x:c>
       <x:c r="B214" s="7" t="n">
         <x:v>10</x:v>
       </x:c>
       <x:c r="C214" s="7" t="n">
-        <x:v>10</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D214" s="7" t="n">
-        <x:v>195</x:v>
+        <x:v>345</x:v>
       </x:c>
       <x:c r="E214" s="7" t="n">
-        <x:v>455</x:v>
+        <x:v>385</x:v>
       </x:c>
     </x:row>
     <x:row r="215" ht="15" hidden="0" customHeight="1">
       <x:c r="A215" s="7" t="n">
-        <x:v>1012</x:v>
+        <x:v>1013</x:v>
       </x:c>
       <x:c r="B215" s="7" t="n">
         <x:v>10</x:v>
       </x:c>
       <x:c r="C215" s="7" t="n">
-        <x:v>11</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="D215" s="7" t="n">
-        <x:v>335</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="E215" s="7" t="n">
-        <x:v>365</x:v>
+        <x:v>435</x:v>
       </x:c>
     </x:row>
     <x:row r="216" ht="15" hidden="0" customHeight="1">
       <x:c r="A216" s="7" t="n">
-        <x:v>1013</x:v>
+        <x:v>1014</x:v>
       </x:c>
       <x:c r="B216" s="7" t="n">
         <x:v>10</x:v>
       </x:c>
       <x:c r="C216" s="7" t="n">
-        <x:v>12</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D216" s="7" t="n">
-        <x:v>95</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="E216" s="7" t="n">
-        <x:v>455</x:v>
+        <x:v>435</x:v>
       </x:c>
     </x:row>
     <x:row r="217" ht="15" hidden="0" customHeight="1">
       <x:c r="A217" s="7" t="n">
-        <x:v>1014</x:v>
+        <x:v>1015</x:v>
       </x:c>
       <x:c r="B217" s="7" t="n">
         <x:v>10</x:v>
       </x:c>
       <x:c r="C217" s="7" t="n">
-        <x:v>13</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="D217" s="7" t="n">
-        <x:v>145</x:v>
+        <x:v>245</x:v>
       </x:c>
       <x:c r="E217" s="7" t="n">
-        <x:v>455</x:v>
+        <x:v>435</x:v>
       </x:c>
     </x:row>
     <x:row r="218" ht="15" hidden="0" customHeight="1">
       <x:c r="A218" s="7" t="n">
-        <x:v>1015</x:v>
+        <x:v>1016</x:v>
       </x:c>
       <x:c r="B218" s="7" t="n">
         <x:v>10</x:v>
       </x:c>
       <x:c r="C218" s="7" t="n">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="D218" s="7" t="n">
-        <x:v>245</x:v>
+        <x:v>345</x:v>
       </x:c>
       <x:c r="E218" s="7" t="n">
-        <x:v>455</x:v>
+        <x:v>435</x:v>
       </x:c>
     </x:row>
     <x:row r="219" ht="15" hidden="0" customHeight="1">
       <x:c r="A219" s="7" t="n">
-        <x:v>1016</x:v>
+        <x:v>1017</x:v>
       </x:c>
       <x:c r="B219" s="7" t="n">
         <x:v>10</x:v>
       </x:c>
       <x:c r="C219" s="7" t="n">
-        <x:v>15</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="D219" s="7" t="n">
-        <x:v>345</x:v>
+        <x:v>245</x:v>
       </x:c>
       <x:c r="E219" s="7" t="n">
-        <x:v>415</x:v>
+        <x:v>485</x:v>
       </x:c>
     </x:row>
     <x:row r="220" ht="15" hidden="0" customHeight="1">
       <x:c r="A220" s="7" t="n">
-        <x:v>1017</x:v>
+        <x:v>1018</x:v>
       </x:c>
       <x:c r="B220" s="7" t="n">
         <x:v>10</x:v>
       </x:c>
       <x:c r="C220" s="7" t="n">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="D220" s="7" t="n">
-        <x:v>45</x:v>
+        <x:v>245</x:v>
       </x:c>
       <x:c r="E220" s="7" t="n">
-        <x:v>455</x:v>
+        <x:v>535</x:v>
       </x:c>
     </x:row>
     <x:row r="221" ht="15" hidden="0" customHeight="1">
       <x:c r="A221" s="7" t="n">
-        <x:v>1018</x:v>
+        <x:v>1019</x:v>
       </x:c>
       <x:c r="B221" s="7" t="n">
         <x:v>10</x:v>
       </x:c>
       <x:c r="C221" s="7" t="n">
-        <x:v>17</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="D221" s="7" t="n">
-        <x:v>225</x:v>
+        <x:v>345</x:v>
       </x:c>
       <x:c r="E221" s="7" t="n">
-        <x:v>505</x:v>
+        <x:v>335</x:v>
       </x:c>
     </x:row>
     <x:row r="222" ht="15" hidden="0" customHeight="1">
       <x:c r="A222" s="7" t="n">
-        <x:v>1019</x:v>
+        <x:v>1020</x:v>
       </x:c>
       <x:c r="B222" s="7" t="n">
         <x:v>10</x:v>
       </x:c>
       <x:c r="C222" s="7" t="n">
-        <x:v>18</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="D222" s="7" t="n">
-        <x:v>225</x:v>
+        <x:v>345</x:v>
       </x:c>
       <x:c r="E222" s="7" t="n">
-        <x:v>555</x:v>
+        <x:v>135</x:v>
       </x:c>
     </x:row>
     <x:row r="223" ht="15" hidden="0" customHeight="1">
       <x:c r="A223" s="7" t="n">
-        <x:v>1020</x:v>
+        <x:v>1021</x:v>
       </x:c>
       <x:c r="B223" s="7" t="n">
         <x:v>10</x:v>
       </x:c>
       <x:c r="C223" s="7" t="n">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="D223" s="7" t="n">
-        <x:v>345</x:v>
+        <x:v>245</x:v>
       </x:c>
       <x:c r="E223" s="7" t="n">
-        <x:v>465</x:v>
+        <x:v>135</x:v>
       </x:c>
     </x:row>
     <x:row r="224" ht="15" hidden="0" customHeight="1">
       <x:c r="A224" s="7" t="n">
-        <x:v>1021</x:v>
+        <x:v>1022</x:v>
       </x:c>
       <x:c r="B224" s="7" t="n">
         <x:v>10</x:v>
       </x:c>
       <x:c r="C224" s="7" t="n">
-        <x:v>20</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="D224" s="7" t="n">
-        <x:v>45</x:v>
+        <x:v>295</x:v>
       </x:c>
       <x:c r="E224" s="7" t="n">
-        <x:v>235</x:v>
+        <x:v>135</x:v>
       </x:c>
     </x:row>
     <x:row r="225" ht="15" hidden="0" customHeight="1">
@@ -4106,10 +4106,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D225" s="7" t="n">
-        <x:v>95</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="E225" s="7" t="n">
-        <x:v>225</x:v>
+        <x:v>235</x:v>
       </x:c>
     </x:row>
     <x:row r="226" ht="15" hidden="0" customHeight="1">
@@ -4123,10 +4123,10 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="D226" s="7" t="n">
-        <x:v>145</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="E226" s="7" t="n">
-        <x:v>225</x:v>
+        <x:v>235</x:v>
       </x:c>
     </x:row>
     <x:row r="227" ht="15" hidden="0" customHeight="1">
@@ -4140,10 +4140,10 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="D227" s="7" t="n">
-        <x:v>195</x:v>
+        <x:v>245</x:v>
       </x:c>
       <x:c r="E227" s="7" t="n">
-        <x:v>225</x:v>
+        <x:v>235</x:v>
       </x:c>
     </x:row>
     <x:row r="228" ht="15" hidden="0" customHeight="1">
@@ -4157,10 +4157,10 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="D228" s="7" t="n">
-        <x:v>245</x:v>
+        <x:v>295</x:v>
       </x:c>
       <x:c r="E228" s="7" t="n">
-        <x:v>225</x:v>
+        <x:v>235</x:v>
       </x:c>
     </x:row>
     <x:row r="229" ht="15" hidden="0" customHeight="1">
@@ -4177,7 +4177,7 @@
         <x:v>295</x:v>
       </x:c>
       <x:c r="E229" s="7" t="n">
-        <x:v>225</x:v>
+        <x:v>135</x:v>
       </x:c>
     </x:row>
     <x:row r="230" ht="15" hidden="0" customHeight="1">
@@ -4191,10 +4191,10 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="D230" s="7" t="n">
-        <x:v>45</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="E230" s="7" t="n">
-        <x:v>235</x:v>
+        <x:v>335</x:v>
       </x:c>
     </x:row>
     <x:row r="231" ht="15" hidden="0" customHeight="1">
@@ -4208,10 +4208,10 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="D231" s="7" t="n">
-        <x:v>95</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="E231" s="7" t="n">
-        <x:v>345</x:v>
+        <x:v>335</x:v>
       </x:c>
     </x:row>
     <x:row r="232" ht="15" hidden="0" customHeight="1">
@@ -4225,10 +4225,10 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="D232" s="7" t="n">
-        <x:v>145</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="E232" s="7" t="n">
-        <x:v>345</x:v>
+        <x:v>335</x:v>
       </x:c>
     </x:row>
     <x:row r="233" ht="15" hidden="0" customHeight="1">
@@ -4242,10 +4242,10 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="D233" s="7" t="n">
-        <x:v>195</x:v>
+        <x:v>245</x:v>
       </x:c>
       <x:c r="E233" s="7" t="n">
-        <x:v>345</x:v>
+        <x:v>335</x:v>
       </x:c>
     </x:row>
     <x:row r="234" ht="15" hidden="0" customHeight="1">
@@ -4259,10 +4259,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D234" s="7" t="n">
-        <x:v>245</x:v>
+        <x:v>295</x:v>
       </x:c>
       <x:c r="E234" s="7" t="n">
-        <x:v>345</x:v>
+        <x:v>335</x:v>
       </x:c>
     </x:row>
     <x:row r="235" ht="15" hidden="0" customHeight="1">
@@ -4276,7 +4276,7 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="D235" s="7" t="n">
-        <x:v>295</x:v>
+        <x:v>345</x:v>
       </x:c>
       <x:c r="E235" s="7" t="n">
         <x:v>335</x:v>
@@ -4296,7 +4296,7 @@
         <x:v>95</x:v>
       </x:c>
       <x:c r="E236" s="7" t="n">
-        <x:v>455</x:v>
+        <x:v>435</x:v>
       </x:c>
     </x:row>
     <x:row r="237" ht="15" hidden="0" customHeight="1">
@@ -4313,7 +4313,7 @@
         <x:v>145</x:v>
       </x:c>
       <x:c r="E237" s="7" t="n">
-        <x:v>455</x:v>
+        <x:v>435</x:v>
       </x:c>
     </x:row>
     <x:row r="238" ht="15" hidden="0" customHeight="1">
@@ -4330,7 +4330,7 @@
         <x:v>195</x:v>
       </x:c>
       <x:c r="E238" s="7" t="n">
-        <x:v>455</x:v>
+        <x:v>435</x:v>
       </x:c>
     </x:row>
     <x:row r="239" ht="15" hidden="0" customHeight="1">
@@ -4344,10 +4344,10 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="D239" s="7" t="n">
-        <x:v>335</x:v>
+        <x:v>345</x:v>
       </x:c>
       <x:c r="E239" s="7" t="n">
-        <x:v>365</x:v>
+        <x:v>385</x:v>
       </x:c>
     </x:row>
     <x:row r="240" ht="15" hidden="0" customHeight="1">
@@ -4364,7 +4364,7 @@
         <x:v>345</x:v>
       </x:c>
       <x:c r="E240" s="7" t="n">
-        <x:v>415</x:v>
+        <x:v>435</x:v>
       </x:c>
     </x:row>
     <x:row r="241" ht="15" hidden="0" customHeight="1">
@@ -4378,10 +4378,10 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="D241" s="7" t="n">
-        <x:v>345</x:v>
+        <x:v>245</x:v>
       </x:c>
       <x:c r="E241" s="7" t="n">
-        <x:v>465</x:v>
+        <x:v>485</x:v>
       </x:c>
     </x:row>
     <x:row r="242" ht="15" hidden="0" customHeight="1">
@@ -4398,7 +4398,7 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="E242" s="7" t="n">
-        <x:v>455</x:v>
+        <x:v>435</x:v>
       </x:c>
     </x:row>
     <x:row r="243" ht="15" hidden="0" customHeight="1">
@@ -4415,7 +4415,7 @@
         <x:v>245</x:v>
       </x:c>
       <x:c r="E243" s="7" t="n">
-        <x:v>455</x:v>
+        <x:v>435</x:v>
       </x:c>
     </x:row>
     <x:row r="244" ht="15" hidden="0" customHeight="1">
@@ -4429,10 +4429,10 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="D244" s="7" t="n">
-        <x:v>225</x:v>
+        <x:v>245</x:v>
       </x:c>
       <x:c r="E244" s="7" t="n">
-        <x:v>505</x:v>
+        <x:v>535</x:v>
       </x:c>
     </x:row>
     <x:row r="245" ht="15" hidden="0" customHeight="1">
@@ -4446,143 +4446,143 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="D245" s="7" t="n">
-        <x:v>225</x:v>
+        <x:v>245</x:v>
       </x:c>
       <x:c r="E245" s="7" t="n">
-        <x:v>555</x:v>
+        <x:v>135</x:v>
       </x:c>
     </x:row>
     <x:row r="246" ht="15" hidden="0" customHeight="1">
       <x:c r="A246" s="7" t="n">
-        <x:v>1201</x:v>
+        <x:v>1122</x:v>
       </x:c>
       <x:c r="B246" s="7" t="n">
-        <x:v>12</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C246" s="7" t="n">
-        <x:v>0</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="D246" s="7" t="n">
-        <x:v>185</x:v>
+        <x:v>345</x:v>
       </x:c>
       <x:c r="E246" s="7" t="n">
-        <x:v>125</x:v>
+        <x:v>135</x:v>
       </x:c>
     </x:row>
     <x:row r="247" ht="15" hidden="0" customHeight="1">
       <x:c r="A247" s="7" t="n">
-        <x:v>1202</x:v>
+        <x:v>1201</x:v>
       </x:c>
       <x:c r="B247" s="7" t="n">
         <x:v>12</x:v>
       </x:c>
       <x:c r="C247" s="7" t="n">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D247" s="7" t="n">
-        <x:v>155</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="E247" s="7" t="n">
-        <x:v>175</x:v>
+        <x:v>135</x:v>
       </x:c>
     </x:row>
     <x:row r="248" ht="15" hidden="0" customHeight="1">
       <x:c r="A248" s="7" t="n">
-        <x:v>1203</x:v>
+        <x:v>1202</x:v>
       </x:c>
       <x:c r="B248" s="7" t="n">
         <x:v>12</x:v>
       </x:c>
       <x:c r="C248" s="7" t="n">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="D248" s="7" t="n">
-        <x:v>170</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="E248" s="7" t="n">
-        <x:v>235</x:v>
+        <x:v>185</x:v>
       </x:c>
     </x:row>
     <x:row r="249" ht="15" hidden="0" customHeight="1">
       <x:c r="A249" s="7" t="n">
-        <x:v>1204</x:v>
+        <x:v>1203</x:v>
       </x:c>
       <x:c r="B249" s="7" t="n">
         <x:v>12</x:v>
       </x:c>
       <x:c r="C249" s="7" t="n">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="D249" s="7" t="n">
-        <x:v>280</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="E249" s="7" t="n">
-        <x:v>185</x:v>
+        <x:v>235</x:v>
       </x:c>
     </x:row>
     <x:row r="250" ht="15" hidden="0" customHeight="1">
       <x:c r="A250" s="7" t="n">
-        <x:v>1205</x:v>
+        <x:v>1204</x:v>
       </x:c>
       <x:c r="B250" s="7" t="n">
         <x:v>12</x:v>
       </x:c>
       <x:c r="C250" s="7" t="n">
-        <x:v>4</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="D250" s="7" t="n">
-        <x:v>170</x:v>
+        <x:v>245</x:v>
       </x:c>
       <x:c r="E250" s="7" t="n">
-        <x:v>285</x:v>
+        <x:v>185</x:v>
       </x:c>
     </x:row>
     <x:row r="251" ht="15" hidden="0" customHeight="1">
       <x:c r="A251" s="7" t="n">
-        <x:v>1206</x:v>
+        <x:v>1205</x:v>
       </x:c>
       <x:c r="B251" s="7" t="n">
         <x:v>12</x:v>
       </x:c>
       <x:c r="C251" s="7" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="D251" s="7" t="n">
-        <x:v>280</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="E251" s="7" t="n">
-        <x:v>235</x:v>
+        <x:v>285</x:v>
       </x:c>
     </x:row>
     <x:row r="252" ht="15" hidden="0" customHeight="1">
       <x:c r="A252" s="7" t="n">
-        <x:v>1207</x:v>
+        <x:v>1206</x:v>
       </x:c>
       <x:c r="B252" s="7" t="n">
         <x:v>12</x:v>
       </x:c>
       <x:c r="C252" s="7" t="n">
-        <x:v>6</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D252" s="7" t="n">
-        <x:v>280</x:v>
+        <x:v>245</x:v>
       </x:c>
       <x:c r="E252" s="7" t="n">
-        <x:v>285</x:v>
+        <x:v>235</x:v>
       </x:c>
     </x:row>
     <x:row r="253" ht="15" hidden="0" customHeight="1">
       <x:c r="A253" s="7" t="n">
-        <x:v>1208</x:v>
+        <x:v>1207</x:v>
       </x:c>
       <x:c r="B253" s="7" t="n">
         <x:v>12</x:v>
       </x:c>
       <x:c r="C253" s="7" t="n">
-        <x:v>7</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="D253" s="7" t="n">
-        <x:v>45</x:v>
+        <x:v>245</x:v>
       </x:c>
       <x:c r="E253" s="7" t="n">
         <x:v>285</x:v>
@@ -4590,16 +4590,16 @@
     </x:row>
     <x:row r="254" ht="15" hidden="0" customHeight="1">
       <x:c r="A254" s="7" t="n">
-        <x:v>1209</x:v>
+        <x:v>1208</x:v>
       </x:c>
       <x:c r="B254" s="7" t="n">
         <x:v>12</x:v>
       </x:c>
       <x:c r="C254" s="7" t="n">
-        <x:v>8</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="D254" s="7" t="n">
-        <x:v>170</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="E254" s="7" t="n">
         <x:v>335</x:v>
@@ -4607,84 +4607,84 @@
     </x:row>
     <x:row r="255" ht="15" hidden="0" customHeight="1">
       <x:c r="A255" s="7" t="n">
-        <x:v>1210</x:v>
+        <x:v>1209</x:v>
       </x:c>
       <x:c r="B255" s="7" t="n">
         <x:v>12</x:v>
       </x:c>
       <x:c r="C255" s="7" t="n">
-        <x:v>9</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="D255" s="7" t="n">
-        <x:v>280</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="E255" s="7" t="n">
-        <x:v>335</x:v>
+        <x:v>385</x:v>
       </x:c>
     </x:row>
     <x:row r="256" ht="15" hidden="0" customHeight="1">
       <x:c r="A256" s="7" t="n">
-        <x:v>1211</x:v>
+        <x:v>1210</x:v>
       </x:c>
       <x:c r="B256" s="7" t="n">
         <x:v>12</x:v>
       </x:c>
       <x:c r="C256" s="7" t="n">
-        <x:v>10</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="D256" s="7" t="n">
-        <x:v>280</x:v>
+        <x:v>245</x:v>
       </x:c>
       <x:c r="E256" s="7" t="n">
-        <x:v>385</x:v>
+        <x:v>335</x:v>
       </x:c>
     </x:row>
     <x:row r="257" ht="15" hidden="0" customHeight="1">
       <x:c r="A257" s="7" t="n">
-        <x:v>1212</x:v>
+        <x:v>1211</x:v>
       </x:c>
       <x:c r="B257" s="7" t="n">
         <x:v>12</x:v>
       </x:c>
       <x:c r="C257" s="7" t="n">
-        <x:v>11</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="D257" s="7" t="n">
-        <x:v>45</x:v>
+        <x:v>245</x:v>
       </x:c>
       <x:c r="E257" s="7" t="n">
-        <x:v>335</x:v>
+        <x:v>385</x:v>
       </x:c>
     </x:row>
     <x:row r="258" ht="15" hidden="0" customHeight="1">
       <x:c r="A258" s="7" t="n">
-        <x:v>1213</x:v>
+        <x:v>1212</x:v>
       </x:c>
       <x:c r="B258" s="7" t="n">
         <x:v>12</x:v>
       </x:c>
       <x:c r="C258" s="7" t="n">
-        <x:v>12</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D258" s="7" t="n">
-        <x:v>170</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="E258" s="7" t="n">
-        <x:v>385</x:v>
+        <x:v>435</x:v>
       </x:c>
     </x:row>
     <x:row r="259" ht="15" hidden="0" customHeight="1">
       <x:c r="A259" s="7" t="n">
-        <x:v>1214</x:v>
+        <x:v>1213</x:v>
       </x:c>
       <x:c r="B259" s="7" t="n">
         <x:v>12</x:v>
       </x:c>
       <x:c r="C259" s="7" t="n">
-        <x:v>13</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="D259" s="7" t="n">
-        <x:v>170</x:v>
+        <x:v>245</x:v>
       </x:c>
       <x:c r="E259" s="7" t="n">
         <x:v>435</x:v>
@@ -4692,645 +4692,645 @@
     </x:row>
     <x:row r="260" ht="15" hidden="0" customHeight="1">
       <x:c r="A260" s="7" t="n">
-        <x:v>1215</x:v>
+        <x:v>1214</x:v>
       </x:c>
       <x:c r="B260" s="7" t="n">
         <x:v>12</x:v>
       </x:c>
       <x:c r="C260" s="7" t="n">
-        <x:v>14</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D260" s="7" t="n">
-        <x:v>285</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="E260" s="7" t="n">
-        <x:v>475</x:v>
+        <x:v>485</x:v>
       </x:c>
     </x:row>
     <x:row r="261" ht="15" hidden="0" customHeight="1">
       <x:c r="A261" s="7" t="n">
-        <x:v>1216</x:v>
+        <x:v>1215</x:v>
       </x:c>
       <x:c r="B261" s="7" t="n">
         <x:v>12</x:v>
       </x:c>
       <x:c r="C261" s="7" t="n">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="D261" s="7" t="n">
-        <x:v>45</x:v>
+        <x:v>245</x:v>
       </x:c>
       <x:c r="E261" s="7" t="n">
-        <x:v>385</x:v>
+        <x:v>485</x:v>
       </x:c>
     </x:row>
     <x:row r="262" ht="15" hidden="0" customHeight="1">
       <x:c r="A262" s="7" t="n">
-        <x:v>1217</x:v>
+        <x:v>1216</x:v>
       </x:c>
       <x:c r="B262" s="7" t="n">
         <x:v>12</x:v>
       </x:c>
       <x:c r="C262" s="7" t="n">
-        <x:v>16</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="D262" s="7" t="n">
-        <x:v>60</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="E262" s="7" t="n">
-        <x:v>435</x:v>
+        <x:v>485</x:v>
       </x:c>
     </x:row>
     <x:row r="263" ht="15" hidden="0" customHeight="1">
       <x:c r="A263" s="7" t="n">
-        <x:v>1218</x:v>
+        <x:v>1217</x:v>
       </x:c>
       <x:c r="B263" s="7" t="n">
         <x:v>12</x:v>
       </x:c>
       <x:c r="C263" s="7" t="n">
-        <x:v>17</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="D263" s="7" t="n">
-        <x:v>170</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="E263" s="7" t="n">
-        <x:v>485</x:v>
+        <x:v>535</x:v>
       </x:c>
     </x:row>
     <x:row r="264" ht="15" hidden="0" customHeight="1">
       <x:c r="A264" s="7" t="n">
-        <x:v>1219</x:v>
+        <x:v>1218</x:v>
       </x:c>
       <x:c r="B264" s="7" t="n">
         <x:v>12</x:v>
       </x:c>
       <x:c r="C264" s="7" t="n">
-        <x:v>18</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="D264" s="7" t="n">
-        <x:v>325</x:v>
+        <x:v>245</x:v>
       </x:c>
       <x:c r="E264" s="7" t="n">
-        <x:v>505</x:v>
+        <x:v>535</x:v>
       </x:c>
     </x:row>
     <x:row r="265" ht="15" hidden="0" customHeight="1">
       <x:c r="A265" s="7" t="n">
-        <x:v>1220</x:v>
+        <x:v>1219</x:v>
       </x:c>
       <x:c r="B265" s="7" t="n">
         <x:v>12</x:v>
       </x:c>
       <x:c r="C265" s="7" t="n">
-        <x:v>19</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="D265" s="7" t="n">
-        <x:v>45</x:v>
+        <x:v>345</x:v>
       </x:c>
       <x:c r="E265" s="7" t="n">
-        <x:v>485</x:v>
+        <x:v>285</x:v>
       </x:c>
     </x:row>
     <x:row r="266" ht="15" hidden="0" customHeight="1">
       <x:c r="A266" s="7" t="n">
-        <x:v>1221</x:v>
+        <x:v>1220</x:v>
       </x:c>
       <x:c r="B266" s="7" t="n">
         <x:v>12</x:v>
       </x:c>
       <x:c r="C266" s="7" t="n">
-        <x:v>20</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="D266" s="7" t="n">
-        <x:v>60</x:v>
+        <x:v>345</x:v>
       </x:c>
       <x:c r="E266" s="7" t="n">
-        <x:v>535</x:v>
+        <x:v>235</x:v>
       </x:c>
     </x:row>
     <x:row r="267" ht="15" hidden="0" customHeight="1">
       <x:c r="A267" s="7" t="n">
-        <x:v>1222</x:v>
+        <x:v>1221</x:v>
       </x:c>
       <x:c r="B267" s="7" t="n">
         <x:v>12</x:v>
       </x:c>
       <x:c r="C267" s="7" t="n">
-        <x:v>21</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="D267" s="7" t="n">
-        <x:v>280</x:v>
+        <x:v>345</x:v>
       </x:c>
       <x:c r="E267" s="7" t="n">
-        <x:v>535</x:v>
+        <x:v>185</x:v>
       </x:c>
     </x:row>
     <x:row r="268" ht="15" hidden="0" customHeight="1">
       <x:c r="A268" s="7" t="n">
-        <x:v>1301</x:v>
+        <x:v>1222</x:v>
       </x:c>
       <x:c r="B268" s="7" t="n">
-        <x:v>13</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C268" s="7" t="n">
-        <x:v>0</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="D268" s="7" t="n">
-        <x:v>245</x:v>
+        <x:v>345</x:v>
       </x:c>
       <x:c r="E268" s="7" t="n">
-        <x:v>165</x:v>
+        <x:v>135</x:v>
       </x:c>
     </x:row>
     <x:row r="269" ht="15" hidden="0" customHeight="1">
       <x:c r="A269" s="7" t="n">
-        <x:v>1302</x:v>
+        <x:v>1301</x:v>
       </x:c>
       <x:c r="B269" s="7" t="n">
         <x:v>13</x:v>
       </x:c>
       <x:c r="C269" s="7" t="n">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D269" s="7" t="n">
         <x:v>245</x:v>
       </x:c>
       <x:c r="E269" s="7" t="n">
-        <x:v>215</x:v>
+        <x:v>185</x:v>
       </x:c>
     </x:row>
     <x:row r="270" ht="15" hidden="0" customHeight="1">
       <x:c r="A270" s="7" t="n">
-        <x:v>1303</x:v>
+        <x:v>1302</x:v>
       </x:c>
       <x:c r="B270" s="7" t="n">
         <x:v>13</x:v>
       </x:c>
       <x:c r="C270" s="7" t="n">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="D270" s="7" t="n">
-        <x:v>345</x:v>
+        <x:v>245</x:v>
       </x:c>
       <x:c r="E270" s="7" t="n">
-        <x:v>225</x:v>
+        <x:v>235</x:v>
       </x:c>
     </x:row>
     <x:row r="271" ht="15" hidden="0" customHeight="1">
       <x:c r="A271" s="7" t="n">
-        <x:v>1304</x:v>
+        <x:v>1303</x:v>
       </x:c>
       <x:c r="B271" s="7" t="n">
         <x:v>13</x:v>
       </x:c>
       <x:c r="C271" s="7" t="n">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="D271" s="7" t="n">
-        <x:v>95</x:v>
+        <x:v>295</x:v>
       </x:c>
       <x:c r="E271" s="7" t="n">
-        <x:v>230</x:v>
+        <x:v>335</x:v>
       </x:c>
     </x:row>
     <x:row r="272" ht="15" hidden="0" customHeight="1">
       <x:c r="A272" s="7" t="n">
-        <x:v>1305</x:v>
+        <x:v>1304</x:v>
       </x:c>
       <x:c r="B272" s="7" t="n">
         <x:v>13</x:v>
       </x:c>
       <x:c r="C272" s="7" t="n">
-        <x:v>4</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="D272" s="7" t="n">
-        <x:v>145</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="E272" s="7" t="n">
-        <x:v>230</x:v>
+        <x:v>235</x:v>
       </x:c>
     </x:row>
     <x:row r="273" ht="15" hidden="0" customHeight="1">
       <x:c r="A273" s="7" t="n">
-        <x:v>1306</x:v>
+        <x:v>1305</x:v>
       </x:c>
       <x:c r="B273" s="7" t="n">
         <x:v>13</x:v>
       </x:c>
       <x:c r="C273" s="7" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="D273" s="7" t="n">
-        <x:v>195</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="E273" s="7" t="n">
-        <x:v>230</x:v>
+        <x:v>235</x:v>
       </x:c>
     </x:row>
     <x:row r="274" ht="15" hidden="0" customHeight="1">
       <x:c r="A274" s="7" t="n">
-        <x:v>1307</x:v>
+        <x:v>1306</x:v>
       </x:c>
       <x:c r="B274" s="7" t="n">
         <x:v>13</x:v>
       </x:c>
       <x:c r="C274" s="7" t="n">
-        <x:v>6</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D274" s="7" t="n">
-        <x:v>245</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="E274" s="7" t="n">
-        <x:v>340</x:v>
+        <x:v>235</x:v>
       </x:c>
     </x:row>
     <x:row r="275" ht="15" hidden="0" customHeight="1">
       <x:c r="A275" s="7" t="n">
-        <x:v>1308</x:v>
+        <x:v>1307</x:v>
       </x:c>
       <x:c r="B275" s="7" t="n">
         <x:v>13</x:v>
       </x:c>
       <x:c r="C275" s="7" t="n">
-        <x:v>7</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="D275" s="7" t="n">
-        <x:v>345</x:v>
+        <x:v>245</x:v>
       </x:c>
       <x:c r="E275" s="7" t="n">
-        <x:v>275</x:v>
+        <x:v>335</x:v>
       </x:c>
     </x:row>
     <x:row r="276" ht="15" hidden="0" customHeight="1">
       <x:c r="A276" s="7" t="n">
-        <x:v>1309</x:v>
+        <x:v>1308</x:v>
       </x:c>
       <x:c r="B276" s="7" t="n">
         <x:v>13</x:v>
       </x:c>
       <x:c r="C276" s="7" t="n">
-        <x:v>8</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="D276" s="7" t="n">
-        <x:v>45</x:v>
+        <x:v>345</x:v>
       </x:c>
       <x:c r="E276" s="7" t="n">
-        <x:v>280</x:v>
+        <x:v>385</x:v>
       </x:c>
     </x:row>
     <x:row r="277" ht="15" hidden="0" customHeight="1">
       <x:c r="A277" s="7" t="n">
-        <x:v>1310</x:v>
+        <x:v>1309</x:v>
       </x:c>
       <x:c r="B277" s="7" t="n">
         <x:v>13</x:v>
       </x:c>
       <x:c r="C277" s="7" t="n">
-        <x:v>9</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="D277" s="7" t="n">
-        <x:v>345</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="E277" s="7" t="n">
-        <x:v>325</x:v>
+        <x:v>285</x:v>
       </x:c>
     </x:row>
     <x:row r="278" ht="15" hidden="0" customHeight="1">
       <x:c r="A278" s="7" t="n">
-        <x:v>1311</x:v>
+        <x:v>1310</x:v>
       </x:c>
       <x:c r="B278" s="7" t="n">
         <x:v>13</x:v>
       </x:c>
       <x:c r="C278" s="7" t="n">
-        <x:v>10</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="D278" s="7" t="n">
-        <x:v>45</x:v>
+        <x:v>345</x:v>
       </x:c>
       <x:c r="E278" s="7" t="n">
-        <x:v>330</x:v>
+        <x:v>435</x:v>
       </x:c>
     </x:row>
     <x:row r="279" ht="15" hidden="0" customHeight="1">
       <x:c r="A279" s="7" t="n">
-        <x:v>1312</x:v>
+        <x:v>1311</x:v>
       </x:c>
       <x:c r="B279" s="7" t="n">
         <x:v>13</x:v>
       </x:c>
       <x:c r="C279" s="7" t="n">
-        <x:v>11</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="D279" s="7" t="n">
-        <x:v>145</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="E279" s="7" t="n">
-        <x:v>340</x:v>
+        <x:v>335</x:v>
       </x:c>
     </x:row>
     <x:row r="280" ht="15" hidden="0" customHeight="1">
       <x:c r="A280" s="7" t="n">
-        <x:v>1313</x:v>
+        <x:v>1312</x:v>
       </x:c>
       <x:c r="B280" s="7" t="n">
         <x:v>13</x:v>
       </x:c>
       <x:c r="C280" s="7" t="n">
-        <x:v>12</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D280" s="7" t="n">
-        <x:v>195</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="E280" s="7" t="n">
-        <x:v>340</x:v>
+        <x:v>335</x:v>
       </x:c>
     </x:row>
     <x:row r="281" ht="15" hidden="0" customHeight="1">
       <x:c r="A281" s="7" t="n">
-        <x:v>1314</x:v>
+        <x:v>1313</x:v>
       </x:c>
       <x:c r="B281" s="7" t="n">
         <x:v>13</x:v>
       </x:c>
       <x:c r="C281" s="7" t="n">
-        <x:v>13</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="D281" s="7" t="n">
-        <x:v>295</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="E281" s="7" t="n">
-        <x:v>330</x:v>
+        <x:v>335</x:v>
       </x:c>
     </x:row>
     <x:row r="282" ht="15" hidden="0" customHeight="1">
       <x:c r="A282" s="7" t="n">
-        <x:v>1315</x:v>
+        <x:v>1314</x:v>
       </x:c>
       <x:c r="B282" s="7" t="n">
         <x:v>13</x:v>
       </x:c>
       <x:c r="C282" s="7" t="n">
-        <x:v>14</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D282" s="7" t="n">
-        <x:v>335</x:v>
+        <x:v>245</x:v>
       </x:c>
       <x:c r="E282" s="7" t="n">
-        <x:v>375</x:v>
+        <x:v>435</x:v>
       </x:c>
     </x:row>
     <x:row r="283" ht="15" hidden="0" customHeight="1">
       <x:c r="A283" s="7" t="n">
-        <x:v>1316</x:v>
+        <x:v>1315</x:v>
       </x:c>
       <x:c r="B283" s="7" t="n">
         <x:v>13</x:v>
       </x:c>
       <x:c r="C283" s="7" t="n">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="D283" s="7" t="n">
-        <x:v>45</x:v>
+        <x:v>345</x:v>
       </x:c>
       <x:c r="E283" s="7" t="n">
-        <x:v>380</x:v>
+        <x:v>485</x:v>
       </x:c>
     </x:row>
     <x:row r="284" ht="15" hidden="0" customHeight="1">
       <x:c r="A284" s="7" t="n">
-        <x:v>1317</x:v>
+        <x:v>1316</x:v>
       </x:c>
       <x:c r="B284" s="7" t="n">
         <x:v>13</x:v>
       </x:c>
       <x:c r="C284" s="7" t="n">
-        <x:v>16</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="D284" s="7" t="n">
-        <x:v>145</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="E284" s="7" t="n">
-        <x:v>450</x:v>
+        <x:v>385</x:v>
       </x:c>
     </x:row>
     <x:row r="285" ht="15" hidden="0" customHeight="1">
       <x:c r="A285" s="7" t="n">
-        <x:v>1318</x:v>
+        <x:v>1317</x:v>
       </x:c>
       <x:c r="B285" s="7" t="n">
         <x:v>13</x:v>
       </x:c>
       <x:c r="C285" s="7" t="n">
-        <x:v>17</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="D285" s="7" t="n">
-        <x:v>195</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="E285" s="7" t="n">
-        <x:v>450</x:v>
+        <x:v>435</x:v>
       </x:c>
     </x:row>
     <x:row r="286" ht="15" hidden="0" customHeight="1">
       <x:c r="A286" s="7" t="n">
-        <x:v>1319</x:v>
+        <x:v>1318</x:v>
       </x:c>
       <x:c r="B286" s="7" t="n">
         <x:v>13</x:v>
       </x:c>
       <x:c r="C286" s="7" t="n">
-        <x:v>18</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="D286" s="7" t="n">
-        <x:v>345</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="E286" s="7" t="n">
-        <x:v>425</x:v>
+        <x:v>435</x:v>
       </x:c>
     </x:row>
     <x:row r="287" ht="15" hidden="0" customHeight="1">
       <x:c r="A287" s="7" t="n">
-        <x:v>1320</x:v>
+        <x:v>1319</x:v>
       </x:c>
       <x:c r="B287" s="7" t="n">
         <x:v>13</x:v>
       </x:c>
       <x:c r="C287" s="7" t="n">
-        <x:v>19</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="D287" s="7" t="n">
-        <x:v>95</x:v>
+        <x:v>295</x:v>
       </x:c>
       <x:c r="E287" s="7" t="n">
-        <x:v>450</x:v>
+        <x:v>535</x:v>
       </x:c>
     </x:row>
     <x:row r="288" ht="15" hidden="0" customHeight="1">
       <x:c r="A288" s="7" t="n">
-        <x:v>1321</x:v>
+        <x:v>1320</x:v>
       </x:c>
       <x:c r="B288" s="7" t="n">
         <x:v>13</x:v>
       </x:c>
       <x:c r="C288" s="7" t="n">
-        <x:v>20</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="D288" s="7" t="n">
-        <x:v>245</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="E288" s="7" t="n">
-        <x:v>450</x:v>
+        <x:v>535</x:v>
       </x:c>
     </x:row>
     <x:row r="289" ht="15" hidden="0" customHeight="1">
       <x:c r="A289" s="7" t="n">
-        <x:v>1322</x:v>
+        <x:v>1321</x:v>
       </x:c>
       <x:c r="B289" s="7" t="n">
         <x:v>13</x:v>
       </x:c>
       <x:c r="C289" s="7" t="n">
-        <x:v>21</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="D289" s="7" t="n">
-        <x:v>345</x:v>
+        <x:v>245</x:v>
       </x:c>
       <x:c r="E289" s="7" t="n">
-        <x:v>475</x:v>
+        <x:v>535</x:v>
       </x:c>
     </x:row>
     <x:row r="290" ht="15" hidden="0" customHeight="1">
       <x:c r="A290" s="7" t="n">
-        <x:v>1401</x:v>
+        <x:v>1322</x:v>
       </x:c>
       <x:c r="B290" s="7" t="n">
-        <x:v>14</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C290" s="7" t="n">
-        <x:v>0</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="D290" s="7" t="n">
-        <x:v>295</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="E290" s="7" t="n">
-        <x:v>175</x:v>
+        <x:v>535</x:v>
       </x:c>
     </x:row>
     <x:row r="291" ht="15" hidden="0" customHeight="1">
       <x:c r="A291" s="7" t="n">
-        <x:v>1402</x:v>
+        <x:v>1401</x:v>
       </x:c>
       <x:c r="B291" s="7" t="n">
         <x:v>14</x:v>
       </x:c>
       <x:c r="C291" s="7" t="n">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D291" s="7" t="n">
-        <x:v>95</x:v>
+        <x:v>295</x:v>
       </x:c>
       <x:c r="E291" s="7" t="n">
-        <x:v>225</x:v>
+        <x:v>185</x:v>
       </x:c>
     </x:row>
     <x:row r="292" ht="15" hidden="0" customHeight="1">
       <x:c r="A292" s="7" t="n">
-        <x:v>1403</x:v>
+        <x:v>1402</x:v>
       </x:c>
       <x:c r="B292" s="7" t="n">
         <x:v>14</x:v>
       </x:c>
       <x:c r="C292" s="7" t="n">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="D292" s="7" t="n">
         <x:v>145</x:v>
       </x:c>
       <x:c r="E292" s="7" t="n">
-        <x:v>225</x:v>
+        <x:v>235</x:v>
       </x:c>
     </x:row>
     <x:row r="293" ht="15" hidden="0" customHeight="1">
       <x:c r="A293" s="7" t="n">
-        <x:v>1404</x:v>
+        <x:v>1403</x:v>
       </x:c>
       <x:c r="B293" s="7" t="n">
         <x:v>14</x:v>
       </x:c>
       <x:c r="C293" s="7" t="n">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="D293" s="7" t="n">
         <x:v>195</x:v>
       </x:c>
       <x:c r="E293" s="7" t="n">
-        <x:v>225</x:v>
+        <x:v>235</x:v>
       </x:c>
     </x:row>
     <x:row r="294" ht="15" hidden="0" customHeight="1">
       <x:c r="A294" s="7" t="n">
-        <x:v>1405</x:v>
+        <x:v>1404</x:v>
       </x:c>
       <x:c r="B294" s="7" t="n">
         <x:v>14</x:v>
       </x:c>
       <x:c r="C294" s="7" t="n">
-        <x:v>4</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="D294" s="7" t="n">
-        <x:v>295</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="E294" s="7" t="n">
-        <x:v>225</x:v>
+        <x:v>135</x:v>
       </x:c>
     </x:row>
     <x:row r="295" ht="15" hidden="0" customHeight="1">
       <x:c r="A295" s="7" t="n">
-        <x:v>1406</x:v>
+        <x:v>1405</x:v>
       </x:c>
       <x:c r="B295" s="7" t="n">
         <x:v>14</x:v>
       </x:c>
       <x:c r="C295" s="7" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="D295" s="7" t="n">
         <x:v>295</x:v>
       </x:c>
       <x:c r="E295" s="7" t="n">
-        <x:v>275</x:v>
+        <x:v>235</x:v>
       </x:c>
     </x:row>
     <x:row r="296" ht="15" hidden="0" customHeight="1">
       <x:c r="A296" s="7" t="n">
-        <x:v>1407</x:v>
+        <x:v>1406</x:v>
       </x:c>
       <x:c r="B296" s="7" t="n">
         <x:v>14</x:v>
       </x:c>
       <x:c r="C296" s="7" t="n">
-        <x:v>6</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D296" s="7" t="n">
-        <x:v>95</x:v>
+        <x:v>295</x:v>
       </x:c>
       <x:c r="E296" s="7" t="n">
-        <x:v>335</x:v>
+        <x:v>285</x:v>
       </x:c>
     </x:row>
     <x:row r="297" ht="15" hidden="0" customHeight="1">
       <x:c r="A297" s="7" t="n">
-        <x:v>1408</x:v>
+        <x:v>1407</x:v>
       </x:c>
       <x:c r="B297" s="7" t="n">
         <x:v>14</x:v>
       </x:c>
       <x:c r="C297" s="7" t="n">
-        <x:v>7</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="D297" s="7" t="n">
-        <x:v>145</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="E297" s="7" t="n">
         <x:v>335</x:v>
@@ -5338,16 +5338,16 @@
     </x:row>
     <x:row r="298" ht="15" hidden="0" customHeight="1">
       <x:c r="A298" s="7" t="n">
-        <x:v>1409</x:v>
+        <x:v>1408</x:v>
       </x:c>
       <x:c r="B298" s="7" t="n">
         <x:v>14</x:v>
       </x:c>
       <x:c r="C298" s="7" t="n">
-        <x:v>8</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="D298" s="7" t="n">
-        <x:v>195</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="E298" s="7" t="n">
         <x:v>335</x:v>
@@ -5355,2719 +5355,2719 @@
     </x:row>
     <x:row r="299" ht="15" hidden="0" customHeight="1">
       <x:c r="A299" s="7" t="n">
-        <x:v>1410</x:v>
+        <x:v>1409</x:v>
       </x:c>
       <x:c r="B299" s="7" t="n">
         <x:v>14</x:v>
       </x:c>
       <x:c r="C299" s="7" t="n">
-        <x:v>9</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="D299" s="7" t="n">
-        <x:v>245</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="E299" s="7" t="n">
-        <x:v>325</x:v>
+        <x:v>335</x:v>
       </x:c>
     </x:row>
     <x:row r="300" ht="15" hidden="0" customHeight="1">
       <x:c r="A300" s="7" t="n">
-        <x:v>1411</x:v>
+        <x:v>1410</x:v>
       </x:c>
       <x:c r="B300" s="7" t="n">
         <x:v>14</x:v>
       </x:c>
       <x:c r="C300" s="7" t="n">
-        <x:v>10</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="D300" s="7" t="n">
-        <x:v>95</x:v>
+        <x:v>245</x:v>
       </x:c>
       <x:c r="E300" s="7" t="n">
-        <x:v>445</x:v>
+        <x:v>335</x:v>
       </x:c>
     </x:row>
     <x:row r="301" ht="15" hidden="0" customHeight="1">
       <x:c r="A301" s="7" t="n">
-        <x:v>1412</x:v>
+        <x:v>1411</x:v>
       </x:c>
       <x:c r="B301" s="7" t="n">
         <x:v>14</x:v>
       </x:c>
       <x:c r="C301" s="7" t="n">
-        <x:v>11</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="D301" s="7" t="n">
-        <x:v>45</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="E301" s="7" t="n">
-        <x:v>445</x:v>
+        <x:v>435</x:v>
       </x:c>
     </x:row>
     <x:row r="302" ht="15" hidden="0" customHeight="1">
       <x:c r="A302" s="7" t="n">
-        <x:v>1413</x:v>
+        <x:v>1412</x:v>
       </x:c>
       <x:c r="B302" s="7" t="n">
         <x:v>14</x:v>
       </x:c>
       <x:c r="C302" s="7" t="n">
-        <x:v>12</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D302" s="7" t="n">
-        <x:v>145</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="E302" s="7" t="n">
-        <x:v>445</x:v>
+        <x:v>435</x:v>
       </x:c>
     </x:row>
     <x:row r="303" ht="15" hidden="0" customHeight="1">
       <x:c r="A303" s="7" t="n">
-        <x:v>1414</x:v>
+        <x:v>1413</x:v>
       </x:c>
       <x:c r="B303" s="7" t="n">
         <x:v>14</x:v>
       </x:c>
       <x:c r="C303" s="7" t="n">
-        <x:v>13</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="D303" s="7" t="n">
-        <x:v>235</x:v>
+        <x:v>295</x:v>
       </x:c>
       <x:c r="E303" s="7" t="n">
-        <x:v>445</x:v>
+        <x:v>535</x:v>
       </x:c>
     </x:row>
     <x:row r="304" ht="15" hidden="0" customHeight="1">
       <x:c r="A304" s="7" t="n">
-        <x:v>1415</x:v>
+        <x:v>1414</x:v>
       </x:c>
       <x:c r="B304" s="7" t="n">
         <x:v>14</x:v>
       </x:c>
       <x:c r="C304" s="7" t="n">
-        <x:v>14</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D304" s="7" t="n">
         <x:v>295</x:v>
       </x:c>
       <x:c r="E304" s="7" t="n">
-        <x:v>345</x:v>
+        <x:v>335</x:v>
       </x:c>
     </x:row>
     <x:row r="305" ht="15" hidden="0" customHeight="1">
       <x:c r="A305" s="7" t="n">
-        <x:v>1416</x:v>
+        <x:v>1415</x:v>
       </x:c>
       <x:c r="B305" s="7" t="n">
         <x:v>14</x:v>
       </x:c>
       <x:c r="C305" s="7" t="n">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="D305" s="7" t="n">
         <x:v>345</x:v>
       </x:c>
       <x:c r="E305" s="7" t="n">
-        <x:v>345</x:v>
+        <x:v>335</x:v>
       </x:c>
     </x:row>
     <x:row r="306" ht="15" hidden="0" customHeight="1">
       <x:c r="A306" s="7" t="n">
-        <x:v>1417</x:v>
+        <x:v>1416</x:v>
       </x:c>
       <x:c r="B306" s="7" t="n">
         <x:v>14</x:v>
       </x:c>
       <x:c r="C306" s="7" t="n">
-        <x:v>16</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="D306" s="7" t="n">
-        <x:v>295</x:v>
+        <x:v>345</x:v>
       </x:c>
       <x:c r="E306" s="7" t="n">
-        <x:v>445</x:v>
+        <x:v>535</x:v>
       </x:c>
     </x:row>
     <x:row r="307" ht="15" hidden="0" customHeight="1">
       <x:c r="A307" s="7" t="n">
-        <x:v>1418</x:v>
+        <x:v>1417</x:v>
       </x:c>
       <x:c r="B307" s="7" t="n">
         <x:v>14</x:v>
       </x:c>
       <x:c r="C307" s="7" t="n">
-        <x:v>17</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="D307" s="7" t="n">
-        <x:v>125</x:v>
+        <x:v>245</x:v>
       </x:c>
       <x:c r="E307" s="7" t="n">
-        <x:v>495</x:v>
+        <x:v>135</x:v>
       </x:c>
     </x:row>
     <x:row r="308" ht="15" hidden="0" customHeight="1">
       <x:c r="A308" s="7" t="n">
-        <x:v>1419</x:v>
+        <x:v>1418</x:v>
       </x:c>
       <x:c r="B308" s="7" t="n">
         <x:v>14</x:v>
       </x:c>
       <x:c r="C308" s="7" t="n">
-        <x:v>18</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="D308" s="7" t="n">
         <x:v>145</x:v>
       </x:c>
       <x:c r="E308" s="7" t="n">
-        <x:v>545</x:v>
+        <x:v>135</x:v>
       </x:c>
     </x:row>
     <x:row r="309" ht="15" hidden="0" customHeight="1">
       <x:c r="A309" s="7" t="n">
-        <x:v>1420</x:v>
+        <x:v>1501</x:v>
       </x:c>
       <x:c r="B309" s="7" t="n">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="C309" s="7" t="n">
-        <x:v>19</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D309" s="7" t="n">
-        <x:v>195</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="E309" s="7" t="n">
-        <x:v>565</x:v>
+        <x:v>235</x:v>
       </x:c>
     </x:row>
     <x:row r="310" ht="15" hidden="0" customHeight="1">
       <x:c r="A310" s="7" t="n">
-        <x:v>1421</x:v>
+        <x:v>1502</x:v>
       </x:c>
       <x:c r="B310" s="7" t="n">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="C310" s="7" t="n">
-        <x:v>20</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="D310" s="7" t="n">
-        <x:v>245</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="E310" s="7" t="n">
-        <x:v>545</x:v>
+        <x:v>235</x:v>
       </x:c>
     </x:row>
     <x:row r="311" ht="15" hidden="0" customHeight="1">
       <x:c r="A311" s="7" t="n">
-        <x:v>1422</x:v>
+        <x:v>1503</x:v>
       </x:c>
       <x:c r="B311" s="7" t="n">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="C311" s="7" t="n">
-        <x:v>21</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="D311" s="7" t="n">
-        <x:v>295</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="E311" s="7" t="n">
-        <x:v>545</x:v>
+        <x:v>235</x:v>
       </x:c>
     </x:row>
     <x:row r="312" ht="15" hidden="0" customHeight="1">
       <x:c r="A312" s="7" t="n">
-        <x:v>1501</x:v>
+        <x:v>1504</x:v>
       </x:c>
       <x:c r="B312" s="7" t="n">
         <x:v>15</x:v>
       </x:c>
       <x:c r="C312" s="7" t="n">
-        <x:v>0</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="D312" s="7" t="n">
-        <x:v>95</x:v>
+        <x:v>245</x:v>
       </x:c>
       <x:c r="E312" s="7" t="n">
-        <x:v>210</x:v>
+        <x:v>235</x:v>
       </x:c>
     </x:row>
     <x:row r="313" ht="15" hidden="0" customHeight="1">
       <x:c r="A313" s="7" t="n">
-        <x:v>1502</x:v>
+        <x:v>1505</x:v>
       </x:c>
       <x:c r="B313" s="7" t="n">
         <x:v>15</x:v>
       </x:c>
       <x:c r="C313" s="7" t="n">
-        <x:v>1</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="D313" s="7" t="n">
-        <x:v>145</x:v>
+        <x:v>345</x:v>
       </x:c>
       <x:c r="E313" s="7" t="n">
-        <x:v>210</x:v>
+        <x:v>285</x:v>
       </x:c>
     </x:row>
     <x:row r="314" ht="15" hidden="0" customHeight="1">
       <x:c r="A314" s="7" t="n">
-        <x:v>1503</x:v>
+        <x:v>1506</x:v>
       </x:c>
       <x:c r="B314" s="7" t="n">
         <x:v>15</x:v>
       </x:c>
       <x:c r="C314" s="7" t="n">
-        <x:v>2</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D314" s="7" t="n">
-        <x:v>195</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="E314" s="7" t="n">
-        <x:v>210</x:v>
+        <x:v>335</x:v>
       </x:c>
     </x:row>
     <x:row r="315" ht="15" hidden="0" customHeight="1">
       <x:c r="A315" s="7" t="n">
-        <x:v>1504</x:v>
+        <x:v>1507</x:v>
       </x:c>
       <x:c r="B315" s="7" t="n">
         <x:v>15</x:v>
       </x:c>
       <x:c r="C315" s="7" t="n">
-        <x:v>3</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="D315" s="7" t="n">
-        <x:v>245</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="E315" s="7" t="n">
-        <x:v>210</x:v>
+        <x:v>335</x:v>
       </x:c>
     </x:row>
     <x:row r="316" ht="15" hidden="0" customHeight="1">
       <x:c r="A316" s="7" t="n">
-        <x:v>1505</x:v>
+        <x:v>1508</x:v>
       </x:c>
       <x:c r="B316" s="7" t="n">
         <x:v>15</x:v>
       </x:c>
       <x:c r="C316" s="7" t="n">
-        <x:v>4</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="D316" s="7" t="n">
-        <x:v>295</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="E316" s="7" t="n">
-        <x:v>200</x:v>
+        <x:v>335</x:v>
       </x:c>
     </x:row>
     <x:row r="317" ht="15" hidden="0" customHeight="1">
       <x:c r="A317" s="7" t="n">
-        <x:v>1506</x:v>
+        <x:v>1509</x:v>
       </x:c>
       <x:c r="B317" s="7" t="n">
         <x:v>15</x:v>
       </x:c>
       <x:c r="C317" s="7" t="n">
-        <x:v>5</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="D317" s="7" t="n">
-        <x:v>95</x:v>
+        <x:v>245</x:v>
       </x:c>
       <x:c r="E317" s="7" t="n">
-        <x:v>320</x:v>
+        <x:v>335</x:v>
       </x:c>
     </x:row>
     <x:row r="318" ht="15" hidden="0" customHeight="1">
       <x:c r="A318" s="7" t="n">
-        <x:v>1507</x:v>
+        <x:v>1510</x:v>
       </x:c>
       <x:c r="B318" s="7" t="n">
         <x:v>15</x:v>
       </x:c>
       <x:c r="C318" s="7" t="n">
-        <x:v>6</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="D318" s="7" t="n">
-        <x:v>145</x:v>
+        <x:v>345</x:v>
       </x:c>
       <x:c r="E318" s="7" t="n">
-        <x:v>320</x:v>
+        <x:v>335</x:v>
       </x:c>
     </x:row>
     <x:row r="319" ht="15" hidden="0" customHeight="1">
       <x:c r="A319" s="7" t="n">
-        <x:v>1508</x:v>
+        <x:v>1511</x:v>
       </x:c>
       <x:c r="B319" s="7" t="n">
         <x:v>15</x:v>
       </x:c>
       <x:c r="C319" s="7" t="n">
-        <x:v>7</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="D319" s="7" t="n">
-        <x:v>195</x:v>
+        <x:v>345</x:v>
       </x:c>
       <x:c r="E319" s="7" t="n">
-        <x:v>320</x:v>
+        <x:v>385</x:v>
       </x:c>
     </x:row>
     <x:row r="320" ht="15" hidden="0" customHeight="1">
       <x:c r="A320" s="7" t="n">
-        <x:v>1509</x:v>
+        <x:v>1512</x:v>
       </x:c>
       <x:c r="B320" s="7" t="n">
         <x:v>15</x:v>
       </x:c>
       <x:c r="C320" s="7" t="n">
-        <x:v>8</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D320" s="7" t="n">
-        <x:v>245</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="E320" s="7" t="n">
-        <x:v>320</x:v>
+        <x:v>335</x:v>
       </x:c>
     </x:row>
     <x:row r="321" ht="15" hidden="0" customHeight="1">
       <x:c r="A321" s="7" t="n">
-        <x:v>1510</x:v>
+        <x:v>1513</x:v>
       </x:c>
       <x:c r="B321" s="7" t="n">
         <x:v>15</x:v>
       </x:c>
       <x:c r="C321" s="7" t="n">
-        <x:v>9</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="D321" s="7" t="n">
-        <x:v>335</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="E321" s="7" t="n">
-        <x:v>235</x:v>
+        <x:v>385</x:v>
       </x:c>
     </x:row>
     <x:row r="322" ht="15" hidden="0" customHeight="1">
       <x:c r="A322" s="7" t="n">
-        <x:v>1511</x:v>
+        <x:v>1514</x:v>
       </x:c>
       <x:c r="B322" s="7" t="n">
         <x:v>15</x:v>
       </x:c>
       <x:c r="C322" s="7" t="n">
-        <x:v>10</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D322" s="7" t="n">
-        <x:v>345</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="E322" s="7" t="n">
-        <x:v>285</x:v>
+        <x:v>435</x:v>
       </x:c>
     </x:row>
     <x:row r="323" ht="15" hidden="0" customHeight="1">
       <x:c r="A323" s="7" t="n">
-        <x:v>1512</x:v>
+        <x:v>1515</x:v>
       </x:c>
       <x:c r="B323" s="7" t="n">
         <x:v>15</x:v>
       </x:c>
       <x:c r="C323" s="7" t="n">
-        <x:v>11</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="D323" s="7" t="n">
-        <x:v>45</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="E323" s="7" t="n">
-        <x:v>320</x:v>
+        <x:v>435</x:v>
       </x:c>
     </x:row>
     <x:row r="324" ht="15" hidden="0" customHeight="1">
       <x:c r="A324" s="7" t="n">
-        <x:v>1513</x:v>
+        <x:v>1516</x:v>
       </x:c>
       <x:c r="B324" s="7" t="n">
         <x:v>15</x:v>
       </x:c>
       <x:c r="C324" s="7" t="n">
-        <x:v>12</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="D324" s="7" t="n">
-        <x:v>45</x:v>
+        <x:v>245</x:v>
       </x:c>
       <x:c r="E324" s="7" t="n">
-        <x:v>370</x:v>
+        <x:v>435</x:v>
       </x:c>
     </x:row>
     <x:row r="325" ht="15" hidden="0" customHeight="1">
       <x:c r="A325" s="7" t="n">
-        <x:v>1514</x:v>
+        <x:v>1517</x:v>
       </x:c>
       <x:c r="B325" s="7" t="n">
         <x:v>15</x:v>
       </x:c>
       <x:c r="C325" s="7" t="n">
-        <x:v>13</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="D325" s="7" t="n">
         <x:v>145</x:v>
       </x:c>
       <x:c r="E325" s="7" t="n">
-        <x:v>420</x:v>
+        <x:v>535</x:v>
       </x:c>
     </x:row>
     <x:row r="326" ht="15" hidden="0" customHeight="1">
       <x:c r="A326" s="7" t="n">
-        <x:v>1515</x:v>
+        <x:v>1518</x:v>
       </x:c>
       <x:c r="B326" s="7" t="n">
         <x:v>15</x:v>
       </x:c>
       <x:c r="C326" s="7" t="n">
-        <x:v>14</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="D326" s="7" t="n">
-        <x:v>195</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="E326" s="7" t="n">
-        <x:v>420</x:v>
+        <x:v>435</x:v>
       </x:c>
     </x:row>
     <x:row r="327" ht="15" hidden="0" customHeight="1">
       <x:c r="A327" s="7" t="n">
-        <x:v>1516</x:v>
+        <x:v>1519</x:v>
       </x:c>
       <x:c r="B327" s="7" t="n">
         <x:v>15</x:v>
       </x:c>
       <x:c r="C327" s="7" t="n">
-        <x:v>15</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="D327" s="7" t="n">
-        <x:v>245</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="E327" s="7" t="n">
-        <x:v>420</x:v>
+        <x:v>535</x:v>
       </x:c>
     </x:row>
     <x:row r="328" ht="15" hidden="0" customHeight="1">
       <x:c r="A328" s="7" t="n">
-        <x:v>1517</x:v>
+        <x:v>1520</x:v>
       </x:c>
       <x:c r="B328" s="7" t="n">
         <x:v>15</x:v>
       </x:c>
       <x:c r="C328" s="7" t="n">
-        <x:v>16</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="D328" s="7" t="n">
-        <x:v>345</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="E328" s="7" t="n">
-        <x:v>335</x:v>
+        <x:v>485</x:v>
       </x:c>
     </x:row>
     <x:row r="329" ht="15" hidden="0" customHeight="1">
       <x:c r="A329" s="7" t="n">
-        <x:v>1518</x:v>
+        <x:v>1521</x:v>
       </x:c>
       <x:c r="B329" s="7" t="n">
         <x:v>15</x:v>
       </x:c>
       <x:c r="C329" s="7" t="n">
-        <x:v>17</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="D329" s="7" t="n">
-        <x:v>45</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="E329" s="7" t="n">
-        <x:v>420</x:v>
+        <x:v>135</x:v>
       </x:c>
     </x:row>
     <x:row r="330" ht="15" hidden="0" customHeight="1">
       <x:c r="A330" s="7" t="n">
-        <x:v>1519</x:v>
+        <x:v>1522</x:v>
       </x:c>
       <x:c r="B330" s="7" t="n">
         <x:v>15</x:v>
       </x:c>
       <x:c r="C330" s="7" t="n">
-        <x:v>18</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="D330" s="7" t="n">
-        <x:v>345</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="E330" s="7" t="n">
-        <x:v>385</x:v>
+        <x:v>135</x:v>
       </x:c>
     </x:row>
     <x:row r="331" ht="15" hidden="0" customHeight="1">
       <x:c r="A331" s="7" t="n">
-        <x:v>1520</x:v>
+        <x:v>1601</x:v>
       </x:c>
       <x:c r="B331" s="7" t="n">
-        <x:v>15</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C331" s="7" t="n">
-        <x:v>19</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D331" s="7" t="n">
-        <x:v>45</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="E331" s="7" t="n">
-        <x:v>470</x:v>
+        <x:v>185</x:v>
       </x:c>
     </x:row>
     <x:row r="332" ht="15" hidden="0" customHeight="1">
       <x:c r="A332" s="7" t="n">
-        <x:v>1521</x:v>
+        <x:v>1602</x:v>
       </x:c>
       <x:c r="B332" s="7" t="n">
-        <x:v>15</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C332" s="7" t="n">
-        <x:v>20</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="D332" s="7" t="n">
-        <x:v>145</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="E332" s="7" t="n">
-        <x:v>520</x:v>
+        <x:v>285</x:v>
       </x:c>
     </x:row>
     <x:row r="333" ht="15" hidden="0" customHeight="1">
       <x:c r="A333" s="7" t="n">
-        <x:v>1522</x:v>
+        <x:v>1603</x:v>
       </x:c>
       <x:c r="B333" s="7" t="n">
-        <x:v>15</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C333" s="7" t="n">
-        <x:v>21</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="D333" s="7" t="n">
-        <x:v>295</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="E333" s="7" t="n">
-        <x:v>420</x:v>
+        <x:v>235</x:v>
       </x:c>
     </x:row>
     <x:row r="334" ht="15" hidden="0" customHeight="1">
       <x:c r="A334" s="7" t="n">
-        <x:v>1601</x:v>
+        <x:v>1604</x:v>
       </x:c>
       <x:c r="B334" s="7" t="n">
         <x:v>16</x:v>
       </x:c>
       <x:c r="C334" s="7" t="n">
-        <x:v>0</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="D334" s="7" t="n">
-        <x:v>195</x:v>
+        <x:v>245</x:v>
       </x:c>
       <x:c r="E334" s="7" t="n">
-        <x:v>150</x:v>
+        <x:v>235</x:v>
       </x:c>
     </x:row>
     <x:row r="335" ht="15" hidden="0" customHeight="1">
       <x:c r="A335" s="7" t="n">
-        <x:v>1602</x:v>
+        <x:v>1605</x:v>
       </x:c>
       <x:c r="B335" s="7" t="n">
         <x:v>16</x:v>
       </x:c>
       <x:c r="C335" s="7" t="n">
-        <x:v>1</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="D335" s="7" t="n">
-        <x:v>95</x:v>
+        <x:v>295</x:v>
       </x:c>
       <x:c r="E335" s="7" t="n">
-        <x:v>200</x:v>
+        <x:v>235</x:v>
       </x:c>
     </x:row>
     <x:row r="336" ht="15" hidden="0" customHeight="1">
       <x:c r="A336" s="7" t="n">
-        <x:v>1603</x:v>
+        <x:v>1606</x:v>
       </x:c>
       <x:c r="B336" s="7" t="n">
         <x:v>16</x:v>
       </x:c>
       <x:c r="C336" s="7" t="n">
-        <x:v>2</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D336" s="7" t="n">
-        <x:v>195</x:v>
+        <x:v>345</x:v>
       </x:c>
       <x:c r="E336" s="7" t="n">
-        <x:v>200</x:v>
+        <x:v>235</x:v>
       </x:c>
     </x:row>
     <x:row r="337" ht="15" hidden="0" customHeight="1">
       <x:c r="A337" s="7" t="n">
-        <x:v>1604</x:v>
+        <x:v>1607</x:v>
       </x:c>
       <x:c r="B337" s="7" t="n">
         <x:v>16</x:v>
       </x:c>
       <x:c r="C337" s="7" t="n">
-        <x:v>3</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="D337" s="7" t="n">
-        <x:v>245</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="E337" s="7" t="n">
-        <x:v>200</x:v>
+        <x:v>335</x:v>
       </x:c>
     </x:row>
     <x:row r="338" ht="15" hidden="0" customHeight="1">
       <x:c r="A338" s="7" t="n">
-        <x:v>1605</x:v>
+        <x:v>1608</x:v>
       </x:c>
       <x:c r="B338" s="7" t="n">
         <x:v>16</x:v>
       </x:c>
       <x:c r="C338" s="7" t="n">
-        <x:v>4</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="D338" s="7" t="n">
-        <x:v>295</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="E338" s="7" t="n">
-        <x:v>200</x:v>
+        <x:v>335</x:v>
       </x:c>
     </x:row>
     <x:row r="339" ht="15" hidden="0" customHeight="1">
       <x:c r="A339" s="7" t="n">
-        <x:v>1606</x:v>
+        <x:v>1609</x:v>
       </x:c>
       <x:c r="B339" s="7" t="n">
         <x:v>16</x:v>
       </x:c>
       <x:c r="C339" s="7" t="n">
-        <x:v>5</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="D339" s="7" t="n">
-        <x:v>345</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="E339" s="7" t="n">
-        <x:v>200</x:v>
+        <x:v>335</x:v>
       </x:c>
     </x:row>
     <x:row r="340" ht="15" hidden="0" customHeight="1">
       <x:c r="A340" s="7" t="n">
-        <x:v>1607</x:v>
+        <x:v>1610</x:v>
       </x:c>
       <x:c r="B340" s="7" t="n">
         <x:v>16</x:v>
       </x:c>
       <x:c r="C340" s="7" t="n">
-        <x:v>6</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="D340" s="7" t="n">
-        <x:v>95</x:v>
+        <x:v>245</x:v>
       </x:c>
       <x:c r="E340" s="7" t="n">
-        <x:v>250</x:v>
+        <x:v>335</x:v>
       </x:c>
     </x:row>
     <x:row r="341" ht="15" hidden="0" customHeight="1">
       <x:c r="A341" s="7" t="n">
-        <x:v>1608</x:v>
+        <x:v>1611</x:v>
       </x:c>
       <x:c r="B341" s="7" t="n">
         <x:v>16</x:v>
       </x:c>
       <x:c r="C341" s="7" t="n">
-        <x:v>7</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="D341" s="7" t="n">
-        <x:v>145</x:v>
+        <x:v>295</x:v>
       </x:c>
       <x:c r="E341" s="7" t="n">
-        <x:v>300</x:v>
+        <x:v>335</x:v>
       </x:c>
     </x:row>
     <x:row r="342" ht="15" hidden="0" customHeight="1">
       <x:c r="A342" s="7" t="n">
-        <x:v>1609</x:v>
+        <x:v>1612</x:v>
       </x:c>
       <x:c r="B342" s="7" t="n">
         <x:v>16</x:v>
       </x:c>
       <x:c r="C342" s="7" t="n">
-        <x:v>8</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D342" s="7" t="n">
-        <x:v>195</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="E342" s="7" t="n">
-        <x:v>310</x:v>
+        <x:v>335</x:v>
       </x:c>
     </x:row>
     <x:row r="343" ht="15" hidden="0" customHeight="1">
       <x:c r="A343" s="7" t="n">
-        <x:v>1610</x:v>
+        <x:v>1613</x:v>
       </x:c>
       <x:c r="B343" s="7" t="n">
         <x:v>16</x:v>
       </x:c>
       <x:c r="C343" s="7" t="n">
-        <x:v>9</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="D343" s="7" t="n">
-        <x:v>245</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="E343" s="7" t="n">
-        <x:v>310</x:v>
+        <x:v>435</x:v>
       </x:c>
     </x:row>
     <x:row r="344" ht="15" hidden="0" customHeight="1">
       <x:c r="A344" s="7" t="n">
-        <x:v>1611</x:v>
+        <x:v>1614</x:v>
       </x:c>
       <x:c r="B344" s="7" t="n">
         <x:v>16</x:v>
       </x:c>
       <x:c r="C344" s="7" t="n">
-        <x:v>10</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D344" s="7" t="n">
-        <x:v>295</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="E344" s="7" t="n">
-        <x:v>310</x:v>
+        <x:v>435</x:v>
       </x:c>
     </x:row>
     <x:row r="345" ht="15" hidden="0" customHeight="1">
       <x:c r="A345" s="7" t="n">
-        <x:v>1612</x:v>
+        <x:v>1615</x:v>
       </x:c>
       <x:c r="B345" s="7" t="n">
         <x:v>16</x:v>
       </x:c>
       <x:c r="C345" s="7" t="n">
-        <x:v>11</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="D345" s="7" t="n">
-        <x:v>45</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="E345" s="7" t="n">
-        <x:v>320</x:v>
+        <x:v>435</x:v>
       </x:c>
     </x:row>
     <x:row r="346" ht="15" hidden="0" customHeight="1">
       <x:c r="A346" s="7" t="n">
-        <x:v>1613</x:v>
+        <x:v>1616</x:v>
       </x:c>
       <x:c r="B346" s="7" t="n">
         <x:v>16</x:v>
       </x:c>
       <x:c r="C346" s="7" t="n">
-        <x:v>12</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="D346" s="7" t="n">
-        <x:v>95</x:v>
+        <x:v>245</x:v>
       </x:c>
       <x:c r="E346" s="7" t="n">
-        <x:v>320</x:v>
+        <x:v>435</x:v>
       </x:c>
     </x:row>
     <x:row r="347" ht="15" hidden="0" customHeight="1">
       <x:c r="A347" s="7" t="n">
-        <x:v>1614</x:v>
+        <x:v>1617</x:v>
       </x:c>
       <x:c r="B347" s="7" t="n">
         <x:v>16</x:v>
       </x:c>
       <x:c r="C347" s="7" t="n">
-        <x:v>13</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="D347" s="7" t="n">
-        <x:v>145</x:v>
+        <x:v>245</x:v>
       </x:c>
       <x:c r="E347" s="7" t="n">
-        <x:v>420</x:v>
+        <x:v>535</x:v>
       </x:c>
     </x:row>
     <x:row r="348" ht="15" hidden="0" customHeight="1">
       <x:c r="A348" s="7" t="n">
-        <x:v>1615</x:v>
+        <x:v>1618</x:v>
       </x:c>
       <x:c r="B348" s="7" t="n">
         <x:v>16</x:v>
       </x:c>
       <x:c r="C348" s="7" t="n">
-        <x:v>14</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="D348" s="7" t="n">
-        <x:v>195</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="E348" s="7" t="n">
-        <x:v>420</x:v>
+        <x:v>535</x:v>
       </x:c>
     </x:row>
     <x:row r="349" ht="15" hidden="0" customHeight="1">
       <x:c r="A349" s="7" t="n">
-        <x:v>1616</x:v>
+        <x:v>1619</x:v>
       </x:c>
       <x:c r="B349" s="7" t="n">
         <x:v>16</x:v>
       </x:c>
       <x:c r="C349" s="7" t="n">
-        <x:v>15</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="D349" s="7" t="n">
-        <x:v>245</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="E349" s="7" t="n">
-        <x:v>420</x:v>
+        <x:v>535</x:v>
       </x:c>
     </x:row>
     <x:row r="350" ht="15" hidden="0" customHeight="1">
       <x:c r="A350" s="7" t="n">
-        <x:v>1617</x:v>
+        <x:v>1620</x:v>
       </x:c>
       <x:c r="B350" s="7" t="n">
         <x:v>16</x:v>
       </x:c>
       <x:c r="C350" s="7" t="n">
-        <x:v>16</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="D350" s="7" t="n">
-        <x:v>295</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="E350" s="7" t="n">
-        <x:v>420</x:v>
+        <x:v>535</x:v>
       </x:c>
     </x:row>
     <x:row r="351" ht="15" hidden="0" customHeight="1">
       <x:c r="A351" s="7" t="n">
-        <x:v>1618</x:v>
+        <x:v>1621</x:v>
       </x:c>
       <x:c r="B351" s="7" t="n">
         <x:v>16</x:v>
       </x:c>
       <x:c r="C351" s="7" t="n">
-        <x:v>17</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="D351" s="7" t="n">
-        <x:v>95</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="E351" s="7" t="n">
-        <x:v>420</x:v>
+        <x:v>535</x:v>
       </x:c>
     </x:row>
     <x:row r="352" ht="15" hidden="0" customHeight="1">
       <x:c r="A352" s="7" t="n">
-        <x:v>1619</x:v>
+        <x:v>1701</x:v>
       </x:c>
       <x:c r="B352" s="7" t="n">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C352" s="7" t="n">
-        <x:v>18</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D352" s="7" t="n">
-        <x:v>145</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="E352" s="7" t="n">
-        <x:v>520</x:v>
+        <x:v>185</x:v>
       </x:c>
     </x:row>
     <x:row r="353" ht="15" hidden="0" customHeight="1">
       <x:c r="A353" s="7" t="n">
-        <x:v>1620</x:v>
+        <x:v>1702</x:v>
       </x:c>
       <x:c r="B353" s="7" t="n">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C353" s="7" t="n">
-        <x:v>19</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="D353" s="7" t="n">
         <x:v>195</x:v>
       </x:c>
       <x:c r="E353" s="7" t="n">
-        <x:v>520</x:v>
+        <x:v>235</x:v>
       </x:c>
     </x:row>
     <x:row r="354" ht="15" hidden="0" customHeight="1">
       <x:c r="A354" s="7" t="n">
-        <x:v>1621</x:v>
+        <x:v>1703</x:v>
       </x:c>
       <x:c r="B354" s="7" t="n">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C354" s="7" t="n">
-        <x:v>20</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="D354" s="7" t="n">
-        <x:v>245</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="E354" s="7" t="n">
-        <x:v>520</x:v>
+        <x:v>235</x:v>
       </x:c>
     </x:row>
     <x:row r="355" ht="15" hidden="0" customHeight="1">
       <x:c r="A355" s="7" t="n">
-        <x:v>1622</x:v>
+        <x:v>1704</x:v>
       </x:c>
       <x:c r="B355" s="7" t="n">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C355" s="7" t="n">
-        <x:v>21</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="D355" s="7" t="n">
-        <x:v>295</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="E355" s="7" t="n">
-        <x:v>520</x:v>
+        <x:v>235</x:v>
       </x:c>
     </x:row>
     <x:row r="356" ht="15" hidden="0" customHeight="1">
       <x:c r="A356" s="7" t="n">
-        <x:v>1701</x:v>
+        <x:v>1705</x:v>
       </x:c>
       <x:c r="B356" s="7" t="n">
         <x:v>17</x:v>
       </x:c>
       <x:c r="C356" s="7" t="n">
-        <x:v>0</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="D356" s="7" t="n">
-        <x:v>245</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="E356" s="7" t="n">
-        <x:v>150</x:v>
+        <x:v>235</x:v>
       </x:c>
     </x:row>
     <x:row r="357" ht="15" hidden="0" customHeight="1">
       <x:c r="A357" s="7" t="n">
-        <x:v>1702</x:v>
+        <x:v>1706</x:v>
       </x:c>
       <x:c r="B357" s="7" t="n">
         <x:v>17</x:v>
       </x:c>
       <x:c r="C357" s="7" t="n">
-        <x:v>1</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D357" s="7" t="n">
-        <x:v>295</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="E357" s="7" t="n">
-        <x:v>150</x:v>
+        <x:v>335</x:v>
       </x:c>
     </x:row>
     <x:row r="358" ht="15" hidden="0" customHeight="1">
       <x:c r="A358" s="7" t="n">
-        <x:v>1703</x:v>
+        <x:v>1707</x:v>
       </x:c>
       <x:c r="B358" s="7" t="n">
         <x:v>17</x:v>
       </x:c>
       <x:c r="C358" s="7" t="n">
-        <x:v>2</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="D358" s="7" t="n">
         <x:v>195</x:v>
       </x:c>
       <x:c r="E358" s="7" t="n">
-        <x:v>200</x:v>
+        <x:v>335</x:v>
       </x:c>
     </x:row>
     <x:row r="359" ht="15" hidden="0" customHeight="1">
       <x:c r="A359" s="7" t="n">
-        <x:v>1704</x:v>
+        <x:v>1708</x:v>
       </x:c>
       <x:c r="B359" s="7" t="n">
         <x:v>17</x:v>
       </x:c>
       <x:c r="C359" s="7" t="n">
-        <x:v>3</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="D359" s="7" t="n">
-        <x:v>45</x:v>
+        <x:v>295</x:v>
       </x:c>
       <x:c r="E359" s="7" t="n">
-        <x:v>250</x:v>
+        <x:v>285</x:v>
       </x:c>
     </x:row>
     <x:row r="360" ht="15" hidden="0" customHeight="1">
       <x:c r="A360" s="7" t="n">
-        <x:v>1705</x:v>
+        <x:v>1709</x:v>
       </x:c>
       <x:c r="B360" s="7" t="n">
         <x:v>17</x:v>
       </x:c>
       <x:c r="C360" s="7" t="n">
-        <x:v>4</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="D360" s="7" t="n">
-        <x:v>95</x:v>
+        <x:v>295</x:v>
       </x:c>
       <x:c r="E360" s="7" t="n">
-        <x:v>250</x:v>
+        <x:v>335</x:v>
       </x:c>
     </x:row>
     <x:row r="361" ht="15" hidden="0" customHeight="1">
       <x:c r="A361" s="7" t="n">
-        <x:v>1706</x:v>
+        <x:v>1710</x:v>
       </x:c>
       <x:c r="B361" s="7" t="n">
         <x:v>17</x:v>
       </x:c>
       <x:c r="C361" s="7" t="n">
-        <x:v>5</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="D361" s="7" t="n">
-        <x:v>145</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="E361" s="7" t="n">
-        <x:v>250</x:v>
+        <x:v>335</x:v>
       </x:c>
     </x:row>
     <x:row r="362" ht="15" hidden="0" customHeight="1">
       <x:c r="A362" s="7" t="n">
-        <x:v>1707</x:v>
+        <x:v>1711</x:v>
       </x:c>
       <x:c r="B362" s="7" t="n">
         <x:v>17</x:v>
       </x:c>
       <x:c r="C362" s="7" t="n">
-        <x:v>6</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="D362" s="7" t="n">
-        <x:v>195</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="E362" s="7" t="n">
-        <x:v>250</x:v>
+        <x:v>435</x:v>
       </x:c>
     </x:row>
     <x:row r="363" ht="15" hidden="0" customHeight="1">
       <x:c r="A363" s="7" t="n">
-        <x:v>1708</x:v>
+        <x:v>1712</x:v>
       </x:c>
       <x:c r="B363" s="7" t="n">
         <x:v>17</x:v>
       </x:c>
       <x:c r="C363" s="7" t="n">
-        <x:v>7</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D363" s="7" t="n">
-        <x:v>295</x:v>
+        <x:v>245</x:v>
       </x:c>
       <x:c r="E363" s="7" t="n">
-        <x:v>250</x:v>
+        <x:v>335</x:v>
       </x:c>
     </x:row>
     <x:row r="364" ht="15" hidden="0" customHeight="1">
       <x:c r="A364" s="7" t="n">
-        <x:v>1709</x:v>
+        <x:v>1713</x:v>
       </x:c>
       <x:c r="B364" s="7" t="n">
         <x:v>17</x:v>
       </x:c>
       <x:c r="C364" s="7" t="n">
-        <x:v>8</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="D364" s="7" t="n">
-        <x:v>295</x:v>
+        <x:v>245</x:v>
       </x:c>
       <x:c r="E364" s="7" t="n">
-        <x:v>300</x:v>
+        <x:v>435</x:v>
       </x:c>
     </x:row>
     <x:row r="365" ht="15" hidden="0" customHeight="1">
       <x:c r="A365" s="7" t="n">
-        <x:v>1710</x:v>
+        <x:v>1714</x:v>
       </x:c>
       <x:c r="B365" s="7" t="n">
         <x:v>17</x:v>
       </x:c>
       <x:c r="C365" s="7" t="n">
-        <x:v>9</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D365" s="7" t="n">
-        <x:v>95</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="E365" s="7" t="n">
-        <x:v>360</x:v>
+        <x:v>535</x:v>
       </x:c>
     </x:row>
     <x:row r="366" ht="15" hidden="0" customHeight="1">
       <x:c r="A366" s="7" t="n">
-        <x:v>1711</x:v>
+        <x:v>1715</x:v>
       </x:c>
       <x:c r="B366" s="7" t="n">
         <x:v>17</x:v>
       </x:c>
       <x:c r="C366" s="7" t="n">
-        <x:v>10</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="D366" s="7" t="n">
-        <x:v>145</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="E366" s="7" t="n">
-        <x:v>360</x:v>
+        <x:v>435</x:v>
       </x:c>
     </x:row>
     <x:row r="367" ht="15" hidden="0" customHeight="1">
       <x:c r="A367" s="7" t="n">
-        <x:v>1712</x:v>
+        <x:v>1716</x:v>
       </x:c>
       <x:c r="B367" s="7" t="n">
         <x:v>17</x:v>
       </x:c>
       <x:c r="C367" s="7" t="n">
-        <x:v>11</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="D367" s="7" t="n">
         <x:v>195</x:v>
       </x:c>
       <x:c r="E367" s="7" t="n">
-        <x:v>360</x:v>
+        <x:v>535</x:v>
       </x:c>
     </x:row>
     <x:row r="368" ht="15" hidden="0" customHeight="1">
       <x:c r="A368" s="7" t="n">
-        <x:v>1713</x:v>
+        <x:v>1717</x:v>
       </x:c>
       <x:c r="B368" s="7" t="n">
         <x:v>17</x:v>
       </x:c>
       <x:c r="C368" s="7" t="n">
-        <x:v>12</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="D368" s="7" t="n">
-        <x:v>245</x:v>
+        <x:v>345</x:v>
       </x:c>
       <x:c r="E368" s="7" t="n">
-        <x:v>350</x:v>
+        <x:v>335</x:v>
       </x:c>
     </x:row>
     <x:row r="369" ht="15" hidden="0" customHeight="1">
       <x:c r="A369" s="7" t="n">
-        <x:v>1714</x:v>
+        <x:v>1718</x:v>
       </x:c>
       <x:c r="B369" s="7" t="n">
         <x:v>17</x:v>
       </x:c>
       <x:c r="C369" s="7" t="n">
-        <x:v>13</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="D369" s="7" t="n">
-        <x:v>95</x:v>
+        <x:v>295</x:v>
       </x:c>
       <x:c r="E369" s="7" t="n">
-        <x:v>470</x:v>
+        <x:v>435</x:v>
       </x:c>
     </x:row>
     <x:row r="370" ht="15" hidden="0" customHeight="1">
       <x:c r="A370" s="7" t="n">
-        <x:v>1715</x:v>
+        <x:v>1719</x:v>
       </x:c>
       <x:c r="B370" s="7" t="n">
         <x:v>17</x:v>
       </x:c>
       <x:c r="C370" s="7" t="n">
-        <x:v>14</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="D370" s="7" t="n">
-        <x:v>145</x:v>
+        <x:v>295</x:v>
       </x:c>
       <x:c r="E370" s="7" t="n">
-        <x:v>470</x:v>
+        <x:v>535</x:v>
       </x:c>
     </x:row>
     <x:row r="371" ht="15" hidden="0" customHeight="1">
       <x:c r="A371" s="7" t="n">
-        <x:v>1716</x:v>
+        <x:v>1720</x:v>
       </x:c>
       <x:c r="B371" s="7" t="n">
         <x:v>17</x:v>
       </x:c>
       <x:c r="C371" s="7" t="n">
-        <x:v>15</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="D371" s="7" t="n">
-        <x:v>195</x:v>
+        <x:v>245</x:v>
       </x:c>
       <x:c r="E371" s="7" t="n">
-        <x:v>470</x:v>
+        <x:v>535</x:v>
       </x:c>
     </x:row>
     <x:row r="372" ht="15" hidden="0" customHeight="1">
       <x:c r="A372" s="7" t="n">
-        <x:v>1717</x:v>
+        <x:v>1721</x:v>
       </x:c>
       <x:c r="B372" s="7" t="n">
         <x:v>17</x:v>
       </x:c>
       <x:c r="C372" s="7" t="n">
-        <x:v>16</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="D372" s="7" t="n">
-        <x:v>295</x:v>
+        <x:v>345</x:v>
       </x:c>
       <x:c r="E372" s="7" t="n">
-        <x:v>370</x:v>
+        <x:v>535</x:v>
       </x:c>
     </x:row>
     <x:row r="373" ht="15" hidden="0" customHeight="1">
       <x:c r="A373" s="7" t="n">
-        <x:v>1718</x:v>
+        <x:v>1801</x:v>
       </x:c>
       <x:c r="B373" s="7" t="n">
-        <x:v>17</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C373" s="7" t="n">
-        <x:v>17</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D373" s="7" t="n">
-        <x:v>345</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="E373" s="7" t="n">
-        <x:v>370</x:v>
+        <x:v>135</x:v>
       </x:c>
     </x:row>
     <x:row r="374" ht="15" hidden="0" customHeight="1">
       <x:c r="A374" s="7" t="n">
-        <x:v>1719</x:v>
+        <x:v>1802</x:v>
       </x:c>
       <x:c r="B374" s="7" t="n">
-        <x:v>17</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C374" s="7" t="n">
-        <x:v>18</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="D374" s="7" t="n">
-        <x:v>295</x:v>
+        <x:v>245</x:v>
       </x:c>
       <x:c r="E374" s="7" t="n">
-        <x:v>470</x:v>
+        <x:v>135</x:v>
       </x:c>
     </x:row>
     <x:row r="375" ht="15" hidden="0" customHeight="1">
       <x:c r="A375" s="7" t="n">
-        <x:v>1720</x:v>
+        <x:v>1803</x:v>
       </x:c>
       <x:c r="B375" s="7" t="n">
-        <x:v>17</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C375" s="7" t="n">
-        <x:v>19</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="D375" s="7" t="n">
-        <x:v>75</x:v>
+        <x:v>345</x:v>
       </x:c>
       <x:c r="E375" s="7" t="n">
-        <x:v>575</x:v>
+        <x:v>185</x:v>
       </x:c>
     </x:row>
     <x:row r="376" ht="15" hidden="0" customHeight="1">
       <x:c r="A376" s="7" t="n">
-        <x:v>1721</x:v>
+        <x:v>1804</x:v>
       </x:c>
       <x:c r="B376" s="7" t="n">
-        <x:v>17</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C376" s="7" t="n">
-        <x:v>20</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="D376" s="7" t="n">
-        <x:v>125</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="E376" s="7" t="n">
-        <x:v>575</x:v>
+        <x:v>235</x:v>
       </x:c>
     </x:row>
     <x:row r="377" ht="15" hidden="0" customHeight="1">
       <x:c r="A377" s="7" t="n">
-        <x:v>1722</x:v>
+        <x:v>1805</x:v>
       </x:c>
       <x:c r="B377" s="7" t="n">
-        <x:v>17</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C377" s="7" t="n">
-        <x:v>21</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="D377" s="7" t="n">
-        <x:v>245</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="E377" s="7" t="n">
-        <x:v>470</x:v>
+        <x:v>285</x:v>
       </x:c>
     </x:row>
     <x:row r="378" ht="15" hidden="0" customHeight="1">
       <x:c r="A378" s="7" t="n">
-        <x:v>1801</x:v>
+        <x:v>1806</x:v>
       </x:c>
       <x:c r="B378" s="7" t="n">
         <x:v>18</x:v>
       </x:c>
       <x:c r="C378" s="7" t="n">
-        <x:v>0</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D378" s="7" t="n">
-        <x:v>160</x:v>
+        <x:v>245</x:v>
       </x:c>
       <x:c r="E378" s="7" t="n">
-        <x:v>155</x:v>
+        <x:v>285</x:v>
       </x:c>
     </x:row>
     <x:row r="379" ht="15" hidden="0" customHeight="1">
       <x:c r="A379" s="7" t="n">
-        <x:v>1802</x:v>
+        <x:v>1807</x:v>
       </x:c>
       <x:c r="B379" s="7" t="n">
         <x:v>18</x:v>
       </x:c>
       <x:c r="C379" s="7" t="n">
-        <x:v>1</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="D379" s="7" t="n">
-        <x:v>245</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="E379" s="7" t="n">
-        <x:v>165</x:v>
+        <x:v>335</x:v>
       </x:c>
     </x:row>
     <x:row r="380" ht="15" hidden="0" customHeight="1">
       <x:c r="A380" s="7" t="n">
-        <x:v>1803</x:v>
+        <x:v>1808</x:v>
       </x:c>
       <x:c r="B380" s="7" t="n">
         <x:v>18</x:v>
       </x:c>
       <x:c r="C380" s="7" t="n">
-        <x:v>2</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="D380" s="7" t="n">
-        <x:v>345</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="E380" s="7" t="n">
-        <x:v>165</x:v>
+        <x:v>235</x:v>
       </x:c>
     </x:row>
     <x:row r="381" ht="15" hidden="0" customHeight="1">
       <x:c r="A381" s="7" t="n">
-        <x:v>1804</x:v>
+        <x:v>1809</x:v>
       </x:c>
       <x:c r="B381" s="7" t="n">
         <x:v>18</x:v>
       </x:c>
       <x:c r="C381" s="7" t="n">
-        <x:v>3</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="D381" s="7" t="n">
-        <x:v>45</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="E381" s="7" t="n">
-        <x:v>225</x:v>
+        <x:v>335</x:v>
       </x:c>
     </x:row>
     <x:row r="382" ht="15" hidden="0" customHeight="1">
       <x:c r="A382" s="7" t="n">
-        <x:v>1805</x:v>
+        <x:v>1810</x:v>
       </x:c>
       <x:c r="B382" s="7" t="n">
         <x:v>18</x:v>
       </x:c>
       <x:c r="C382" s="7" t="n">
-        <x:v>4</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="D382" s="7" t="n">
-        <x:v>55</x:v>
+        <x:v>245</x:v>
       </x:c>
       <x:c r="E382" s="7" t="n">
-        <x:v>325</x:v>
+        <x:v>235</x:v>
       </x:c>
     </x:row>
     <x:row r="383" ht="15" hidden="0" customHeight="1">
       <x:c r="A383" s="7" t="n">
-        <x:v>1806</x:v>
+        <x:v>1811</x:v>
       </x:c>
       <x:c r="B383" s="7" t="n">
         <x:v>18</x:v>
       </x:c>
       <x:c r="C383" s="7" t="n">
-        <x:v>5</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="D383" s="7" t="n">
-        <x:v>280</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="E383" s="7" t="n">
-        <x:v>265</x:v>
+        <x:v>435</x:v>
       </x:c>
     </x:row>
     <x:row r="384" ht="15" hidden="0" customHeight="1">
       <x:c r="A384" s="7" t="n">
-        <x:v>1807</x:v>
+        <x:v>1812</x:v>
       </x:c>
       <x:c r="B384" s="7" t="n">
         <x:v>18</x:v>
       </x:c>
       <x:c r="C384" s="7" t="n">
-        <x:v>6</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D384" s="7" t="n">
         <x:v>45</x:v>
       </x:c>
       <x:c r="E384" s="7" t="n">
-        <x:v>275</x:v>
+        <x:v>385</x:v>
       </x:c>
     </x:row>
     <x:row r="385" ht="15" hidden="0" customHeight="1">
       <x:c r="A385" s="7" t="n">
-        <x:v>1808</x:v>
+        <x:v>1813</x:v>
       </x:c>
       <x:c r="B385" s="7" t="n">
         <x:v>18</x:v>
       </x:c>
       <x:c r="C385" s="7" t="n">
-        <x:v>7</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="D385" s="7" t="n">
-        <x:v>165</x:v>
+        <x:v>245</x:v>
       </x:c>
       <x:c r="E385" s="7" t="n">
-        <x:v>215</x:v>
+        <x:v>435</x:v>
       </x:c>
     </x:row>
     <x:row r="386" ht="15" hidden="0" customHeight="1">
       <x:c r="A386" s="7" t="n">
-        <x:v>1809</x:v>
+        <x:v>1814</x:v>
       </x:c>
       <x:c r="B386" s="7" t="n">
         <x:v>18</x:v>
       </x:c>
       <x:c r="C386" s="7" t="n">
-        <x:v>8</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D386" s="7" t="n">
-        <x:v>170</x:v>
+        <x:v>245</x:v>
       </x:c>
       <x:c r="E386" s="7" t="n">
-        <x:v>265</x:v>
+        <x:v>335</x:v>
       </x:c>
     </x:row>
     <x:row r="387" ht="15" hidden="0" customHeight="1">
       <x:c r="A387" s="7" t="n">
-        <x:v>1810</x:v>
+        <x:v>1815</x:v>
       </x:c>
       <x:c r="B387" s="7" t="n">
         <x:v>18</x:v>
       </x:c>
       <x:c r="C387" s="7" t="n">
-        <x:v>9</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="D387" s="7" t="n">
-        <x:v>295</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="E387" s="7" t="n">
-        <x:v>165</x:v>
+        <x:v>435</x:v>
       </x:c>
     </x:row>
     <x:row r="388" ht="15" hidden="0" customHeight="1">
       <x:c r="A388" s="7" t="n">
-        <x:v>1811</x:v>
+        <x:v>1816</x:v>
       </x:c>
       <x:c r="B388" s="7" t="n">
         <x:v>18</x:v>
       </x:c>
       <x:c r="C388" s="7" t="n">
-        <x:v>10</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="D388" s="7" t="n">
-        <x:v>45</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="E388" s="7" t="n">
-        <x:v>425</x:v>
+        <x:v>335</x:v>
       </x:c>
     </x:row>
     <x:row r="389" ht="15" hidden="0" customHeight="1">
       <x:c r="A389" s="7" t="n">
-        <x:v>1812</x:v>
+        <x:v>1817</x:v>
       </x:c>
       <x:c r="B389" s="7" t="n">
         <x:v>18</x:v>
       </x:c>
       <x:c r="C389" s="7" t="n">
-        <x:v>11</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="D389" s="7" t="n">
         <x:v>95</x:v>
       </x:c>
       <x:c r="E389" s="7" t="n">
-        <x:v>405</x:v>
+        <x:v>535</x:v>
       </x:c>
     </x:row>
     <x:row r="390" ht="15" hidden="0" customHeight="1">
       <x:c r="A390" s="7" t="n">
-        <x:v>1813</x:v>
+        <x:v>1818</x:v>
       </x:c>
       <x:c r="B390" s="7" t="n">
         <x:v>18</x:v>
       </x:c>
       <x:c r="C390" s="7" t="n">
-        <x:v>12</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="D390" s="7" t="n">
-        <x:v>245</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="E390" s="7" t="n">
-        <x:v>405</x:v>
+        <x:v>435</x:v>
       </x:c>
     </x:row>
     <x:row r="391" ht="15" hidden="0" customHeight="1">
       <x:c r="A391" s="7" t="n">
-        <x:v>1814</x:v>
+        <x:v>1819</x:v>
       </x:c>
       <x:c r="B391" s="7" t="n">
         <x:v>18</x:v>
       </x:c>
       <x:c r="C391" s="7" t="n">
-        <x:v>13</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="D391" s="7" t="n">
-        <x:v>280</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="E391" s="7" t="n">
-        <x:v>315</x:v>
+        <x:v>535</x:v>
       </x:c>
     </x:row>
     <x:row r="392" ht="15" hidden="0" customHeight="1">
       <x:c r="A392" s="7" t="n">
-        <x:v>1815</x:v>
+        <x:v>1820</x:v>
       </x:c>
       <x:c r="B392" s="7" t="n">
         <x:v>18</x:v>
       </x:c>
       <x:c r="C392" s="7" t="n">
-        <x:v>14</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="D392" s="7" t="n">
-        <x:v>55</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="E392" s="7" t="n">
-        <x:v>375</x:v>
+        <x:v>185</x:v>
       </x:c>
     </x:row>
     <x:row r="393" ht="15" hidden="0" customHeight="1">
       <x:c r="A393" s="7" t="n">
-        <x:v>1816</x:v>
+        <x:v>1821</x:v>
       </x:c>
       <x:c r="B393" s="7" t="n">
         <x:v>18</x:v>
       </x:c>
       <x:c r="C393" s="7" t="n">
-        <x:v>15</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="D393" s="7" t="n">
-        <x:v>280</x:v>
+        <x:v>345</x:v>
       </x:c>
       <x:c r="E393" s="7" t="n">
-        <x:v>365</x:v>
+        <x:v>235</x:v>
       </x:c>
     </x:row>
     <x:row r="394" ht="15" hidden="0" customHeight="1">
       <x:c r="A394" s="7" t="n">
-        <x:v>1817</x:v>
+        <x:v>1822</x:v>
       </x:c>
       <x:c r="B394" s="7" t="n">
         <x:v>18</x:v>
       </x:c>
       <x:c r="C394" s="7" t="n">
-        <x:v>16</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="D394" s="7" t="n">
-        <x:v>65</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="E394" s="7" t="n">
-        <x:v>555</x:v>
+        <x:v>135</x:v>
       </x:c>
     </x:row>
     <x:row r="395" ht="15" hidden="0" customHeight="1">
       <x:c r="A395" s="7" t="n">
-        <x:v>1818</x:v>
+        <x:v>1901</x:v>
       </x:c>
       <x:c r="B395" s="7" t="n">
-        <x:v>18</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C395" s="7" t="n">
-        <x:v>17</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D395" s="7" t="n">
-        <x:v>145</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="E395" s="7" t="n">
-        <x:v>395</x:v>
+        <x:v>185</x:v>
       </x:c>
     </x:row>
     <x:row r="396" ht="15" hidden="0" customHeight="1">
       <x:c r="A396" s="7" t="n">
-        <x:v>1819</x:v>
+        <x:v>1902</x:v>
       </x:c>
       <x:c r="B396" s="7" t="n">
-        <x:v>18</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C396" s="7" t="n">
-        <x:v>18</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="D396" s="7" t="n">
-        <x:v>195</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="E396" s="7" t="n">
-        <x:v>395</x:v>
+        <x:v>185</x:v>
       </x:c>
     </x:row>
     <x:row r="397" ht="15" hidden="0" customHeight="1">
       <x:c r="A397" s="7" t="n">
-        <x:v>1820</x:v>
+        <x:v>1903</x:v>
       </x:c>
       <x:c r="B397" s="7" t="n">
-        <x:v>18</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C397" s="7" t="n">
-        <x:v>19</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="D397" s="7" t="n">
-        <x:v>45</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="E397" s="7" t="n">
-        <x:v>505</x:v>
+        <x:v>185</x:v>
       </x:c>
     </x:row>
     <x:row r="398" ht="15" hidden="0" customHeight="1">
       <x:c r="A398" s="7" t="n">
-        <x:v>1901</x:v>
+        <x:v>1904</x:v>
       </x:c>
       <x:c r="B398" s="7" t="n">
         <x:v>19</x:v>
       </x:c>
       <x:c r="C398" s="7" t="n">
-        <x:v>0</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="D398" s="7" t="n">
-        <x:v>95</x:v>
+        <x:v>245</x:v>
       </x:c>
       <x:c r="E398" s="7" t="n">
-        <x:v>200</x:v>
+        <x:v>185</x:v>
       </x:c>
     </x:row>
     <x:row r="399" ht="15" hidden="0" customHeight="1">
       <x:c r="A399" s="7" t="n">
-        <x:v>1902</x:v>
+        <x:v>1905</x:v>
       </x:c>
       <x:c r="B399" s="7" t="n">
         <x:v>19</x:v>
       </x:c>
       <x:c r="C399" s="7" t="n">
-        <x:v>1</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="D399" s="7" t="n">
-        <x:v>145</x:v>
+        <x:v>295</x:v>
       </x:c>
       <x:c r="E399" s="7" t="n">
-        <x:v>200</x:v>
+        <x:v>235</x:v>
       </x:c>
     </x:row>
     <x:row r="400" ht="15" hidden="0" customHeight="1">
       <x:c r="A400" s="7" t="n">
-        <x:v>1903</x:v>
+        <x:v>1906</x:v>
       </x:c>
       <x:c r="B400" s="7" t="n">
         <x:v>19</x:v>
       </x:c>
       <x:c r="C400" s="7" t="n">
-        <x:v>2</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D400" s="7" t="n">
-        <x:v>195</x:v>
+        <x:v>295</x:v>
       </x:c>
       <x:c r="E400" s="7" t="n">
-        <x:v>200</x:v>
+        <x:v>285</x:v>
       </x:c>
     </x:row>
     <x:row r="401" ht="15" hidden="0" customHeight="1">
       <x:c r="A401" s="7" t="n">
-        <x:v>1904</x:v>
+        <x:v>1907</x:v>
       </x:c>
       <x:c r="B401" s="7" t="n">
         <x:v>19</x:v>
       </x:c>
       <x:c r="C401" s="7" t="n">
-        <x:v>3</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="D401" s="7" t="n">
-        <x:v>245</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="E401" s="7" t="n">
-        <x:v>200</x:v>
+        <x:v>285</x:v>
       </x:c>
     </x:row>
     <x:row r="402" ht="15" hidden="0" customHeight="1">
       <x:c r="A402" s="7" t="n">
-        <x:v>1905</x:v>
+        <x:v>1908</x:v>
       </x:c>
       <x:c r="B402" s="7" t="n">
         <x:v>19</x:v>
       </x:c>
       <x:c r="C402" s="7" t="n">
-        <x:v>4</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="D402" s="7" t="n">
-        <x:v>295</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="E402" s="7" t="n">
-        <x:v>200</x:v>
+        <x:v>285</x:v>
       </x:c>
     </x:row>
     <x:row r="403" ht="15" hidden="0" customHeight="1">
       <x:c r="A403" s="7" t="n">
-        <x:v>1906</x:v>
+        <x:v>1909</x:v>
       </x:c>
       <x:c r="B403" s="7" t="n">
         <x:v>19</x:v>
       </x:c>
       <x:c r="C403" s="7" t="n">
-        <x:v>5</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="D403" s="7" t="n">
-        <x:v>295</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="E403" s="7" t="n">
-        <x:v>250</x:v>
+        <x:v>285</x:v>
       </x:c>
     </x:row>
     <x:row r="404" ht="15" hidden="0" customHeight="1">
       <x:c r="A404" s="7" t="n">
-        <x:v>1907</x:v>
+        <x:v>1910</x:v>
       </x:c>
       <x:c r="B404" s="7" t="n">
         <x:v>19</x:v>
       </x:c>
       <x:c r="C404" s="7" t="n">
-        <x:v>6</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="D404" s="7" t="n">
-        <x:v>45</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="E404" s="7" t="n">
-        <x:v>300</x:v>
+        <x:v>285</x:v>
       </x:c>
     </x:row>
     <x:row r="405" ht="15" hidden="0" customHeight="1">
       <x:c r="A405" s="7" t="n">
-        <x:v>1908</x:v>
+        <x:v>1911</x:v>
       </x:c>
       <x:c r="B405" s="7" t="n">
         <x:v>19</x:v>
       </x:c>
       <x:c r="C405" s="7" t="n">
-        <x:v>7</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="D405" s="7" t="n">
-        <x:v>95</x:v>
+        <x:v>295</x:v>
       </x:c>
       <x:c r="E405" s="7" t="n">
-        <x:v>300</x:v>
+        <x:v>335</x:v>
       </x:c>
     </x:row>
     <x:row r="406" ht="15" hidden="0" customHeight="1">
       <x:c r="A406" s="7" t="n">
-        <x:v>1909</x:v>
+        <x:v>1912</x:v>
       </x:c>
       <x:c r="B406" s="7" t="n">
         <x:v>19</x:v>
       </x:c>
       <x:c r="C406" s="7" t="n">
-        <x:v>8</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D406" s="7" t="n">
-        <x:v>145</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="E406" s="7" t="n">
-        <x:v>310</x:v>
+        <x:v>335</x:v>
       </x:c>
     </x:row>
     <x:row r="407" ht="15" hidden="0" customHeight="1">
       <x:c r="A407" s="7" t="n">
-        <x:v>1910</x:v>
+        <x:v>1913</x:v>
       </x:c>
       <x:c r="B407" s="7" t="n">
         <x:v>19</x:v>
       </x:c>
       <x:c r="C407" s="7" t="n">
-        <x:v>9</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="D407" s="7" t="n">
-        <x:v>195</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="E407" s="7" t="n">
-        <x:v>310</x:v>
+        <x:v>385</x:v>
       </x:c>
     </x:row>
     <x:row r="408" ht="15" hidden="0" customHeight="1">
       <x:c r="A408" s="7" t="n">
-        <x:v>1911</x:v>
+        <x:v>1914</x:v>
       </x:c>
       <x:c r="B408" s="7" t="n">
         <x:v>19</x:v>
       </x:c>
       <x:c r="C408" s="7" t="n">
-        <x:v>10</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D408" s="7" t="n">
-        <x:v>295</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="E408" s="7" t="n">
-        <x:v>300</x:v>
+        <x:v>385</x:v>
       </x:c>
     </x:row>
     <x:row r="409" ht="15" hidden="0" customHeight="1">
       <x:c r="A409" s="7" t="n">
-        <x:v>1912</x:v>
+        <x:v>1915</x:v>
       </x:c>
       <x:c r="B409" s="7" t="n">
         <x:v>19</x:v>
       </x:c>
       <x:c r="C409" s="7" t="n">
-        <x:v>11</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="D409" s="7" t="n">
-        <x:v>45</x:v>
+        <x:v>245</x:v>
       </x:c>
       <x:c r="E409" s="7" t="n">
-        <x:v>355</x:v>
+        <x:v>385</x:v>
       </x:c>
     </x:row>
     <x:row r="410" ht="15" hidden="0" customHeight="1">
       <x:c r="A410" s="7" t="n">
-        <x:v>1913</x:v>
+        <x:v>1916</x:v>
       </x:c>
       <x:c r="B410" s="7" t="n">
         <x:v>19</x:v>
       </x:c>
       <x:c r="C410" s="7" t="n">
-        <x:v>12</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="D410" s="7" t="n">
-        <x:v>145</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="E410" s="7" t="n">
-        <x:v>420</x:v>
+        <x:v>385</x:v>
       </x:c>
     </x:row>
     <x:row r="411" ht="15" hidden="0" customHeight="1">
       <x:c r="A411" s="7" t="n">
-        <x:v>1914</x:v>
+        <x:v>1917</x:v>
       </x:c>
       <x:c r="B411" s="7" t="n">
         <x:v>19</x:v>
       </x:c>
       <x:c r="C411" s="7" t="n">
-        <x:v>13</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="D411" s="7" t="n">
-        <x:v>195</x:v>
+        <x:v>245</x:v>
       </x:c>
       <x:c r="E411" s="7" t="n">
-        <x:v>420</x:v>
+        <x:v>485</x:v>
       </x:c>
     </x:row>
     <x:row r="412" ht="15" hidden="0" customHeight="1">
       <x:c r="A412" s="7" t="n">
-        <x:v>1915</x:v>
+        <x:v>1918</x:v>
       </x:c>
       <x:c r="B412" s="7" t="n">
         <x:v>19</x:v>
       </x:c>
       <x:c r="C412" s="7" t="n">
-        <x:v>14</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="D412" s="7" t="n">
-        <x:v>295</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="E412" s="7" t="n">
-        <x:v>350</x:v>
+        <x:v>435</x:v>
       </x:c>
     </x:row>
     <x:row r="413" ht="15" hidden="0" customHeight="1">
       <x:c r="A413" s="7" t="n">
-        <x:v>1916</x:v>
+        <x:v>1919</x:v>
       </x:c>
       <x:c r="B413" s="7" t="n">
         <x:v>19</x:v>
       </x:c>
       <x:c r="C413" s="7" t="n">
-        <x:v>15</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="D413" s="7" t="n">
-        <x:v>45</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="E413" s="7" t="n">
-        <x:v>405</x:v>
+        <x:v>485</x:v>
       </x:c>
     </x:row>
     <x:row r="414" ht="15" hidden="0" customHeight="1">
       <x:c r="A414" s="7" t="n">
-        <x:v>1917</x:v>
+        <x:v>1920</x:v>
       </x:c>
       <x:c r="B414" s="7" t="n">
         <x:v>19</x:v>
       </x:c>
       <x:c r="C414" s="7" t="n">
-        <x:v>16</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="D414" s="7" t="n">
-        <x:v>295</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="E414" s="7" t="n">
-        <x:v>405</x:v>
+        <x:v>485</x:v>
       </x:c>
     </x:row>
     <x:row r="415" ht="15" hidden="0" customHeight="1">
       <x:c r="A415" s="7" t="n">
-        <x:v>1918</x:v>
+        <x:v>1921</x:v>
       </x:c>
       <x:c r="B415" s="7" t="n">
         <x:v>19</x:v>
       </x:c>
       <x:c r="C415" s="7" t="n">
-        <x:v>17</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="D415" s="7" t="n">
-        <x:v>45</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="E415" s="7" t="n">
-        <x:v>455</x:v>
+        <x:v>485</x:v>
       </x:c>
     </x:row>
     <x:row r="416" ht="15" hidden="0" customHeight="1">
       <x:c r="A416" s="7" t="n">
-        <x:v>1919</x:v>
+        <x:v>2001</x:v>
       </x:c>
       <x:c r="B416" s="7" t="n">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="C416" s="7" t="n">
-        <x:v>18</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D416" s="7" t="n">
-        <x:v>245</x:v>
+        <x:v>345</x:v>
       </x:c>
       <x:c r="E416" s="7" t="n">
-        <x:v>420</x:v>
+        <x:v>185</x:v>
       </x:c>
     </x:row>
     <x:row r="417" ht="15" hidden="0" customHeight="1">
       <x:c r="A417" s="7" t="n">
-        <x:v>1920</x:v>
+        <x:v>2002</x:v>
       </x:c>
       <x:c r="B417" s="7" t="n">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="C417" s="7" t="n">
-        <x:v>19</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="D417" s="7" t="n">
-        <x:v>195</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="E417" s="7" t="n">
-        <x:v>520</x:v>
+        <x:v>235</x:v>
       </x:c>
     </x:row>
     <x:row r="418" ht="15" hidden="0" customHeight="1">
       <x:c r="A418" s="7" t="n">
-        <x:v>1921</x:v>
+        <x:v>2003</x:v>
       </x:c>
       <x:c r="B418" s="7" t="n">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="C418" s="7" t="n">
-        <x:v>20</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="D418" s="7" t="n">
-        <x:v>245</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="E418" s="7" t="n">
-        <x:v>520</x:v>
+        <x:v>185</x:v>
       </x:c>
     </x:row>
     <x:row r="419" ht="15" hidden="0" customHeight="1">
       <x:c r="A419" s="7" t="n">
-        <x:v>1922</x:v>
+        <x:v>2004</x:v>
       </x:c>
       <x:c r="B419" s="7" t="n">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="C419" s="7" t="n">
-        <x:v>21</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="D419" s="7" t="n">
-        <x:v>45</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="E419" s="7" t="n">
-        <x:v>505</x:v>
+        <x:v>185</x:v>
       </x:c>
     </x:row>
     <x:row r="420" ht="15" hidden="0" customHeight="1">
       <x:c r="A420" s="7" t="n">
-        <x:v>2001</x:v>
+        <x:v>2005</x:v>
       </x:c>
       <x:c r="B420" s="7" t="n">
         <x:v>20</x:v>
       </x:c>
       <x:c r="C420" s="7" t="n">
-        <x:v>0</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="D420" s="7" t="n">
-        <x:v>345</x:v>
+        <x:v>245</x:v>
       </x:c>
       <x:c r="E420" s="7" t="n">
-        <x:v>150</x:v>
+        <x:v>185</x:v>
       </x:c>
     </x:row>
     <x:row r="421" ht="15" hidden="0" customHeight="1">
       <x:c r="A421" s="7" t="n">
-        <x:v>2002</x:v>
+        <x:v>2006</x:v>
       </x:c>
       <x:c r="B421" s="7" t="n">
         <x:v>20</x:v>
       </x:c>
       <x:c r="C421" s="7" t="n">
-        <x:v>1</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D421" s="7" t="n">
-        <x:v>45</x:v>
+        <x:v>245</x:v>
       </x:c>
       <x:c r="E421" s="7" t="n">
-        <x:v>215</x:v>
+        <x:v>285</x:v>
       </x:c>
     </x:row>
     <x:row r="422" ht="15" hidden="0" customHeight="1">
       <x:c r="A422" s="7" t="n">
-        <x:v>2003</x:v>
+        <x:v>2007</x:v>
       </x:c>
       <x:c r="B422" s="7" t="n">
         <x:v>20</x:v>
       </x:c>
       <x:c r="C422" s="7" t="n">
-        <x:v>2</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="D422" s="7" t="n">
-        <x:v>95</x:v>
+        <x:v>345</x:v>
       </x:c>
       <x:c r="E422" s="7" t="n">
-        <x:v>200</x:v>
+        <x:v>235</x:v>
       </x:c>
     </x:row>
     <x:row r="423" ht="15" hidden="0" customHeight="1">
       <x:c r="A423" s="7" t="n">
-        <x:v>2004</x:v>
+        <x:v>2008</x:v>
       </x:c>
       <x:c r="B423" s="7" t="n">
         <x:v>20</x:v>
       </x:c>
       <x:c r="C423" s="7" t="n">
-        <x:v>3</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="D423" s="7" t="n">
-        <x:v>145</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="E423" s="7" t="n">
-        <x:v>200</x:v>
+        <x:v>285</x:v>
       </x:c>
     </x:row>
     <x:row r="424" ht="15" hidden="0" customHeight="1">
       <x:c r="A424" s="7" t="n">
-        <x:v>2005</x:v>
+        <x:v>2009</x:v>
       </x:c>
       <x:c r="B424" s="7" t="n">
         <x:v>20</x:v>
       </x:c>
       <x:c r="C424" s="7" t="n">
-        <x:v>4</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="D424" s="7" t="n">
-        <x:v>195</x:v>
+        <x:v>345</x:v>
       </x:c>
       <x:c r="E424" s="7" t="n">
-        <x:v>200</x:v>
+        <x:v>285</x:v>
       </x:c>
     </x:row>
     <x:row r="425" ht="15" hidden="0" customHeight="1">
       <x:c r="A425" s="7" t="n">
-        <x:v>2006</x:v>
+        <x:v>2010</x:v>
       </x:c>
       <x:c r="B425" s="7" t="n">
         <x:v>20</x:v>
       </x:c>
       <x:c r="C425" s="7" t="n">
-        <x:v>5</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="D425" s="7" t="n">
-        <x:v>245</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="E425" s="7" t="n">
-        <x:v>200</x:v>
+        <x:v>385</x:v>
       </x:c>
     </x:row>
     <x:row r="426" ht="15" hidden="0" customHeight="1">
       <x:c r="A426" s="7" t="n">
-        <x:v>2007</x:v>
+        <x:v>2011</x:v>
       </x:c>
       <x:c r="B426" s="7" t="n">
         <x:v>20</x:v>
       </x:c>
       <x:c r="C426" s="7" t="n">
-        <x:v>6</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="D426" s="7" t="n">
-        <x:v>345</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="E426" s="7" t="n">
-        <x:v>200</x:v>
+        <x:v>285</x:v>
       </x:c>
     </x:row>
     <x:row r="427" ht="15" hidden="0" customHeight="1">
       <x:c r="A427" s="7" t="n">
-        <x:v>2008</x:v>
+        <x:v>2012</x:v>
       </x:c>
       <x:c r="B427" s="7" t="n">
         <x:v>20</x:v>
       </x:c>
       <x:c r="C427" s="7" t="n">
-        <x:v>7</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D427" s="7" t="n">
-        <x:v>45</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="E427" s="7" t="n">
-        <x:v>265</x:v>
+        <x:v>285</x:v>
       </x:c>
     </x:row>
     <x:row r="428" ht="15" hidden="0" customHeight="1">
       <x:c r="A428" s="7" t="n">
-        <x:v>2009</x:v>
+        <x:v>2013</x:v>
       </x:c>
       <x:c r="B428" s="7" t="n">
         <x:v>20</x:v>
       </x:c>
       <x:c r="C428" s="7" t="n">
-        <x:v>8</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="D428" s="7" t="n">
-        <x:v>345</x:v>
+        <x:v>295</x:v>
       </x:c>
       <x:c r="E428" s="7" t="n">
-        <x:v>250</x:v>
+        <x:v>285</x:v>
       </x:c>
     </x:row>
     <x:row r="429" ht="15" hidden="0" customHeight="1">
       <x:c r="A429" s="7" t="n">
-        <x:v>2010</x:v>
+        <x:v>2014</x:v>
       </x:c>
       <x:c r="B429" s="7" t="n">
         <x:v>20</x:v>
       </x:c>
       <x:c r="C429" s="7" t="n">
-        <x:v>9</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D429" s="7" t="n">
-        <x:v>45</x:v>
+        <x:v>295</x:v>
       </x:c>
       <x:c r="E429" s="7" t="n">
-        <x:v>315</x:v>
+        <x:v>385</x:v>
       </x:c>
     </x:row>
     <x:row r="430" ht="15" hidden="0" customHeight="1">
       <x:c r="A430" s="7" t="n">
-        <x:v>2011</x:v>
+        <x:v>2015</x:v>
       </x:c>
       <x:c r="B430" s="7" t="n">
         <x:v>20</x:v>
       </x:c>
       <x:c r="C430" s="7" t="n">
-        <x:v>10</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="D430" s="7" t="n">
-        <x:v>145</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="E430" s="7" t="n">
-        <x:v>310</x:v>
+        <x:v>435</x:v>
       </x:c>
     </x:row>
     <x:row r="431" ht="15" hidden="0" customHeight="1">
       <x:c r="A431" s="7" t="n">
-        <x:v>2012</x:v>
+        <x:v>2016</x:v>
       </x:c>
       <x:c r="B431" s="7" t="n">
         <x:v>20</x:v>
       </x:c>
       <x:c r="C431" s="7" t="n">
-        <x:v>11</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="D431" s="7" t="n">
-        <x:v>195</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="E431" s="7" t="n">
-        <x:v>310</x:v>
+        <x:v>385</x:v>
       </x:c>
     </x:row>
     <x:row r="432" ht="15" hidden="0" customHeight="1">
       <x:c r="A432" s="7" t="n">
-        <x:v>2013</x:v>
+        <x:v>2017</x:v>
       </x:c>
       <x:c r="B432" s="7" t="n">
         <x:v>20</x:v>
       </x:c>
       <x:c r="C432" s="7" t="n">
-        <x:v>12</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="D432" s="7" t="n">
-        <x:v>245</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="E432" s="7" t="n">
-        <x:v>310</x:v>
+        <x:v>385</x:v>
       </x:c>
     </x:row>
     <x:row r="433" ht="15" hidden="0" customHeight="1">
       <x:c r="A433" s="7" t="n">
-        <x:v>2014</x:v>
+        <x:v>2018</x:v>
       </x:c>
       <x:c r="B433" s="7" t="n">
         <x:v>20</x:v>
       </x:c>
       <x:c r="C433" s="7" t="n">
-        <x:v>13</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="D433" s="7" t="n">
-        <x:v>295</x:v>
+        <x:v>245</x:v>
       </x:c>
       <x:c r="E433" s="7" t="n">
-        <x:v>300</x:v>
+        <x:v>385</x:v>
       </x:c>
     </x:row>
     <x:row r="434" ht="15" hidden="0" customHeight="1">
       <x:c r="A434" s="7" t="n">
-        <x:v>2015</x:v>
+        <x:v>2019</x:v>
       </x:c>
       <x:c r="B434" s="7" t="n">
         <x:v>20</x:v>
       </x:c>
       <x:c r="C434" s="7" t="n">
-        <x:v>14</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="D434" s="7" t="n">
-        <x:v>45</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="E434" s="7" t="n">
-        <x:v>365</x:v>
+        <x:v>485</x:v>
       </x:c>
     </x:row>
     <x:row r="435" ht="15" hidden="0" customHeight="1">
       <x:c r="A435" s="7" t="n">
-        <x:v>2016</x:v>
+        <x:v>2020</x:v>
       </x:c>
       <x:c r="B435" s="7" t="n">
         <x:v>20</x:v>
       </x:c>
       <x:c r="C435" s="7" t="n">
-        <x:v>15</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="D435" s="7" t="n">
-        <x:v>145</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="E435" s="7" t="n">
-        <x:v>420</x:v>
+        <x:v>535</x:v>
       </x:c>
     </x:row>
     <x:row r="436" ht="15" hidden="0" customHeight="1">
       <x:c r="A436" s="7" t="n">
-        <x:v>2017</x:v>
+        <x:v>2021</x:v>
       </x:c>
       <x:c r="B436" s="7" t="n">
         <x:v>20</x:v>
       </x:c>
       <x:c r="C436" s="7" t="n">
-        <x:v>16</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="D436" s="7" t="n">
-        <x:v>195</x:v>
+        <x:v>245</x:v>
       </x:c>
       <x:c r="E436" s="7" t="n">
-        <x:v>420</x:v>
+        <x:v>485</x:v>
       </x:c>
     </x:row>
     <x:row r="437" ht="15" hidden="0" customHeight="1">
       <x:c r="A437" s="7" t="n">
-        <x:v>2018</x:v>
+        <x:v>2022</x:v>
       </x:c>
       <x:c r="B437" s="7" t="n">
         <x:v>20</x:v>
       </x:c>
       <x:c r="C437" s="7" t="n">
-        <x:v>17</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="D437" s="7" t="n">
-        <x:v>245</x:v>
+        <x:v>295</x:v>
       </x:c>
       <x:c r="E437" s="7" t="n">
-        <x:v>420</x:v>
+        <x:v>485</x:v>
       </x:c>
     </x:row>
     <x:row r="438" ht="15" hidden="0" customHeight="1">
       <x:c r="A438" s="7" t="n">
-        <x:v>2019</x:v>
+        <x:v>2023</x:v>
       </x:c>
       <x:c r="B438" s="7" t="n">
-        <x:v>20</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C438" s="7" t="n">
-        <x:v>18</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D438" s="7" t="n">
-        <x:v>95</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="E438" s="7" t="n">
-        <x:v>420</x:v>
+        <x:v>185</x:v>
       </x:c>
     </x:row>
     <x:row r="439" ht="15" hidden="0" customHeight="1">
       <x:c r="A439" s="7" t="n">
-        <x:v>2020</x:v>
+        <x:v>2024</x:v>
       </x:c>
       <x:c r="B439" s="7" t="n">
-        <x:v>20</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C439" s="7" t="n">
-        <x:v>19</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="D439" s="7" t="n">
-        <x:v>95</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="E439" s="7" t="n">
-        <x:v>470</x:v>
+        <x:v>185</x:v>
       </x:c>
     </x:row>
     <x:row r="440" ht="15" hidden="0" customHeight="1">
       <x:c r="A440" s="7" t="n">
-        <x:v>2021</x:v>
+        <x:v>2025</x:v>
       </x:c>
       <x:c r="B440" s="7" t="n">
-        <x:v>20</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C440" s="7" t="n">
-        <x:v>20</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="D440" s="7" t="n">
-        <x:v>195</x:v>
+        <x:v>245</x:v>
       </x:c>
       <x:c r="E440" s="7" t="n">
-        <x:v>520</x:v>
+        <x:v>185</x:v>
       </x:c>
     </x:row>
     <x:row r="441" ht="15" hidden="0" customHeight="1">
       <x:c r="A441" s="7" t="n">
-        <x:v>2022</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="B441" s="7" t="n">
-        <x:v>20</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C441" s="7" t="n">
-        <x:v>21</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="D441" s="7" t="n">
-        <x:v>245</x:v>
+        <x:v>295</x:v>
       </x:c>
       <x:c r="E441" s="7" t="n">
-        <x:v>520</x:v>
+        <x:v>185</x:v>
       </x:c>
     </x:row>
     <x:row r="442" ht="15" hidden="0" customHeight="1">
       <x:c r="A442" s="7" t="n">
-        <x:v>2023</x:v>
+        <x:v>2027</x:v>
       </x:c>
       <x:c r="B442" s="7" t="n">
         <x:v>21</x:v>
       </x:c>
       <x:c r="C442" s="7" t="n">
-        <x:v>0</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="D442" s="7" t="n">
         <x:v>145</x:v>
       </x:c>
       <x:c r="E442" s="7" t="n">
-        <x:v>185</x:v>
+        <x:v>235</x:v>
       </x:c>
     </x:row>
     <x:row r="443" ht="15" hidden="0" customHeight="1">
       <x:c r="A443" s="7" t="n">
-        <x:v>2024</x:v>
+        <x:v>2028</x:v>
       </x:c>
       <x:c r="B443" s="7" t="n">
         <x:v>21</x:v>
       </x:c>
       <x:c r="C443" s="7" t="n">
-        <x:v>1</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D443" s="7" t="n">
         <x:v>195</x:v>
       </x:c>
       <x:c r="E443" s="7" t="n">
-        <x:v>185</x:v>
+        <x:v>235</x:v>
       </x:c>
     </x:row>
     <x:row r="444" ht="15" hidden="0" customHeight="1">
       <x:c r="A444" s="7" t="n">
-        <x:v>2025</x:v>
+        <x:v>2029</x:v>
       </x:c>
       <x:c r="B444" s="7" t="n">
         <x:v>21</x:v>
       </x:c>
       <x:c r="C444" s="7" t="n">
-        <x:v>2</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="D444" s="7" t="n">
         <x:v>245</x:v>
       </x:c>
       <x:c r="E444" s="7" t="n">
-        <x:v>185</x:v>
+        <x:v>235</x:v>
       </x:c>
     </x:row>
     <x:row r="445" ht="15" hidden="0" customHeight="1">
       <x:c r="A445" s="7" t="n">
-        <x:v>2026</x:v>
+        <x:v>2030</x:v>
       </x:c>
       <x:c r="B445" s="7" t="n">
         <x:v>21</x:v>
       </x:c>
       <x:c r="C445" s="7" t="n">
-        <x:v>3</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="D445" s="7" t="n">
         <x:v>295</x:v>
       </x:c>
       <x:c r="E445" s="7" t="n">
-        <x:v>185</x:v>
+        <x:v>235</x:v>
       </x:c>
     </x:row>
     <x:row r="446">
       <x:c r="A446" t="n">
-        <x:v>2027</x:v>
+        <x:v>2031</x:v>
       </x:c>
       <x:c r="B446" t="n">
         <x:v>21</x:v>
       </x:c>
       <x:c r="C446" t="n">
-        <x:v>4</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="D446" t="n">
-        <x:v>145</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="E446" t="n">
-        <x:v>235</x:v>
+        <x:v>335</x:v>
       </x:c>
     </x:row>
     <x:row r="447">
       <x:c r="A447" t="n">
-        <x:v>2028</x:v>
+        <x:v>2032</x:v>
       </x:c>
       <x:c r="B447" t="n">
         <x:v>21</x:v>
       </x:c>
       <x:c r="C447" t="n">
-        <x:v>5</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="D447" t="n">
-        <x:v>195</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="E447" t="n">
-        <x:v>235</x:v>
+        <x:v>335</x:v>
       </x:c>
     </x:row>
     <x:row r="448">
       <x:c r="A448" t="n">
-        <x:v>2029</x:v>
+        <x:v>2033</x:v>
       </x:c>
       <x:c r="B448" t="n">
         <x:v>21</x:v>
       </x:c>
       <x:c r="C448" t="n">
-        <x:v>6</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="D448" t="n">
-        <x:v>245</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="E448" t="n">
-        <x:v>235</x:v>
+        <x:v>335</x:v>
       </x:c>
     </x:row>
     <x:row r="449">
       <x:c r="A449" t="n">
-        <x:v>2030</x:v>
+        <x:v>2034</x:v>
       </x:c>
       <x:c r="B449" t="n">
         <x:v>21</x:v>
       </x:c>
       <x:c r="C449" t="n">
-        <x:v>7</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D449" t="n">
-        <x:v>295</x:v>
+        <x:v>245</x:v>
       </x:c>
       <x:c r="E449" t="n">
-        <x:v>235</x:v>
+        <x:v>335</x:v>
       </x:c>
     </x:row>
     <x:row r="450">
       <x:c r="A450" t="n">
-        <x:v>2031</x:v>
+        <x:v>2035</x:v>
       </x:c>
       <x:c r="B450" t="n">
         <x:v>21</x:v>
       </x:c>
       <x:c r="C450" t="n">
-        <x:v>8</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="D450" t="n">
         <x:v>95</x:v>
       </x:c>
       <x:c r="E450" t="n">
-        <x:v>335</x:v>
+        <x:v>385</x:v>
       </x:c>
     </x:row>
     <x:row r="451">
       <x:c r="A451" t="n">
-        <x:v>2032</x:v>
+        <x:v>2036</x:v>
       </x:c>
       <x:c r="B451" t="n">
         <x:v>21</x:v>
       </x:c>
       <x:c r="C451" t="n">
-        <x:v>9</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D451" t="n">
         <x:v>145</x:v>
       </x:c>
       <x:c r="E451" t="n">
-        <x:v>335</x:v>
+        <x:v>385</x:v>
       </x:c>
     </x:row>
     <x:row r="452">
       <x:c r="A452" t="n">
-        <x:v>2033</x:v>
+        <x:v>2037</x:v>
       </x:c>
       <x:c r="B452" t="n">
         <x:v>21</x:v>
       </x:c>
       <x:c r="C452" t="n">
-        <x:v>10</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="D452" t="n">
         <x:v>195</x:v>
       </x:c>
       <x:c r="E452" t="n">
-        <x:v>335</x:v>
+        <x:v>385</x:v>
       </x:c>
     </x:row>
     <x:row r="453">
       <x:c r="A453" t="n">
-        <x:v>2034</x:v>
+        <x:v>2038</x:v>
       </x:c>
       <x:c r="B453" t="n">
         <x:v>21</x:v>
       </x:c>
       <x:c r="C453" t="n">
-        <x:v>11</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="D453" t="n">
         <x:v>245</x:v>
       </x:c>
       <x:c r="E453" t="n">
-        <x:v>335</x:v>
+        <x:v>385</x:v>
       </x:c>
     </x:row>
     <x:row r="454">
       <x:c r="A454" t="n">
-        <x:v>2035</x:v>
+        <x:v>2039</x:v>
       </x:c>
       <x:c r="B454" t="n">
         <x:v>21</x:v>
       </x:c>
       <x:c r="C454" t="n">
-        <x:v>12</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="D454" t="n">
-        <x:v>95</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="E454" t="n">
-        <x:v>385</x:v>
+        <x:v>485</x:v>
       </x:c>
     </x:row>
     <x:row r="455">
       <x:c r="A455" t="n">
-        <x:v>2036</x:v>
+        <x:v>2040</x:v>
       </x:c>
       <x:c r="B455" t="n">
         <x:v>21</x:v>
       </x:c>
       <x:c r="C455" t="n">
-        <x:v>13</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="D455" t="n">
-        <x:v>145</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="E455" t="n">
-        <x:v>385</x:v>
+        <x:v>485</x:v>
       </x:c>
     </x:row>
     <x:row r="456">
       <x:c r="A456" t="n">
-        <x:v>2037</x:v>
+        <x:v>2041</x:v>
       </x:c>
       <x:c r="B456" t="n">
         <x:v>21</x:v>
       </x:c>
       <x:c r="C456" t="n">
-        <x:v>14</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="D456" t="n">
-        <x:v>195</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="E456" t="n">
-        <x:v>385</x:v>
+        <x:v>485</x:v>
       </x:c>
     </x:row>
     <x:row r="457">
       <x:c r="A457" t="n">
-        <x:v>2038</x:v>
+        <x:v>2042</x:v>
       </x:c>
       <x:c r="B457" t="n">
         <x:v>21</x:v>
       </x:c>
       <x:c r="C457" t="n">
-        <x:v>15</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="D457" t="n">
-        <x:v>245</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="E457" t="n">
-        <x:v>385</x:v>
+        <x:v>485</x:v>
       </x:c>
     </x:row>
     <x:row r="458">
       <x:c r="A458" t="n">
-        <x:v>2039</x:v>
+        <x:v>2043</x:v>
       </x:c>
       <x:c r="B458" t="n">
         <x:v>21</x:v>
       </x:c>
       <x:c r="C458" t="n">
-        <x:v>16</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="D458" t="n">
-        <x:v>45</x:v>
+        <x:v>245</x:v>
       </x:c>
       <x:c r="E458" t="n">
         <x:v>485</x:v>
@@ -8075,88 +8075,48 @@
     </x:row>
     <x:row r="459">
       <x:c r="A459" t="n">
-        <x:v>2040</x:v>
+        <x:v>2044</x:v>
       </x:c>
       <x:c r="B459" t="n">
         <x:v>21</x:v>
       </x:c>
       <x:c r="C459" t="n">
-        <x:v>17</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="D459" t="n">
-        <x:v>95</x:v>
+        <x:v>245</x:v>
       </x:c>
       <x:c r="E459" t="n">
-        <x:v>485</x:v>
+        <x:v>535</x:v>
       </x:c>
     </x:row>
     <x:row r="460">
-      <x:c r="A460" t="n">
-        <x:v>2041</x:v>
-      </x:c>
-      <x:c r="B460" t="n">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="C460" t="n">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="D460" t="n">
-        <x:v>145</x:v>
-      </x:c>
-      <x:c r="E460" t="n">
-        <x:v>485</x:v>
-      </x:c>
+      <x:c r="A460"/>
+      <x:c r="B460"/>
+      <x:c r="C460"/>
+      <x:c r="D460"/>
+      <x:c r="E460"/>
     </x:row>
     <x:row r="461">
-      <x:c r="A461" t="n">
-        <x:v>2042</x:v>
-      </x:c>
-      <x:c r="B461" t="n">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="C461" t="n">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="D461" t="n">
-        <x:v>195</x:v>
-      </x:c>
-      <x:c r="E461" t="n">
-        <x:v>485</x:v>
-      </x:c>
+      <x:c r="A461"/>
+      <x:c r="B461"/>
+      <x:c r="C461"/>
+      <x:c r="D461"/>
+      <x:c r="E461"/>
     </x:row>
     <x:row r="462">
-      <x:c r="A462" t="n">
-        <x:v>2043</x:v>
-      </x:c>
-      <x:c r="B462" t="n">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="C462" t="n">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="D462" t="n">
-        <x:v>245</x:v>
-      </x:c>
-      <x:c r="E462" t="n">
-        <x:v>485</x:v>
-      </x:c>
+      <x:c r="A462"/>
+      <x:c r="B462"/>
+      <x:c r="C462"/>
+      <x:c r="D462"/>
+      <x:c r="E462"/>
     </x:row>
     <x:row r="463">
-      <x:c r="A463" t="n">
-        <x:v>2044</x:v>
-      </x:c>
-      <x:c r="B463" t="n">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="C463" t="n">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="D463" t="n">
-        <x:v>245</x:v>
-      </x:c>
-      <x:c r="E463" t="n">
-        <x:v>535</x:v>
-      </x:c>
+      <x:c r="A463"/>
+      <x:c r="B463"/>
+      <x:c r="C463"/>
+      <x:c r="D463"/>
+      <x:c r="E463"/>
     </x:row>
     <x:row r="464">
       <x:c r="A464"/>

--- a/design/tables/Spot.xlsx
+++ b/design/tables/Spot.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Spot" sheetId="1" r:id="R7c9b13a390984a02"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Spot" sheetId="1" r:id="R6ac20fc86e964e84"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -8091,60 +8091,3727 @@
       </x:c>
     </x:row>
     <x:row r="460">
-      <x:c r="A460"/>
-      <x:c r="B460"/>
-      <x:c r="C460"/>
-      <x:c r="D460"/>
-      <x:c r="E460"/>
+      <x:c r="A460" t="n">
+        <x:v>2201</x:v>
+      </x:c>
+      <x:c r="B460" t="n">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="C460" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D460" t="n">
+        <x:v>145</x:v>
+      </x:c>
+      <x:c r="E460" t="n">
+        <x:v>235</x:v>
+      </x:c>
     </x:row>
     <x:row r="461">
-      <x:c r="A461"/>
-      <x:c r="B461"/>
-      <x:c r="C461"/>
-      <x:c r="D461"/>
-      <x:c r="E461"/>
+      <x:c r="A461" t="n">
+        <x:v>2202</x:v>
+      </x:c>
+      <x:c r="B461" t="n">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="C461" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D461" t="n">
+        <x:v>195</x:v>
+      </x:c>
+      <x:c r="E461" t="n">
+        <x:v>235</x:v>
+      </x:c>
     </x:row>
     <x:row r="462">
-      <x:c r="A462"/>
-      <x:c r="B462"/>
-      <x:c r="C462"/>
-      <x:c r="D462"/>
-      <x:c r="E462"/>
+      <x:c r="A462" t="n">
+        <x:v>2203</x:v>
+      </x:c>
+      <x:c r="B462" t="n">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="C462" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D462" t="n">
+        <x:v>245</x:v>
+      </x:c>
+      <x:c r="E462" t="n">
+        <x:v>235</x:v>
+      </x:c>
     </x:row>
     <x:row r="463">
-      <x:c r="A463"/>
-      <x:c r="B463"/>
-      <x:c r="C463"/>
-      <x:c r="D463"/>
-      <x:c r="E463"/>
+      <x:c r="A463" t="n">
+        <x:v>2204</x:v>
+      </x:c>
+      <x:c r="B463" t="n">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="C463" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D463" t="n">
+        <x:v>295</x:v>
+      </x:c>
+      <x:c r="E463" t="n">
+        <x:v>235</x:v>
+      </x:c>
     </x:row>
     <x:row r="464">
-      <x:c r="A464"/>
-      <x:c r="B464"/>
-      <x:c r="C464"/>
-      <x:c r="D464"/>
-      <x:c r="E464"/>
+      <x:c r="A464" t="n">
+        <x:v>2205</x:v>
+      </x:c>
+      <x:c r="B464" t="n">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="C464" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D464" t="n">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="E464" t="n">
+        <x:v>335</x:v>
+      </x:c>
     </x:row>
     <x:row r="465">
-      <x:c r="A465"/>
-      <x:c r="B465"/>
-      <x:c r="C465"/>
-      <x:c r="D465"/>
-      <x:c r="E465"/>
+      <x:c r="A465" t="n">
+        <x:v>2206</x:v>
+      </x:c>
+      <x:c r="B465" t="n">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="C465" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D465" t="n">
+        <x:v>145</x:v>
+      </x:c>
+      <x:c r="E465" t="n">
+        <x:v>335</x:v>
+      </x:c>
     </x:row>
     <x:row r="466">
-      <x:c r="A466"/>
-      <x:c r="B466"/>
-      <x:c r="C466"/>
-      <x:c r="D466"/>
-      <x:c r="E466"/>
+      <x:c r="A466" t="n">
+        <x:v>2207</x:v>
+      </x:c>
+      <x:c r="B466" t="n">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="C466" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="D466" t="n">
+        <x:v>195</x:v>
+      </x:c>
+      <x:c r="E466" t="n">
+        <x:v>335</x:v>
+      </x:c>
     </x:row>
     <x:row r="467">
-      <x:c r="A467"/>
-      <x:c r="B467"/>
-      <x:c r="C467"/>
-      <x:c r="D467"/>
-      <x:c r="E467"/>
+      <x:c r="A467" t="n">
+        <x:v>2208</x:v>
+      </x:c>
+      <x:c r="B467" t="n">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="C467" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="D467" t="n">
+        <x:v>245</x:v>
+      </x:c>
+      <x:c r="E467" t="n">
+        <x:v>335</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="468">
+      <x:c r="A468" s="7" t="n">
+        <x:v>2209</x:v>
+      </x:c>
+      <x:c r="B468" s="7" t="n">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="C468" s="7" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="D468" s="7" t="n">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="E468" s="7" t="n">
+        <x:v>385</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="469">
+      <x:c r="A469" s="7" t="n">
+        <x:v>2210</x:v>
+      </x:c>
+      <x:c r="B469" s="7" t="n">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="C469" s="7" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="D469" s="7" t="n">
+        <x:v>145</x:v>
+      </x:c>
+      <x:c r="E469" s="7" t="n">
+        <x:v>435</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="470">
+      <x:c r="A470" s="7" t="n">
+        <x:v>2211</x:v>
+      </x:c>
+      <x:c r="B470" s="7" t="n">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="C470" s="7" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="D470" s="7" t="n">
+        <x:v>195</x:v>
+      </x:c>
+      <x:c r="E470" s="7" t="n">
+        <x:v>435</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="471">
+      <x:c r="A471" s="7" t="n">
+        <x:v>2212</x:v>
+      </x:c>
+      <x:c r="B471" s="7" t="n">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="C471" s="7" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="D471" s="7" t="n">
+        <x:v>245</x:v>
+      </x:c>
+      <x:c r="E471" s="7" t="n">
+        <x:v>435</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="472">
+      <x:c r="A472" s="7" t="n">
+        <x:v>2213</x:v>
+      </x:c>
+      <x:c r="B472" s="7" t="n">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="C472" s="7" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="D472" s="7" t="n">
+        <x:v>345</x:v>
+      </x:c>
+      <x:c r="E472" s="7" t="n">
+        <x:v>335</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="473">
+      <x:c r="A473" s="7" t="n">
+        <x:v>2214</x:v>
+      </x:c>
+      <x:c r="B473" s="7" t="n">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="C473" s="7" t="n">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="D473" s="7" t="n">
+        <x:v>345</x:v>
+      </x:c>
+      <x:c r="E473" s="7" t="n">
+        <x:v>385</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="474">
+      <x:c r="A474" s="7" t="n">
+        <x:v>2215</x:v>
+      </x:c>
+      <x:c r="B474" s="7" t="n">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="C474" s="7" t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="D474" s="7" t="n">
+        <x:v>245</x:v>
+      </x:c>
+      <x:c r="E474" s="7" t="n">
+        <x:v>535</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="475">
+      <x:c r="A475" s="7" t="n">
+        <x:v>2216</x:v>
+      </x:c>
+      <x:c r="B475" s="7" t="n">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="C475" s="7" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="D475" s="7" t="n">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="E475" s="7" t="n">
+        <x:v>435</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="476">
+      <x:c r="A476" s="7" t="n">
+        <x:v>2217</x:v>
+      </x:c>
+      <x:c r="B476" s="7" t="n">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="C476" s="7" t="n">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="D476" s="7" t="n">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="E476" s="7" t="n">
+        <x:v>485</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="477">
+      <x:c r="A477" s="7" t="n">
+        <x:v>2218</x:v>
+      </x:c>
+      <x:c r="B477" s="7" t="n">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="C477" s="7" t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="D477" s="7" t="n">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="E477" s="7" t="n">
+        <x:v>535</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="478">
+      <x:c r="A478" s="7" t="n">
+        <x:v>2219</x:v>
+      </x:c>
+      <x:c r="B478" s="7" t="n">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="C478" s="7" t="n">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="D478" s="7" t="n">
+        <x:v>145</x:v>
+      </x:c>
+      <x:c r="E478" s="7" t="n">
+        <x:v>535</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="479">
+      <x:c r="A479" s="7" t="n">
+        <x:v>2220</x:v>
+      </x:c>
+      <x:c r="B479" s="7" t="n">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="C479" s="7" t="n">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="D479" s="7" t="n">
+        <x:v>195</x:v>
+      </x:c>
+      <x:c r="E479" s="7" t="n">
+        <x:v>535</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="480">
+      <x:c r="A480" s="7" t="n">
+        <x:v>2221</x:v>
+      </x:c>
+      <x:c r="B480" s="7" t="n">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="C480" s="7" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="D480" s="7" t="n">
+        <x:v>345</x:v>
+      </x:c>
+      <x:c r="E480" s="7" t="n">
+        <x:v>285</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="481">
+      <x:c r="A481" s="7" t="n">
+        <x:v>2222</x:v>
+      </x:c>
+      <x:c r="B481" s="7" t="n">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="C481" s="7" t="n">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="D481" s="7" t="n">
+        <x:v>145</x:v>
+      </x:c>
+      <x:c r="E481" s="7" t="n">
+        <x:v>185</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="482">
+      <x:c r="A482" s="7" t="n">
+        <x:v>2301</x:v>
+      </x:c>
+      <x:c r="B482" s="7" t="n">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="C482" s="7" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D482" s="7" t="n">
+        <x:v>145</x:v>
+      </x:c>
+      <x:c r="E482" s="7" t="n">
+        <x:v>235</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="483">
+      <x:c r="A483" s="7" t="n">
+        <x:v>2302</x:v>
+      </x:c>
+      <x:c r="B483" s="7" t="n">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="C483" s="7" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D483" s="7" t="n">
+        <x:v>195</x:v>
+      </x:c>
+      <x:c r="E483" s="7" t="n">
+        <x:v>235</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="484">
+      <x:c r="A484" s="7" t="n">
+        <x:v>2303</x:v>
+      </x:c>
+      <x:c r="B484" s="7" t="n">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="C484" s="7" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D484" s="7" t="n">
+        <x:v>245</x:v>
+      </x:c>
+      <x:c r="E484" s="7" t="n">
+        <x:v>235</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="485">
+      <x:c r="A485" s="7" t="n">
+        <x:v>2304</x:v>
+      </x:c>
+      <x:c r="B485" s="7" t="n">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="C485" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D485" s="7" t="n">
+        <x:v>295</x:v>
+      </x:c>
+      <x:c r="E485" s="7" t="n">
+        <x:v>235</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="486">
+      <x:c r="A486" s="7" t="n">
+        <x:v>2305</x:v>
+      </x:c>
+      <x:c r="B486" s="7" t="n">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="C486" s="7" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D486" s="7" t="n">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="E486" s="7" t="n">
+        <x:v>335</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="487">
+      <x:c r="A487" s="7" t="n">
+        <x:v>2306</x:v>
+      </x:c>
+      <x:c r="B487" s="7" t="n">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="C487" s="7" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D487" s="7" t="n">
+        <x:v>145</x:v>
+      </x:c>
+      <x:c r="E487" s="7" t="n">
+        <x:v>335</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="488">
+      <x:c r="A488" s="7" t="n">
+        <x:v>2307</x:v>
+      </x:c>
+      <x:c r="B488" s="7" t="n">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="C488" s="7" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="D488" s="7" t="n">
+        <x:v>195</x:v>
+      </x:c>
+      <x:c r="E488" s="7" t="n">
+        <x:v>335</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="489">
+      <x:c r="A489" s="7" t="n">
+        <x:v>2308</x:v>
+      </x:c>
+      <x:c r="B489" s="7" t="n">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="C489" s="7" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="D489" s="7" t="n">
+        <x:v>245</x:v>
+      </x:c>
+      <x:c r="E489" s="7" t="n">
+        <x:v>335</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="490">
+      <x:c r="A490" s="7" t="n">
+        <x:v>2309</x:v>
+      </x:c>
+      <x:c r="B490" s="7" t="n">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="C490" s="7" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="D490" s="7" t="n">
+        <x:v>295</x:v>
+      </x:c>
+      <x:c r="E490" s="7" t="n">
+        <x:v>335</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="491">
+      <x:c r="A491" s="7" t="n">
+        <x:v>2310</x:v>
+      </x:c>
+      <x:c r="B491" s="7" t="n">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="C491" s="7" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="D491" s="7" t="n">
+        <x:v>345</x:v>
+      </x:c>
+      <x:c r="E491" s="7" t="n">
+        <x:v>335</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="492">
+      <x:c r="A492" s="7" t="n">
+        <x:v>2311</x:v>
+      </x:c>
+      <x:c r="B492" s="7" t="n">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="C492" s="7" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="D492" s="7" t="n">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="E492" s="7" t="n">
+        <x:v>435</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="493">
+      <x:c r="A493" s="7" t="n">
+        <x:v>2312</x:v>
+      </x:c>
+      <x:c r="B493" s="7" t="n">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="C493" s="7" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="D493" s="7" t="n">
+        <x:v>145</x:v>
+      </x:c>
+      <x:c r="E493" s="7" t="n">
+        <x:v>435</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="494">
+      <x:c r="A494" s="7" t="n">
+        <x:v>2313</x:v>
+      </x:c>
+      <x:c r="B494" s="7" t="n">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="C494" s="7" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="D494" s="7" t="n">
+        <x:v>195</x:v>
+      </x:c>
+      <x:c r="E494" s="7" t="n">
+        <x:v>435</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="495">
+      <x:c r="A495" s="7" t="n">
+        <x:v>2314</x:v>
+      </x:c>
+      <x:c r="B495" s="7" t="n">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="C495" s="7" t="n">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="D495" s="7" t="n">
+        <x:v>245</x:v>
+      </x:c>
+      <x:c r="E495" s="7" t="n">
+        <x:v>435</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="496">
+      <x:c r="A496" s="7" t="n">
+        <x:v>2315</x:v>
+      </x:c>
+      <x:c r="B496" s="7" t="n">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="C496" s="7" t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="D496" s="7" t="n">
+        <x:v>345</x:v>
+      </x:c>
+      <x:c r="E496" s="7" t="n">
+        <x:v>385</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="497">
+      <x:c r="A497" s="7" t="n">
+        <x:v>2316</x:v>
+      </x:c>
+      <x:c r="B497" s="7" t="n">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="C497" s="7" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="D497" s="7" t="n">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="E497" s="7" t="n">
+        <x:v>435</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="498">
+      <x:c r="A498" s="7" t="n">
+        <x:v>2317</x:v>
+      </x:c>
+      <x:c r="B498" s="7" t="n">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="C498" s="7" t="n">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="D498" s="7" t="n">
+        <x:v>245</x:v>
+      </x:c>
+      <x:c r="E498" s="7" t="n">
+        <x:v>485</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="499">
+      <x:c r="A499" s="7" t="n">
+        <x:v>2318</x:v>
+      </x:c>
+      <x:c r="B499" s="7" t="n">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="C499" s="7" t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="D499" s="7" t="n">
+        <x:v>245</x:v>
+      </x:c>
+      <x:c r="E499" s="7" t="n">
+        <x:v>135</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="500">
+      <x:c r="A500" s="7" t="n">
+        <x:v>2319</x:v>
+      </x:c>
+      <x:c r="B500" s="7" t="n">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="C500" s="7" t="n">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="D500" s="7" t="n">
+        <x:v>345</x:v>
+      </x:c>
+      <x:c r="E500" s="7" t="n">
+        <x:v>135</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="501">
+      <x:c r="A501" s="7" t="n">
+        <x:v>2320</x:v>
+      </x:c>
+      <x:c r="B501" s="7" t="n">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="C501" s="7" t="n">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="D501" s="7" t="n">
+        <x:v>295</x:v>
+      </x:c>
+      <x:c r="E501" s="7" t="n">
+        <x:v>135</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="502">
+      <x:c r="A502" s="7" t="n">
+        <x:v>2321</x:v>
+      </x:c>
+      <x:c r="B502" s="7" t="n">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="C502" s="7" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="D502" s="7" t="n">
+        <x:v>195</x:v>
+      </x:c>
+      <x:c r="E502" s="7" t="n">
+        <x:v>135</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="503">
+      <x:c r="A503" s="7" t="n">
+        <x:v>2322</x:v>
+      </x:c>
+      <x:c r="B503" s="7" t="n">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="C503" s="7" t="n">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="D503" s="7" t="n">
+        <x:v>145</x:v>
+      </x:c>
+      <x:c r="E503" s="7" t="n">
+        <x:v>135</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="504">
+      <x:c r="A504" s="7" t="n">
+        <x:v>2401</x:v>
+      </x:c>
+      <x:c r="B504" s="7" t="n">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="C504" s="7" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D504" s="7" t="n">
+        <x:v>145</x:v>
+      </x:c>
+      <x:c r="E504" s="7" t="n">
+        <x:v>235</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="505">
+      <x:c r="A505" s="7" t="n">
+        <x:v>2402</x:v>
+      </x:c>
+      <x:c r="B505" s="7" t="n">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="C505" s="7" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D505" s="7" t="n">
+        <x:v>145</x:v>
+      </x:c>
+      <x:c r="E505" s="7" t="n">
+        <x:v>285</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="506">
+      <x:c r="A506" s="7" t="n">
+        <x:v>2403</x:v>
+      </x:c>
+      <x:c r="B506" s="7" t="n">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="C506" s="7" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D506" s="7" t="n">
+        <x:v>145</x:v>
+      </x:c>
+      <x:c r="E506" s="7" t="n">
+        <x:v>335</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="507">
+      <x:c r="A507" s="7" t="n">
+        <x:v>2404</x:v>
+      </x:c>
+      <x:c r="B507" s="7" t="n">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="C507" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D507" s="7" t="n">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="E507" s="7" t="n">
+        <x:v>435</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="508">
+      <x:c r="A508" s="7" t="n">
+        <x:v>2405</x:v>
+      </x:c>
+      <x:c r="B508" s="7" t="n">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="C508" s="7" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D508" s="7" t="n">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="E508" s="7" t="n">
+        <x:v>485</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="509">
+      <x:c r="A509" s="7" t="n">
+        <x:v>2406</x:v>
+      </x:c>
+      <x:c r="B509" s="7" t="n">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="C509" s="7" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D509" s="7" t="n">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="E509" s="7" t="n">
+        <x:v>535</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="510">
+      <x:c r="A510" s="7" t="n">
+        <x:v>2407</x:v>
+      </x:c>
+      <x:c r="B510" s="7" t="n">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="C510" s="7" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="D510" s="7" t="n">
+        <x:v>145</x:v>
+      </x:c>
+      <x:c r="E510" s="7" t="n">
+        <x:v>485</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="511">
+      <x:c r="A511" s="7" t="n">
+        <x:v>2408</x:v>
+      </x:c>
+      <x:c r="B511" s="7" t="n">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="C511" s="7" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="D511" s="7" t="n">
+        <x:v>145</x:v>
+      </x:c>
+      <x:c r="E511" s="7" t="n">
+        <x:v>135</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="512">
+      <x:c r="A512" s="7" t="n">
+        <x:v>2409</x:v>
+      </x:c>
+      <x:c r="B512" s="7" t="n">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="C512" s="7" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="D512" s="7" t="n">
+        <x:v>145</x:v>
+      </x:c>
+      <x:c r="E512" s="7" t="n">
+        <x:v>185</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="513">
+      <x:c r="A513" s="7" t="n">
+        <x:v>2410</x:v>
+      </x:c>
+      <x:c r="B513" s="7" t="n">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="C513" s="7" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="D513" s="7" t="n">
+        <x:v>245</x:v>
+      </x:c>
+      <x:c r="E513" s="7" t="n">
+        <x:v>235</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="514">
+      <x:c r="A514" s="7" t="n">
+        <x:v>2411</x:v>
+      </x:c>
+      <x:c r="B514" s="7" t="n">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="C514" s="7" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="D514" s="7" t="n">
+        <x:v>245</x:v>
+      </x:c>
+      <x:c r="E514" s="7" t="n">
+        <x:v>285</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="515">
+      <x:c r="A515" s="7" t="n">
+        <x:v>2412</x:v>
+      </x:c>
+      <x:c r="B515" s="7" t="n">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="C515" s="7" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="D515" s="7" t="n">
+        <x:v>145</x:v>
+      </x:c>
+      <x:c r="E515" s="7" t="n">
+        <x:v>385</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="516">
+      <x:c r="A516" s="7" t="n">
+        <x:v>2413</x:v>
+      </x:c>
+      <x:c r="B516" s="7" t="n">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="C516" s="7" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="D516" s="7" t="n">
+        <x:v>145</x:v>
+      </x:c>
+      <x:c r="E516" s="7" t="n">
+        <x:v>435</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="517">
+      <x:c r="A517" s="7" t="n">
+        <x:v>2414</x:v>
+      </x:c>
+      <x:c r="B517" s="7" t="n">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="C517" s="7" t="n">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="D517" s="7" t="n">
+        <x:v>245</x:v>
+      </x:c>
+      <x:c r="E517" s="7" t="n">
+        <x:v>435</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="518">
+      <x:c r="A518" s="7" t="n">
+        <x:v>2415</x:v>
+      </x:c>
+      <x:c r="B518" s="7" t="n">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="C518" s="7" t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="D518" s="7" t="n">
+        <x:v>245</x:v>
+      </x:c>
+      <x:c r="E518" s="7" t="n">
+        <x:v>485</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="519">
+      <x:c r="A519" s="7" t="n">
+        <x:v>2416</x:v>
+      </x:c>
+      <x:c r="B519" s="7" t="n">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="C519" s="7" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="D519" s="7" t="n">
+        <x:v>245</x:v>
+      </x:c>
+      <x:c r="E519" s="7" t="n">
+        <x:v>185</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="520">
+      <x:c r="A520" s="7" t="n">
+        <x:v>2417</x:v>
+      </x:c>
+      <x:c r="B520" s="7" t="n">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="C520" s="7" t="n">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="D520" s="7" t="n">
+        <x:v>345</x:v>
+      </x:c>
+      <x:c r="E520" s="7" t="n">
+        <x:v>235</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="521">
+      <x:c r="A521" s="7" t="n">
+        <x:v>2418</x:v>
+      </x:c>
+      <x:c r="B521" s="7" t="n">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="C521" s="7" t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="D521" s="7" t="n">
+        <x:v>245</x:v>
+      </x:c>
+      <x:c r="E521" s="7" t="n">
+        <x:v>335</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="522">
+      <x:c r="A522" s="7" t="n">
+        <x:v>2419</x:v>
+      </x:c>
+      <x:c r="B522" s="7" t="n">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="C522" s="7" t="n">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="D522" s="7" t="n">
+        <x:v>245</x:v>
+      </x:c>
+      <x:c r="E522" s="7" t="n">
+        <x:v>385</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="523">
+      <x:c r="A523" s="7" t="n">
+        <x:v>2420</x:v>
+      </x:c>
+      <x:c r="B523" s="7" t="n">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="C523" s="7" t="n">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="D523" s="7" t="n">
+        <x:v>245</x:v>
+      </x:c>
+      <x:c r="E523" s="7" t="n">
+        <x:v>535</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="524">
+      <x:c r="A524" s="7" t="n">
+        <x:v>2421</x:v>
+      </x:c>
+      <x:c r="B524" s="7" t="n">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="C524" s="7" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="D524" s="7" t="n">
+        <x:v>345</x:v>
+      </x:c>
+      <x:c r="E524" s="7" t="n">
+        <x:v>185</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="525">
+      <x:c r="A525" s="7" t="n">
+        <x:v>2422</x:v>
+      </x:c>
+      <x:c r="B525" s="7" t="n">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="C525" s="7" t="n">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="D525" s="7" t="n">
+        <x:v>345</x:v>
+      </x:c>
+      <x:c r="E525" s="7" t="n">
+        <x:v>135</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="526">
+      <x:c r="A526" s="7" t="n">
+        <x:v>2501</x:v>
+      </x:c>
+      <x:c r="B526" s="7" t="n">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="C526" s="7" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D526" s="7" t="n">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="E526" s="7" t="n">
+        <x:v>185</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="527">
+      <x:c r="A527" s="7" t="n">
+        <x:v>2502</x:v>
+      </x:c>
+      <x:c r="B527" s="7" t="n">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="C527" s="7" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D527" s="7" t="n">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="E527" s="7" t="n">
+        <x:v>185</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="528">
+      <x:c r="A528" s="7" t="n">
+        <x:v>2503</x:v>
+      </x:c>
+      <x:c r="B528" s="7" t="n">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="C528" s="7" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D528" s="7" t="n">
+        <x:v>145</x:v>
+      </x:c>
+      <x:c r="E528" s="7" t="n">
+        <x:v>185</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="529">
+      <x:c r="A529" s="7" t="n">
+        <x:v>2504</x:v>
+      </x:c>
+      <x:c r="B529" s="7" t="n">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="C529" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D529" s="7" t="n">
+        <x:v>195</x:v>
+      </x:c>
+      <x:c r="E529" s="7" t="n">
+        <x:v>185</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="530">
+      <x:c r="A530" s="7" t="n">
+        <x:v>2505</x:v>
+      </x:c>
+      <x:c r="B530" s="7" t="n">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="C530" s="7" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D530" s="7" t="n">
+        <x:v>245</x:v>
+      </x:c>
+      <x:c r="E530" s="7" t="n">
+        <x:v>185</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="531">
+      <x:c r="A531" s="7" t="n">
+        <x:v>2506</x:v>
+      </x:c>
+      <x:c r="B531" s="7" t="n">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="C531" s="7" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D531" s="7" t="n">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="E531" s="7" t="n">
+        <x:v>285</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="532">
+      <x:c r="A532" s="7" t="n">
+        <x:v>2507</x:v>
+      </x:c>
+      <x:c r="B532" s="7" t="n">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="C532" s="7" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="D532" s="7" t="n">
+        <x:v>145</x:v>
+      </x:c>
+      <x:c r="E532" s="7" t="n">
+        <x:v>285</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="533">
+      <x:c r="A533" s="7" t="n">
+        <x:v>2508</x:v>
+      </x:c>
+      <x:c r="B533" s="7" t="n">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="C533" s="7" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="D533" s="7" t="n">
+        <x:v>195</x:v>
+      </x:c>
+      <x:c r="E533" s="7" t="n">
+        <x:v>285</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="534">
+      <x:c r="A534" s="7" t="n">
+        <x:v>2509</x:v>
+      </x:c>
+      <x:c r="B534" s="7" t="n">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="C534" s="7" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="D534" s="7" t="n">
+        <x:v>245</x:v>
+      </x:c>
+      <x:c r="E534" s="7" t="n">
+        <x:v>285</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="535">
+      <x:c r="A535" s="7" t="n">
+        <x:v>2510</x:v>
+      </x:c>
+      <x:c r="B535" s="7" t="n">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="C535" s="7" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="D535" s="7" t="n">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="E535" s="7" t="n">
+        <x:v>435</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="536">
+      <x:c r="A536" s="7" t="n">
+        <x:v>2511</x:v>
+      </x:c>
+      <x:c r="B536" s="7" t="n">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="C536" s="7" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="D536" s="7" t="n">
+        <x:v>145</x:v>
+      </x:c>
+      <x:c r="E536" s="7" t="n">
+        <x:v>385</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="537">
+      <x:c r="A537" s="7" t="n">
+        <x:v>2512</x:v>
+      </x:c>
+      <x:c r="B537" s="7" t="n">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="C537" s="7" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="D537" s="7" t="n">
+        <x:v>195</x:v>
+      </x:c>
+      <x:c r="E537" s="7" t="n">
+        <x:v>385</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="538">
+      <x:c r="A538" s="7" t="n">
+        <x:v>2513</x:v>
+      </x:c>
+      <x:c r="B538" s="7" t="n">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="C538" s="7" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="D538" s="7" t="n">
+        <x:v>295</x:v>
+      </x:c>
+      <x:c r="E538" s="7" t="n">
+        <x:v>285</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="539">
+      <x:c r="A539" s="7" t="n">
+        <x:v>2514</x:v>
+      </x:c>
+      <x:c r="B539" s="7" t="n">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="C539" s="7" t="n">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="D539" s="7" t="n">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="E539" s="7" t="n">
+        <x:v>385</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="540">
+      <x:c r="A540" s="7" t="n">
+        <x:v>2515</x:v>
+      </x:c>
+      <x:c r="B540" s="7" t="n">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="C540" s="7" t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="D540" s="7" t="n">
+        <x:v>195</x:v>
+      </x:c>
+      <x:c r="E540" s="7" t="n">
+        <x:v>485</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="541">
+      <x:c r="A541" s="7" t="n">
+        <x:v>2516</x:v>
+      </x:c>
+      <x:c r="B541" s="7" t="n">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="C541" s="7" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="D541" s="7" t="n">
+        <x:v>245</x:v>
+      </x:c>
+      <x:c r="E541" s="7" t="n">
+        <x:v>385</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="542">
+      <x:c r="A542" s="7" t="n">
+        <x:v>2517</x:v>
+      </x:c>
+      <x:c r="B542" s="7" t="n">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="C542" s="7" t="n">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="D542" s="7" t="n">
+        <x:v>295</x:v>
+      </x:c>
+      <x:c r="E542" s="7" t="n">
+        <x:v>385</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="543">
+      <x:c r="A543" s="7" t="n">
+        <x:v>2518</x:v>
+      </x:c>
+      <x:c r="B543" s="7" t="n">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="C543" s="7" t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="D543" s="7" t="n">
+        <x:v>295</x:v>
+      </x:c>
+      <x:c r="E543" s="7" t="n">
+        <x:v>485</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="544">
+      <x:c r="A544" s="7" t="n">
+        <x:v>2519</x:v>
+      </x:c>
+      <x:c r="B544" s="7" t="n">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="C544" s="7" t="n">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="D544" s="7" t="n">
+        <x:v>195</x:v>
+      </x:c>
+      <x:c r="E544" s="7" t="n">
+        <x:v>535</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="545">
+      <x:c r="A545" s="7" t="n">
+        <x:v>2520</x:v>
+      </x:c>
+      <x:c r="B545" s="7" t="n">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="C545" s="7" t="n">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="D545" s="7" t="n">
+        <x:v>245</x:v>
+      </x:c>
+      <x:c r="E545" s="7" t="n">
+        <x:v>485</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="546">
+      <x:c r="A546" s="7" t="n">
+        <x:v>2521</x:v>
+      </x:c>
+      <x:c r="B546" s="7" t="n">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="C546" s="7" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="D546" s="7" t="n">
+        <x:v>345</x:v>
+      </x:c>
+      <x:c r="E546" s="7" t="n">
+        <x:v>285</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="547">
+      <x:c r="A547" s="7" t="n">
+        <x:v>2522</x:v>
+      </x:c>
+      <x:c r="B547" s="7" t="n">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="C547" s="7" t="n">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="D547" s="7" t="n">
+        <x:v>245</x:v>
+      </x:c>
+      <x:c r="E547" s="7" t="n">
+        <x:v>135</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="548">
+      <x:c r="A548" s="7" t="n">
+        <x:v>2601</x:v>
+      </x:c>
+      <x:c r="B548" s="7" t="n">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="C548" s="7" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D548" s="7" t="n">
+        <x:v>145</x:v>
+      </x:c>
+      <x:c r="E548" s="7" t="n">
+        <x:v>235</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="549">
+      <x:c r="A549" s="7" t="n">
+        <x:v>2602</x:v>
+      </x:c>
+      <x:c r="B549" s="7" t="n">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="C549" s="7" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D549" s="7" t="n">
+        <x:v>195</x:v>
+      </x:c>
+      <x:c r="E549" s="7" t="n">
+        <x:v>235</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="550">
+      <x:c r="A550" s="7" t="n">
+        <x:v>2603</x:v>
+      </x:c>
+      <x:c r="B550" s="7" t="n">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="C550" s="7" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D550" s="7" t="n">
+        <x:v>245</x:v>
+      </x:c>
+      <x:c r="E550" s="7" t="n">
+        <x:v>235</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="551">
+      <x:c r="A551" s="7" t="n">
+        <x:v>2604</x:v>
+      </x:c>
+      <x:c r="B551" s="7" t="n">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="C551" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D551" s="7" t="n">
+        <x:v>295</x:v>
+      </x:c>
+      <x:c r="E551" s="7" t="n">
+        <x:v>235</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="552">
+      <x:c r="A552" s="7" t="n">
+        <x:v>2605</x:v>
+      </x:c>
+      <x:c r="B552" s="7" t="n">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="C552" s="7" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D552" s="7" t="n">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="E552" s="7" t="n">
+        <x:v>335</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="553">
+      <x:c r="A553" s="7" t="n">
+        <x:v>2606</x:v>
+      </x:c>
+      <x:c r="B553" s="7" t="n">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="C553" s="7" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D553" s="7" t="n">
+        <x:v>195</x:v>
+      </x:c>
+      <x:c r="E553" s="7" t="n">
+        <x:v>335</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="554">
+      <x:c r="A554" s="7" t="n">
+        <x:v>2607</x:v>
+      </x:c>
+      <x:c r="B554" s="7" t="n">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="C554" s="7" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="D554" s="7" t="n">
+        <x:v>245</x:v>
+      </x:c>
+      <x:c r="E554" s="7" t="n">
+        <x:v>335</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="555">
+      <x:c r="A555" s="7" t="n">
+        <x:v>2608</x:v>
+      </x:c>
+      <x:c r="B555" s="7" t="n">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="C555" s="7" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="D555" s="7" t="n">
+        <x:v>295</x:v>
+      </x:c>
+      <x:c r="E555" s="7" t="n">
+        <x:v>335</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="556">
+      <x:c r="A556" s="7" t="n">
+        <x:v>2609</x:v>
+      </x:c>
+      <x:c r="B556" s="7" t="n">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="C556" s="7" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="D556" s="7" t="n">
+        <x:v>145</x:v>
+      </x:c>
+      <x:c r="E556" s="7" t="n">
+        <x:v>335</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="557">
+      <x:c r="A557" s="7" t="n">
+        <x:v>2610</x:v>
+      </x:c>
+      <x:c r="B557" s="7" t="n">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="C557" s="7" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="D557" s="7" t="n">
+        <x:v>145</x:v>
+      </x:c>
+      <x:c r="E557" s="7" t="n">
+        <x:v>435</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="558">
+      <x:c r="A558" s="7" t="n">
+        <x:v>2611</x:v>
+      </x:c>
+      <x:c r="B558" s="7" t="n">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="C558" s="7" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="D558" s="7" t="n">
+        <x:v>195</x:v>
+      </x:c>
+      <x:c r="E558" s="7" t="n">
+        <x:v>435</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="559">
+      <x:c r="A559" s="7" t="n">
+        <x:v>2612</x:v>
+      </x:c>
+      <x:c r="B559" s="7" t="n">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="C559" s="7" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="D559" s="7" t="n">
+        <x:v>345</x:v>
+      </x:c>
+      <x:c r="E559" s="7" t="n">
+        <x:v>385</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="560">
+      <x:c r="A560" s="7" t="n">
+        <x:v>2613</x:v>
+      </x:c>
+      <x:c r="B560" s="7" t="n">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="C560" s="7" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="D560" s="7" t="n">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="E560" s="7" t="n">
+        <x:v>435</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="561">
+      <x:c r="A561" s="7" t="n">
+        <x:v>2614</x:v>
+      </x:c>
+      <x:c r="B561" s="7" t="n">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="C561" s="7" t="n">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="D561" s="7" t="n">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="E561" s="7" t="n">
+        <x:v>435</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="562">
+      <x:c r="A562" s="7" t="n">
+        <x:v>2615</x:v>
+      </x:c>
+      <x:c r="B562" s="7" t="n">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="C562" s="7" t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="D562" s="7" t="n">
+        <x:v>245</x:v>
+      </x:c>
+      <x:c r="E562" s="7" t="n">
+        <x:v>435</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="563">
+      <x:c r="A563" s="7" t="n">
+        <x:v>2616</x:v>
+      </x:c>
+      <x:c r="B563" s="7" t="n">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="C563" s="7" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="D563" s="7" t="n">
+        <x:v>345</x:v>
+      </x:c>
+      <x:c r="E563" s="7" t="n">
+        <x:v>435</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="564">
+      <x:c r="A564" s="7" t="n">
+        <x:v>2617</x:v>
+      </x:c>
+      <x:c r="B564" s="7" t="n">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="C564" s="7" t="n">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="D564" s="7" t="n">
+        <x:v>245</x:v>
+      </x:c>
+      <x:c r="E564" s="7" t="n">
+        <x:v>485</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="565">
+      <x:c r="A565" s="7" t="n">
+        <x:v>2618</x:v>
+      </x:c>
+      <x:c r="B565" s="7" t="n">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="C565" s="7" t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="D565" s="7" t="n">
+        <x:v>245</x:v>
+      </x:c>
+      <x:c r="E565" s="7" t="n">
+        <x:v>535</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="566">
+      <x:c r="A566" s="7" t="n">
+        <x:v>2619</x:v>
+      </x:c>
+      <x:c r="B566" s="7" t="n">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="C566" s="7" t="n">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="D566" s="7" t="n">
+        <x:v>345</x:v>
+      </x:c>
+      <x:c r="E566" s="7" t="n">
+        <x:v>335</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="567">
+      <x:c r="A567" s="7" t="n">
+        <x:v>2620</x:v>
+      </x:c>
+      <x:c r="B567" s="7" t="n">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="C567" s="7" t="n">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="D567" s="7" t="n">
+        <x:v>345</x:v>
+      </x:c>
+      <x:c r="E567" s="7" t="n">
+        <x:v>135</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="568">
+      <x:c r="A568" s="7" t="n">
+        <x:v>2621</x:v>
+      </x:c>
+      <x:c r="B568" s="7" t="n">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="C568" s="7" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="D568" s="7" t="n">
+        <x:v>245</x:v>
+      </x:c>
+      <x:c r="E568" s="7" t="n">
+        <x:v>135</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="569">
+      <x:c r="A569" s="7" t="n">
+        <x:v>2622</x:v>
+      </x:c>
+      <x:c r="B569" s="7" t="n">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="C569" s="7" t="n">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="D569" s="7" t="n">
+        <x:v>295</x:v>
+      </x:c>
+      <x:c r="E569" s="7" t="n">
+        <x:v>135</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="570">
+      <x:c r="A570" s="7" t="n">
+        <x:v>2701</x:v>
+      </x:c>
+      <x:c r="B570" s="7" t="n">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="C570" s="7" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D570" s="7" t="n">
+        <x:v>145</x:v>
+      </x:c>
+      <x:c r="E570" s="7" t="n">
+        <x:v>235</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="571">
+      <x:c r="A571" s="7" t="n">
+        <x:v>2702</x:v>
+      </x:c>
+      <x:c r="B571" s="7" t="n">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="C571" s="7" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D571" s="7" t="n">
+        <x:v>195</x:v>
+      </x:c>
+      <x:c r="E571" s="7" t="n">
+        <x:v>235</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="572">
+      <x:c r="A572" s="7" t="n">
+        <x:v>2703</x:v>
+      </x:c>
+      <x:c r="B572" s="7" t="n">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="C572" s="7" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D572" s="7" t="n">
+        <x:v>245</x:v>
+      </x:c>
+      <x:c r="E572" s="7" t="n">
+        <x:v>235</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="573">
+      <x:c r="A573" s="7" t="n">
+        <x:v>2704</x:v>
+      </x:c>
+      <x:c r="B573" s="7" t="n">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="C573" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D573" s="7" t="n">
+        <x:v>295</x:v>
+      </x:c>
+      <x:c r="E573" s="7" t="n">
+        <x:v>235</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="574">
+      <x:c r="A574" s="7" t="n">
+        <x:v>2705</x:v>
+      </x:c>
+      <x:c r="B574" s="7" t="n">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="C574" s="7" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D574" s="7" t="n">
+        <x:v>295</x:v>
+      </x:c>
+      <x:c r="E574" s="7" t="n">
+        <x:v>135</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="575">
+      <x:c r="A575" s="7" t="n">
+        <x:v>2706</x:v>
+      </x:c>
+      <x:c r="B575" s="7" t="n">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="C575" s="7" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D575" s="7" t="n">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="E575" s="7" t="n">
+        <x:v>335</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="576">
+      <x:c r="A576" s="7" t="n">
+        <x:v>2707</x:v>
+      </x:c>
+      <x:c r="B576" s="7" t="n">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="C576" s="7" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="D576" s="7" t="n">
+        <x:v>145</x:v>
+      </x:c>
+      <x:c r="E576" s="7" t="n">
+        <x:v>335</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="577">
+      <x:c r="A577" s="7" t="n">
+        <x:v>2708</x:v>
+      </x:c>
+      <x:c r="B577" s="7" t="n">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="C577" s="7" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="D577" s="7" t="n">
+        <x:v>195</x:v>
+      </x:c>
+      <x:c r="E577" s="7" t="n">
+        <x:v>335</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="578">
+      <x:c r="A578" s="7" t="n">
+        <x:v>2709</x:v>
+      </x:c>
+      <x:c r="B578" s="7" t="n">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="C578" s="7" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="D578" s="7" t="n">
+        <x:v>245</x:v>
+      </x:c>
+      <x:c r="E578" s="7" t="n">
+        <x:v>335</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="579">
+      <x:c r="A579" s="7" t="n">
+        <x:v>2710</x:v>
+      </x:c>
+      <x:c r="B579" s="7" t="n">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="C579" s="7" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="D579" s="7" t="n">
+        <x:v>295</x:v>
+      </x:c>
+      <x:c r="E579" s="7" t="n">
+        <x:v>335</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="580">
+      <x:c r="A580" s="7" t="n">
+        <x:v>2711</x:v>
+      </x:c>
+      <x:c r="B580" s="7" t="n">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="C580" s="7" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="D580" s="7" t="n">
+        <x:v>345</x:v>
+      </x:c>
+      <x:c r="E580" s="7" t="n">
+        <x:v>335</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="581">
+      <x:c r="A581" s="7" t="n">
+        <x:v>2712</x:v>
+      </x:c>
+      <x:c r="B581" s="7" t="n">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="C581" s="7" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="D581" s="7" t="n">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="E581" s="7" t="n">
+        <x:v>435</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="582">
+      <x:c r="A582" s="7" t="n">
+        <x:v>2713</x:v>
+      </x:c>
+      <x:c r="B582" s="7" t="n">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="C582" s="7" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="D582" s="7" t="n">
+        <x:v>145</x:v>
+      </x:c>
+      <x:c r="E582" s="7" t="n">
+        <x:v>435</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="583">
+      <x:c r="A583" s="7" t="n">
+        <x:v>2714</x:v>
+      </x:c>
+      <x:c r="B583" s="7" t="n">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="C583" s="7" t="n">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="D583" s="7" t="n">
+        <x:v>195</x:v>
+      </x:c>
+      <x:c r="E583" s="7" t="n">
+        <x:v>435</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="584">
+      <x:c r="A584" s="7" t="n">
+        <x:v>2715</x:v>
+      </x:c>
+      <x:c r="B584" s="7" t="n">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="C584" s="7" t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="D584" s="7" t="n">
+        <x:v>345</x:v>
+      </x:c>
+      <x:c r="E584" s="7" t="n">
+        <x:v>385</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="585">
+      <x:c r="A585" s="7" t="n">
+        <x:v>2716</x:v>
+      </x:c>
+      <x:c r="B585" s="7" t="n">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="C585" s="7" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="D585" s="7" t="n">
+        <x:v>345</x:v>
+      </x:c>
+      <x:c r="E585" s="7" t="n">
+        <x:v>435</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="586">
+      <x:c r="A586" s="7" t="n">
+        <x:v>2717</x:v>
+      </x:c>
+      <x:c r="B586" s="7" t="n">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="C586" s="7" t="n">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="D586" s="7" t="n">
+        <x:v>245</x:v>
+      </x:c>
+      <x:c r="E586" s="7" t="n">
+        <x:v>485</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="587">
+      <x:c r="A587" s="7" t="n">
+        <x:v>2718</x:v>
+      </x:c>
+      <x:c r="B587" s="7" t="n">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="C587" s="7" t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="D587" s="7" t="n">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="E587" s="7" t="n">
+        <x:v>435</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="588">
+      <x:c r="A588" s="7" t="n">
+        <x:v>2719</x:v>
+      </x:c>
+      <x:c r="B588" s="7" t="n">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="C588" s="7" t="n">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="D588" s="7" t="n">
+        <x:v>245</x:v>
+      </x:c>
+      <x:c r="E588" s="7" t="n">
+        <x:v>435</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="589">
+      <x:c r="A589" s="7" t="n">
+        <x:v>2720</x:v>
+      </x:c>
+      <x:c r="B589" s="7" t="n">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="C589" s="7" t="n">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="D589" s="7" t="n">
+        <x:v>245</x:v>
+      </x:c>
+      <x:c r="E589" s="7" t="n">
+        <x:v>535</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="590">
+      <x:c r="A590" s="7" t="n">
+        <x:v>2721</x:v>
+      </x:c>
+      <x:c r="B590" s="7" t="n">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="C590" s="7" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="D590" s="7" t="n">
+        <x:v>245</x:v>
+      </x:c>
+      <x:c r="E590" s="7" t="n">
+        <x:v>135</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="591">
+      <x:c r="A591" s="7" t="n">
+        <x:v>2722</x:v>
+      </x:c>
+      <x:c r="B591" s="7" t="n">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="C591" s="7" t="n">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="D591" s="7" t="n">
+        <x:v>345</x:v>
+      </x:c>
+      <x:c r="E591" s="7" t="n">
+        <x:v>135</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="592">
+      <x:c r="A592" s="7" t="n">
+        <x:v>2801</x:v>
+      </x:c>
+      <x:c r="B592" s="7" t="n">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="C592" s="7" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D592" s="7" t="n">
+        <x:v>145</x:v>
+      </x:c>
+      <x:c r="E592" s="7" t="n">
+        <x:v>135</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="593">
+      <x:c r="A593" s="7" t="n">
+        <x:v>2802</x:v>
+      </x:c>
+      <x:c r="B593" s="7" t="n">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="C593" s="7" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D593" s="7" t="n">
+        <x:v>145</x:v>
+      </x:c>
+      <x:c r="E593" s="7" t="n">
+        <x:v>185</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="594">
+      <x:c r="A594" s="7" t="n">
+        <x:v>2803</x:v>
+      </x:c>
+      <x:c r="B594" s="7" t="n">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="C594" s="7" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D594" s="7" t="n">
+        <x:v>145</x:v>
+      </x:c>
+      <x:c r="E594" s="7" t="n">
+        <x:v>235</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="595">
+      <x:c r="A595" s="7" t="n">
+        <x:v>2804</x:v>
+      </x:c>
+      <x:c r="B595" s="7" t="n">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="C595" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D595" s="7" t="n">
+        <x:v>245</x:v>
+      </x:c>
+      <x:c r="E595" s="7" t="n">
+        <x:v>185</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="596">
+      <x:c r="A596" s="7" t="n">
+        <x:v>2805</x:v>
+      </x:c>
+      <x:c r="B596" s="7" t="n">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="C596" s="7" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D596" s="7" t="n">
+        <x:v>145</x:v>
+      </x:c>
+      <x:c r="E596" s="7" t="n">
+        <x:v>285</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="597">
+      <x:c r="A597" s="7" t="n">
+        <x:v>2806</x:v>
+      </x:c>
+      <x:c r="B597" s="7" t="n">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="C597" s="7" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D597" s="7" t="n">
+        <x:v>245</x:v>
+      </x:c>
+      <x:c r="E597" s="7" t="n">
+        <x:v>235</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="598">
+      <x:c r="A598" s="7" t="n">
+        <x:v>2807</x:v>
+      </x:c>
+      <x:c r="B598" s="7" t="n">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="C598" s="7" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="D598" s="7" t="n">
+        <x:v>245</x:v>
+      </x:c>
+      <x:c r="E598" s="7" t="n">
+        <x:v>285</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="599">
+      <x:c r="A599" s="7" t="n">
+        <x:v>2808</x:v>
+      </x:c>
+      <x:c r="B599" s="7" t="n">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="C599" s="7" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="D599" s="7" t="n">
+        <x:v>145</x:v>
+      </x:c>
+      <x:c r="E599" s="7" t="n">
+        <x:v>335</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="600">
+      <x:c r="A600" s="7" t="n">
+        <x:v>2809</x:v>
+      </x:c>
+      <x:c r="B600" s="7" t="n">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="C600" s="7" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="D600" s="7" t="n">
+        <x:v>145</x:v>
+      </x:c>
+      <x:c r="E600" s="7" t="n">
+        <x:v>385</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="601">
+      <x:c r="A601" s="7" t="n">
+        <x:v>2810</x:v>
+      </x:c>
+      <x:c r="B601" s="7" t="n">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="C601" s="7" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="D601" s="7" t="n">
+        <x:v>245</x:v>
+      </x:c>
+      <x:c r="E601" s="7" t="n">
+        <x:v>335</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="602">
+      <x:c r="A602" s="7" t="n">
+        <x:v>2811</x:v>
+      </x:c>
+      <x:c r="B602" s="7" t="n">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="C602" s="7" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="D602" s="7" t="n">
+        <x:v>245</x:v>
+      </x:c>
+      <x:c r="E602" s="7" t="n">
+        <x:v>385</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="603">
+      <x:c r="A603" s="7" t="n">
+        <x:v>2812</x:v>
+      </x:c>
+      <x:c r="B603" s="7" t="n">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="C603" s="7" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="D603" s="7" t="n">
+        <x:v>145</x:v>
+      </x:c>
+      <x:c r="E603" s="7" t="n">
+        <x:v>435</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="604">
+      <x:c r="A604" s="7" t="n">
+        <x:v>2813</x:v>
+      </x:c>
+      <x:c r="B604" s="7" t="n">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="C604" s="7" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="D604" s="7" t="n">
+        <x:v>245</x:v>
+      </x:c>
+      <x:c r="E604" s="7" t="n">
+        <x:v>435</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="605">
+      <x:c r="A605" s="7" t="n">
+        <x:v>2814</x:v>
+      </x:c>
+      <x:c r="B605" s="7" t="n">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="C605" s="7" t="n">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="D605" s="7" t="n">
+        <x:v>145</x:v>
+      </x:c>
+      <x:c r="E605" s="7" t="n">
+        <x:v>485</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="606">
+      <x:c r="A606" s="7" t="n">
+        <x:v>2815</x:v>
+      </x:c>
+      <x:c r="B606" s="7" t="n">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="C606" s="7" t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="D606" s="7" t="n">
+        <x:v>245</x:v>
+      </x:c>
+      <x:c r="E606" s="7" t="n">
+        <x:v>485</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="607">
+      <x:c r="A607" s="7" t="n">
+        <x:v>2816</x:v>
+      </x:c>
+      <x:c r="B607" s="7" t="n">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="C607" s="7" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="D607" s="7" t="n">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="E607" s="7" t="n">
+        <x:v>485</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="608">
+      <x:c r="A608" s="7" t="n">
+        <x:v>2817</x:v>
+      </x:c>
+      <x:c r="B608" s="7" t="n">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="C608" s="7" t="n">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="D608" s="7" t="n">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="E608" s="7" t="n">
+        <x:v>535</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="609">
+      <x:c r="A609" s="7" t="n">
+        <x:v>2818</x:v>
+      </x:c>
+      <x:c r="B609" s="7" t="n">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="C609" s="7" t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="D609" s="7" t="n">
+        <x:v>245</x:v>
+      </x:c>
+      <x:c r="E609" s="7" t="n">
+        <x:v>535</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="610">
+      <x:c r="A610" s="7" t="n">
+        <x:v>2819</x:v>
+      </x:c>
+      <x:c r="B610" s="7" t="n">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="C610" s="7" t="n">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="D610" s="7" t="n">
+        <x:v>345</x:v>
+      </x:c>
+      <x:c r="E610" s="7" t="n">
+        <x:v>285</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="611">
+      <x:c r="A611" s="7" t="n">
+        <x:v>2820</x:v>
+      </x:c>
+      <x:c r="B611" s="7" t="n">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="C611" s="7" t="n">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="D611" s="7" t="n">
+        <x:v>345</x:v>
+      </x:c>
+      <x:c r="E611" s="7" t="n">
+        <x:v>235</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="612">
+      <x:c r="A612" s="7" t="n">
+        <x:v>2821</x:v>
+      </x:c>
+      <x:c r="B612" s="7" t="n">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="C612" s="7" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="D612" s="7" t="n">
+        <x:v>345</x:v>
+      </x:c>
+      <x:c r="E612" s="7" t="n">
+        <x:v>185</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="613">
+      <x:c r="A613" s="7" t="n">
+        <x:v>2822</x:v>
+      </x:c>
+      <x:c r="B613" s="7" t="n">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="C613" s="7" t="n">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="D613" s="7" t="n">
+        <x:v>345</x:v>
+      </x:c>
+      <x:c r="E613" s="7" t="n">
+        <x:v>135</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="614">
+      <x:c r="A614" s="7" t="n">
+        <x:v>2901</x:v>
+      </x:c>
+      <x:c r="B614" s="7" t="n">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="C614" s="7" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D614" s="7" t="n">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="E614" s="7" t="n">
+        <x:v>235</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="615">
+      <x:c r="A615" s="7" t="n">
+        <x:v>2902</x:v>
+      </x:c>
+      <x:c r="B615" s="7" t="n">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="C615" s="7" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D615" s="7" t="n">
+        <x:v>145</x:v>
+      </x:c>
+      <x:c r="E615" s="7" t="n">
+        <x:v>235</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="616">
+      <x:c r="A616" s="7" t="n">
+        <x:v>2903</x:v>
+      </x:c>
+      <x:c r="B616" s="7" t="n">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="C616" s="7" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D616" s="7" t="n">
+        <x:v>195</x:v>
+      </x:c>
+      <x:c r="E616" s="7" t="n">
+        <x:v>235</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="617">
+      <x:c r="A617" s="7" t="n">
+        <x:v>2904</x:v>
+      </x:c>
+      <x:c r="B617" s="7" t="n">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="C617" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D617" s="7" t="n">
+        <x:v>245</x:v>
+      </x:c>
+      <x:c r="E617" s="7" t="n">
+        <x:v>235</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="618">
+      <x:c r="A618" s="7" t="n">
+        <x:v>2905</x:v>
+      </x:c>
+      <x:c r="B618" s="7" t="n">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="C618" s="7" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D618" s="7" t="n">
+        <x:v>345</x:v>
+      </x:c>
+      <x:c r="E618" s="7" t="n">
+        <x:v>285</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="619">
+      <x:c r="A619" s="7" t="n">
+        <x:v>2906</x:v>
+      </x:c>
+      <x:c r="B619" s="7" t="n">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="C619" s="7" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D619" s="7" t="n">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="E619" s="7" t="n">
+        <x:v>335</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="620">
+      <x:c r="A620" s="7" t="n">
+        <x:v>2907</x:v>
+      </x:c>
+      <x:c r="B620" s="7" t="n">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="C620" s="7" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="D620" s="7" t="n">
+        <x:v>145</x:v>
+      </x:c>
+      <x:c r="E620" s="7" t="n">
+        <x:v>335</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="621">
+      <x:c r="A621" s="7" t="n">
+        <x:v>2908</x:v>
+      </x:c>
+      <x:c r="B621" s="7" t="n">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="C621" s="7" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="D621" s="7" t="n">
+        <x:v>195</x:v>
+      </x:c>
+      <x:c r="E621" s="7" t="n">
+        <x:v>335</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="622">
+      <x:c r="A622" s="7" t="n">
+        <x:v>2909</x:v>
+      </x:c>
+      <x:c r="B622" s="7" t="n">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="C622" s="7" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="D622" s="7" t="n">
+        <x:v>245</x:v>
+      </x:c>
+      <x:c r="E622" s="7" t="n">
+        <x:v>335</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="623">
+      <x:c r="A623" s="7" t="n">
+        <x:v>2910</x:v>
+      </x:c>
+      <x:c r="B623" s="7" t="n">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="C623" s="7" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="D623" s="7" t="n">
+        <x:v>345</x:v>
+      </x:c>
+      <x:c r="E623" s="7" t="n">
+        <x:v>335</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="624">
+      <x:c r="A624" s="7" t="n">
+        <x:v>2911</x:v>
+      </x:c>
+      <x:c r="B624" s="7" t="n">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="C624" s="7" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="D624" s="7" t="n">
+        <x:v>345</x:v>
+      </x:c>
+      <x:c r="E624" s="7" t="n">
+        <x:v>385</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="625">
+      <x:c r="A625" s="7" t="n">
+        <x:v>2912</x:v>
+      </x:c>
+      <x:c r="B625" s="7" t="n">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="C625" s="7" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="D625" s="7" t="n">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="E625" s="7" t="n">
+        <x:v>335</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="626">
+      <x:c r="A626" s="7" t="n">
+        <x:v>2913</x:v>
+      </x:c>
+      <x:c r="B626" s="7" t="n">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="C626" s="7" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="D626" s="7" t="n">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="E626" s="7" t="n">
+        <x:v>385</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="627">
+      <x:c r="A627" s="7" t="n">
+        <x:v>2914</x:v>
+      </x:c>
+      <x:c r="B627" s="7" t="n">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="C627" s="7" t="n">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="D627" s="7" t="n">
+        <x:v>145</x:v>
+      </x:c>
+      <x:c r="E627" s="7" t="n">
+        <x:v>435</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="628">
+      <x:c r="A628" s="7" t="n">
+        <x:v>2915</x:v>
+      </x:c>
+      <x:c r="B628" s="7" t="n">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="C628" s="7" t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="D628" s="7" t="n">
+        <x:v>195</x:v>
+      </x:c>
+      <x:c r="E628" s="7" t="n">
+        <x:v>435</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="629">
+      <x:c r="A629" s="7" t="n">
+        <x:v>2916</x:v>
+      </x:c>
+      <x:c r="B629" s="7" t="n">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="C629" s="7" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="D629" s="7" t="n">
+        <x:v>245</x:v>
+      </x:c>
+      <x:c r="E629" s="7" t="n">
+        <x:v>435</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="630">
+      <x:c r="A630" s="7" t="n">
+        <x:v>2917</x:v>
+      </x:c>
+      <x:c r="B630" s="7" t="n">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="C630" s="7" t="n">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="D630" s="7" t="n">
+        <x:v>145</x:v>
+      </x:c>
+      <x:c r="E630" s="7" t="n">
+        <x:v>535</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="631">
+      <x:c r="A631" s="7" t="n">
+        <x:v>2918</x:v>
+      </x:c>
+      <x:c r="B631" s="7" t="n">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="C631" s="7" t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="D631" s="7" t="n">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="E631" s="7" t="n">
+        <x:v>435</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="632">
+      <x:c r="A632" s="7" t="n">
+        <x:v>2919</x:v>
+      </x:c>
+      <x:c r="B632" s="7" t="n">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="C632" s="7" t="n">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="D632" s="7" t="n">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="E632" s="7" t="n">
+        <x:v>535</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="633">
+      <x:c r="A633" s="7" t="n">
+        <x:v>2920</x:v>
+      </x:c>
+      <x:c r="B633" s="7" t="n">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="C633" s="7" t="n">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="D633" s="7" t="n">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="E633" s="7" t="n">
+        <x:v>485</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="634">
+      <x:c r="A634" s="7" t="n">
+        <x:v>2921</x:v>
+      </x:c>
+      <x:c r="B634" s="7" t="n">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="C634" s="7" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="D634" s="7" t="n">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="E634" s="7" t="n">
+        <x:v>135</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="635">
+      <x:c r="A635" s="7" t="n">
+        <x:v>2922</x:v>
+      </x:c>
+      <x:c r="B635" s="7" t="n">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="C635" s="7" t="n">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="D635" s="7" t="n">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="E635" s="7" t="n">
+        <x:v>135</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="636">
+      <x:c r="A636" s="7" t="n">
+        <x:v>3001</x:v>
+      </x:c>
+      <x:c r="B636" s="7" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="C636" s="7" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D636" s="7" t="n">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="E636" s="7" t="n">
+        <x:v>185</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="637">
+      <x:c r="A637" s="7" t="n">
+        <x:v>3002</x:v>
+      </x:c>
+      <x:c r="B637" s="7" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="C637" s="7" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D637" s="7" t="n">
+        <x:v>145</x:v>
+      </x:c>
+      <x:c r="E637" s="7" t="n">
+        <x:v>185</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="638">
+      <x:c r="A638" s="7" t="n">
+        <x:v>3003</x:v>
+      </x:c>
+      <x:c r="B638" s="7" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="C638" s="7" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D638" s="7" t="n">
+        <x:v>195</x:v>
+      </x:c>
+      <x:c r="E638" s="7" t="n">
+        <x:v>185</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="639">
+      <x:c r="A639" s="7" t="n">
+        <x:v>3004</x:v>
+      </x:c>
+      <x:c r="B639" s="7" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="C639" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D639" s="7" t="n">
+        <x:v>245</x:v>
+      </x:c>
+      <x:c r="E639" s="7" t="n">
+        <x:v>185</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="640">
+      <x:c r="A640" s="7" t="n">
+        <x:v>3005</x:v>
+      </x:c>
+      <x:c r="B640" s="7" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="C640" s="7" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D640" s="7" t="n">
+        <x:v>295</x:v>
+      </x:c>
+      <x:c r="E640" s="7" t="n">
+        <x:v>235</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="641">
+      <x:c r="A641" s="7" t="n">
+        <x:v>3006</x:v>
+      </x:c>
+      <x:c r="B641" s="7" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="C641" s="7" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D641" s="7" t="n">
+        <x:v>295</x:v>
+      </x:c>
+      <x:c r="E641" s="7" t="n">
+        <x:v>285</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="642">
+      <x:c r="A642" s="7" t="n">
+        <x:v>3007</x:v>
+      </x:c>
+      <x:c r="B642" s="7" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="C642" s="7" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="D642" s="7" t="n">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="E642" s="7" t="n">
+        <x:v>285</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="643">
+      <x:c r="A643" s="7" t="n">
+        <x:v>3008</x:v>
+      </x:c>
+      <x:c r="B643" s="7" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="C643" s="7" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="D643" s="7" t="n">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="E643" s="7" t="n">
+        <x:v>285</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="644">
+      <x:c r="A644" s="7" t="n">
+        <x:v>3009</x:v>
+      </x:c>
+      <x:c r="B644" s="7" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="C644" s="7" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="D644" s="7" t="n">
+        <x:v>145</x:v>
+      </x:c>
+      <x:c r="E644" s="7" t="n">
+        <x:v>285</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="645">
+      <x:c r="A645" s="7" t="n">
+        <x:v>3010</x:v>
+      </x:c>
+      <x:c r="B645" s="7" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="C645" s="7" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="D645" s="7" t="n">
+        <x:v>195</x:v>
+      </x:c>
+      <x:c r="E645" s="7" t="n">
+        <x:v>285</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="646">
+      <x:c r="A646" s="7" t="n">
+        <x:v>3011</x:v>
+      </x:c>
+      <x:c r="B646" s="7" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="C646" s="7" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="D646" s="7" t="n">
+        <x:v>295</x:v>
+      </x:c>
+      <x:c r="E646" s="7" t="n">
+        <x:v>335</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="647">
+      <x:c r="A647" s="7" t="n">
+        <x:v>3012</x:v>
+      </x:c>
+      <x:c r="B647" s="7" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="C647" s="7" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="D647" s="7" t="n">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="E647" s="7" t="n">
+        <x:v>335</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="648">
+      <x:c r="A648" s="7" t="n">
+        <x:v>3013</x:v>
+      </x:c>
+      <x:c r="B648" s="7" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="C648" s="7" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="D648" s="7" t="n">
+        <x:v>145</x:v>
+      </x:c>
+      <x:c r="E648" s="7" t="n">
+        <x:v>385</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="649">
+      <x:c r="A649" s="7" t="n">
+        <x:v>3014</x:v>
+      </x:c>
+      <x:c r="B649" s="7" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="C649" s="7" t="n">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="D649" s="7" t="n">
+        <x:v>195</x:v>
+      </x:c>
+      <x:c r="E649" s="7" t="n">
+        <x:v>385</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="650">
+      <x:c r="A650" s="7" t="n">
+        <x:v>3015</x:v>
+      </x:c>
+      <x:c r="B650" s="7" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="C650" s="7" t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="D650" s="7" t="n">
+        <x:v>245</x:v>
+      </x:c>
+      <x:c r="E650" s="7" t="n">
+        <x:v>385</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="651">
+      <x:c r="A651" s="7" t="n">
+        <x:v>3016</x:v>
+      </x:c>
+      <x:c r="B651" s="7" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="C651" s="7" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="D651" s="7" t="n">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="E651" s="7" t="n">
+        <x:v>385</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="652">
+      <x:c r="A652" s="7" t="n">
+        <x:v>3017</x:v>
+      </x:c>
+      <x:c r="B652" s="7" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="C652" s="7" t="n">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="D652" s="7" t="n">
+        <x:v>245</x:v>
+      </x:c>
+      <x:c r="E652" s="7" t="n">
+        <x:v>485</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="653">
+      <x:c r="A653" s="7" t="n">
+        <x:v>3018</x:v>
+      </x:c>
+      <x:c r="B653" s="7" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="C653" s="7" t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="D653" s="7" t="n">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="E653" s="7" t="n">
+        <x:v>435</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="654">
+      <x:c r="A654" s="7" t="n">
+        <x:v>3019</x:v>
+      </x:c>
+      <x:c r="B654" s="7" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="C654" s="7" t="n">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="D654" s="7" t="n">
+        <x:v>195</x:v>
+      </x:c>
+      <x:c r="E654" s="7" t="n">
+        <x:v>485</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="655">
+      <x:c r="A655" s="7" t="n">
+        <x:v>3020</x:v>
+      </x:c>
+      <x:c r="B655" s="7" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="C655" s="7" t="n">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="D655" s="7" t="n">
+        <x:v>145</x:v>
+      </x:c>
+      <x:c r="E655" s="7" t="n">
+        <x:v>485</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="656">
+      <x:c r="A656" s="7" t="n">
+        <x:v>3021</x:v>
+      </x:c>
+      <x:c r="B656" s="7" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="C656" s="7" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="D656" s="7" t="n">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="E656" s="7" t="n">
+        <x:v>485</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="657">
+      <x:c r="A657" s="7" t="n">
+        <x:v>3101</x:v>
+      </x:c>
+      <x:c r="B657" s="7" t="n">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="C657" s="7" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D657" s="7" t="n">
+        <x:v>345</x:v>
+      </x:c>
+      <x:c r="E657" s="7" t="n">
+        <x:v>185</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="658">
+      <x:c r="A658" s="7" t="n">
+        <x:v>3102</x:v>
+      </x:c>
+      <x:c r="B658" s="7" t="n">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="C658" s="7" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D658" s="7" t="n">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="E658" s="7" t="n">
+        <x:v>235</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="659">
+      <x:c r="A659" s="7" t="n">
+        <x:v>3103</x:v>
+      </x:c>
+      <x:c r="B659" s="7" t="n">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="C659" s="7" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D659" s="7" t="n">
+        <x:v>145</x:v>
+      </x:c>
+      <x:c r="E659" s="7" t="n">
+        <x:v>185</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="660">
+      <x:c r="A660" s="7" t="n">
+        <x:v>3104</x:v>
+      </x:c>
+      <x:c r="B660" s="7" t="n">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="C660" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D660" s="7" t="n">
+        <x:v>195</x:v>
+      </x:c>
+      <x:c r="E660" s="7" t="n">
+        <x:v>185</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="661">
+      <x:c r="A661" s="7" t="n">
+        <x:v>3105</x:v>
+      </x:c>
+      <x:c r="B661" s="7" t="n">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="C661" s="7" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D661" s="7" t="n">
+        <x:v>245</x:v>
+      </x:c>
+      <x:c r="E661" s="7" t="n">
+        <x:v>185</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="662">
+      <x:c r="A662" s="7" t="n">
+        <x:v>3106</x:v>
+      </x:c>
+      <x:c r="B662" s="7" t="n">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="C662" s="7" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D662" s="7" t="n">
+        <x:v>245</x:v>
+      </x:c>
+      <x:c r="E662" s="7" t="n">
+        <x:v>285</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="663">
+      <x:c r="A663" s="7" t="n">
+        <x:v>3107</x:v>
+      </x:c>
+      <x:c r="B663" s="7" t="n">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="C663" s="7" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="D663" s="7" t="n">
+        <x:v>345</x:v>
+      </x:c>
+      <x:c r="E663" s="7" t="n">
+        <x:v>235</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="664">
+      <x:c r="A664" s="7" t="n">
+        <x:v>3108</x:v>
+      </x:c>
+      <x:c r="B664" s="7" t="n">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="C664" s="7" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="D664" s="7" t="n">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="E664" s="7" t="n">
+        <x:v>285</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="665">
+      <x:c r="A665" s="7" t="n">
+        <x:v>3109</x:v>
+      </x:c>
+      <x:c r="B665" s="7" t="n">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="C665" s="7" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="D665" s="7" t="n">
+        <x:v>345</x:v>
+      </x:c>
+      <x:c r="E665" s="7" t="n">
+        <x:v>285</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="666">
+      <x:c r="A666" s="7" t="n">
+        <x:v>3110</x:v>
+      </x:c>
+      <x:c r="B666" s="7" t="n">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="C666" s="7" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="D666" s="7" t="n">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="E666" s="7" t="n">
+        <x:v>385</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="667">
+      <x:c r="A667" s="7" t="n">
+        <x:v>3111</x:v>
+      </x:c>
+      <x:c r="B667" s="7" t="n">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="C667" s="7" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="D667" s="7" t="n">
+        <x:v>145</x:v>
+      </x:c>
+      <x:c r="E667" s="7" t="n">
+        <x:v>285</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="668">
+      <x:c r="A668" s="7" t="n">
+        <x:v>3112</x:v>
+      </x:c>
+      <x:c r="B668" s="7" t="n">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="C668" s="7" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="D668" s="7" t="n">
+        <x:v>195</x:v>
+      </x:c>
+      <x:c r="E668" s="7" t="n">
+        <x:v>285</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="669">
+      <x:c r="A669" s="7" t="n">
+        <x:v>3113</x:v>
+      </x:c>
+      <x:c r="B669" s="7" t="n">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="C669" s="7" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="D669" s="7" t="n">
+        <x:v>295</x:v>
+      </x:c>
+      <x:c r="E669" s="7" t="n">
+        <x:v>285</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="670">
+      <x:c r="A670" s="7" t="n">
+        <x:v>3114</x:v>
+      </x:c>
+      <x:c r="B670" s="7" t="n">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="C670" s="7" t="n">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="D670" s="7" t="n">
+        <x:v>295</x:v>
+      </x:c>
+      <x:c r="E670" s="7" t="n">
+        <x:v>385</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="671">
+      <x:c r="A671" s="7" t="n">
+        <x:v>3115</x:v>
+      </x:c>
+      <x:c r="B671" s="7" t="n">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="C671" s="7" t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="D671" s="7" t="n">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="E671" s="7" t="n">
+        <x:v>435</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="672">
+      <x:c r="A672" s="7" t="n">
+        <x:v>3116</x:v>
+      </x:c>
+      <x:c r="B672" s="7" t="n">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="C672" s="7" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="D672" s="7" t="n">
+        <x:v>145</x:v>
+      </x:c>
+      <x:c r="E672" s="7" t="n">
+        <x:v>385</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="673">
+      <x:c r="A673" s="7" t="n">
+        <x:v>3117</x:v>
+      </x:c>
+      <x:c r="B673" s="7" t="n">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="C673" s="7" t="n">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="D673" s="7" t="n">
+        <x:v>195</x:v>
+      </x:c>
+      <x:c r="E673" s="7" t="n">
+        <x:v>385</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="674">
+      <x:c r="A674" s="7" t="n">
+        <x:v>3118</x:v>
+      </x:c>
+      <x:c r="B674" s="7" t="n">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="C674" s="7" t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="D674" s="7" t="n">
+        <x:v>245</x:v>
+      </x:c>
+      <x:c r="E674" s="7" t="n">
+        <x:v>385</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="675">
+      <x:c r="A675" s="7" t="n">
+        <x:v>3119</x:v>
+      </x:c>
+      <x:c r="B675" s="7" t="n">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="C675" s="7" t="n">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="D675" s="7" t="n">
+        <x:v>195</x:v>
+      </x:c>
+      <x:c r="E675" s="7" t="n">
+        <x:v>485</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="676">
+      <x:c r="A676" s="7" t="n">
+        <x:v>3120</x:v>
+      </x:c>
+      <x:c r="B676" s="7" t="n">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="C676" s="7" t="n">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="D676" s="7" t="n">
+        <x:v>195</x:v>
+      </x:c>
+      <x:c r="E676" s="7" t="n">
+        <x:v>535</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="677">
+      <x:c r="A677" s="7" t="n">
+        <x:v>3121</x:v>
+      </x:c>
+      <x:c r="B677" s="7" t="n">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="C677" s="7" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="D677" s="7" t="n">
+        <x:v>245</x:v>
+      </x:c>
+      <x:c r="E677" s="7" t="n">
+        <x:v>485</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="678">
+      <x:c r="A678" s="7" t="n">
+        <x:v>3122</x:v>
+      </x:c>
+      <x:c r="B678" s="7" t="n">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="C678" s="7" t="n">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="D678" s="7" t="n">
+        <x:v>295</x:v>
+      </x:c>
+      <x:c r="E678" s="7" t="n">
+        <x:v>485</x:v>
+      </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
